--- a/tame_output/ON/bt/strategyON_20240826.xlsx
+++ b/tame_output/ON/bt/strategyON_20240826.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>58.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-78.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-29.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.3%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>428.2%</t>
+          <t>430.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-662.6%</t>
+          <t>-664.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-166.4%</t>
+          <t>-167.2%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-281.2%</t>
+          <t>-281.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.75357116580319</v>
       </c>
       <c r="C1945" t="n">
         <v>2.75858326319385</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.932784975351878</v>
+        <v>-3.96885187823265</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.185112848739352</v>
+        <v>1.170686087587043</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5642899207513363</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.687855955085216</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.839974493901019</v>
+        <v>-3.876041396781791</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.151509733211062</v>
+        <v>1.137082972058753</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6571004022021957</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560423</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.689729431009817</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.884363963230446</v>
+        <v>-3.920430866111218</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.135627421403891</v>
+        <v>1.121200660251582</v>
       </c>
       <c r="F1947" t="n">
         <v>0.612710932872768</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472735</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.68480513952154</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.000905568335789</v>
+        <v>-4.036972471216561</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.084086487873477</v>
+        <v>1.069659726721168</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4961693277674253</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.690296435352207</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.040829662918361</v>
+        <v>-4.076896565799133</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.073608145871116</v>
+        <v>1.059181384718807</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4961693277674253</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.701793637120746</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.068610060819713</v>
+        <v>-4.104676963700486</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.073993188479114</v>
+        <v>1.059566427326805</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4683889298660722</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170532</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.5401493571214</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.186990733549852</v>
+        <v>-4.223057636430624</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8649966393877115</v>
+        <v>0.8505698782354025</v>
       </c>
       <c r="F1951" t="n">
         <v>0.401171077715096</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729264</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.660299017840605</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.295604811993183</v>
+        <v>-4.331671714873956</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9417006687295848</v>
+        <v>0.9272739075772756</v>
       </c>
       <c r="F1952" t="n">
         <v>0.401171077715096</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190764</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.674812043942928</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.26019577374504</v>
+        <v>-4.296262676625813</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9703773101311648</v>
+        <v>0.9559505489788558</v>
       </c>
       <c r="F1953" t="n">
         <v>0.401171077715096</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.672231485285297</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.221812111186889</v>
+        <v>-4.257879014067662</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.983150216496794</v>
+        <v>0.968723455344485</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4395547402732472</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.668960514130599</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.044695781151723</v>
+        <v>-4.080762684032496</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.050725777356162</v>
+        <v>1.036299016203853</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4395547402732472</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.669643905892512</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.089788025985269</v>
+        <v>-4.125854928866041</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.033372271184657</v>
+        <v>1.018945510032348</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3776586971038574</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.663430881198926</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.910412604746501</v>
+        <v>-3.946479507627274</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.098909414986579</v>
+        <v>1.08448265383427</v>
       </c>
       <c r="F1957" t="n">
         <v>0.534435455274576</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982225</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.644238336530516</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.955426818267107</v>
+        <v>-3.99149372114788</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.061711184909926</v>
+        <v>1.047284423757617</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5040865599599714</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.649929898869462</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.222431328539543</v>
+        <v>-4.258498231420315</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9606009431398974</v>
+        <v>0.9461741819875884</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3097235219170228</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.649133820765963</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.323629109976715</v>
+        <v>-4.359696012857488</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9193257524615297</v>
+        <v>0.9048989913092207</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2413147083717037</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815454</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64673378232028</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.317118143362403</v>
+        <v>-4.353185046243175</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9195301006615715</v>
+        <v>0.9051033395092625</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2413147083717037</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.643258501528525</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.298080015655105</v>
+        <v>-4.334146918535878</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9236700709527355</v>
+        <v>0.9092433098004262</v>
       </c>
       <c r="F1962" t="n">
         <v>0.1831310970405091</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.762552903162715</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.350595817929926</v>
+        <v>-4.386662720810699</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.021958151676998</v>
+        <v>1.007531390524689</v>
       </c>
       <c r="F1963" t="n">
         <v>0.1831310970405091</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067861</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.763386232148849</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.364462579263844</v>
+        <v>-4.400529482144616</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.017244776129564</v>
+        <v>1.002818014977255</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1452731803066862</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789118</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.769394762545775</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.319658407723914</v>
+        <v>-4.355725310604686</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.041174975142462</v>
+        <v>1.026748213990153</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1452731803066862</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.667344983822974</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.171915437488911</v>
+        <v>-4.207982340369684</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9982223845136624</v>
+        <v>0.9837956233613534</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3130805375415693</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.670138605354455</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.25573665876361</v>
+        <v>-4.291803561644382</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.967487517535264</v>
+        <v>0.953060756382955</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3130805375415693</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.670800953746113</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.249583952710825</v>
+        <v>-4.285650855591598</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9706109483480361</v>
+        <v>0.9561841871957271</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3192332435943536</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.669881430486224</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.266393250861327</v>
+        <v>-4.3024601537421</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9629677058279456</v>
+        <v>0.9485409446756365</v>
       </c>
       <c r="F1969" t="n">
         <v>0.302423945443852</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.736216984283045</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.204095252085205</v>
+        <v>-4.240162154965978</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.054222459135215</v>
+        <v>1.039795697982906</v>
       </c>
       <c r="F1970" t="n">
         <v>0.347718209718294</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.538508985997172</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.002305054420047</v>
+        <v>-4.03837195730082</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9372305399154057</v>
+        <v>0.9228037787630965</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5457364018874484</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.608799218319347</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.053191767106242</v>
+        <v>-4.089258669987014</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9871660871631029</v>
+        <v>0.9727393260107939</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4948496892012539</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.623426954435391</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.966581024456434</v>
+        <v>-4.002647927337208</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.03643812033907</v>
+        <v>1.02201135918676</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5734754204064122</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.621962935260062</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.026790322461719</v>
+        <v>-4.062857225342492</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.010890381961628</v>
+        <v>0.9964636208093183</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5132661224011277</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.620454553299991</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.950368276029792</v>
+        <v>-3.986435178910566</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.039950818574327</v>
+        <v>1.025524057422018</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5132661224011277</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.620317420735427</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.905995144391223</v>
+        <v>-3.942062047271997</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.05756293866519</v>
+        <v>1.043136177512881</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5576392540396963</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.614711214874017</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.928475495250108</v>
+        <v>-3.964542398130882</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.042964592460227</v>
+        <v>1.028537831307918</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5576392540396963</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.621092971901822</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.880819764689052</v>
+        <v>-3.916886667569826</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.068408641712454</v>
+        <v>1.053981880560145</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6052949846007519</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.625985345276547</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.780301606190298</v>
+        <v>-3.816368509071071</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.113508278486681</v>
+        <v>1.099081517334372</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7058131430995065</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.612740017752419</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.764396276757945</v>
+        <v>-3.800463179638719</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.106625082735494</v>
+        <v>1.092198321583185</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6267004823902675</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
         <v>2.616837720363048</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.719557875149547</v>
+        <v>-3.755624778030321</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.128658145989482</v>
+        <v>1.114231384837173</v>
       </c>
       <c r="F1981" t="n">
         <v>0.631243915335137</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.620998659994126</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.739056331391555</v>
+        <v>-3.775123234272329</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.125019703123756</v>
+        <v>1.110592941971447</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5831592740552327</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.626878262521963</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.694853494305655</v>
+        <v>-3.730920397186428</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.148580440485954</v>
+        <v>1.134153679333645</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6273621111411332</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.62528826299121</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.702413160142702</v>
+        <v>-3.738480063023475</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.143966574620382</v>
+        <v>1.129539813468073</v>
       </c>
       <c r="F1984" t="n">
         <v>0.6821655151509525</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.67653602817425</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.544121742603429</v>
+        <v>-3.580188645484203</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.258530906819131</v>
+        <v>1.244104145666822</v>
       </c>
       <c r="F1985" t="n">
         <v>0.6821655151509525</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
         <v>2.674976732768503</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.336479738968953</v>
+        <v>-3.372546641849727</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.340028412867175</v>
+        <v>1.325601651714865</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8898075187854286</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
         <v>2.669924961006773</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.285447646246425</v>
+        <v>-3.321514549127199</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.355389478194456</v>
+        <v>1.340962717042147</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9408396115079566</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.687112365099478</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.220223465119219</v>
+        <v>-3.256290367999993</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.398666554738043</v>
+        <v>1.384239793585734</v>
       </c>
       <c r="F1988" t="n">
         <v>1.006063792635162</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.683073337398759</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.182796445048086</v>
+        <v>-3.218863347928859</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.409598335065777</v>
+        <v>1.395171573913468</v>
       </c>
       <c r="F1989" t="n">
         <v>1.011315330664344</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.684330129729999</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.202908101082794</v>
+        <v>-3.238975003963568</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.402810464983134</v>
+        <v>1.388383703830825</v>
       </c>
       <c r="F1990" t="n">
         <v>1.022342675661763</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84488790075121</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.17449483798291</v>
+        <v>-3.210561740863684</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.574733541244298</v>
+        <v>1.560306780091989</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9633671129153341</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>2.965000809969027</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.099712576957898</v>
+        <v>-3.135779479838671</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.724759354872121</v>
+        <v>1.710332593719811</v>
       </c>
       <c r="F1992" t="n">
         <v>1.038149373940347</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
         <v>2.956708785982886</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.07362849269409</v>
+        <v>-3.109695395574863</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.726900964591503</v>
+        <v>1.712474203439194</v>
       </c>
       <c r="F1993" t="n">
         <v>1.038149373940347</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
         <v>2.954901981566665</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.985750579584969</v>
+        <v>-3.021817482465743</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.76024532541893</v>
+        <v>1.745818564266621</v>
       </c>
       <c r="F1994" t="n">
         <v>1.154075016363698</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>2.972456387293457</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.976858118191686</v>
+        <v>-3.012925021072459</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.781356715703035</v>
+        <v>1.766929954550726</v>
       </c>
       <c r="F1995" t="n">
         <v>1.154075016363698</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.964311434698041</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.145334235161564</v>
+        <v>-3.181401138042337</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.705821316319668</v>
+        <v>1.691394555167359</v>
       </c>
       <c r="F1996" t="n">
         <v>1.126127180647117</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.945581131885902</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.699078042532124</v>
+        <v>-2.735144945412897</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.865593490559306</v>
+        <v>1.851166729406997</v>
       </c>
       <c r="F1997" t="n">
         <v>1.031408510977484</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
         <v>2.936245154382807</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.676356938848971</v>
+        <v>-2.712423841729745</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.865345954529471</v>
+        <v>1.850919193377162</v>
       </c>
       <c r="F1998" t="n">
         <v>1.031408510977484</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.095151280233976</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.805558752143014</v>
+        <v>-2.841625655023787</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.972571355063023</v>
+        <v>1.958144593910714</v>
       </c>
       <c r="F1999" t="n">
         <v>0.902206697683442</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>3.132229102727623</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.831433150617039</v>
+        <v>-2.867500053497813</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.99929941816706</v>
+        <v>1.98487265701475</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9471183063951831</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
         <v>3.128904458717168</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.824378460401866</v>
+        <v>-2.860445363282639</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.998796650242674</v>
+        <v>1.984369889090365</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9541729966103569</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.138910612361909</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.797427236075378</v>
+        <v>-2.833494138956151</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.019583293618011</v>
+        <v>2.005156532465702</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9690533426380761</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.323013744506869</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.933380244131694</v>
+        <v>-2.969447147012468</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.149305222540444</v>
+        <v>2.134878461388135</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9690533426380761</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
         <v>3.315130439409862</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.955788361936566</v>
+        <v>-2.99185526481734</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.132458670321489</v>
+        <v>2.118031909169179</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9690533426380761</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.3171844389595</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.984012597514166</v>
+        <v>-3.02007950039494</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.123222975640086</v>
+        <v>2.108796214487777</v>
       </c>
       <c r="F2005" t="n">
         <v>0.9870300950893847</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
         <v>3.373438156681347</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.993453523402696</v>
+        <v>-3.02952042628347</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.175700323006521</v>
+        <v>2.161273561854212</v>
       </c>
       <c r="F2006" t="n">
         <v>1.109457212632776</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.376329251226648</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.045727130738338</v>
+        <v>-3.081794033619111</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.157681974617566</v>
+        <v>2.143255213465256</v>
       </c>
       <c r="F2007" t="n">
         <v>1.057183605297135</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.374441064120423</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.122057108339244</v>
+        <v>-3.158124011220017</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.125261796470978</v>
+        <v>2.110835035318669</v>
       </c>
       <c r="F2008" t="n">
         <v>1.057183605297135</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.369261293723285</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.324310828663597</v>
+        <v>-3.360377731544371</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.039180537944099</v>
+        <v>2.02475377679179</v>
       </c>
       <c r="F2009" t="n">
         <v>0.8549298849727813</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
         <v>3.367695303933437</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.485879254190852</v>
+        <v>-3.521946157071626</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.972987177943349</v>
+        <v>1.95856041679104</v>
       </c>
       <c r="F2010" t="n">
         <v>0.728146961174902</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389349</v>
       </c>
       <c r="C2011" t="n">
         <v>3.380768710799356</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.594179916060972</v>
+        <v>-3.630246818941745</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.94274032006122</v>
+        <v>1.928313558908911</v>
       </c>
       <c r="F2011" t="n">
         <v>0.728146961174902</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.749882691378393</v>
       </c>
       <c r="C2012" t="n">
         <v>3.372773907582296</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.687327387364338</v>
+        <v>-3.723394290245112</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.897486528322814</v>
+        <v>1.883059767170504</v>
       </c>
       <c r="F2012" t="n">
         <v>0.6053177498923692</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006976</v>
       </c>
       <c r="C2013" t="n">
         <v>3.371297948709298</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.715228174473811</v>
+        <v>-3.751295077354585</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.884850254606026</v>
+        <v>1.870423493453717</v>
       </c>
       <c r="F2013" t="n">
         <v>0.5707208257494344</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
         <v>3.368062392686497</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.837754277176705</v>
+        <v>-3.873821180057479</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.832604257502068</v>
+        <v>1.818177496349758</v>
       </c>
       <c r="F2014" t="n">
         <v>0.4481947230465405</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.434768352277001</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.068268773362294</v>
+        <v>-4.104335676243068</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.807104418618336</v>
+        <v>1.792677657466027</v>
       </c>
       <c r="F2015" t="n">
         <v>0.2176802268609518</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.575080071278848</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.324989591357118</v>
+        <v>-4.361056494237892</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.844727810422253</v>
+        <v>1.830301049269944</v>
       </c>
       <c r="F2016" t="n">
         <v>0.109265652717137</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.644060340424487</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.478976009133259</v>
+        <v>-4.515042912014033</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.852113512457437</v>
+        <v>1.837686751305127</v>
       </c>
       <c r="F2017" t="n">
         <v>0.109265652717137</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
         <v>3.630111542544608</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.428454105305593</v>
+        <v>-4.464521008186367</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.858373476108624</v>
+        <v>1.843946714956315</v>
       </c>
       <c r="F2018" t="n">
         <v>0.109265652717137</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609753</v>
       </c>
       <c r="C2019" t="n">
         <v>3.641982031600022</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.680929259313317</v>
+        <v>-4.716996162194091</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.769253903560948</v>
+        <v>1.754827142408639</v>
       </c>
       <c r="F2019" t="n">
         <v>0.109265652717137</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
         <v>3.643192566118966</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.97382501579273</v>
+        <v>-5.009891918673503</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.653306135488127</v>
+        <v>1.638879374335818</v>
       </c>
       <c r="F2020" t="n">
         <v>0.109265652717137</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.647314308346287</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.160489143927538</v>
+        <v>-5.196556046808311</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.582762226461525</v>
+        <v>1.568335465309216</v>
       </c>
       <c r="F2021" t="n">
         <v>0.08252668189257706</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
         <v>3.642392161082477</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.3065098308415</v>
+        <v>-5.342576733722273</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.51943180443213</v>
+        <v>1.50500504327982</v>
       </c>
       <c r="F2022" t="n">
         <v>0.07344359009872009</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830329</v>
       </c>
       <c r="C2023" t="n">
         <v>3.804596217781521</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.398223839951084</v>
+        <v>-5.434290742831858</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.64495025748734</v>
+        <v>1.630523496335031</v>
       </c>
       <c r="F2023" t="n">
         <v>0.07344359009872009</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
         <v>3.799442855745335</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.429875499011054</v>
+        <v>-5.465942401891827</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.627136231827166</v>
+        <v>1.612709470674857</v>
       </c>
       <c r="F2024" t="n">
         <v>0.06827513285427989</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.809672273313826</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.511810317279937</v>
+        <v>-5.547877220160711</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.604591722088104</v>
+        <v>1.590164960935795</v>
       </c>
       <c r="F2025" t="n">
         <v>0.0583403872671997</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.818597911769729</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.613786439528345</v>
+        <v>-5.649853342409118</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.572726911644644</v>
+        <v>1.558300150492335</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.04363573498120787</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.810750799013904</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.503780156051123</v>
+        <v>-5.539847058931897</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.608882312279707</v>
+        <v>1.594455551127398</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.02043116306393267</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
         <v>3.815000809735878</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.360720580310197</v>
+        <v>-5.396787483190971</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.670356153298052</v>
+        <v>1.655929392145743</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.01241773647395339</v>
@@ -48212,16 +48212,16 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
         <v>3.822261692618414</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.059273854838359</v>
+        <v>-5.095340757719133</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.798195726369323</v>
+        <v>1.783768965217014</v>
       </c>
       <c r="F2029" t="n">
         <v>0.2890289889978839</v>
@@ -48235,16 +48235,16 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
         <v>3.823232870371125</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.083864099073543</v>
+        <v>-5.119931001954317</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.78933080642796</v>
+        <v>1.774904045275651</v>
       </c>
       <c r="F2030" t="n">
         <v>0.2890289889978839</v>
@@ -48258,16 +48258,16 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
         <v>3.82407577475088</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.032825723067023</v>
+        <v>-5.068892625947797</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.810589061210324</v>
+        <v>1.796162300058015</v>
       </c>
       <c r="F2031" t="n">
         <v>0.2890289889978839</v>
@@ -48281,16 +48281,16 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
         <v>3.843113873625026</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.991686428200392</v>
+        <v>-5.027753331081166</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.846082878031122</v>
+        <v>1.831656116878813</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3301682838645147</v>
@@ -48304,16 +48304,16 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
         <v>3.65929786974896</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.895051516181752</v>
+        <v>-4.931118419062526</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.700920838962512</v>
+        <v>1.686494077810203</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4268031958831546</v>
@@ -48327,16 +48327,16 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
         <v>3.662799913822925</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.025632250712595</v>
+        <v>-5.061699153593368</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.652190589224139</v>
+        <v>1.63776382807183</v>
       </c>
       <c r="F2034" t="n">
         <v>0.2962224613523121</v>
@@ -48350,16 +48350,16 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.647226732899007</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.861135916521633</v>
+        <v>-4.897202819402406</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.702415941976607</v>
+        <v>1.687989180824298</v>
       </c>
       <c r="F2035" t="n">
         <v>0.460718795543274</v>
@@ -48373,16 +48373,16 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.646414443335437</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.888505849206065</v>
+        <v>-4.924572752086839</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.690655679339264</v>
+        <v>1.676228918186955</v>
       </c>
       <c r="F2036" t="n">
         <v>0.460718795543274</v>
@@ -48396,16 +48396,16 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.656283222460509</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.898891044095954</v>
+        <v>-4.934957946976728</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.69637038050838</v>
+        <v>1.681943619356071</v>
       </c>
       <c r="F2037" t="n">
         <v>0.4503336006533847</v>
@@ -48419,16 +48419,16 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
         <v>3.727120228236934</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.917479202818179</v>
+        <v>-4.953546105698953</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.759772122795916</v>
+        <v>1.745345361643606</v>
       </c>
       <c r="F2038" t="n">
         <v>0.4317454419311593</v>
@@ -48442,16 +48442,16 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.723989239055233</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.917777749514215</v>
+        <v>-4.953844652394989</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.7565217149358</v>
+        <v>1.74209495378349</v>
       </c>
       <c r="F2039" t="n">
         <v>0.4314468952351234</v>
@@ -48465,16 +48465,16 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.728520133994624</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.816954615823787</v>
+        <v>-4.853021518704561</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.801381863351362</v>
+        <v>1.786955102199053</v>
       </c>
       <c r="F2040" t="n">
         <v>0.4439111107194773</v>
@@ -48488,16 +48488,16 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
         <v>3.728649387473168</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.626173255071381</v>
+        <v>-4.662240157952154</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.877823661130868</v>
+        <v>1.863396899978559</v>
       </c>
       <c r="F2041" t="n">
         <v>0.6346924714718847</v>
@@ -48511,16 +48511,16 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
         <v>3.708486233210764</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.60765640102956</v>
+        <v>-4.643723303910334</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.865067248485193</v>
+        <v>1.850640487332884</v>
       </c>
       <c r="F2042" t="n">
         <v>0.6476226008970929</v>
@@ -48534,16 +48534,16 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912983</v>
       </c>
       <c r="C2043" t="n">
         <v>3.743453169822823</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.552325813127798</v>
+        <v>-4.588392716008571</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.922166420257956</v>
+        <v>1.907739659105647</v>
       </c>
       <c r="F2043" t="n">
         <v>0.702953188798855</v>
@@ -48557,16 +48557,16 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.743767956539893</v>
       </c>
       <c r="C2044" t="n">
         <v>3.73713973772426</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.540271686214835</v>
+        <v>-4.576338589095609</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.920674638924579</v>
+        <v>1.90624787777227</v>
       </c>
       <c r="F2044" t="n">
         <v>0.7150073157118179</v>
@@ -48580,16 +48580,16 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811007</v>
       </c>
       <c r="C2045" t="n">
         <v>3.739020367908396</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.581426805783056</v>
+        <v>-4.617493708663829</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.906093221281427</v>
+        <v>1.891666460129118</v>
       </c>
       <c r="F2045" t="n">
         <v>0.6738521961435969</v>
@@ -48603,16 +48603,16 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382918</v>
       </c>
       <c r="C2046" t="n">
         <v>3.751871393786279</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.478546216254463</v>
+        <v>-4.514613119135237</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.960096482970746</v>
+        <v>1.945669721818437</v>
       </c>
       <c r="F2046" t="n">
         <v>0.7767327856721898</v>
@@ -48626,16 +48626,16 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760312</v>
+        <v>3.646857607760314</v>
       </c>
       <c r="C2047" t="n">
         <v>3.772074063959873</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.710146609423964</v>
+        <v>-4.746213512304737</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.88765899587654</v>
+        <v>1.873232234724231</v>
       </c>
       <c r="F2047" t="n">
         <v>0.7767327856721898</v>
@@ -48649,16 +48649,16 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781703</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
         <v>3.772074063959873</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.728219117715575</v>
+        <v>-4.764286020596349</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.880429992559896</v>
+        <v>1.866003231407587</v>
       </c>
       <c r="F2048" t="n">
         <v>0.7767327856721898</v>
@@ -48672,16 +48672,16 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082832</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
         <v>3.73232597755334</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.90332595029202</v>
+        <v>-4.939392853172794</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.770639173122784</v>
+        <v>1.756212411970475</v>
       </c>
       <c r="F2049" t="n">
         <v>0.7767327856721898</v>
@@ -48695,16 +48695,16 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
         <v>3.73934859655028</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.872039929751565</v>
+        <v>-4.908106832632338</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.790176200335906</v>
+        <v>1.775749439183597</v>
       </c>
       <c r="F2050" t="n">
         <v>0.8080188062126452</v>
@@ -48718,16 +48718,16 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677822</v>
+        <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
         <v>3.838519596123184</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.71901453763828</v>
+        <v>-4.755081440519054</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.950557356754125</v>
+        <v>1.936130595601815</v>
       </c>
       <c r="F2051" t="n">
         <v>0.9610441983259294</v>
@@ -48741,16 +48741,16 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073881</v>
+        <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
         <v>4.025985821031476</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.747321851511551</v>
+        <v>-4.783388754392324</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.126700656113108</v>
+        <v>2.1122738949608</v>
       </c>
       <c r="F2052" t="n">
         <v>0.9610441983259294</v>
@@ -48764,16 +48764,16 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903166</v>
+        <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
         <v>3.995388772385558</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.913915076625073</v>
+        <v>-4.949981979505846</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.029466317421782</v>
+        <v>2.015039556269473</v>
       </c>
       <c r="F2053" t="n">
         <v>0.794450973212407</v>
@@ -48787,16 +48787,16 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568381</v>
+        <v>3.708202704568382</v>
       </c>
       <c r="C2054" t="n">
         <v>3.999065175047276</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.740850697242773</v>
+        <v>-4.776917600123546</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.10236847183642</v>
+        <v>2.08794171068411</v>
       </c>
       <c r="F2054" t="n">
         <v>0.794450973212407</v>
@@ -48810,16 +48810,16 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682202</v>
+        <v>3.740601586682204</v>
       </c>
       <c r="C2055" t="n">
         <v>3.996683230170771</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.711604716787076</v>
+        <v>-4.74767161966785</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.111684919142194</v>
+        <v>2.097258157989884</v>
       </c>
       <c r="F2055" t="n">
         <v>0.794450973212407</v>
@@ -48833,16 +48833,16 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539105</v>
+        <v>3.699424827539107</v>
       </c>
       <c r="C2056" t="n">
         <v>3.993976469328406</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.818530264664927</v>
+        <v>-4.854597167545701</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.066207939148688</v>
+        <v>2.051781177996379</v>
       </c>
       <c r="F2056" t="n">
         <v>0.6875254253345556</v>
@@ -48856,16 +48856,16 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983735</v>
+        <v>3.689962785983737</v>
       </c>
       <c r="C2057" t="n">
         <v>3.995405271471641</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.963548823172176</v>
+        <v>-4.99961572605295</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.009629317889023</v>
+        <v>1.995202556736714</v>
       </c>
       <c r="F2057" t="n">
         <v>0.5425068668273071</v>
@@ -48879,16 +48879,16 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969747</v>
+        <v>3.711872614969749</v>
       </c>
       <c r="C2058" t="n">
         <v>4.095336510729394</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.081890588956893</v>
+        <v>-5.117957491837667</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.062223850832889</v>
+        <v>2.04779708968058</v>
       </c>
       <c r="F2058" t="n">
         <v>0.5531929053901972</v>
@@ -48902,16 +48902,16 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073537</v>
+        <v>3.714899237073539</v>
       </c>
       <c r="C2059" t="n">
         <v>4.093122207855332</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.133301011277601</v>
+        <v>-5.169367914158375</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.039445379030544</v>
+        <v>2.025018617878235</v>
       </c>
       <c r="F2059" t="n">
         <v>0.5531929053901972</v>
@@ -48925,16 +48925,16 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720064</v>
+        <v>3.704778134720065</v>
       </c>
       <c r="C2060" t="n">
         <v>4.093025335929622</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.212720462485353</v>
+        <v>-5.248787365366127</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.007580726621733</v>
+        <v>1.993153965469424</v>
       </c>
       <c r="F2060" t="n">
         <v>0.5531929053901972</v>
@@ -48948,16 +48948,16 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581131</v>
+        <v>3.736825137581133</v>
       </c>
       <c r="C2061" t="n">
         <v>4.093019229487665</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.308183460402571</v>
+        <v>-5.344250363283344</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.969389421012889</v>
+        <v>1.95496265986058</v>
       </c>
       <c r="F2061" t="n">
         <v>0.5531929053901972</v>
@@ -48971,16 +48971,16 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500733</v>
+        <v>3.715393145500735</v>
       </c>
       <c r="C2062" t="n">
         <v>4.091115626050276</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.348203458446354</v>
+        <v>-5.384270361327128</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.951477818357987</v>
+        <v>1.937051057205678</v>
       </c>
       <c r="F2062" t="n">
         <v>0.5131729073464133</v>
@@ -48994,16 +48994,16 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636268</v>
+        <v>3.73610959863627</v>
       </c>
       <c r="C2063" t="n">
         <v>4.096849443798003</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.403572620578548</v>
+        <v>-5.439639523459322</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.935063971252836</v>
+        <v>1.920637210100527</v>
       </c>
       <c r="F2063" t="n">
         <v>0.5131729073464133</v>
@@ -49017,16 +49017,16 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396012</v>
+        <v>3.736843055396013</v>
       </c>
       <c r="C2064" t="n">
         <v>4.096387807140935</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.449010400409375</v>
+        <v>-5.485077303290149</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.916427222663438</v>
+        <v>1.902000461511129</v>
       </c>
       <c r="F2064" t="n">
         <v>0.4703279166682536</v>
@@ -49040,16 +49040,16 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396421</v>
+        <v>3.790292685396422</v>
       </c>
       <c r="C2065" t="n">
         <v>4.116262199991255</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.365784943561711</v>
+        <v>-5.401851846442485</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.969591798252823</v>
+        <v>1.955165037100514</v>
       </c>
       <c r="F2065" t="n">
         <v>0.4703279166682536</v>
@@ -49063,16 +49063,16 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299175</v>
+        <v>3.794507029299177</v>
       </c>
       <c r="C2066" t="n">
         <v>4.099962900515982</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.189494718956404</v>
+        <v>-5.225561621837177</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.023808588619674</v>
+        <v>2.009381827467365</v>
       </c>
       <c r="F2066" t="n">
         <v>0.4703279166682536</v>
@@ -49086,16 +49086,16 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.483187597670875</v>
+        <v>3.861547938638983</v>
       </c>
       <c r="C2067" t="n">
         <v>4.102393849980028</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.010316227655055</v>
+        <v>-5.029399679683903</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.097910934604259</v>
+        <v>2.09027755379272</v>
       </c>
       <c r="F2067" t="n">
         <v>0.4703279166682536</v>

--- a/tame_output/ON/bt/strategyON_20240826.xlsx
+++ b/tame_output/ON/bt/strategyON_20240826.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>50.5%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>94.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-29.5%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-48.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.4%</t>
+          <t>430.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-664.5%</t>
+          <t>-662.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,22 +1155,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-167.2%</t>
+          <t>-170.3%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-281.4%</t>
+          <t>-281.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>84.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-11.6%</t>
         </is>
       </c>
     </row>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355688</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511402</v>
+        <v>3.367379938511403</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998558</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082122</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.29349053375792</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760738</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706666</v>
+        <v>3.298730590706667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296833</v>
+        <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201484</v>
+        <v>3.295507330201485</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153003</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537423</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382188</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074619</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911635</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213491</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416041</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382323</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495494</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347049</v>
+        <v>3.299136146347052</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130011</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178237</v>
+        <v>3.31588437417824</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207807</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310976</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006528</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309418</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970899</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330517</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191731</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108633</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097814</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094109</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199278</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969586</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923078</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297741</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317609</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737163</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341306</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539457</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937496</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141699</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729888</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440631</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608598</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410269</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764393</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390583</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297395</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367402532254</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158918</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940714</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770574</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615277</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812097</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646211</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611563</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955322</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232407</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436223</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311943</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097238</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017765</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839719</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388723</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626468</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291809</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390425</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471879410595</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960983</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607641</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987897</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710809</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.873530691357055</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409201</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.864816705103577</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098106</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.857856093008484</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493417</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.872318447389627</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722814</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.866850567848822</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792043</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.864348661859399</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919903</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.872049640096724</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.867830348443774</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057522</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.86995466236379</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635497427918</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.862696737347493</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011493</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.866295860868141</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392981</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.879623366922695</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632775</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.878643844538992</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883069</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.883338645593309</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074777</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.864532904377105</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.866275981001982</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367679</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.870205294836802</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879959</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.870883878754142</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.867881949974136</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.86946098698475</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.885355169786573</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.886501014226875</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.896589116788315</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.882626608189741</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.897915777423949</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.805559976746391</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003596</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.724821838231692</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.715258546863584</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.852289383555786</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.856856615547574</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225439</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.832598644308781</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.761136957710231</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.771309344142363</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.766255614716223</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.758031390160749</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.75357116580319</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.75858326319385</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.96885187823265</v>
+        <v>-3.932784975351878</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.170686087587043</v>
+        <v>1.185112848739352</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5642899207513363</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.687855955085216</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.876041396781791</v>
+        <v>-3.839974493901019</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.137082972058753</v>
+        <v>1.151509733211062</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6571004022021957</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.689729431009817</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.920430866111218</v>
+        <v>-3.884363963230446</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.121200660251582</v>
+        <v>1.135627421403891</v>
       </c>
       <c r="F1947" t="n">
         <v>0.612710932872768</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.68480513952154</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.036972471216561</v>
+        <v>-4.000905568335789</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.069659726721168</v>
+        <v>1.084086487873477</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4961693277674253</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.690296435352207</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.076896565799133</v>
+        <v>-4.040829662918361</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.059181384718807</v>
+        <v>1.073608145871116</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4961693277674253</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498864</v>
       </c>
       <c r="C1950" t="n">
         <v>2.701793637120746</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.104676963700486</v>
+        <v>-4.068610060819713</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.059566427326805</v>
+        <v>1.073993188479114</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4683889298660722</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.5401493571214</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.223057636430624</v>
+        <v>-4.186990733549852</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8505698782354025</v>
+        <v>0.8649966393877115</v>
       </c>
       <c r="F1951" t="n">
         <v>0.401171077715096</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.660299017840605</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.331671714873956</v>
+        <v>-4.295604811993183</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9272739075772756</v>
+        <v>0.9417006687295848</v>
       </c>
       <c r="F1952" t="n">
         <v>0.401171077715096</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.674812043942928</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.296262676625813</v>
+        <v>-4.26019577374504</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9559505489788558</v>
+        <v>0.9703773101311648</v>
       </c>
       <c r="F1953" t="n">
         <v>0.401171077715096</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.672231485285297</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.257879014067662</v>
+        <v>-4.221812111186889</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.968723455344485</v>
+        <v>0.983150216496794</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4395547402732472</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.668960514130599</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.080762684032496</v>
+        <v>-4.044695781151723</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.036299016203853</v>
+        <v>1.050725777356162</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4395547402732472</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.669643905892512</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.125854928866041</v>
+        <v>-4.089788025985269</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.018945510032348</v>
+        <v>1.033372271184657</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3776586971038574</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.663430881198926</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.946479507627274</v>
+        <v>-3.910412604746501</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.08448265383427</v>
+        <v>1.098909414986579</v>
       </c>
       <c r="F1957" t="n">
         <v>0.534435455274576</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.644238336530516</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.99149372114788</v>
+        <v>-3.955426818267107</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.047284423757617</v>
+        <v>1.061711184909926</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5040865599599714</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.649929898869462</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.258498231420315</v>
+        <v>-4.222431328539543</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9461741819875884</v>
+        <v>0.9606009431398974</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3097235219170228</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.649133820765963</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.359696012857488</v>
+        <v>-4.323629109976715</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9048989913092207</v>
+        <v>0.9193257524615297</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2413147083717037</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64673378232028</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.353185046243175</v>
+        <v>-4.317118143362403</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9051033395092625</v>
+        <v>0.9195301006615715</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2413147083717037</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.643258501528525</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.334146918535878</v>
+        <v>-4.298080015655105</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9092433098004262</v>
+        <v>0.9236700709527355</v>
       </c>
       <c r="F1962" t="n">
         <v>0.1831310970405091</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.762552903162715</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.386662720810699</v>
+        <v>-4.350595817929926</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.007531390524689</v>
+        <v>1.021958151676998</v>
       </c>
       <c r="F1963" t="n">
         <v>0.1831310970405091</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.763386232148849</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.400529482144616</v>
+        <v>-4.364462579263844</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.002818014977255</v>
+        <v>1.017244776129564</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1452731803066862</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.769394762545775</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.355725310604686</v>
+        <v>-4.319658407723914</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.026748213990153</v>
+        <v>1.041174975142462</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1452731803066862</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.667344983822974</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.207982340369684</v>
+        <v>-4.171915437488911</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9837956233613534</v>
+        <v>0.9982223845136624</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3130805375415693</v>
@@ -46792,10 +46792,10 @@
         <v>2.670138605354455</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.291803561644382</v>
+        <v>-4.25573665876361</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.953060756382955</v>
+        <v>0.967487517535264</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3130805375415693</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.670800953746113</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.285650855591598</v>
+        <v>-4.249583952710825</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9561841871957271</v>
+        <v>0.9706109483480361</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3192332435943536</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.669881430486224</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.3024601537421</v>
+        <v>-4.266393250861327</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9485409446756365</v>
+        <v>0.9629677058279456</v>
       </c>
       <c r="F1969" t="n">
         <v>0.302423945443852</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.736216984283045</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.240162154965978</v>
+        <v>-4.204095252085205</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.039795697982906</v>
+        <v>1.054222459135215</v>
       </c>
       <c r="F1970" t="n">
         <v>0.347718209718294</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.538508985997172</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.03837195730082</v>
+        <v>-4.002305054420047</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9228037787630965</v>
+        <v>0.9372305399154057</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5457364018874484</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.608799218319347</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.089258669987014</v>
+        <v>-4.053191767106242</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9727393260107939</v>
+        <v>0.9871660871631029</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4948496892012539</v>
@@ -46930,10 +46930,10 @@
         <v>2.623426954435391</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.002647927337208</v>
+        <v>-3.966581024456434</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.02201135918676</v>
+        <v>1.03643812033907</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5734754204064122</v>
@@ -46953,10 +46953,10 @@
         <v>2.621962935260062</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.062857225342492</v>
+        <v>-4.026790322461719</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9964636208093183</v>
+        <v>1.010890381961628</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5132661224011277</v>
@@ -46976,10 +46976,10 @@
         <v>2.620454553299991</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.986435178910566</v>
+        <v>-3.950368276029792</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.025524057422018</v>
+        <v>1.039950818574327</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5132661224011277</v>
@@ -46999,10 +46999,10 @@
         <v>2.620317420735427</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.942062047271997</v>
+        <v>-3.905995144391223</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.043136177512881</v>
+        <v>1.05756293866519</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5576392540396963</v>
@@ -47022,10 +47022,10 @@
         <v>2.614711214874017</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.964542398130882</v>
+        <v>-3.928475495250108</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.028537831307918</v>
+        <v>1.042964592460227</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5576392540396963</v>
@@ -47045,10 +47045,10 @@
         <v>2.621092971901822</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.916886667569826</v>
+        <v>-3.880819764689052</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.053981880560145</v>
+        <v>1.068408641712454</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6052949846007519</v>
@@ -47068,10 +47068,10 @@
         <v>2.625985345276547</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.816368509071071</v>
+        <v>-3.780301606190298</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.099081517334372</v>
+        <v>1.113508278486681</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7058131430995065</v>
@@ -47091,10 +47091,10 @@
         <v>2.612740017752419</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.800463179638719</v>
+        <v>-3.764396276757945</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.092198321583185</v>
+        <v>1.106625082735494</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6267004823902675</v>
@@ -47114,10 +47114,10 @@
         <v>2.616837720363048</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.755624778030321</v>
+        <v>-3.719557875149547</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.114231384837173</v>
+        <v>1.128658145989482</v>
       </c>
       <c r="F1981" t="n">
         <v>0.631243915335137</v>
@@ -47137,10 +47137,10 @@
         <v>2.620998659994126</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.775123234272329</v>
+        <v>-3.739056331391555</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.110592941971447</v>
+        <v>1.125019703123756</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5831592740552327</v>
@@ -47160,10 +47160,10 @@
         <v>2.626878262521963</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.730920397186428</v>
+        <v>-3.694853494305655</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.134153679333645</v>
+        <v>1.148580440485954</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6273621111411332</v>
@@ -47183,10 +47183,10 @@
         <v>2.62528826299121</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.738480063023475</v>
+        <v>-3.702413160142702</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.129539813468073</v>
+        <v>1.143966574620382</v>
       </c>
       <c r="F1984" t="n">
         <v>0.6821655151509525</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
         <v>2.67653602817425</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.580188645484203</v>
+        <v>-3.544121742603429</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.244104145666822</v>
+        <v>1.258530906819131</v>
       </c>
       <c r="F1985" t="n">
         <v>0.6821655151509525</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.674976732768503</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.372546641849727</v>
+        <v>-3.336479738968953</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.325601651714865</v>
+        <v>1.340028412867175</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8898075187854286</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.669924961006773</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.321514549127199</v>
+        <v>-3.285447646246425</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.340962717042147</v>
+        <v>1.355389478194456</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9408396115079566</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.687112365099478</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.256290367999993</v>
+        <v>-3.220223465119219</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.384239793585734</v>
+        <v>1.398666554738043</v>
       </c>
       <c r="F1988" t="n">
         <v>1.006063792635162</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.683073337398759</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.218863347928859</v>
+        <v>-3.182796445048086</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.395171573913468</v>
+        <v>1.409598335065777</v>
       </c>
       <c r="F1989" t="n">
         <v>1.011315330664344</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.684330129729999</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.238975003963568</v>
+        <v>-3.202908101082794</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.388383703830825</v>
+        <v>1.402810464983134</v>
       </c>
       <c r="F1990" t="n">
         <v>1.022342675661763</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84488790075121</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.210561740863684</v>
+        <v>-3.17449483798291</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.560306780091989</v>
+        <v>1.574733541244298</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9633671129153341</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.965000809969027</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.135779479838671</v>
+        <v>-3.099712576957898</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.710332593719811</v>
+        <v>1.724759354872121</v>
       </c>
       <c r="F1992" t="n">
         <v>1.038149373940347</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.956708785982886</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.109695395574863</v>
+        <v>-3.07362849269409</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.712474203439194</v>
+        <v>1.726900964591503</v>
       </c>
       <c r="F1993" t="n">
         <v>1.038149373940347</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.954901981566665</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.021817482465743</v>
+        <v>-2.985750579584969</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.745818564266621</v>
+        <v>1.76024532541893</v>
       </c>
       <c r="F1994" t="n">
         <v>1.154075016363698</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.972456387293457</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.012925021072459</v>
+        <v>-2.976858118191686</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.766929954550726</v>
+        <v>1.781356715703035</v>
       </c>
       <c r="F1995" t="n">
         <v>1.154075016363698</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>2.964311434698041</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.181401138042337</v>
+        <v>-3.145334235161564</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.691394555167359</v>
+        <v>1.705821316319668</v>
       </c>
       <c r="F1996" t="n">
         <v>1.126127180647117</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.945581131885902</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.735144945412897</v>
+        <v>-2.699078042532124</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.851166729406997</v>
+        <v>1.865593490559306</v>
       </c>
       <c r="F1997" t="n">
         <v>1.031408510977484</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.936245154382807</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.712423841729745</v>
+        <v>-2.676356938848971</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.850919193377162</v>
+        <v>1.865345954529471</v>
       </c>
       <c r="F1998" t="n">
         <v>1.031408510977484</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>3.095151280233976</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.841625655023787</v>
+        <v>-2.805558752143014</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.958144593910714</v>
+        <v>1.972571355063023</v>
       </c>
       <c r="F1999" t="n">
         <v>0.902206697683442</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>3.132229102727623</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.867500053497813</v>
+        <v>-2.831433150617039</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.98487265701475</v>
+        <v>1.99929941816706</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9471183063951831</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.128904458717168</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.860445363282639</v>
+        <v>-2.824378460401866</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.984369889090365</v>
+        <v>1.998796650242674</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9541729966103569</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>3.138910612361909</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.833494138956151</v>
+        <v>-2.797427236075378</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.005156532465702</v>
+        <v>2.019583293618011</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9690533426380761</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.323013744506869</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.969447147012468</v>
+        <v>-2.933380244131694</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.134878461388135</v>
+        <v>2.149305222540444</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9690533426380761</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.315130439409862</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.99185526481734</v>
+        <v>-2.955788361936566</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.118031909169179</v>
+        <v>2.132458670321489</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9690533426380761</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.3171844389595</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.02007950039494</v>
+        <v>-2.984012597514166</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.108796214487777</v>
+        <v>2.123222975640086</v>
       </c>
       <c r="F2005" t="n">
         <v>0.9870300950893847</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
         <v>3.373438156681347</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.02952042628347</v>
+        <v>-2.993453523402696</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.161273561854212</v>
+        <v>2.175700323006521</v>
       </c>
       <c r="F2006" t="n">
         <v>1.109457212632776</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
         <v>3.376329251226648</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.081794033619111</v>
+        <v>-3.045727130738338</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.143255213465256</v>
+        <v>2.157681974617566</v>
       </c>
       <c r="F2007" t="n">
         <v>1.057183605297135</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.374441064120423</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.158124011220017</v>
+        <v>-3.122057108339244</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.110835035318669</v>
+        <v>2.125261796470978</v>
       </c>
       <c r="F2008" t="n">
         <v>1.057183605297135</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.369261293723285</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.360377731544371</v>
+        <v>-3.324310828663597</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.02475377679179</v>
+        <v>2.039180537944099</v>
       </c>
       <c r="F2009" t="n">
         <v>0.8549298849727813</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343067</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.367695303933437</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.521946157071626</v>
+        <v>-3.485879254190852</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.95856041679104</v>
+        <v>1.972987177943349</v>
       </c>
       <c r="F2010" t="n">
         <v>0.728146961174902</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389349</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.380768710799356</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.630246818941745</v>
+        <v>-3.594179916060972</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.928313558908911</v>
+        <v>1.94274032006122</v>
       </c>
       <c r="F2011" t="n">
         <v>0.728146961174902</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378393</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.372773907582296</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.723394290245112</v>
+        <v>-3.687327387364338</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.883059767170504</v>
+        <v>1.897486528322814</v>
       </c>
       <c r="F2012" t="n">
         <v>0.6053177498923692</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006976</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.371297948709298</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.751295077354585</v>
+        <v>-3.715228174473811</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.870423493453717</v>
+        <v>1.884850254606026</v>
       </c>
       <c r="F2013" t="n">
         <v>0.5707208257494344</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.368062392686497</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.873821180057479</v>
+        <v>-3.837754277176705</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.818177496349758</v>
+        <v>1.832604257502068</v>
       </c>
       <c r="F2014" t="n">
         <v>0.4481947230465405</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.434768352277001</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.104335676243068</v>
+        <v>-4.068268773362294</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.792677657466027</v>
+        <v>1.807104418618336</v>
       </c>
       <c r="F2015" t="n">
         <v>0.2176802268609518</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.575080071278848</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.361056494237892</v>
+        <v>-4.324989591357118</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.830301049269944</v>
+        <v>1.844727810422253</v>
       </c>
       <c r="F2016" t="n">
         <v>0.109265652717137</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.644060340424487</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.515042912014033</v>
+        <v>-4.478976009133259</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.837686751305127</v>
+        <v>1.852113512457437</v>
       </c>
       <c r="F2017" t="n">
         <v>0.109265652717137</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.630111542544608</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.464521008186367</v>
+        <v>-4.428454105305593</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.843946714956315</v>
+        <v>1.858373476108624</v>
       </c>
       <c r="F2018" t="n">
         <v>0.109265652717137</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609753</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.641982031600022</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.716996162194091</v>
+        <v>-4.680929259313317</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.754827142408639</v>
+        <v>1.769253903560948</v>
       </c>
       <c r="F2019" t="n">
         <v>0.109265652717137</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973158</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.643192566118966</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.009891918673503</v>
+        <v>-4.97382501579273</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.638879374335818</v>
+        <v>1.653306135488127</v>
       </c>
       <c r="F2020" t="n">
         <v>0.109265652717137</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.647314308346287</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.196556046808311</v>
+        <v>-5.160489143927538</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.568335465309216</v>
+        <v>1.582762226461525</v>
       </c>
       <c r="F2021" t="n">
         <v>0.08252668189257706</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.652149152916199</v>
       </c>
       <c r="C2022" t="n">
         <v>3.642392161082477</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.342576733722273</v>
+        <v>-5.3065098308415</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.50500504327982</v>
+        <v>1.51943180443213</v>
       </c>
       <c r="F2022" t="n">
         <v>0.07344359009872009</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830329</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
         <v>3.804596217781521</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.434290742831858</v>
+        <v>-5.398223839951084</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.630523496335031</v>
+        <v>1.64495025748734</v>
       </c>
       <c r="F2023" t="n">
         <v>0.07344359009872009</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
         <v>3.799442855745335</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.465942401891827</v>
+        <v>-5.429875499011054</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.612709470674857</v>
+        <v>1.627136231827166</v>
       </c>
       <c r="F2024" t="n">
         <v>0.06827513285427989</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.809672273313826</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.547877220160711</v>
+        <v>-5.511810317279937</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.590164960935795</v>
+        <v>1.604591722088104</v>
       </c>
       <c r="F2025" t="n">
         <v>0.0583403872671997</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.818597911769729</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.649853342409118</v>
+        <v>-5.613786439528345</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.558300150492335</v>
+        <v>1.572726911644644</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.04363573498120787</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.810750799013904</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.539847058931897</v>
+        <v>-5.503780156051123</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.594455551127398</v>
+        <v>1.608882312279707</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.02043116306393267</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.815000809735878</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.396787483190971</v>
+        <v>-5.360720580310197</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.655929392145743</v>
+        <v>1.670356153298052</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.01241773647395339</v>
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.822261692618414</v>
+        <v>3.781490685150103</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.095340757719133</v>
+        <v>-5.059273854838359</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.783768965217014</v>
+        <v>1.757424718901011</v>
       </c>
       <c r="F2029" t="n">
         <v>0.2890289889978839</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.995679086017144</v>
+        <v>3.954908078548833</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.823232870371125</v>
+        <v>3.782461862902813</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.119931001954317</v>
+        <v>-5.083864099073543</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.774904045275651</v>
+        <v>1.748559798959649</v>
       </c>
       <c r="F2030" t="n">
         <v>0.2890289889978839</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.996650263769856</v>
+        <v>3.955879256301544</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.82407577475088</v>
+        <v>3.783304767282569</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.068892625947797</v>
+        <v>-5.032825723067023</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.796162300058015</v>
+        <v>1.769818053742013</v>
       </c>
       <c r="F2031" t="n">
         <v>0.2890289889978839</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.997493168149611</v>
+        <v>3.956722160681299</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.843113873625026</v>
+        <v>3.802342866156714</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.027753331081166</v>
+        <v>-4.991686428200392</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.831656116878813</v>
+        <v>1.80531187056281</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3301682838645147</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.041214843943735</v>
+        <v>4.000443836475423</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.65929786974896</v>
+        <v>3.618526862280649</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.931118419062526</v>
+        <v>-4.895051516181752</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.686494077810203</v>
+        <v>1.660149831494201</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4268031958831546</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.915379787278853</v>
+        <v>3.874608779810542</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.662799913822925</v>
+        <v>3.622028906354613</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.061699153593368</v>
+        <v>-5.025632250712595</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.63776382807183</v>
+        <v>1.611419581755828</v>
       </c>
       <c r="F2034" t="n">
         <v>0.2962224613523121</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.840533390634312</v>
+        <v>3.799762383166001</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.647226732899007</v>
+        <v>3.606455725430695</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.897202819402406</v>
+        <v>-4.861135916521633</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.687989180824298</v>
+        <v>1.661644934508295</v>
       </c>
       <c r="F2035" t="n">
         <v>0.460718795543274</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.923658010224972</v>
+        <v>3.88288700275666</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.646414443335437</v>
+        <v>3.605643435867125</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.924572752086839</v>
+        <v>-4.888505849206065</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.676228918186955</v>
+        <v>1.649884671870952</v>
       </c>
       <c r="F2036" t="n">
         <v>0.460718795543274</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.922845720661401</v>
+        <v>3.88207471319309</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147908</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.656283222460509</v>
+        <v>3.615512214992198</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.934957946976728</v>
+        <v>-4.898891044095954</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.681943619356071</v>
+        <v>1.655599373040069</v>
       </c>
       <c r="F2037" t="n">
         <v>0.4503336006533847</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.92648338285254</v>
+        <v>3.885712375384229</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.727120228236934</v>
+        <v>3.686349220768623</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.953546105698953</v>
+        <v>-4.917479202818179</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.745345361643606</v>
+        <v>1.719001115327604</v>
       </c>
       <c r="F2038" t="n">
         <v>0.4317454419311593</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.98616749339563</v>
+        <v>3.945396485927319</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.723989239055233</v>
+        <v>3.683218231586921</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.953844652394989</v>
+        <v>-4.917777749514215</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.74209495378349</v>
+        <v>1.715750707467488</v>
       </c>
       <c r="F2039" t="n">
         <v>0.4314468952351234</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.982857376196307</v>
+        <v>3.942086368727995</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.728520133994624</v>
+        <v>3.687749126526313</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.853021518704561</v>
+        <v>-4.816954615823787</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.786955102199053</v>
+        <v>1.76061085588305</v>
       </c>
       <c r="F2040" t="n">
         <v>0.4439111107194773</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.994866800426311</v>
+        <v>3.954095792957999</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121465</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.728649387473168</v>
+        <v>3.687878380004856</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.662240157952154</v>
+        <v>-4.626173255071381</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.863396899978559</v>
+        <v>1.837052653662556</v>
       </c>
       <c r="F2041" t="n">
         <v>0.6346924714718847</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.109464870356299</v>
+        <v>4.068693862887987</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.708486233210764</v>
+        <v>3.667715225742453</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.643723303910334</v>
+        <v>-4.60765640102956</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.850640487332884</v>
+        <v>1.824296241016881</v>
       </c>
       <c r="F2042" t="n">
         <v>0.6476226008970929</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.09705979374902</v>
+        <v>4.056288786280708</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912983</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.743453169822823</v>
+        <v>3.702682162354511</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.588392716008571</v>
+        <v>-4.552325813127798</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.907739659105647</v>
+        <v>1.881395412789645</v>
       </c>
       <c r="F2043" t="n">
         <v>0.702953188798855</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.165225083102136</v>
+        <v>4.124454075633825</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539893</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.73713973772426</v>
+        <v>3.696368730255949</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.576338589095609</v>
+        <v>-4.540271686214835</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.90624787777227</v>
+        <v>1.879903631456267</v>
       </c>
       <c r="F2044" t="n">
         <v>0.7150073157118179</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.166144127151352</v>
+        <v>4.12537311968304</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811007</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.739020367908396</v>
+        <v>3.698249360440085</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.617493708663829</v>
+        <v>-4.581426805783056</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.891666460129118</v>
+        <v>1.865322213813115</v>
       </c>
       <c r="F2045" t="n">
         <v>0.6738521961435969</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.143331685594554</v>
+        <v>4.102560678126243</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382918</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.751871393786279</v>
+        <v>3.711100386317967</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.514613119135237</v>
+        <v>-4.478546216254463</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.945669721818437</v>
+        <v>1.919325475502434</v>
       </c>
       <c r="F2046" t="n">
         <v>0.7767327856721898</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.217911065189593</v>
+        <v>4.177140057721282</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760314</v>
+        <v>3.646857607760312</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.772074063959873</v>
+        <v>3.731303056491561</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.746213512304737</v>
+        <v>-4.710146609423964</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.873232234724231</v>
+        <v>1.846887988408229</v>
       </c>
       <c r="F2047" t="n">
         <v>0.7767327856721898</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.238113735363187</v>
+        <v>4.197342727894876</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.772074063959873</v>
+        <v>3.731303056491561</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.764286020596349</v>
+        <v>-4.728219117715575</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.866003231407587</v>
+        <v>1.839658985091584</v>
       </c>
       <c r="F2048" t="n">
         <v>0.7767327856721898</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.238113735363187</v>
+        <v>4.197342727894876</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082832</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.73232597755334</v>
+        <v>3.691554970085028</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.939392853172794</v>
+        <v>-4.90332595029202</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.756212411970475</v>
+        <v>1.729868165654473</v>
       </c>
       <c r="F2049" t="n">
         <v>0.7767327856721898</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.198365648956654</v>
+        <v>4.157594641488342</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.73934859655028</v>
+        <v>3.698577589081968</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.908106832632338</v>
+        <v>-4.872039929751565</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.775749439183597</v>
+        <v>1.749405192867595</v>
       </c>
       <c r="F2050" t="n">
         <v>0.8080188062126452</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.224159880277867</v>
+        <v>4.183388872809555</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677824</v>
+        <v>3.730590658677821</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.838519596123184</v>
+        <v>3.797748588654872</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.755081440519054</v>
+        <v>-4.71901453763828</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.936130595601815</v>
+        <v>1.909786349285813</v>
       </c>
       <c r="F2051" t="n">
         <v>0.9610441983259294</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.415146115118742</v>
+        <v>4.37437510765043</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.741298518073881</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.025985821031476</v>
+        <v>3.985214813563164</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.783388754392324</v>
+        <v>-4.747321851511551</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.1122738949608</v>
+        <v>2.085929648644797</v>
       </c>
       <c r="F2052" t="n">
         <v>0.9610441983259294</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.602612340027034</v>
+        <v>4.561841332558722</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.699135800903166</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.995388772385558</v>
+        <v>3.954617764917247</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.949981979505846</v>
+        <v>-4.913915076625073</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.015039556269473</v>
+        <v>1.98869530995347</v>
       </c>
       <c r="F2053" t="n">
         <v>0.794450973212407</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.472059356313003</v>
+        <v>4.431288348844691</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568382</v>
+        <v>3.70820270456838</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.999065175047276</v>
+        <v>3.958294167578964</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.776917600123546</v>
+        <v>-4.740850697242773</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.08794171068411</v>
+        <v>2.061597464368108</v>
       </c>
       <c r="F2054" t="n">
         <v>0.794450973212407</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.475735758974721</v>
+        <v>4.434964751506409</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682204</v>
+        <v>3.740601586682201</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.996683230170771</v>
+        <v>3.95591222270246</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.74767161966785</v>
+        <v>-4.711604716787076</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.097258157989884</v>
+        <v>2.070913911673882</v>
       </c>
       <c r="F2055" t="n">
         <v>0.794450973212407</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.473353814098216</v>
+        <v>4.432582806629904</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539107</v>
+        <v>3.699424827539104</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.993976469328406</v>
+        <v>3.953205461860095</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.854597167545701</v>
+        <v>-4.818530264664927</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.051781177996379</v>
+        <v>2.025436931680376</v>
       </c>
       <c r="F2056" t="n">
         <v>0.6875254253345556</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.40649172452914</v>
+        <v>4.365720717060828</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983737</v>
+        <v>3.689962785983735</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.995405271471641</v>
+        <v>3.954634264003329</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.99961572605295</v>
+        <v>-4.963548823172176</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.995202556736714</v>
+        <v>1.968858310420711</v>
       </c>
       <c r="F2057" t="n">
         <v>0.5425068668273071</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.320909391568025</v>
+        <v>4.280138384099714</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969749</v>
+        <v>3.711872614969746</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.095336510729394</v>
+        <v>4.054565503261082</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.117957491837667</v>
+        <v>-5.081890588956893</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.04779708968058</v>
+        <v>2.021452843364577</v>
       </c>
       <c r="F2058" t="n">
         <v>0.5531929053901972</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.427252253963512</v>
+        <v>4.3864812464952</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073539</v>
+        <v>3.714899237073535</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.093122207855332</v>
+        <v>4.052351200387021</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.169367914158375</v>
+        <v>-5.133301011277601</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.025018617878235</v>
+        <v>1.998674371562233</v>
       </c>
       <c r="F2059" t="n">
         <v>0.5531929053901972</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.42503795108945</v>
+        <v>4.384266943621139</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720065</v>
+        <v>3.704778134720062</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.093025335929622</v>
+        <v>4.05225432846131</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.248787365366127</v>
+        <v>-5.212720462485353</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.993153965469424</v>
+        <v>1.966809719153422</v>
       </c>
       <c r="F2060" t="n">
         <v>0.5531929053901972</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.42494107916374</v>
+        <v>4.384170071695428</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581133</v>
+        <v>3.736825137581129</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.093019229487665</v>
+        <v>4.052248222019354</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.344250363283344</v>
+        <v>-5.308183460402571</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.95496265986058</v>
+        <v>1.928618413544578</v>
       </c>
       <c r="F2061" t="n">
         <v>0.5531929053901972</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.424934972721783</v>
+        <v>4.384163965253472</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500735</v>
+        <v>3.715393145500731</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.091115626050276</v>
+        <v>4.050344618581964</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.384270361327128</v>
+        <v>-5.348203458446354</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.937051057205678</v>
+        <v>1.910706810889675</v>
       </c>
       <c r="F2062" t="n">
         <v>0.5131729073464133</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.399019370458124</v>
+        <v>4.358248362989812</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.73610959863627</v>
+        <v>3.736109598636267</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.096849443798003</v>
+        <v>4.056078436329691</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.439639523459322</v>
+        <v>-5.403572620578548</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.920637210100527</v>
+        <v>1.894292963784524</v>
       </c>
       <c r="F2063" t="n">
         <v>0.5131729073464133</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.40475318820585</v>
+        <v>4.363982180737539</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396013</v>
+        <v>3.73684305539601</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.096387807140935</v>
+        <v>4.055616799672624</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.485077303290149</v>
+        <v>-5.449010400409375</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.902000461511129</v>
+        <v>1.875656215195126</v>
       </c>
       <c r="F2064" t="n">
         <v>0.4703279166682536</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.378584557141888</v>
+        <v>4.337813549673577</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396422</v>
+        <v>3.790292685396419</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.116262199991255</v>
+        <v>4.075491192522943</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.401851846442485</v>
+        <v>-5.365784943561711</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.955165037100514</v>
+        <v>1.928820790784511</v>
       </c>
       <c r="F2065" t="n">
         <v>0.4703279166682536</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.398458949992207</v>
+        <v>4.357687942523896</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299177</v>
+        <v>3.794507029299173</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.099962900515982</v>
+        <v>4.059191893047671</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.225561621837177</v>
+        <v>-5.189494718956404</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.009381827467365</v>
+        <v>1.983037581151362</v>
       </c>
       <c r="F2066" t="n">
         <v>0.4703279166682536</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.382159650516935</v>
+        <v>4.341388643048623</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.861547938638983</v>
+        <v>3.785443209555928</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.102393849980028</v>
+        <v>4.061622842511716</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.029399679683903</v>
+        <v>-5.006283055823308</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.09027755379272</v>
+        <v>2.058753195868646</v>
       </c>
       <c r="F2067" t="n">
         <v>0.4703279166682536</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.384590599980981</v>
+        <v>4.343819592512669</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240826.xlsx
+++ b/tame_output/ON/bt/strategyON_20240826.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>24.6%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>98.6%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.5%</t>
+          <t>428.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-662.2%</t>
+          <t>-678.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-170.3%</t>
+          <t>-172.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-281.8%</t>
+          <t>-285.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-177.0%</t>
+          <t>-192.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-17.0%</t>
         </is>
       </c>
     </row>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296835</v>
+        <v>3.299918119296834</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911636</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213492</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416042</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.235981977382324</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.278199702495495</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347052</v>
+        <v>3.29913614634705</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130012</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178238</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207808</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309419</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.37443904309411</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199279</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969587</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923079</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297742</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.44775050131761</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646212</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611563</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955323</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017766</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839719</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388723</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626468</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.78471879410595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607641</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987897</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.873530691357055</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.864816705103577</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.857856093008484</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493416</v>
       </c>
       <c r="C1913" t="n">
         <v>2.872318447389627</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722812</v>
       </c>
       <c r="C1914" t="n">
         <v>2.866850567848822</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792041</v>
       </c>
       <c r="C1915" t="n">
         <v>2.864348661859399</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919901</v>
       </c>
       <c r="C1916" t="n">
         <v>2.872049640096724</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318088</v>
       </c>
       <c r="C1917" t="n">
         <v>2.867830348443774</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.82431123305752</v>
       </c>
       <c r="C1918" t="n">
         <v>2.86995466236379</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279178</v>
       </c>
       <c r="C1919" t="n">
         <v>2.862696737347493</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011491</v>
       </c>
       <c r="C1920" t="n">
         <v>2.866295860868141</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392979</v>
       </c>
       <c r="C1921" t="n">
         <v>2.879623366922695</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632774</v>
       </c>
       <c r="C1922" t="n">
         <v>2.878643844538992</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883067</v>
       </c>
       <c r="C1923" t="n">
         <v>2.883338645593309</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074776</v>
       </c>
       <c r="C1924" t="n">
         <v>2.864532904377105</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242287</v>
       </c>
       <c r="C1925" t="n">
         <v>2.866275981001982</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367677</v>
       </c>
       <c r="C1926" t="n">
         <v>2.870205294836802</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879958</v>
       </c>
       <c r="C1927" t="n">
         <v>2.870883878754142</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.84861662650233</v>
       </c>
       <c r="C1928" t="n">
         <v>2.867881949974136</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675936</v>
+        <v>3.818668951675932</v>
       </c>
       <c r="C1929" t="n">
         <v>2.86946098698475</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539948</v>
+        <v>3.843274527539943</v>
       </c>
       <c r="C1930" t="n">
         <v>2.885355169786573</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496256</v>
       </c>
       <c r="C1931" t="n">
         <v>2.886501014226875</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.896589116788315</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942098</v>
       </c>
       <c r="C1933" t="n">
         <v>2.882626608189741</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674509</v>
       </c>
       <c r="C1934" t="n">
         <v>2.897915777423949</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430688</v>
       </c>
       <c r="C1935" t="n">
         <v>2.805559976746391</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003595</v>
       </c>
       <c r="C1936" t="n">
         <v>2.724821838231692</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.715258546863584</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417698</v>
       </c>
       <c r="C1938" t="n">
         <v>2.852289383555786</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205893</v>
       </c>
       <c r="C1939" t="n">
         <v>2.856856615547574</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225437</v>
       </c>
       <c r="C1940" t="n">
         <v>2.832598644308781</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.761136957710231</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.771309344142363</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.766255614716223</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.758031390160749</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.75858326319385</v>
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.687855955085216</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.839974493901019</v>
+        <v>-3.997936051545109</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.151509733211062</v>
+        <v>1.088325110153425</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6571004022021957</v>
+        <v>0.4991388445581053</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.082116196406534</v>
+        <v>2.98733926182008</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560423</v>
       </c>
       <c r="C1947" t="n">
         <v>2.689729431009817</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.884363963230446</v>
+        <v>-4.042325520874536</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.135627421403891</v>
+        <v>1.072442798346255</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.612710932872768</v>
+        <v>0.4547493752286776</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.057355990733478</v>
+        <v>2.962579056147024</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472735</v>
       </c>
       <c r="C1948" t="n">
         <v>2.68480513952154</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.000905568335789</v>
+        <v>-4.158867125979879</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.084086487873477</v>
+        <v>1.020901864815841</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4961693277674253</v>
+        <v>0.3382077701233349</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.982506736181995</v>
+        <v>2.887729801595541</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.690296435352207</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.040829662918361</v>
+        <v>-4.198791220562451</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.073608145871116</v>
+        <v>1.010423522813479</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4961693277674253</v>
+        <v>0.3382077701233349</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.987998032012662</v>
+        <v>2.893221097426208</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498864</v>
+        <v>3.68959784049886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.701793637120746</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.068610060819713</v>
+        <v>-4.226571618463804</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.073993188479114</v>
+        <v>1.010808565421478</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4683889298660722</v>
+        <v>0.3104273722219818</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.98282699504039</v>
+        <v>2.888050060453935</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.64306962170532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.5401493571214</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.186990733549852</v>
+        <v>-4.344952291193942</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8649966393877115</v>
+        <v>0.8018120163300755</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.401171077715096</v>
+        <v>0.2432095200710056</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.780852003750458</v>
+        <v>2.686075069164003</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729264</v>
       </c>
       <c r="C1952" t="n">
         <v>2.660299017840605</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.295604811993183</v>
+        <v>-4.453566369637273</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9417006687295848</v>
+        <v>0.8785160456719487</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.401171077715096</v>
+        <v>0.2432095200710056</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.901001664469663</v>
+        <v>2.806224729883209</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190764</v>
       </c>
       <c r="C1953" t="n">
         <v>2.674812043942928</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.26019577374504</v>
+        <v>-4.41815733138913</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9703773101311648</v>
+        <v>0.9071926870735287</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.401171077715096</v>
+        <v>0.2432095200710056</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.915514690571986</v>
+        <v>2.820737755985532</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.672231485285297</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.221812111186889</v>
+        <v>-4.379773668830979</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.983150216496794</v>
+        <v>0.919965593439158</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4395547402732472</v>
+        <v>0.2815931826291568</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.935964329449245</v>
+        <v>2.841187394862791</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.668960514130599</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.044695781151723</v>
+        <v>-4.202657338795813</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.050725777356162</v>
+        <v>0.9875411542985262</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4395547402732472</v>
+        <v>0.2815931826291568</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.932693358294547</v>
+        <v>2.837916423708093</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.669643905892512</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.089788025985269</v>
+        <v>-4.247749583629359</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.033372271184657</v>
+        <v>0.9701876481270211</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3776586971038574</v>
+        <v>0.219697139459767</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.896239124154826</v>
+        <v>2.801462189568372</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.663430881198926</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.910412604746501</v>
+        <v>-4.068374162390591</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.098909414986579</v>
+        <v>1.035724791928943</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.534435455274576</v>
+        <v>0.3764738976304857</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.984092154363672</v>
+        <v>2.889315219777218</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982225</v>
       </c>
       <c r="C1958" t="n">
         <v>2.644238336530516</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.955426818267107</v>
+        <v>-4.113388375911198</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.061711184909926</v>
+        <v>0.9985265618522896</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5040865599599714</v>
+        <v>0.3461250023158811</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.946690272506499</v>
+        <v>2.851913337920045</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.649929898869462</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.222431328539543</v>
+        <v>-4.380392886183633</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9606009431398974</v>
+        <v>0.8974163200822614</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3097235219170228</v>
+        <v>0.1517619642729325</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.835764012019676</v>
+        <v>2.740987077433222</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.649133820765963</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.323629109976715</v>
+        <v>-4.481590667620805</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9193257524615297</v>
+        <v>0.8561411294038936</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2413147083717037</v>
+        <v>0.08335315072761329</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.793922645788986</v>
+        <v>2.699145711202531</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64673378232028</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.317118143362403</v>
+        <v>-4.475079701006493</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9195301006615715</v>
+        <v>0.8563454776039354</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2413147083717037</v>
+        <v>0.08335315072761329</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.791522607343302</v>
+        <v>2.696745672756848</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.643258501528525</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.298080015655105</v>
+        <v>-4.456041573299196</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9236700709527355</v>
+        <v>0.8604854478950994</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1831310970405091</v>
+        <v>0.02516953939641875</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.753137159752831</v>
+        <v>2.658360225166376</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.762552903162715</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.350595817929926</v>
+        <v>-4.508557375574016</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.021958151676998</v>
+        <v>0.9587735286193615</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1831310970405091</v>
+        <v>0.02516953939641875</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.872431561387021</v>
+        <v>2.777654626800567</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.763386232148849</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.364462579263844</v>
+        <v>-4.522424136907934</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.017244776129564</v>
+        <v>0.9540601530719279</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1452731803066862</v>
+        <v>-0.01268837733740419</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.850550140332861</v>
+        <v>2.755773205746407</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.769394762545775</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.319658407723914</v>
+        <v>-4.477619965368004</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.041174975142462</v>
+        <v>0.9779903520848259</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1452731803066862</v>
+        <v>-0.01268837733740419</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.856558670729787</v>
+        <v>2.761781736143333</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.667344983822974</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.171915437488911</v>
+        <v>-4.329876995133001</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9982223845136624</v>
+        <v>0.9350377614560264</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3130805375415693</v>
+        <v>0.155118979897479</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.855193306347916</v>
+        <v>2.760416371761462</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.670138605354455</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.25573665876361</v>
+        <v>-4.4136982164077</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.967487517535264</v>
+        <v>0.9043028944776279</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3130805375415693</v>
+        <v>0.155118979897479</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.857986927879397</v>
+        <v>2.763209993292943</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.670800953746113</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.249583952710825</v>
+        <v>-4.407545510354915</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9706109483480361</v>
+        <v>0.9074263252904</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3192332435943536</v>
+        <v>0.1612716859502633</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.862340899902726</v>
+        <v>2.767563965316272</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.669881430486224</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.266393250861327</v>
+        <v>-4.424354808505417</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9629677058279456</v>
+        <v>0.8997830827703095</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.302423945443852</v>
+        <v>0.1444623877997616</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.851335797752535</v>
+        <v>2.756558863166081</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.736216984283045</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.204095252085205</v>
+        <v>-4.362056809729295</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.054222459135215</v>
+        <v>0.9910378360775793</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.347718209718294</v>
+        <v>0.1897566520742037</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.944847910114021</v>
+        <v>2.850070975527567</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.538508985997172</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.002305054420047</v>
+        <v>-4.160266612064137</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9372305399154057</v>
+        <v>0.8740459168577694</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5457364018874484</v>
+        <v>0.3877748442433581</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.865950827129641</v>
+        <v>2.771173892543187</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.608799218319347</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.053191767106242</v>
+        <v>-4.211153324750332</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9871660871631029</v>
+        <v>0.9239814641054669</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4948496892012539</v>
+        <v>0.3368881315571635</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.905709031840099</v>
+        <v>2.810932097253645</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.623426954435391</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.966581024456434</v>
+        <v>-4.124542582100525</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.03643812033907</v>
+        <v>0.9732534972814333</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5734754204064122</v>
+        <v>0.4155138627623218</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.967512206679238</v>
+        <v>2.872735272092784</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.621962935260062</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.026790322461719</v>
+        <v>-4.18475188010581</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.010890381961628</v>
+        <v>0.947705758903991</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5132661224011277</v>
+        <v>0.3553045647570373</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.929922608700739</v>
+        <v>2.835145674114285</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.620454553299991</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.950368276029792</v>
+        <v>-4.108329833673883</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.039950818574327</v>
+        <v>0.9767661955166902</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5132661224011277</v>
+        <v>0.3553045647570373</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.928414226740668</v>
+        <v>2.833637292154213</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.620317420735427</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.905995144391223</v>
+        <v>-4.063956702035314</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.05756293866519</v>
+        <v>0.9943783156075539</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5576392540396963</v>
+        <v>0.3996776963956059</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.954900973159245</v>
+        <v>2.860124038572791</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.614711214874017</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.928475495250108</v>
+        <v>-4.086437052894199</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.042964592460227</v>
+        <v>0.9797799694025904</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5576392540396963</v>
+        <v>0.3996776963956059</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.949294767297836</v>
+        <v>2.854517832711381</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.621092971901822</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.880819764689052</v>
+        <v>-4.038781322333143</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.068408641712454</v>
+        <v>1.005224018654817</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6052949846007519</v>
+        <v>0.4473334269566615</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.984269962662274</v>
+        <v>2.889493028075819</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.625985345276547</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.780301606190298</v>
+        <v>-3.938263163834389</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.113508278486681</v>
+        <v>1.050323655429044</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7058131430995065</v>
+        <v>0.547851585455416</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.049473231136251</v>
+        <v>2.954696296549797</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.612740017752419</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.764396276757945</v>
+        <v>-3.922357834402036</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.106625082735494</v>
+        <v>1.043440459677857</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6267004823902675</v>
+        <v>0.4687389247461771</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.98876030718658</v>
+        <v>2.893983372600126</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932768</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.616837720363048</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.719557875149547</v>
+        <v>-3.877519432793638</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.128658145989482</v>
+        <v>1.065473522931845</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.631243915335137</v>
+        <v>0.4732823576910466</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.99558406956413</v>
+        <v>2.900807134977676</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.620998659994126</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.739056331391555</v>
+        <v>-3.897017889035646</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.125019703123756</v>
+        <v>1.06183508006612</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5831592740552327</v>
+        <v>0.4251977164111423</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.970894224427266</v>
+        <v>2.876117289840812</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.626878262521963</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.694853494305655</v>
+        <v>-3.852815051949746</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.148580440485954</v>
+        <v>1.085395817428317</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6273621111411332</v>
+        <v>0.4694005534970427</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.003295529206643</v>
+        <v>2.908518594620189</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.62528826299121</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.702413160142702</v>
+        <v>-3.860374717786793</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.143966574620382</v>
+        <v>1.080781951562746</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6821655151509525</v>
+        <v>0.524203957506862</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.034587572081782</v>
+        <v>2.939810637495328</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.67653602817425</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.544121742603429</v>
+        <v>-3.702083300247521</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.258530906819131</v>
+        <v>1.195346283761495</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6821655151509525</v>
+        <v>0.524203957506862</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.085835337264822</v>
+        <v>2.991058402678368</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.674976732768503</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.336479738968953</v>
+        <v>-3.494441296613044</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.340028412867175</v>
+        <v>1.276843789809538</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8898075187854286</v>
+        <v>0.7318459611413382</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.208861244039761</v>
+        <v>3.114084309453307</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.669924961006773</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.285447646246425</v>
+        <v>-3.443409203890516</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.355389478194456</v>
+        <v>1.292204855136819</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9408396115079566</v>
+        <v>0.7828780538638661</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.234428727911547</v>
+        <v>3.139651793325093</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.687112365099478</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.220223465119219</v>
+        <v>-3.378185022763311</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.398666554738043</v>
+        <v>1.335481931680407</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.006063792635162</v>
+        <v>0.8481022349910717</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.290750640680576</v>
+        <v>3.195973706094121</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.683073337398759</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.182796445048086</v>
+        <v>-3.340758002692177</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.409598335065777</v>
+        <v>1.346413712008141</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.011315330664344</v>
+        <v>0.8533537730202534</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.289862535797365</v>
+        <v>3.195085601210911</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.684330129729999</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.202908101082794</v>
+        <v>-3.360869658726885</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.402810464983134</v>
+        <v>1.339625841925498</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.022342675661763</v>
+        <v>0.8643811180176726</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.297735735127057</v>
+        <v>3.202958800540602</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.84488790075121</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.17449483798291</v>
+        <v>-3.332456395627001</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.574733541244298</v>
+        <v>1.511548918186662</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9633671129153341</v>
+        <v>0.8054055552712438</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.42290816850041</v>
+        <v>3.328131233913956</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.965000809969027</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.099712576957898</v>
+        <v>-3.257674134601989</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.724759354872121</v>
+        <v>1.661574731814484</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.038149373940347</v>
+        <v>0.8801878162962564</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.587890434333235</v>
+        <v>3.493113499746781</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.956708785982886</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.07362849269409</v>
+        <v>-3.231590050338181</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.726900964591503</v>
+        <v>1.663716341533866</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.038149373940347</v>
+        <v>0.8801878162962564</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.579598410347094</v>
+        <v>3.48482147576064</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.954901981566665</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.985750579584969</v>
+        <v>-3.14371213722906</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.76024532541893</v>
+        <v>1.697060702361294</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.154075016363698</v>
+        <v>0.9961134587196074</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.647346991384884</v>
+        <v>3.55257005679843</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.972456387293457</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.976858118191686</v>
+        <v>-3.134819675835777</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.781356715703035</v>
+        <v>1.718172092645398</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.154075016363698</v>
+        <v>0.9961134587196074</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.664901397111676</v>
+        <v>3.570124462525222</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.964311434698041</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.145334235161564</v>
+        <v>-3.303295792805655</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.705821316319668</v>
+        <v>1.642636693262031</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.126127180647117</v>
+        <v>0.9681656230030267</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.639987743086311</v>
+        <v>3.545210808499857</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>2.945581131885902</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.699078042532124</v>
+        <v>-2.857039600176215</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.865593490559306</v>
+        <v>1.802408867501669</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.031408510977484</v>
+        <v>0.8734469533333939</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.564426238472393</v>
+        <v>3.469649303885939</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.936245154382807</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.676356938848971</v>
+        <v>-2.834318496493062</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.865345954529471</v>
+        <v>1.802161331471835</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.031408510977484</v>
+        <v>0.8734469533333939</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.555090260969298</v>
+        <v>3.460313326382844</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.095151280233976</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.805558752143014</v>
+        <v>-2.963520309787105</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.972571355063023</v>
+        <v>1.909386732005387</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.902206697683442</v>
+        <v>0.7442451400393517</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.636475298844041</v>
+        <v>3.541698364257587</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.132229102727623</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.831433150617039</v>
+        <v>-2.989394708261131</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.99929941816706</v>
+        <v>1.936114795109423</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9471183063951831</v>
+        <v>0.7891567487510929</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.700500086564733</v>
+        <v>3.605723151978279</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.128904458717168</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.824378460401866</v>
+        <v>-2.982340018045957</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.998796650242674</v>
+        <v>1.935612027185038</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9541729966103569</v>
+        <v>0.7962114389662667</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.701408256683382</v>
+        <v>3.606631322096928</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.138910612361909</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.797427236075378</v>
+        <v>-2.955388793719469</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.019583293618011</v>
+        <v>1.956398670560374</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9690533426380761</v>
+        <v>0.8110917849939858</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.720342617944755</v>
+        <v>3.625565683358301</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.323013744506869</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.933380244131694</v>
+        <v>-3.091341801775785</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.149305222540444</v>
+        <v>2.086120599482808</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9690533426380761</v>
+        <v>0.8110917849939858</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.904445750089715</v>
+        <v>3.809668815503261</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.315130439409862</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.955788361936566</v>
+        <v>-3.113749919580657</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.132458670321489</v>
+        <v>2.069274047263852</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9690533426380761</v>
+        <v>0.8110917849939858</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.896562444992708</v>
+        <v>3.801785510406254</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.3171844389595</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.984012597514166</v>
+        <v>-3.141974155158258</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.123222975640086</v>
+        <v>2.060038352582449</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9870300950893847</v>
+        <v>0.8290685374452944</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.909402496013131</v>
+        <v>3.814625561426676</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
         <v>3.373438156681347</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.993453523402696</v>
+        <v>-3.151415081046788</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.175700323006521</v>
+        <v>2.112515699948884</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.109457212632776</v>
+        <v>0.9514956549886858</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.039112484261013</v>
+        <v>3.944335549674559</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
         <v>3.376329251226648</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.045727130738338</v>
+        <v>-3.203688688382429</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.157681974617566</v>
+        <v>2.094497351559929</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.057183605297135</v>
+        <v>0.8992220476530446</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.010639414404928</v>
+        <v>3.915862479818474</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.374441064120423</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.122057108339244</v>
+        <v>-3.280018665983335</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.125261796470978</v>
+        <v>2.062077173413342</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.057183605297135</v>
+        <v>0.8992220476530446</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.008751227298704</v>
+        <v>3.91397429271225</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.369261293723285</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.324310828663597</v>
+        <v>-3.482272386307688</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.039180537944099</v>
+        <v>1.975995914886463</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8549298849727813</v>
+        <v>0.6969683273286911</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.882219224706954</v>
+        <v>3.7874422901205</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.367695303933437</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.485879254190852</v>
+        <v>-3.643840811834943</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.972987177943349</v>
+        <v>1.909802554885713</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.728146961174902</v>
+        <v>0.5701854035308117</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.804583480638379</v>
+        <v>3.709806546051925</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
         <v>3.380768710799356</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.594179916060972</v>
+        <v>-3.752141473705063</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.94274032006122</v>
+        <v>1.879555697003584</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.728146961174902</v>
+        <v>0.5701854035308117</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.817656887504298</v>
+        <v>3.722879952917843</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.372773907582296</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.687327387364338</v>
+        <v>-3.845288945008429</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.897486528322814</v>
+        <v>1.834301905265177</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6053177498923692</v>
+        <v>0.4473561922482789</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.735964557517718</v>
+        <v>3.641187622931263</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.371297948709298</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.715228174473811</v>
+        <v>-3.873189732117902</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.884850254606026</v>
+        <v>1.82166563154839</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5707208257494344</v>
+        <v>0.4127592681053441</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.713730444158959</v>
+        <v>3.618953509572505</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.368062392686497</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.837754277176705</v>
+        <v>-3.995715834820796</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.832604257502068</v>
+        <v>1.769419634444431</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4481947230465405</v>
+        <v>0.2902331654024503</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.636979226514421</v>
+        <v>3.542202291927967</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
         <v>3.434768352277001</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.068268773362294</v>
+        <v>-4.226230331006385</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.807104418618336</v>
+        <v>1.743919795560699</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2176802268609518</v>
+        <v>0.05971866921686153</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.565376488393572</v>
+        <v>3.470599553807117</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.575080071278848</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.324989591357118</v>
+        <v>-4.48295114900121</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.844727810422253</v>
+        <v>1.781543187364616</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.109265652717137</v>
+        <v>-0.0486959049269533</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.64063946290913</v>
+        <v>3.545862528322676</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.644060340424487</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.478976009133259</v>
+        <v>-4.63693756677735</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.852113512457437</v>
+        <v>1.7889288893998</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.109265652717137</v>
+        <v>-0.0486959049269533</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.70961973205477</v>
+        <v>3.614842797468316</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.630111542544608</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.428454105305593</v>
+        <v>-4.586415662949684</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.858373476108624</v>
+        <v>1.795188853050987</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.109265652717137</v>
+        <v>-0.0486959049269533</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.695670934174891</v>
+        <v>3.600893999588437</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.641982031600022</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.680929259313317</v>
+        <v>-4.838890816957409</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.769253903560948</v>
+        <v>1.706069280503312</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.109265652717137</v>
+        <v>-0.0486959049269533</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.707541423230305</v>
+        <v>3.612764488643851</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
         <v>3.643192566118966</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.97382501579273</v>
+        <v>-5.131786573436821</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.653306135488127</v>
+        <v>1.59012151243049</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.109265652717137</v>
+        <v>-0.0486959049269533</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.708751957749248</v>
+        <v>3.613975023162794</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251945</v>
       </c>
       <c r="C2021" t="n">
         <v>3.647314308346287</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.160489143927538</v>
+        <v>-5.318450701571629</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.582762226461525</v>
+        <v>1.519577603403889</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.08252668189257706</v>
+        <v>-0.0754348757515132</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.696830317481834</v>
+        <v>3.60205338289538</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916199</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.642392161082477</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.3065098308415</v>
+        <v>-5.464471388485591</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.51943180443213</v>
+        <v>1.456247181374493</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.07344359009872009</v>
+        <v>-0.08451796754537017</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.686458315141709</v>
+        <v>3.591681380555255</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.804596217781521</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.398223839951084</v>
+        <v>-5.556185397595176</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.64495025748734</v>
+        <v>1.581765634429703</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.07344359009872009</v>
+        <v>-0.08451796754537017</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.848662371840753</v>
+        <v>3.753885437254299</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
         <v>3.799442855745335</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.429875499011054</v>
+        <v>-5.587837056655145</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.627136231827166</v>
+        <v>1.56395160876953</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.06827513285427989</v>
+        <v>-0.08968642478981037</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.840407935457903</v>
+        <v>3.745631000871449</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.809672273313826</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.511810317279937</v>
+        <v>-5.669771874924028</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.604591722088104</v>
+        <v>1.541407099030468</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.0583403872671997</v>
+        <v>-0.09962117037689056</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.844676505674146</v>
+        <v>3.749899571087692</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.818597911769729</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.613786439528345</v>
+        <v>-5.771747997172436</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.572726911644644</v>
+        <v>1.509542288587007</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.04363573498120787</v>
+        <v>-0.2015972926252981</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.792416470781004</v>
+        <v>3.69763953619455</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.810750799013904</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.503780156051123</v>
+        <v>-5.661741713695214</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.608882312279707</v>
+        <v>1.545697689222071</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.02043116306393267</v>
+        <v>-0.1783927207080229</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.798492101175545</v>
+        <v>3.70371516658909</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
         <v>3.815000809735878</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.360720580310197</v>
+        <v>-5.518682137954288</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.670356153298052</v>
+        <v>1.607171530240416</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.01241773647395339</v>
+        <v>-0.1703792941180436</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.807550167851506</v>
+        <v>3.712773233265052</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.781490685150103</v>
+        <v>3.822261692618414</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.059273854838359</v>
+        <v>-5.21723541248245</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.757424718901011</v>
+        <v>1.735011103311687</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2890289889978839</v>
+        <v>0.1310674313537936</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.954908078548833</v>
+        <v>3.900902151430691</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.782461862902813</v>
+        <v>3.823232870371125</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.083864099073543</v>
+        <v>-5.241825656717634</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.748559798959649</v>
+        <v>1.726146183370324</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2890289889978839</v>
+        <v>0.1310674313537936</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.955879256301544</v>
+        <v>3.901873329183402</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.783304767282569</v>
+        <v>3.82407577475088</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.032825723067023</v>
+        <v>-5.190787280711114</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.769818053742013</v>
+        <v>1.747404438152687</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2890289889978839</v>
+        <v>0.1310674313537936</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.956722160681299</v>
+        <v>3.902716233563157</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.802342866156714</v>
+        <v>3.843113873625026</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.991686428200392</v>
+        <v>-5.149647985844483</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.80531187056281</v>
+        <v>1.782898254973485</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3301682838645147</v>
+        <v>0.1722067262204244</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.000443836475423</v>
+        <v>3.946437909357281</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.618526862280649</v>
+        <v>3.65929786974896</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.895051516181752</v>
+        <v>-5.053013073825843</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.660149831494201</v>
+        <v>1.637736215904876</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4268031958831546</v>
+        <v>0.2688416382390644</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.874608779810542</v>
+        <v>3.820602852692399</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.622028906354613</v>
+        <v>3.662799913822925</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.025632250712595</v>
+        <v>-5.183593808356686</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.611419581755828</v>
+        <v>1.589005966166503</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2962224613523121</v>
+        <v>0.1382609037082219</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.799762383166001</v>
+        <v>3.745756456047858</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.606455725430695</v>
+        <v>3.647226732899007</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.861135916521633</v>
+        <v>-5.019097474165724</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.661644934508295</v>
+        <v>1.63923131891897</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.460718795543274</v>
+        <v>0.3027572378991837</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.88288700275666</v>
+        <v>3.828881075638518</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.605643435867125</v>
+        <v>3.646414443335437</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.888505849206065</v>
+        <v>-5.046467406850156</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.649884671870952</v>
+        <v>1.627471056281627</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.460718795543274</v>
+        <v>0.3027572378991837</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.88207471319309</v>
+        <v>3.828068786074947</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147908</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.615512214992198</v>
+        <v>3.656283222460509</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.898891044095954</v>
+        <v>-5.056852601740045</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.655599373040069</v>
+        <v>1.633185757450744</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4503336006533847</v>
+        <v>0.2923720430092944</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.885712375384229</v>
+        <v>3.831706448266086</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.686349220768623</v>
+        <v>3.727120228236934</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.917479202818179</v>
+        <v>-5.07544076046227</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.719001115327604</v>
+        <v>1.696587499738279</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4317454419311593</v>
+        <v>0.2737838842870691</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.945396485927319</v>
+        <v>3.891390558809176</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.683218231586921</v>
+        <v>3.723989239055233</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.917777749514215</v>
+        <v>-5.075739307158306</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.715750707467488</v>
+        <v>1.693337091878163</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4314468952351234</v>
+        <v>0.2734853375910332</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.942086368727995</v>
+        <v>3.888080441609853</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.687749126526313</v>
+        <v>3.728520133994624</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.816954615823787</v>
+        <v>-4.974916173467879</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.76061085588305</v>
+        <v>1.738197240293726</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4439111107194773</v>
+        <v>0.285949553075387</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.954095792957999</v>
+        <v>3.900089865839857</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.687878380004856</v>
+        <v>3.728649387473168</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.626173255071381</v>
+        <v>-4.784134812715472</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.837052653662556</v>
+        <v>1.814639038073232</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6346924714718847</v>
+        <v>0.4767309138277944</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.068693862887987</v>
+        <v>4.014687935769844</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.667715225742453</v>
+        <v>3.708486233210764</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.60765640102956</v>
+        <v>-4.765617958673651</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.824296241016881</v>
+        <v>1.801882625427556</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6476226008970929</v>
+        <v>0.4896610432530026</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.056288786280708</v>
+        <v>4.002282859162566</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912983</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.702682162354511</v>
+        <v>3.743453169822823</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.552325813127798</v>
+        <v>-4.710287370771889</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.881395412789645</v>
+        <v>1.85898179720032</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.702953188798855</v>
+        <v>0.5449916311547648</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.124454075633825</v>
+        <v>4.070448148515681</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.743767956539893</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.696368730255949</v>
+        <v>3.73713973772426</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.540271686214835</v>
+        <v>-4.698233243858926</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.879903631456267</v>
+        <v>1.857490015866943</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7150073157118179</v>
+        <v>0.5570457580677276</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.12537311968304</v>
+        <v>4.071367192564897</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811007</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.698249360440085</v>
+        <v>3.739020367908396</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.581426805783056</v>
+        <v>-4.739388363427147</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.865322213813115</v>
+        <v>1.84290859822379</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6738521961435969</v>
+        <v>0.5158906384995067</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.102560678126243</v>
+        <v>4.0485547510081</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382918</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.711100386317967</v>
+        <v>3.751871393786279</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.478546216254463</v>
+        <v>-4.636507773898554</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.919325475502434</v>
+        <v>1.89691185991311</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7767327856721898</v>
+        <v>0.6187712280280996</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.177140057721282</v>
+        <v>4.123134130603138</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760312</v>
+        <v>3.646857607760314</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.731303056491561</v>
+        <v>3.772074063959873</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.710146609423964</v>
+        <v>-4.868108167068055</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.846887988408229</v>
+        <v>1.824474372818904</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7767327856721898</v>
+        <v>0.6187712280280996</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.197342727894876</v>
+        <v>4.143336800776733</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781703</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.731303056491561</v>
+        <v>3.772074063959873</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.728219117715575</v>
+        <v>-4.886180675359666</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.839658985091584</v>
+        <v>1.817245369502259</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7767327856721898</v>
+        <v>0.6187712280280996</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.197342727894876</v>
+        <v>4.143336800776733</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082832</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.691554970085028</v>
+        <v>3.73232597755334</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.90332595029202</v>
+        <v>-5.061287507936111</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.729868165654473</v>
+        <v>1.707454550065148</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7767327856721898</v>
+        <v>0.6187712280280996</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.157594641488342</v>
+        <v>4.1035887143702</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.698577589081968</v>
+        <v>3.73934859655028</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.872039929751565</v>
+        <v>-5.030001487395656</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.749405192867595</v>
+        <v>1.72699157727827</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8080188062126452</v>
+        <v>0.650057248568555</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.183388872809555</v>
+        <v>4.129382945691413</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677821</v>
+        <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.797748588654872</v>
+        <v>3.838519596123184</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.71901453763828</v>
+        <v>-4.876976095282371</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.909786349285813</v>
+        <v>1.887372733696488</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9610441983259294</v>
+        <v>0.8030826406818391</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.37437510765043</v>
+        <v>4.320369180532287</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073881</v>
+        <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.985214813563164</v>
+        <v>4.025985821031476</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.747321851511551</v>
+        <v>-4.905283409155642</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.085929648644797</v>
+        <v>2.063516033055472</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9610441983259294</v>
+        <v>0.8030826406818391</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.561841332558722</v>
+        <v>4.50783540544058</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903166</v>
+        <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.954617764917247</v>
+        <v>3.995388772385558</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.913915076625073</v>
+        <v>-5.071876634269164</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.98869530995347</v>
+        <v>1.966281694364146</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.794450973212407</v>
+        <v>0.6364894155683167</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.431288348844691</v>
+        <v>4.377282421726549</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.70820270456838</v>
+        <v>3.708202704568382</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.958294167578964</v>
+        <v>3.999065175047276</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.740850697242773</v>
+        <v>-4.898812254886864</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.061597464368108</v>
+        <v>2.039183848778783</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.794450973212407</v>
+        <v>0.6364894155683167</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.434964751506409</v>
+        <v>4.380958824388267</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682201</v>
+        <v>3.740601586682204</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.95591222270246</v>
+        <v>3.996683230170771</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.711604716787076</v>
+        <v>-4.869566274431167</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.070913911673882</v>
+        <v>2.048500296084557</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.794450973212407</v>
+        <v>0.6364894155683167</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.432582806629904</v>
+        <v>4.378576879511762</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539104</v>
+        <v>3.699424827539107</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.953205461860095</v>
+        <v>3.993976469328406</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.818530264664927</v>
+        <v>-4.976491822309018</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.025436931680376</v>
+        <v>2.003023316091052</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6875254253345556</v>
+        <v>0.5295638676904654</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.365720717060828</v>
+        <v>4.311714789942686</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983735</v>
+        <v>3.689962785983737</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.954634264003329</v>
+        <v>3.995405271471641</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.963548823172176</v>
+        <v>-5.121510380816267</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.968858310420711</v>
+        <v>1.946444694831386</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5425068668273071</v>
+        <v>0.3845453091832168</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.280138384099714</v>
+        <v>4.226132456981571</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969746</v>
+        <v>3.711872614969749</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.054565503261082</v>
+        <v>4.095336510729394</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.081890588956893</v>
+        <v>-5.239852146600985</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.021452843364577</v>
+        <v>1.999039227775252</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5531929053901972</v>
+        <v>0.3952313477461069</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.3864812464952</v>
+        <v>4.332475319377058</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073535</v>
+        <v>3.714899237073539</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.052351200387021</v>
+        <v>4.093122207855332</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.133301011277601</v>
+        <v>-5.291262568921693</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.998674371562233</v>
+        <v>1.976260755972908</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5531929053901972</v>
+        <v>0.3952313477461069</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.384266943621139</v>
+        <v>4.330261016502996</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720062</v>
+        <v>3.704778134720065</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.05225432846131</v>
+        <v>4.093025335929622</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.212720462485353</v>
+        <v>-5.370682020129444</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.966809719153422</v>
+        <v>1.944396103564097</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5531929053901972</v>
+        <v>0.3952313477461069</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.384170071695428</v>
+        <v>4.330164144577286</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581129</v>
+        <v>3.736825137581133</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.052248222019354</v>
+        <v>4.093019229487665</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.308183460402571</v>
+        <v>-5.466145018046662</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.928618413544578</v>
+        <v>1.906204797955253</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5531929053901972</v>
+        <v>0.3952313477461069</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.384163965253472</v>
+        <v>4.33015803813533</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500731</v>
+        <v>3.715393145500735</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.050344618581964</v>
+        <v>4.091115626050276</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.348203458446354</v>
+        <v>-5.506165016090446</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.910706810889675</v>
+        <v>1.888293195300351</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.5131729073464133</v>
+        <v>0.3552113497023231</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.358248362989812</v>
+        <v>4.30424243587167</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636267</v>
+        <v>3.73610959863627</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.056078436329691</v>
+        <v>4.096849443798003</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.403572620578548</v>
+        <v>-5.561534178222639</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.894292963784524</v>
+        <v>1.8718793481952</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.5131729073464133</v>
+        <v>0.3552113497023231</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.363982180737539</v>
+        <v>4.309976253619396</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.73684305539601</v>
+        <v>3.736843055396013</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.055616799672624</v>
+        <v>4.096387807140935</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.449010400409375</v>
+        <v>-5.606971958053466</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.875656215195126</v>
+        <v>1.853242599605802</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.4703279166682536</v>
+        <v>0.3123663590241634</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.337813549673577</v>
+        <v>4.283807622555433</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396419</v>
+        <v>3.790292685396422</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.075491192522943</v>
+        <v>4.116262199991255</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.365784943561711</v>
+        <v>-5.523746501205802</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.928820790784511</v>
+        <v>1.906407175195187</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.4703279166682536</v>
+        <v>0.3123663590241634</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.357687942523896</v>
+        <v>4.303682015405752</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299173</v>
+        <v>3.794507029299177</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.059191893047671</v>
+        <v>4.099962900515982</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.189494718956404</v>
+        <v>-5.347456276600495</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.983037581151362</v>
+        <v>1.960623965562037</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.4703279166682536</v>
+        <v>0.3123663590241634</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.341388643048623</v>
+        <v>4.28738271593048</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.785443209555928</v>
+        <v>3.526961010913507</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.061622842511716</v>
+        <v>4.102393849980028</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.006283055823308</v>
+        <v>-5.1642446134674</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.058753195868646</v>
+        <v>2.036339580279321</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.4703279166682536</v>
+        <v>0.3123663590241634</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.343819592512669</v>
+        <v>4.289813665394526</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240826.xlsx
+++ b/tame_output/ON/bt/strategyON_20240826.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>58.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>112.2%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-78.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>428.4%</t>
+          <t>430.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-678.0%</t>
+          <t>-665.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-172.6%</t>
+          <t>-167.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,16 +1242,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-285.3%</t>
+          <t>-281.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-192.8%</t>
+          <t>-177.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>74.8%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-22.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2067"/>
+  <dimension ref="A1:G2068"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.311888301355688</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279812</v>
+        <v>3.385382209279811</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511403</v>
+        <v>3.367379938511402</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082122</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.29349053375792</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.293766719760738</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706667</v>
+        <v>3.298730590706666</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296834</v>
+        <v>3.299918119296833</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201485</v>
+        <v>3.295507330201484</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153003</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.271168579537423</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.272760131382188</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074619</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911636</v>
+        <v>3.233800325911635</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213492</v>
+        <v>3.223539378213491</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416042</v>
+        <v>3.231167537416041</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382324</v>
+        <v>3.235981977382323</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495495</v>
+        <v>3.278199702495494</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.29913614634705</v>
+        <v>3.299136146347049</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130012</v>
+        <v>3.287377576130011</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178238</v>
+        <v>3.315884374178237</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207808</v>
+        <v>3.305316798207807</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310977</v>
+        <v>3.284619513310976</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.305849539006528</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309419</v>
+        <v>3.311086391309418</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.3047157169709</v>
+        <v>3.304715716970899</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330517</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191731</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108633</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097815</v>
+        <v>3.341378723097814</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309411</v>
+        <v>3.374439043094109</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199279</v>
+        <v>3.405960511199278</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969587</v>
+        <v>3.424633354969586</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923079</v>
+        <v>3.419979433923078</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297742</v>
+        <v>3.458100091297741</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131761</v>
+        <v>3.447750501317609</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737163</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.503170282341306</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539457</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937496</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.496851904729888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608598</v>
+        <v>3.490059241608597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.57367402532254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.600038265158918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940715</v>
+        <v>3.691571733940714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770575</v>
+        <v>3.676841549770574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615278</v>
+        <v>3.685161381615277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812098</v>
+        <v>3.684843823812097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646212</v>
+        <v>3.710935533646211</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955323</v>
+        <v>3.728577929955322</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232408</v>
+        <v>3.747702660232407</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436224</v>
+        <v>3.766317079436223</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311944</v>
+        <v>3.784684521311943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097239</v>
+        <v>3.800829354097238</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017766</v>
+        <v>3.789311112017765</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390425</v>
+        <v>3.763182248390424</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098106</v>
+        <v>3.729969716098105</v>
       </c>
       <c r="C1912" t="n">
         <v>2.857856093008484</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722812</v>
+        <v>3.828551486722813</v>
       </c>
       <c r="C1914" t="n">
         <v>2.866850567848822</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792041</v>
+        <v>3.828052928792042</v>
       </c>
       <c r="C1915" t="n">
         <v>2.864348661859399</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919901</v>
+        <v>3.812453678919902</v>
       </c>
       <c r="C1916" t="n">
         <v>2.872049640096724</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576993</v>
+        <v>3.791273551576992</v>
       </c>
       <c r="C1932" t="n">
         <v>2.896589116788315</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.75858326319385</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.932784975351878</v>
+        <v>-3.96885187823265</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.185112848739352</v>
+        <v>1.170686087587043</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5642899207513363</v>
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.687855955085216</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.997936051545109</v>
+        <v>-3.876041396781791</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.088325110153425</v>
+        <v>1.137082972058753</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.4991388445581053</v>
+        <v>0.6571004022021957</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.98733926182008</v>
+        <v>3.082116196406534</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560423</v>
+        <v>3.748285816560421</v>
       </c>
       <c r="C1947" t="n">
         <v>2.689729431009817</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.042325520874536</v>
+        <v>-3.920430866111218</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.072442798346255</v>
+        <v>1.121200660251582</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4547493752286776</v>
+        <v>0.612710932872768</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.962579056147024</v>
+        <v>3.057355990733478</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472735</v>
+        <v>3.721077195472733</v>
       </c>
       <c r="C1948" t="n">
         <v>2.68480513952154</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.158867125979879</v>
+        <v>-4.036972471216561</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.020901864815841</v>
+        <v>1.069659726721168</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.3382077701233349</v>
+        <v>0.4961693277674253</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.887729801595541</v>
+        <v>2.982506736181995</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798532</v>
       </c>
       <c r="C1949" t="n">
         <v>2.690296435352207</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.198791220562451</v>
+        <v>-4.076896565799133</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.010423522813479</v>
+        <v>1.059181384718807</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.3382077701233349</v>
+        <v>0.4961693277674253</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.893221097426208</v>
+        <v>2.987998032012662</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498858</v>
       </c>
       <c r="C1950" t="n">
         <v>2.701793637120746</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.226571618463804</v>
+        <v>-4.104676963700486</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.010808565421478</v>
+        <v>1.059566427326805</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.3104273722219818</v>
+        <v>0.4683889298660722</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.888050060453935</v>
+        <v>2.98282699504039</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170532</v>
+        <v>3.643069621705318</v>
       </c>
       <c r="C1951" t="n">
         <v>2.5401493571214</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.344952291193942</v>
+        <v>-4.223057636430624</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8018120163300755</v>
+        <v>0.8505698782354025</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.2432095200710056</v>
+        <v>0.401171077715096</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.686075069164003</v>
+        <v>2.780852003750458</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729264</v>
+        <v>3.682716310729262</v>
       </c>
       <c r="C1952" t="n">
         <v>2.660299017840605</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.453566369637273</v>
+        <v>-4.331671714873956</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8785160456719487</v>
+        <v>0.9272739075772756</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.2432095200710056</v>
+        <v>0.401171077715096</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.806224729883209</v>
+        <v>2.901001664469663</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190764</v>
+        <v>3.733012441190763</v>
       </c>
       <c r="C1953" t="n">
         <v>2.674812043942928</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.41815733138913</v>
+        <v>-4.296262676625813</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9071926870735287</v>
+        <v>0.9559505489788558</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.2432095200710056</v>
+        <v>0.401171077715096</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.820737755985532</v>
+        <v>2.915514690571986</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.74117406991342</v>
       </c>
       <c r="C1954" t="n">
         <v>2.672231485285297</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.379773668830979</v>
+        <v>-4.257879014067662</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.919965593439158</v>
+        <v>0.968723455344485</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.2815931826291568</v>
+        <v>0.4395547402732472</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.841187394862791</v>
+        <v>2.935964329449245</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.668960514130599</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.202657338795813</v>
+        <v>-4.080762684032496</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9875411542985262</v>
+        <v>1.036299016203853</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.2815931826291568</v>
+        <v>0.4395547402732472</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.837916423708093</v>
+        <v>2.932693358294547</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793897</v>
       </c>
       <c r="C1956" t="n">
         <v>2.669643905892512</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.247749583629359</v>
+        <v>-4.125854928866041</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9701876481270211</v>
+        <v>1.018945510032348</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.219697139459767</v>
+        <v>0.3776586971038574</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.801462189568372</v>
+        <v>2.896239124154826</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011229</v>
       </c>
       <c r="C1957" t="n">
         <v>2.663430881198926</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.068374162390591</v>
+        <v>-3.946479507627274</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.035724791928943</v>
+        <v>1.08448265383427</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.3764738976304857</v>
+        <v>0.534435455274576</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.889315219777218</v>
+        <v>2.984092154363672</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982225</v>
+        <v>3.716991718982223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.644238336530516</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.113388375911198</v>
+        <v>-3.99149372114788</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9985265618522896</v>
+        <v>1.047284423757617</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.3461250023158811</v>
+        <v>0.5040865599599714</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.851913337920045</v>
+        <v>2.946690272506499</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509532</v>
       </c>
       <c r="C1959" t="n">
         <v>2.649929898869462</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.380392886183633</v>
+        <v>-4.258498231420315</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8974163200822614</v>
+        <v>0.9461741819875884</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.1517619642729325</v>
+        <v>0.3097235219170228</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.740987077433222</v>
+        <v>2.835764012019676</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.649133820765963</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.481590667620805</v>
+        <v>-4.359696012857488</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8561411294038936</v>
+        <v>0.9048989913092207</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.08335315072761329</v>
+        <v>0.2413147083717037</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.699145711202531</v>
+        <v>2.793922645788986</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815452</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64673378232028</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.475079701006493</v>
+        <v>-4.353185046243175</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8563454776039354</v>
+        <v>0.9051033395092625</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.08335315072761329</v>
+        <v>0.2413147083717037</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.696745672756848</v>
+        <v>2.791522607343302</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378097</v>
       </c>
       <c r="C1962" t="n">
         <v>2.643258501528525</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.456041573299196</v>
+        <v>-4.334146918535878</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8604854478950994</v>
+        <v>0.9092433098004262</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.02516953939641875</v>
+        <v>0.1831310970405091</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.658360225166376</v>
+        <v>2.753137159752831</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.762552903162715</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.508557375574016</v>
+        <v>-4.386662720810699</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9587735286193615</v>
+        <v>1.007531390524689</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.02516953939641875</v>
+        <v>0.1831310970405091</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.777654626800567</v>
+        <v>2.872431561387021</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067859</v>
       </c>
       <c r="C1964" t="n">
         <v>2.763386232148849</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.522424136907934</v>
+        <v>-4.400529482144616</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9540601530719279</v>
+        <v>1.002818014977255</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.01268837733740419</v>
+        <v>0.1452731803066862</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.755773205746407</v>
+        <v>2.850550140332861</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789116</v>
       </c>
       <c r="C1965" t="n">
         <v>2.769394762545775</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.477619965368004</v>
+        <v>-4.355725310604686</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9779903520848259</v>
+        <v>1.026748213990153</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.01268837733740419</v>
+        <v>0.1452731803066862</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.761781736143333</v>
+        <v>2.856558670729787</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519903</v>
       </c>
       <c r="C1966" t="n">
         <v>2.667344983822974</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.329876995133001</v>
+        <v>-4.207982340369684</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9350377614560264</v>
+        <v>0.9837956233613534</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.155118979897479</v>
+        <v>0.3130805375415693</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.760416371761462</v>
+        <v>2.855193306347916</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.670138605354455</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.4136982164077</v>
+        <v>-4.291803561644382</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9043028944776279</v>
+        <v>0.953060756382955</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.155118979897479</v>
+        <v>0.3130805375415693</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.763209993292943</v>
+        <v>2.857986927879397</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
         <v>2.670800953746113</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.407545510354915</v>
+        <v>-4.285650855591598</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9074263252904</v>
+        <v>0.9561841871957271</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.1612716859502633</v>
+        <v>0.3192332435943536</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.767563965316272</v>
+        <v>2.862340899902726</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890607</v>
       </c>
       <c r="C1969" t="n">
         <v>2.669881430486224</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.424354808505417</v>
+        <v>-4.3024601537421</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8997830827703095</v>
+        <v>0.9485409446756365</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.1444623877997616</v>
+        <v>0.302423945443852</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.756558863166081</v>
+        <v>2.851335797752535</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.86736263679842</v>
       </c>
       <c r="C1970" t="n">
         <v>2.736216984283045</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.362056809729295</v>
+        <v>-4.240162154965978</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9910378360775793</v>
+        <v>1.039795697982906</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.1897566520742037</v>
+        <v>0.347718209718294</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.850070975527567</v>
+        <v>2.944847910114021</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992186</v>
       </c>
       <c r="C1971" t="n">
         <v>2.538508985997172</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.160266612064137</v>
+        <v>-4.03837195730082</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8740459168577694</v>
+        <v>0.9228037787630965</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.3877748442433581</v>
+        <v>0.5457364018874484</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.771173892543187</v>
+        <v>2.865950827129641</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.608799218319347</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.211153324750332</v>
+        <v>-4.089258669987014</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9239814641054669</v>
+        <v>0.9727393260107939</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.3368881315571635</v>
+        <v>0.4948496892012539</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.810932097253645</v>
+        <v>2.905709031840099</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.81906330031954</v>
       </c>
       <c r="C1973" t="n">
         <v>2.623426954435391</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.124542582100525</v>
+        <v>-4.002647927337208</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9732534972814333</v>
+        <v>1.02201135918676</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.4155138627623218</v>
+        <v>0.5734754204064122</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.872735272092784</v>
+        <v>2.967512206679238</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.621962935260062</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.18475188010581</v>
+        <v>-4.062857225342492</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.947705758903991</v>
+        <v>0.9964636208093183</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3553045647570373</v>
+        <v>0.5132661224011277</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.835145674114285</v>
+        <v>2.929922608700739</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397789</v>
       </c>
       <c r="C1975" t="n">
         <v>2.620454553299991</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.108329833673883</v>
+        <v>-3.986435178910566</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9767661955166902</v>
+        <v>1.025524057422018</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3553045647570373</v>
+        <v>0.5132661224011277</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.833637292154213</v>
+        <v>2.928414226740668</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316244</v>
       </c>
       <c r="C1976" t="n">
         <v>2.620317420735427</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.063956702035314</v>
+        <v>-3.942062047271997</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9943783156075539</v>
+        <v>1.043136177512881</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3996776963956059</v>
+        <v>0.5576392540396963</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.860124038572791</v>
+        <v>2.954900973159245</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.614711214874017</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.086437052894199</v>
+        <v>-3.964542398130882</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9797799694025904</v>
+        <v>1.028537831307918</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3996776963956059</v>
+        <v>0.5576392540396963</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.854517832711381</v>
+        <v>2.949294767297836</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.621092971901822</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.038781322333143</v>
+        <v>-3.916886667569826</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.005224018654817</v>
+        <v>1.053981880560145</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4473334269566615</v>
+        <v>0.6052949846007519</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.889493028075819</v>
+        <v>2.984269962662274</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569611</v>
       </c>
       <c r="C1979" t="n">
         <v>2.625985345276547</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.938263163834389</v>
+        <v>-3.816368509071071</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.050323655429044</v>
+        <v>1.099081517334372</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.547851585455416</v>
+        <v>0.7058131430995065</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.954696296549797</v>
+        <v>3.049473231136251</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557288</v>
       </c>
       <c r="C1980" t="n">
         <v>2.612740017752419</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.922357834402036</v>
+        <v>-3.800463179638719</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.043440459677857</v>
+        <v>1.092198321583185</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4687389247461771</v>
+        <v>0.6267004823902675</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.893983372600126</v>
+        <v>2.98876030718658</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932763</v>
       </c>
       <c r="C1981" t="n">
         <v>2.616837720363048</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.877519432793638</v>
+        <v>-3.755624778030321</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.065473522931845</v>
+        <v>1.114231384837173</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4732823576910466</v>
+        <v>0.631243915335137</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.900807134977676</v>
+        <v>2.99558406956413</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
         <v>2.620998659994126</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.897017889035646</v>
+        <v>-3.775123234272329</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.06183508006612</v>
+        <v>1.110592941971447</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4251977164111423</v>
+        <v>0.5831592740552327</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.876117289840812</v>
+        <v>2.970894224427266</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405954</v>
       </c>
       <c r="C1983" t="n">
         <v>2.626878262521963</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.852815051949746</v>
+        <v>-3.730920397186428</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.085395817428317</v>
+        <v>1.134153679333645</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4694005534970427</v>
+        <v>0.6273621111411332</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.908518594620189</v>
+        <v>3.003295529206643</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265638</v>
       </c>
       <c r="C1984" t="n">
         <v>2.62528826299121</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.860374717786793</v>
+        <v>-3.738480063023475</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.080781951562746</v>
+        <v>1.129539813468073</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.524203957506862</v>
+        <v>0.6821655151509525</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.939810637495328</v>
+        <v>3.034587572081782</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284873</v>
       </c>
       <c r="C1985" t="n">
         <v>2.67653602817425</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.702083300247521</v>
+        <v>-3.580188645484203</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.195346283761495</v>
+        <v>1.244104145666822</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.524203957506862</v>
+        <v>0.6821655151509525</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.991058402678368</v>
+        <v>3.085835337264822</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321017</v>
       </c>
       <c r="C1986" t="n">
         <v>2.674976732768503</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.494441296613044</v>
+        <v>-3.372546641849727</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.276843789809538</v>
+        <v>1.325601651714865</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7318459611413382</v>
+        <v>0.8898075187854286</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.114084309453307</v>
+        <v>3.208861244039761</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475133</v>
       </c>
       <c r="C1987" t="n">
         <v>2.669924961006773</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.443409203890516</v>
+        <v>-3.321514549127199</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.292204855136819</v>
+        <v>1.340962717042147</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7828780538638661</v>
+        <v>0.9408396115079566</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.139651793325093</v>
+        <v>3.234428727911547</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404847</v>
       </c>
       <c r="C1988" t="n">
         <v>2.687112365099478</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.378185022763311</v>
+        <v>-3.256290367999993</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.335481931680407</v>
+        <v>1.384239793585734</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8481022349910717</v>
+        <v>1.006063792635162</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.195973706094121</v>
+        <v>3.290750640680576</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882551</v>
       </c>
       <c r="C1989" t="n">
         <v>2.683073337398759</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.340758002692177</v>
+        <v>-3.218863347928859</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.346413712008141</v>
+        <v>1.395171573913468</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8533537730202534</v>
+        <v>1.011315330664344</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.195085601210911</v>
+        <v>3.289862535797365</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
         <v>2.684330129729999</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.360869658726885</v>
+        <v>-3.238975003963568</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.339625841925498</v>
+        <v>1.388383703830825</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8643811180176726</v>
+        <v>1.022342675661763</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.202958800540602</v>
+        <v>3.297735735127057</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636281</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84488790075121</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.332456395627001</v>
+        <v>-3.210561740863684</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.511548918186662</v>
+        <v>1.560306780091989</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8054055552712438</v>
+        <v>0.9633671129153341</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.328131233913956</v>
+        <v>3.42290816850041</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957619</v>
       </c>
       <c r="C1992" t="n">
         <v>2.965000809969027</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.257674134601989</v>
+        <v>-3.135779479838671</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.661574731814484</v>
+        <v>1.710332593719811</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.8801878162962564</v>
+        <v>1.038149373940347</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.493113499746781</v>
+        <v>3.587890434333235</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.956708785982886</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.231590050338181</v>
+        <v>-3.109695395574863</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.663716341533866</v>
+        <v>1.712474203439194</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.8801878162962564</v>
+        <v>1.038149373940347</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.48482147576064</v>
+        <v>3.579598410347094</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896923</v>
       </c>
       <c r="C1994" t="n">
         <v>2.954901981566665</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.14371213722906</v>
+        <v>-3.021817482465743</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.697060702361294</v>
+        <v>1.745818564266621</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9961134587196074</v>
+        <v>1.154075016363698</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.55257005679843</v>
+        <v>3.647346991384884</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959851</v>
       </c>
       <c r="C1995" t="n">
         <v>2.972456387293457</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.134819675835777</v>
+        <v>-3.012925021072459</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.718172092645398</v>
+        <v>1.766929954550726</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9961134587196074</v>
+        <v>1.154075016363698</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.570124462525222</v>
+        <v>3.664901397111676</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945358</v>
       </c>
       <c r="C1996" t="n">
         <v>2.964311434698041</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.303295792805655</v>
+        <v>-3.181401138042337</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.642636693262031</v>
+        <v>1.691394555167359</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9681656230030267</v>
+        <v>1.126127180647117</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.545210808499857</v>
+        <v>3.639987743086311</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782702</v>
       </c>
       <c r="C1997" t="n">
         <v>2.945581131885902</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.857039600176215</v>
+        <v>-2.735144945412897</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.802408867501669</v>
+        <v>1.851166729406997</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.8734469533333939</v>
+        <v>1.031408510977484</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.469649303885939</v>
+        <v>3.564426238472393</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.78467134563263</v>
       </c>
       <c r="C1998" t="n">
         <v>2.936245154382807</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.834318496493062</v>
+        <v>-2.712423841729745</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.802161331471835</v>
+        <v>1.850919193377162</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.8734469533333939</v>
+        <v>1.031408510977484</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.460313326382844</v>
+        <v>3.555090260969298</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777666</v>
       </c>
       <c r="C1999" t="n">
         <v>3.095151280233976</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.963520309787105</v>
+        <v>-2.841625655023787</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.909386732005387</v>
+        <v>1.958144593910714</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7442451400393517</v>
+        <v>0.902206697683442</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.541698364257587</v>
+        <v>3.636475298844041</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644406</v>
       </c>
       <c r="C2000" t="n">
         <v>3.132229102727623</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.989394708261131</v>
+        <v>-2.867500053497813</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.936114795109423</v>
+        <v>1.98487265701475</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7891567487510929</v>
+        <v>0.9471183063951831</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.605723151978279</v>
+        <v>3.700500086564733</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799957</v>
       </c>
       <c r="C2001" t="n">
         <v>3.128904458717168</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.982340018045957</v>
+        <v>-2.860445363282639</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.935612027185038</v>
+        <v>1.984369889090365</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7962114389662667</v>
+        <v>0.9541729966103569</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.606631322096928</v>
+        <v>3.701408256683382</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331109</v>
       </c>
       <c r="C2002" t="n">
         <v>3.138910612361909</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.955388793719469</v>
+        <v>-2.833494138956151</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.956398670560374</v>
+        <v>2.005156532465702</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8110917849939858</v>
+        <v>0.9690533426380761</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.625565683358301</v>
+        <v>3.720342617944755</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784101</v>
       </c>
       <c r="C2003" t="n">
         <v>3.323013744506869</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.091341801775785</v>
+        <v>-2.969447147012468</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.086120599482808</v>
+        <v>2.134878461388135</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8110917849939858</v>
+        <v>0.9690533426380761</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.809668815503261</v>
+        <v>3.904445750089715</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.74392550571442</v>
       </c>
       <c r="C2004" t="n">
         <v>3.315130439409862</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.113749919580657</v>
+        <v>-2.99185526481734</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.069274047263852</v>
+        <v>2.118031909169179</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8110917849939858</v>
+        <v>0.9690533426380761</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.801785510406254</v>
+        <v>3.896562444992708</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155026</v>
       </c>
       <c r="C2005" t="n">
         <v>3.3171844389595</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.141974155158258</v>
+        <v>-3.02007950039494</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.060038352582449</v>
+        <v>2.108796214487777</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.8290685374452944</v>
+        <v>0.9870300950893847</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.814625561426676</v>
+        <v>3.909402496013131</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.72945228516197</v>
       </c>
       <c r="C2006" t="n">
         <v>3.373438156681347</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.151415081046788</v>
+        <v>-3.02952042628347</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.112515699948884</v>
+        <v>2.161273561854212</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.9514956549886858</v>
+        <v>1.109457212632776</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.944335549674559</v>
+        <v>4.039112484261013</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.714941193321627</v>
       </c>
       <c r="C2007" t="n">
         <v>3.376329251226648</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.203688688382429</v>
+        <v>-3.081794033619111</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.094497351559929</v>
+        <v>2.143255213465256</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8992220476530446</v>
+        <v>1.057183605297135</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.915862479818474</v>
+        <v>4.010639414404928</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347696</v>
       </c>
       <c r="C2008" t="n">
         <v>3.374441064120423</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.280018665983335</v>
+        <v>-3.158124011220017</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.062077173413342</v>
+        <v>2.110835035318669</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8992220476530446</v>
+        <v>1.057183605297135</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.91397429271225</v>
+        <v>4.008751227298704</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887741</v>
       </c>
       <c r="C2009" t="n">
         <v>3.369261293723285</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.482272386307688</v>
+        <v>-3.360377731544371</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.975995914886463</v>
+        <v>2.02475377679179</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.6969683273286911</v>
+        <v>0.8549298849727813</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.7874422901205</v>
+        <v>3.882219224706954</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.71289761234306</v>
       </c>
       <c r="C2010" t="n">
         <v>3.367695303933437</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.643840811834943</v>
+        <v>-3.521946157071626</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.909802554885713</v>
+        <v>1.95856041679104</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.5701854035308117</v>
+        <v>0.728146961174902</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.709806546051925</v>
+        <v>3.804583480638379</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389342</v>
       </c>
       <c r="C2011" t="n">
         <v>3.380768710799356</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.752141473705063</v>
+        <v>-3.630246818941745</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.879555697003584</v>
+        <v>1.928313558908911</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.5701854035308117</v>
+        <v>0.728146961174902</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.722879952917843</v>
+        <v>3.817656887504298</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.749882691378386</v>
       </c>
       <c r="C2012" t="n">
         <v>3.372773907582296</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.845288945008429</v>
+        <v>-3.723394290245112</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.834301905265177</v>
+        <v>1.883059767170504</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4473561922482789</v>
+        <v>0.6053177498923692</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.641187622931263</v>
+        <v>3.735964557517718</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006968</v>
       </c>
       <c r="C2013" t="n">
         <v>3.371297948709298</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.873189732117902</v>
+        <v>-3.751295077354585</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.82166563154839</v>
+        <v>1.870423493453717</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4127592681053441</v>
+        <v>0.5707208257494344</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.618953509572505</v>
+        <v>3.713730444158959</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.68489577878738</v>
       </c>
       <c r="C2014" t="n">
         <v>3.368062392686497</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.995715834820796</v>
+        <v>-3.873821180057479</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.769419634444431</v>
+        <v>1.818177496349758</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2902331654024503</v>
+        <v>0.4481947230465405</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.542202291927967</v>
+        <v>3.636979226514421</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585931</v>
       </c>
       <c r="C2015" t="n">
         <v>3.434768352277001</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.226230331006385</v>
+        <v>-4.104335676243068</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.743919795560699</v>
+        <v>1.792677657466027</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.05971866921686153</v>
+        <v>0.2176802268609518</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.470599553807117</v>
+        <v>3.565376488393572</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814658</v>
       </c>
       <c r="C2016" t="n">
         <v>3.575080071278848</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.48295114900121</v>
+        <v>-4.361056494237892</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.781543187364616</v>
+        <v>1.830301049269944</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.0486959049269533</v>
+        <v>0.109265652717137</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.545862528322676</v>
+        <v>3.64063946290913</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237087</v>
       </c>
       <c r="C2017" t="n">
         <v>3.644060340424487</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.63693756677735</v>
+        <v>-4.515042912014033</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.7889288893998</v>
+        <v>1.837686751305127</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.0486959049269533</v>
+        <v>0.109265652717137</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.614842797468316</v>
+        <v>3.70961973205477</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.61992301642338</v>
       </c>
       <c r="C2018" t="n">
         <v>3.630111542544608</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.586415662949684</v>
+        <v>-4.464521008186367</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.795188853050987</v>
+        <v>1.843946714956315</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.0486959049269533</v>
+        <v>0.109265652717137</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.600893999588437</v>
+        <v>3.695670934174891</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609746</v>
       </c>
       <c r="C2019" t="n">
         <v>3.641982031600022</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.838890816957409</v>
+        <v>-4.716996162194091</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.706069280503312</v>
+        <v>1.754827142408639</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.0486959049269533</v>
+        <v>0.109265652717137</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.612764488643851</v>
+        <v>3.707541423230305</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973151</v>
       </c>
       <c r="C2020" t="n">
         <v>3.643192566118966</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.131786573436821</v>
+        <v>-5.009891918673503</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.59012151243049</v>
+        <v>1.638879374335818</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.0486959049269533</v>
+        <v>0.109265652717137</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.613975023162794</v>
+        <v>3.708751957749248</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251945</v>
+        <v>3.663509457251939</v>
       </c>
       <c r="C2021" t="n">
         <v>3.647314308346287</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.318450701571629</v>
+        <v>-5.196556046808311</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.519577603403889</v>
+        <v>1.568335465309216</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.0754348757515132</v>
+        <v>0.08252668189257706</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.60205338289538</v>
+        <v>3.696830317481834</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916195</v>
       </c>
       <c r="C2022" t="n">
         <v>3.642392161082477</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.464471388485591</v>
+        <v>-5.342576733722273</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.456247181374493</v>
+        <v>1.50500504327982</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.08451796754537017</v>
+        <v>0.07344359009872009</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.591681380555255</v>
+        <v>3.686458315141709</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830322</v>
       </c>
       <c r="C2023" t="n">
         <v>3.804596217781521</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.556185397595176</v>
+        <v>-5.434290742831858</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.581765634429703</v>
+        <v>1.630523496335031</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.08451796754537017</v>
+        <v>0.07344359009872009</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.753885437254299</v>
+        <v>3.848662371840753</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071544</v>
       </c>
       <c r="C2024" t="n">
         <v>3.799442855745335</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.587837056655145</v>
+        <v>-5.465942401891827</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.56395160876953</v>
+        <v>1.612709470674857</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.08968642478981037</v>
+        <v>0.06827513285427989</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.745631000871449</v>
+        <v>3.840407935457903</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868138</v>
       </c>
       <c r="C2025" t="n">
         <v>3.809672273313826</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.669771874924028</v>
+        <v>-5.547877220160711</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.541407099030468</v>
+        <v>1.590164960935795</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.09962117037689056</v>
+        <v>0.0583403872671997</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.749899571087692</v>
+        <v>3.844676505674146</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332683</v>
       </c>
       <c r="C2026" t="n">
         <v>3.818597911769729</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.771747997172436</v>
+        <v>-5.649853342409118</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.509542288587007</v>
+        <v>1.558300150492335</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2015972926252981</v>
+        <v>-0.04363573498120787</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.69763953619455</v>
+        <v>3.792416470781004</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.7982967842318</v>
       </c>
       <c r="C2027" t="n">
         <v>3.810750799013904</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.661741713695214</v>
+        <v>-5.539847058931897</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.545697689222071</v>
+        <v>1.594455551127398</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1783927207080229</v>
+        <v>-0.02043116306393267</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.70371516658909</v>
+        <v>3.798492101175545</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.785563924818515</v>
       </c>
       <c r="C2028" t="n">
         <v>3.815000809735878</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.518682137954288</v>
+        <v>-5.396787483190971</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.607171530240416</v>
+        <v>1.655929392145743</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1703792941180436</v>
+        <v>-0.01241773647395339</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.712773233265052</v>
+        <v>3.807550167851506</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051782</v>
       </c>
       <c r="C2029" t="n">
         <v>3.822261692618414</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.21723541248245</v>
+        <v>-5.095340757719133</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.735011103311687</v>
+        <v>1.783768965217014</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1310674313537936</v>
+        <v>0.2890289889978839</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.900902151430691</v>
+        <v>3.995679086017144</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679618</v>
       </c>
       <c r="C2030" t="n">
         <v>3.823232870371125</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.241825656717634</v>
+        <v>-5.119931001954317</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.726146183370324</v>
+        <v>1.774904045275651</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1310674313537936</v>
+        <v>0.2890289889978839</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.901873329183402</v>
+        <v>3.996650263769856</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474153</v>
       </c>
       <c r="C2031" t="n">
         <v>3.82407577475088</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.190787280711114</v>
+        <v>-5.068892625947797</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.747404438152687</v>
+        <v>1.796162300058015</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1310674313537936</v>
+        <v>0.2890289889978839</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.902716233563157</v>
+        <v>3.997493168149611</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969536</v>
       </c>
       <c r="C2032" t="n">
         <v>3.843113873625026</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.149647985844483</v>
+        <v>-5.027753331081166</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.782898254973485</v>
+        <v>1.831656116878813</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1722067262204244</v>
+        <v>0.3301682838645147</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.946437909357281</v>
+        <v>4.041214843943735</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700472</v>
       </c>
       <c r="C2033" t="n">
         <v>3.65929786974896</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.053013073825843</v>
+        <v>-4.931118419062526</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.637736215904876</v>
+        <v>1.686494077810203</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2688416382390644</v>
+        <v>0.4268031958831546</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.820602852692399</v>
+        <v>3.915379787278853</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077633</v>
       </c>
       <c r="C2034" t="n">
         <v>3.662799913822925</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.183593808356686</v>
+        <v>-5.061699153593368</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.589005966166503</v>
+        <v>1.63776382807183</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.1382609037082219</v>
+        <v>0.2962224613523121</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.745756456047858</v>
+        <v>3.840533390634312</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833451</v>
       </c>
       <c r="C2035" t="n">
         <v>3.647226732899007</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.019097474165724</v>
+        <v>-4.897202819402406</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.63923131891897</v>
+        <v>1.687989180824298</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3027572378991837</v>
+        <v>0.460718795543274</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.828881075638518</v>
+        <v>3.923658010224972</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077621</v>
       </c>
       <c r="C2036" t="n">
         <v>3.646414443335437</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.046467406850156</v>
+        <v>-4.924572752086839</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.627471056281627</v>
+        <v>1.676228918186955</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3027572378991837</v>
+        <v>0.460718795543274</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.828068786074947</v>
+        <v>3.922845720661401</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147903</v>
       </c>
       <c r="C2037" t="n">
         <v>3.656283222460509</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.056852601740045</v>
+        <v>-4.934957946976728</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.633185757450744</v>
+        <v>1.681943619356071</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2923720430092944</v>
+        <v>0.4503336006533847</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.831706448266086</v>
+        <v>3.92648338285254</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735275</v>
       </c>
       <c r="C2038" t="n">
         <v>3.727120228236934</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.07544076046227</v>
+        <v>-4.953546105698953</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.696587499738279</v>
+        <v>1.745345361643606</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.2737838842870691</v>
+        <v>0.4317454419311593</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.891390558809176</v>
+        <v>3.98616749339563</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496548</v>
       </c>
       <c r="C2039" t="n">
         <v>3.723989239055233</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.075739307158306</v>
+        <v>-4.953844652394989</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.693337091878163</v>
+        <v>1.74209495378349</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.2734853375910332</v>
+        <v>0.4314468952351234</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.888080441609853</v>
+        <v>3.982857376196307</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.81564321210885</v>
       </c>
       <c r="C2040" t="n">
         <v>3.728520133994624</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.974916173467879</v>
+        <v>-4.853021518704561</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.738197240293726</v>
+        <v>1.786955102199053</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.285949553075387</v>
+        <v>0.4439111107194773</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.900089865839857</v>
+        <v>3.994866800426311</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121465</v>
+        <v>3.807356168121459</v>
       </c>
       <c r="C2041" t="n">
         <v>3.728649387473168</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.784134812715472</v>
+        <v>-4.662240157952154</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.814639038073232</v>
+        <v>1.863396899978559</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4767309138277944</v>
+        <v>0.6346924714718847</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.014687935769844</v>
+        <v>4.109464870356299</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.775233033906073</v>
       </c>
       <c r="C2042" t="n">
         <v>3.708486233210764</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.765617958673651</v>
+        <v>-4.643723303910334</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.801882625427556</v>
+        <v>1.850640487332884</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.4896610432530026</v>
+        <v>0.6476226008970929</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.002282859162566</v>
+        <v>4.09705979374902</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912983</v>
+        <v>3.785761685912978</v>
       </c>
       <c r="C2043" t="n">
         <v>3.743453169822823</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.710287370771889</v>
+        <v>-4.588392716008571</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.85898179720032</v>
+        <v>1.907739659105647</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.5449916311547648</v>
+        <v>0.702953188798855</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.070448148515681</v>
+        <v>4.165225083102136</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539893</v>
+        <v>3.743767956539887</v>
       </c>
       <c r="C2044" t="n">
         <v>3.73713973772426</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.698233243858926</v>
+        <v>-4.576338589095609</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.857490015866943</v>
+        <v>1.90624787777227</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.5570457580677276</v>
+        <v>0.7150073157118179</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.071367192564897</v>
+        <v>4.166144127151352</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811007</v>
+        <v>3.725010844811002</v>
       </c>
       <c r="C2045" t="n">
         <v>3.739020367908396</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.739388363427147</v>
+        <v>-4.617493708663829</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.84290859822379</v>
+        <v>1.891666460129118</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5158906384995067</v>
+        <v>0.6738521961435969</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.0485547510081</v>
+        <v>4.143331685594554</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382918</v>
+        <v>3.612322444382913</v>
       </c>
       <c r="C2046" t="n">
         <v>3.751871393786279</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.636507773898554</v>
+        <v>-4.514613119135237</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.89691185991311</v>
+        <v>1.945669721818437</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6187712280280996</v>
+        <v>0.7767327856721898</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.123134130603138</v>
+        <v>4.217911065189593</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760314</v>
+        <v>3.646857607760309</v>
       </c>
       <c r="C2047" t="n">
         <v>3.772074063959873</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.868108167068055</v>
+        <v>-4.746213512304737</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.824474372818904</v>
+        <v>1.873232234724231</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6187712280280996</v>
+        <v>0.7767327856721898</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.143336800776733</v>
+        <v>4.238113735363187</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781699</v>
       </c>
       <c r="C2048" t="n">
         <v>3.772074063959873</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.886180675359666</v>
+        <v>-4.764286020596349</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.817245369502259</v>
+        <v>1.866003231407587</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6187712280280996</v>
+        <v>0.7767327856721898</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.143336800776733</v>
+        <v>4.238113735363187</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082827</v>
       </c>
       <c r="C2049" t="n">
         <v>3.73232597755334</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.061287507936111</v>
+        <v>-4.939392853172794</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.707454550065148</v>
+        <v>1.756212411970475</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6187712280280996</v>
+        <v>0.7767327856721898</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.1035887143702</v>
+        <v>4.198365648956654</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943579</v>
       </c>
       <c r="C2050" t="n">
         <v>3.73934859655028</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.030001487395656</v>
+        <v>-4.908106832632338</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.72699157727827</v>
+        <v>1.775749439183597</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.650057248568555</v>
+        <v>0.8080188062126452</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.129382945691413</v>
+        <v>4.224159880277867</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677824</v>
+        <v>3.730590658677817</v>
       </c>
       <c r="C2051" t="n">
         <v>3.838519596123184</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.876976095282371</v>
+        <v>-4.755081440519054</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.887372733696488</v>
+        <v>1.936130595601815</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8030826406818391</v>
+        <v>0.9610441983259294</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.320369180532287</v>
+        <v>4.415146115118742</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.741298518073877</v>
       </c>
       <c r="C2052" t="n">
         <v>4.025985821031476</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.905283409155642</v>
+        <v>-4.783388754392324</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.063516033055472</v>
+        <v>2.1122738949608</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8030826406818391</v>
+        <v>0.9610441983259294</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.50783540544058</v>
+        <v>4.602612340027034</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.699135800903162</v>
       </c>
       <c r="C2053" t="n">
         <v>3.995388772385558</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.071876634269164</v>
+        <v>-4.949981979505846</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.966281694364146</v>
+        <v>2.015039556269473</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.6364894155683167</v>
+        <v>0.794450973212407</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.377282421726549</v>
+        <v>4.472059356313003</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568382</v>
+        <v>3.708202704568376</v>
       </c>
       <c r="C2054" t="n">
         <v>3.999065175047276</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.898812254886864</v>
+        <v>-4.776917600123546</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.039183848778783</v>
+        <v>2.08794171068411</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.6364894155683167</v>
+        <v>0.794450973212407</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.380958824388267</v>
+        <v>4.475735758974721</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682204</v>
+        <v>3.740601586682198</v>
       </c>
       <c r="C2055" t="n">
         <v>3.996683230170771</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.869566274431167</v>
+        <v>-4.74767161966785</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.048500296084557</v>
+        <v>2.097258157989884</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.6364894155683167</v>
+        <v>0.794450973212407</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.378576879511762</v>
+        <v>4.473353814098216</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539107</v>
+        <v>3.699424827539101</v>
       </c>
       <c r="C2056" t="n">
         <v>3.993976469328406</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.976491822309018</v>
+        <v>-4.854597167545701</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.003023316091052</v>
+        <v>2.051781177996379</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.5295638676904654</v>
+        <v>0.6875254253345556</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.311714789942686</v>
+        <v>4.40649172452914</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983737</v>
+        <v>3.689962785983731</v>
       </c>
       <c r="C2057" t="n">
         <v>3.995405271471641</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.121510380816267</v>
+        <v>-4.99961572605295</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.946444694831386</v>
+        <v>1.995202556736714</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.3845453091832168</v>
+        <v>0.5425068668273071</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.226132456981571</v>
+        <v>4.320909391568025</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969749</v>
+        <v>3.711872614969742</v>
       </c>
       <c r="C2058" t="n">
         <v>4.095336510729394</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.239852146600985</v>
+        <v>-5.117957491837667</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.999039227775252</v>
+        <v>2.04779708968058</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.3952313477461069</v>
+        <v>0.5531929053901972</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.332475319377058</v>
+        <v>4.427252253963512</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073539</v>
+        <v>3.714899237073531</v>
       </c>
       <c r="C2059" t="n">
         <v>4.093122207855332</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.291262568921693</v>
+        <v>-5.169367914158375</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.976260755972908</v>
+        <v>2.025018617878235</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.3952313477461069</v>
+        <v>0.5531929053901972</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.330261016502996</v>
+        <v>4.42503795108945</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720065</v>
+        <v>3.704778134720058</v>
       </c>
       <c r="C2060" t="n">
         <v>4.093025335929622</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.370682020129444</v>
+        <v>-5.248787365366127</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.944396103564097</v>
+        <v>1.993153965469424</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.3952313477461069</v>
+        <v>0.5531929053901972</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.330164144577286</v>
+        <v>4.42494107916374</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581133</v>
+        <v>3.736825137581126</v>
       </c>
       <c r="C2061" t="n">
         <v>4.093019229487665</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.466145018046662</v>
+        <v>-5.344250363283344</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.906204797955253</v>
+        <v>1.95496265986058</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.3952313477461069</v>
+        <v>0.5531929053901972</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.33015803813533</v>
+        <v>4.424934972721783</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500735</v>
+        <v>3.715393145500728</v>
       </c>
       <c r="C2062" t="n">
         <v>4.091115626050276</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.506165016090446</v>
+        <v>-5.384270361327128</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.888293195300351</v>
+        <v>1.937051057205678</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.3552113497023231</v>
+        <v>0.5131729073464133</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.30424243587167</v>
+        <v>4.399019370458124</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.73610959863627</v>
+        <v>3.736109598636263</v>
       </c>
       <c r="C2063" t="n">
         <v>4.096849443798003</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.561534178222639</v>
+        <v>-5.439639523459322</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.8718793481952</v>
+        <v>1.920637210100527</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.3552113497023231</v>
+        <v>0.5131729073464133</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.309976253619396</v>
+        <v>4.40475318820585</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396013</v>
+        <v>3.736843055396006</v>
       </c>
       <c r="C2064" t="n">
         <v>4.096387807140935</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.606971958053466</v>
+        <v>-5.485077303290149</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.853242599605802</v>
+        <v>1.902000461511129</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.3123663590241634</v>
+        <v>0.4703279166682536</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.283807622555433</v>
+        <v>4.378584557141888</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396422</v>
+        <v>3.790292685396415</v>
       </c>
       <c r="C2065" t="n">
         <v>4.116262199991255</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.523746501205802</v>
+        <v>-5.401851846442485</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.906407175195187</v>
+        <v>1.955165037100514</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.3123663590241634</v>
+        <v>0.4703279166682536</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.303682015405752</v>
+        <v>4.398458949992207</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299177</v>
+        <v>3.79450702929917</v>
       </c>
       <c r="C2066" t="n">
         <v>4.099962900515982</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.347456276600495</v>
+        <v>-5.225561621837177</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.960623965562037</v>
+        <v>2.009381827467365</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.3123663590241634</v>
+        <v>0.4703279166682536</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.28738271593048</v>
+        <v>4.382159650516935</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,45 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.526961010913507</v>
+        <v>3.794725278590406</v>
       </c>
       <c r="C2067" t="n">
         <v>4.102393849980028</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.1642446134674</v>
+        <v>-5.042349958704082</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.036339580279321</v>
+        <v>2.085097442184648</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.3123663590241634</v>
+        <v>0.4703279166682536</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.289813665394526</v>
+        <v>4.384590599980981</v>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" s="2" t="n">
+        <v>45530</v>
+      </c>
+      <c r="B2068" t="n">
+        <v>3.861533357823034</v>
+      </c>
+      <c r="C2068" t="n">
+        <v>4.23788073859869</v>
+      </c>
+      <c r="D2068" t="n">
+        <v>-5.042349958704082</v>
+      </c>
+      <c r="E2068" t="n">
+        <v>2.085097442184648</v>
+      </c>
+      <c r="F2068" t="n">
+        <v>0.4703279166682536</v>
+      </c>
+      <c r="G2068" t="n">
+        <v>4.230944535585058</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240826.xlsx
+++ b/tame_output/ON/bt/strategyON_20240826.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>50.5%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>112.2%</t>
+          <t>101.9%</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.4%</t>
+          <t>430.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-167.7%</t>
+          <t>-172.0%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-281.4%</t>
+          <t>-281.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-33.1%</t>
         </is>
       </c>
     </row>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279811</v>
+        <v>3.385382209279812</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511402</v>
+        <v>3.367379938511403</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082122</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.29349053375792</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760738</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706666</v>
+        <v>3.298730590706667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296833</v>
+        <v>3.299918119296834</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201484</v>
+        <v>3.295507330201485</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153003</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537423</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382188</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074619</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911635</v>
+        <v>3.233800325911636</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213491</v>
+        <v>3.223539378213492</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416041</v>
+        <v>3.231167537416042</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382323</v>
+        <v>3.235981977382324</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495494</v>
+        <v>3.278199702495495</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347049</v>
+        <v>3.29913614634705</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130011</v>
+        <v>3.287377576130012</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178237</v>
+        <v>3.315884374178238</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207807</v>
+        <v>3.305316798207808</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310976</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006528</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309418</v>
+        <v>3.311086391309419</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970899</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330517</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191731</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108633</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097814</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094109</v>
+        <v>3.37443904309411</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199278</v>
+        <v>3.405960511199279</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969586</v>
+        <v>3.424633354969587</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923078</v>
+        <v>3.419979433923079</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297741</v>
+        <v>3.458100091297742</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317609</v>
+        <v>3.44775050131761</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737163</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341306</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539457</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937496</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141699</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729888</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440631</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608597</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410269</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764393</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390583</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297395</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367402532254</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158918</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940714</v>
+        <v>3.691571733940715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770574</v>
+        <v>3.676841549770575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615277</v>
+        <v>3.685161381615278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812097</v>
+        <v>3.684843823812098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646211</v>
+        <v>3.710935533646212</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955322</v>
+        <v>3.728577929955323</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232407</v>
+        <v>3.747702660232408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436223</v>
+        <v>3.766317079436224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311943</v>
+        <v>3.784684521311944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097238</v>
+        <v>3.800829354097239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017765</v>
+        <v>3.789311112017766</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390424</v>
+        <v>3.763182248390425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471879410595</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960983</v>
+        <v>3.753882571960984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607641</v>
+        <v>3.692931855607642</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987897</v>
+        <v>3.770422583987898</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710809</v>
+        <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.873530691357055</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409201</v>
+        <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.864816705103577</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098105</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.857856093008484</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493416</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.872318447389627</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722813</v>
+        <v>3.828551486722814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.866850567848822</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792042</v>
+        <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
         <v>2.864348661859399</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919902</v>
+        <v>3.812453678919903</v>
       </c>
       <c r="C1916" t="n">
         <v>2.872049640096724</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318088</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.867830348443774</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.82431123305752</v>
+        <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.86995466236379</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279178</v>
+        <v>3.82635497427918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.862696737347493</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011491</v>
+        <v>3.835957987011493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.866295860868141</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392979</v>
+        <v>3.780933911392981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.879623366922695</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632774</v>
+        <v>3.773765222632775</v>
       </c>
       <c r="C1922" t="n">
         <v>2.878643844538992</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883067</v>
+        <v>3.764617879883069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.883338645593309</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074776</v>
+        <v>3.798814771074777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.864532904377105</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242287</v>
+        <v>3.797694884242289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.866275981001982</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367677</v>
+        <v>3.821593509367679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.870205294836802</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879958</v>
+        <v>3.822326997879959</v>
       </c>
       <c r="C1927" t="n">
         <v>2.870883878754142</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650233</v>
+        <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.867881949974136</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675932</v>
+        <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.86946098698475</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539943</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.885355169786573</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496256</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.886501014226875</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576992</v>
+        <v>3.791273551576994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.896589116788315</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942098</v>
+        <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
         <v>2.882626608189741</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674509</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.897915777423949</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430688</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.805559976746391</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003595</v>
+        <v>3.743220196003596</v>
       </c>
       <c r="C1936" t="n">
         <v>2.724821838231692</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508364</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.715258546863584</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417698</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
         <v>2.852289383555786</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205893</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.856856615547574</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225437</v>
+        <v>3.765024323225439</v>
       </c>
       <c r="C1940" t="n">
         <v>2.832598644308781</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.761136957710231</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.771309344142363</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.766255614716223</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316044</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.758031390160749</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803187</v>
+        <v>3.75357116580319</v>
       </c>
       <c r="C1945" t="n">
         <v>2.75858326319385</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.687855955085216</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560421</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.689729431009817</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472733</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.68480513952154</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798532</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.690296435352207</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498858</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.701793637120746</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705318</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.5401493571214</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729262</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.660299017840605</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190763</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.674812043942928</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.74117406991342</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.672231485285297</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.668960514130599</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793897</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.669643905892512</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011229</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.663430881198926</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982223</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.644238336530516</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509532</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.649929898869462</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.649133820765963</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815452</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64673378232028</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378097</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.643258501528525</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.762552903162715</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067859</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.763386232148849</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789116</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.769394762545775</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519903</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.667344983822974</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.670138605354455</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394724</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.670800953746113</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890607</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.669881430486224</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.86736263679842</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.736216984283045</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992186</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.538508985997172</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.608799218319347</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031954</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.623426954435391</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.621962935260062</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397789</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.620454553299991</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316244</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.620317420735427</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.614711214874017</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.621092971901822</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569611</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.625985345276547</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557288</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.612740017752419</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932763</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.616837720363048</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917046</v>
+        <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
         <v>2.620998659994126</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405954</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.626878262521963</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265638</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.62528826299121</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284873</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.67653602817425</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321017</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.674976732768503</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475133</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.669924961006773</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404847</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.687112365099478</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882551</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.683073337398759</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992654</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.684330129729999</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636281</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84488790075121</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957619</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.965000809969027</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.956708785982886</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896923</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.954901981566665</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959851</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.972456387293457</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945358</v>
+        <v>3.794424941945362</v>
       </c>
       <c r="C1996" t="n">
         <v>2.964311434698041</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782702</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.945581131885902</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.78467134563263</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.936245154382807</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777666</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>3.095151280233976</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644406</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>3.132229102727623</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799957</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.128904458717168</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331109</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>3.138910612361909</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784101</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.323013744506869</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74392550571442</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.315130439409862</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155026</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.3171844389595</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516197</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.373438156681347</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321627</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.376329251226648</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347696</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.374441064120423</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887741</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.369261293723285</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.71289761234306</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.367695303933437</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389342</v>
+        <v>3.754596135389346</v>
       </c>
       <c r="C2011" t="n">
         <v>3.380768710799356</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378386</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.372773907582296</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006968</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.371297948709298</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.68489577878738</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.368062392686497</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585931</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.434768352277001</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814658</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.575080071278848</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237087</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.644060340424487</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.61992301642338</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.630111542544608</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609746</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.641982031600022</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973151</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.643192566118966</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251939</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.647314308346287</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916195</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
         <v>3.642392161082477</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830322</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.804596217781521</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071544</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.799442855745335</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868138</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.809672273313826</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332683</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.818597911769729</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.7982967842318</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.810750799013904</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818515</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.815000809735878</v>
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051782</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.822261692618414</v>
+        <v>3.779176473537764</v>
       </c>
       <c r="D2029" t="n">
         <v>-5.095340757719133</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.783768965217014</v>
+        <v>1.740683746136364</v>
       </c>
       <c r="F2029" t="n">
         <v>0.2890289889978839</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.995679086017144</v>
+        <v>3.952593866936494</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679618</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.823232870371125</v>
+        <v>3.780147651290475</v>
       </c>
       <c r="D2030" t="n">
         <v>-5.119931001954317</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.774904045275651</v>
+        <v>1.731818826195001</v>
       </c>
       <c r="F2030" t="n">
         <v>0.2890289889978839</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.996650263769856</v>
+        <v>3.953565044689205</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474153</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.82407577475088</v>
+        <v>3.78099055567023</v>
       </c>
       <c r="D2031" t="n">
         <v>-5.068892625947797</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.796162300058015</v>
+        <v>1.753077080977365</v>
       </c>
       <c r="F2031" t="n">
         <v>0.2890289889978839</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.997493168149611</v>
+        <v>3.954407949068961</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969536</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.843113873625026</v>
+        <v>3.800028654544376</v>
       </c>
       <c r="D2032" t="n">
         <v>-5.027753331081166</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.831656116878813</v>
+        <v>1.788570897798162</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3301682838645147</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.041214843943735</v>
+        <v>3.998129624863084</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700472</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.65929786974896</v>
+        <v>3.61621265066831</v>
       </c>
       <c r="D2033" t="n">
         <v>-4.931118419062526</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.686494077810203</v>
+        <v>1.643408858729553</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4268031958831546</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.915379787278853</v>
+        <v>3.872294568198203</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077633</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.662799913822925</v>
+        <v>3.619714694742274</v>
       </c>
       <c r="D2034" t="n">
         <v>-5.061699153593368</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.63776382807183</v>
+        <v>1.59467860899118</v>
       </c>
       <c r="F2034" t="n">
         <v>0.2962224613523121</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.840533390634312</v>
+        <v>3.797448171553662</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833451</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.647226732899007</v>
+        <v>3.604141513818357</v>
       </c>
       <c r="D2035" t="n">
         <v>-4.897202819402406</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.687989180824298</v>
+        <v>1.644903961743648</v>
       </c>
       <c r="F2035" t="n">
         <v>0.460718795543274</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.923658010224972</v>
+        <v>3.880572791144322</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077621</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.646414443335437</v>
+        <v>3.603329224254787</v>
       </c>
       <c r="D2036" t="n">
         <v>-4.924572752086839</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.676228918186955</v>
+        <v>1.633143699106304</v>
       </c>
       <c r="F2036" t="n">
         <v>0.460718795543274</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.922845720661401</v>
+        <v>3.879760501580751</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147903</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.656283222460509</v>
+        <v>3.613198003379859</v>
       </c>
       <c r="D2037" t="n">
         <v>-4.934957946976728</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.681943619356071</v>
+        <v>1.638858400275421</v>
       </c>
       <c r="F2037" t="n">
         <v>0.4503336006533847</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.92648338285254</v>
+        <v>3.88339816377189</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735275</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.727120228236934</v>
+        <v>3.684035009156284</v>
       </c>
       <c r="D2038" t="n">
         <v>-4.953546105698953</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.745345361643606</v>
+        <v>1.702260142562956</v>
       </c>
       <c r="F2038" t="n">
         <v>0.4317454419311593</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.98616749339563</v>
+        <v>3.94308227431498</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496548</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.723989239055233</v>
+        <v>3.680904019974583</v>
       </c>
       <c r="D2039" t="n">
         <v>-4.953844652394989</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.74209495378349</v>
+        <v>1.69900973470284</v>
       </c>
       <c r="F2039" t="n">
         <v>0.4314468952351234</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.982857376196307</v>
+        <v>3.939772157115657</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.81564321210885</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.728520133994624</v>
+        <v>3.685434914913974</v>
       </c>
       <c r="D2040" t="n">
         <v>-4.853021518704561</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.786955102199053</v>
+        <v>1.743869883118403</v>
       </c>
       <c r="F2040" t="n">
         <v>0.4439111107194773</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.994866800426311</v>
+        <v>3.951781581345661</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121459</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.728649387473168</v>
+        <v>3.685564168392518</v>
       </c>
       <c r="D2041" t="n">
         <v>-4.662240157952154</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.863396899978559</v>
+        <v>1.820311680897909</v>
       </c>
       <c r="F2041" t="n">
         <v>0.6346924714718847</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.109464870356299</v>
+        <v>4.066379651275649</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906073</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.708486233210764</v>
+        <v>3.665401014130114</v>
       </c>
       <c r="D2042" t="n">
         <v>-4.643723303910334</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.850640487332884</v>
+        <v>1.807555268252234</v>
       </c>
       <c r="F2042" t="n">
         <v>0.6476226008970929</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.09705979374902</v>
+        <v>4.05397457466837</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912978</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.743453169822823</v>
+        <v>3.700367950742173</v>
       </c>
       <c r="D2043" t="n">
         <v>-4.588392716008571</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.907739659105647</v>
+        <v>1.864654440024997</v>
       </c>
       <c r="F2043" t="n">
         <v>0.702953188798855</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.165225083102136</v>
+        <v>4.122139864021486</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539887</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.73713973772426</v>
+        <v>3.69405451864361</v>
       </c>
       <c r="D2044" t="n">
         <v>-4.576338589095609</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.90624787777227</v>
+        <v>1.86316265869162</v>
       </c>
       <c r="F2044" t="n">
         <v>0.7150073157118179</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.166144127151352</v>
+        <v>4.123058908070702</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811002</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.739020367908396</v>
+        <v>3.695935148827746</v>
       </c>
       <c r="D2045" t="n">
         <v>-4.617493708663829</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.891666460129118</v>
+        <v>1.848581241048467</v>
       </c>
       <c r="F2045" t="n">
         <v>0.6738521961435969</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.143331685594554</v>
+        <v>4.100246466513904</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382913</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.751871393786279</v>
+        <v>3.708786174705629</v>
       </c>
       <c r="D2046" t="n">
         <v>-4.514613119135237</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.945669721818437</v>
+        <v>1.902584502737787</v>
       </c>
       <c r="F2046" t="n">
         <v>0.7767327856721898</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.217911065189593</v>
+        <v>4.174825846108943</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760309</v>
+        <v>3.646857607760312</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.772074063959873</v>
+        <v>3.728988844879223</v>
       </c>
       <c r="D2047" t="n">
         <v>-4.746213512304737</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.873232234724231</v>
+        <v>1.830147015643581</v>
       </c>
       <c r="F2047" t="n">
         <v>0.7767327856721898</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.238113735363187</v>
+        <v>4.195028516282537</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781699</v>
+        <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.772074063959873</v>
+        <v>3.728988844879223</v>
       </c>
       <c r="D2048" t="n">
         <v>-4.764286020596349</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.866003231407587</v>
+        <v>1.822918012326936</v>
       </c>
       <c r="F2048" t="n">
         <v>0.7767327856721898</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.238113735363187</v>
+        <v>4.195028516282537</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082827</v>
+        <v>3.670068888082832</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.73232597755334</v>
+        <v>3.689240758472689</v>
       </c>
       <c r="D2049" t="n">
         <v>-4.939392853172794</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.756212411970475</v>
+        <v>1.713127192889825</v>
       </c>
       <c r="F2049" t="n">
         <v>0.7767327856721898</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.198365648956654</v>
+        <v>4.155280429876004</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943579</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.73934859655028</v>
+        <v>3.696263377469629</v>
       </c>
       <c r="D2050" t="n">
         <v>-4.908106832632338</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.775749439183597</v>
+        <v>1.732664220102947</v>
       </c>
       <c r="F2050" t="n">
         <v>0.8080188062126452</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.224159880277867</v>
+        <v>4.181074661197217</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677817</v>
+        <v>3.730590658677822</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.838519596123184</v>
+        <v>3.795434377042534</v>
       </c>
       <c r="D2051" t="n">
         <v>-4.755081440519054</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.936130595601815</v>
+        <v>1.893045376521165</v>
       </c>
       <c r="F2051" t="n">
         <v>0.9610441983259294</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.415146115118742</v>
+        <v>4.372060896038092</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073877</v>
+        <v>3.741298518073881</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.025985821031476</v>
+        <v>3.982900601950826</v>
       </c>
       <c r="D2052" t="n">
         <v>-4.783388754392324</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.1122738949608</v>
+        <v>2.06918867588015</v>
       </c>
       <c r="F2052" t="n">
         <v>0.9610441983259294</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.602612340027034</v>
+        <v>4.559527120946384</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903162</v>
+        <v>3.699135800903166</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.995388772385558</v>
+        <v>3.952303553304908</v>
       </c>
       <c r="D2053" t="n">
         <v>-4.949981979505846</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.015039556269473</v>
+        <v>1.971954337188823</v>
       </c>
       <c r="F2053" t="n">
         <v>0.794450973212407</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.472059356313003</v>
+        <v>4.428974137232353</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568376</v>
+        <v>3.708202704568381</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.999065175047276</v>
+        <v>3.955979955966626</v>
       </c>
       <c r="D2054" t="n">
         <v>-4.776917600123546</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.08794171068411</v>
+        <v>2.04485649160346</v>
       </c>
       <c r="F2054" t="n">
         <v>0.794450973212407</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.475735758974721</v>
+        <v>4.432650539894071</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682198</v>
+        <v>3.740601586682202</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.996683230170771</v>
+        <v>3.953598011090121</v>
       </c>
       <c r="D2055" t="n">
         <v>-4.74767161966785</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.097258157989884</v>
+        <v>2.054172938909234</v>
       </c>
       <c r="F2055" t="n">
         <v>0.794450973212407</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.473353814098216</v>
+        <v>4.430268595017566</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539101</v>
+        <v>3.699424827539105</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.993976469328406</v>
+        <v>3.950891250247756</v>
       </c>
       <c r="D2056" t="n">
         <v>-4.854597167545701</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.051781177996379</v>
+        <v>2.008695958915729</v>
       </c>
       <c r="F2056" t="n">
         <v>0.6875254253345556</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.40649172452914</v>
+        <v>4.36340650544849</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983731</v>
+        <v>3.689962785983735</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.995405271471641</v>
+        <v>3.95232005239099</v>
       </c>
       <c r="D2057" t="n">
         <v>-4.99961572605295</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.995202556736714</v>
+        <v>1.952117337656063</v>
       </c>
       <c r="F2057" t="n">
         <v>0.5425068668273071</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.320909391568025</v>
+        <v>4.277824172487375</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969742</v>
+        <v>3.711872614969747</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.095336510729394</v>
+        <v>4.052251291648743</v>
       </c>
       <c r="D2058" t="n">
         <v>-5.117957491837667</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.04779708968058</v>
+        <v>2.00471187059993</v>
       </c>
       <c r="F2058" t="n">
         <v>0.5531929053901972</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.427252253963512</v>
+        <v>4.384167034882862</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073531</v>
+        <v>3.714899237073537</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.093122207855332</v>
+        <v>4.050036988774682</v>
       </c>
       <c r="D2059" t="n">
         <v>-5.169367914158375</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.025018617878235</v>
+        <v>1.981933398797585</v>
       </c>
       <c r="F2059" t="n">
         <v>0.5531929053901972</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.42503795108945</v>
+        <v>4.3819527320088</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720058</v>
+        <v>3.704778134720064</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.093025335929622</v>
+        <v>4.049940116848972</v>
       </c>
       <c r="D2060" t="n">
         <v>-5.248787365366127</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.993153965469424</v>
+        <v>1.950068746388774</v>
       </c>
       <c r="F2060" t="n">
         <v>0.5531929053901972</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.42494107916374</v>
+        <v>4.38185586008309</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581126</v>
+        <v>3.736825137581131</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.093019229487665</v>
+        <v>4.049934010407015</v>
       </c>
       <c r="D2061" t="n">
         <v>-5.344250363283344</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.95496265986058</v>
+        <v>1.91187744077993</v>
       </c>
       <c r="F2061" t="n">
         <v>0.5531929053901972</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.424934972721783</v>
+        <v>4.381849753641133</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500728</v>
+        <v>3.715393145500733</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.091115626050276</v>
+        <v>4.048030406969626</v>
       </c>
       <c r="D2062" t="n">
         <v>-5.384270361327128</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.937051057205678</v>
+        <v>1.893965838125028</v>
       </c>
       <c r="F2062" t="n">
         <v>0.5131729073464133</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.399019370458124</v>
+        <v>4.355934151377474</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636263</v>
+        <v>3.736109598636268</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.096849443798003</v>
+        <v>4.053764224717352</v>
       </c>
       <c r="D2063" t="n">
         <v>-5.439639523459322</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.920637210100527</v>
+        <v>1.877551991019877</v>
       </c>
       <c r="F2063" t="n">
         <v>0.5131729073464133</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.40475318820585</v>
+        <v>4.3616679691252</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396006</v>
+        <v>3.736843055396012</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.096387807140935</v>
+        <v>4.053302588060285</v>
       </c>
       <c r="D2064" t="n">
         <v>-5.485077303290149</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.902000461511129</v>
+        <v>1.858915242430479</v>
       </c>
       <c r="F2064" t="n">
         <v>0.4703279166682536</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.378584557141888</v>
+        <v>4.335499338061238</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396415</v>
+        <v>3.790292685396421</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.116262199991255</v>
+        <v>4.073176980910604</v>
       </c>
       <c r="D2065" t="n">
         <v>-5.401851846442485</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.955165037100514</v>
+        <v>1.912079818019864</v>
       </c>
       <c r="F2065" t="n">
         <v>0.4703279166682536</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.398458949992207</v>
+        <v>4.355373730911557</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.79450702929917</v>
+        <v>3.794507029299175</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.099962900515982</v>
+        <v>4.056877681435332</v>
       </c>
       <c r="D2066" t="n">
         <v>-5.225561621837177</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.009381827467365</v>
+        <v>1.966296608386715</v>
       </c>
       <c r="F2066" t="n">
         <v>0.4703279166682536</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.382159650516935</v>
+        <v>4.339074431436285</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590406</v>
+        <v>3.794725278590411</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.102393849980028</v>
+        <v>4.059308630899378</v>
       </c>
       <c r="D2067" t="n">
         <v>-5.042349958704082</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.085097442184648</v>
+        <v>2.042012223103998</v>
       </c>
       <c r="F2067" t="n">
         <v>0.4703279166682536</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.384590599980981</v>
+        <v>4.341505380900331</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.861533357823034</v>
+        <v>3.785445234918883</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.23788073859869</v>
+        <v>4.135729644065447</v>
       </c>
       <c r="D2068" t="n">
         <v>-5.042349958704082</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.085097442184648</v>
+        <v>2.042012223103998</v>
       </c>
       <c r="F2068" t="n">
         <v>0.4703279166682536</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.230944535585058</v>
+        <v>4.128793441051815</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240826.xlsx
+++ b/tame_output/ON/bt/strategyON_20240826.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>78.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>101.9%</t>
+          <t>114.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>108.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.8%</t>
+          <t>124.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-597.3%</t>
+          <t>-604.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.3%</t>
+          <t>437.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-665.8%</t>
+          <t>-678.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-239.3%</t>
+          <t>-242.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,22 +1155,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.5%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-172.0%</t>
+          <t>-172.6%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-228.8%</t>
+          <t>-236.2%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-281.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-177.0%</t>
+          <t>-192.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-137.6%</t>
+          <t>-142.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-23.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-20.6%</t>
         </is>
       </c>
     </row>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355688</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.3634908492490375</v>
+        <v>0.2888670980769374</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.26761008749881</v>
+        <v>3.23776058702997</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.70757260984084</v>
+        <v>1.63294885866874</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.147113738017447</v>
+        <v>4.102339487314187</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.2397963636932034</v>
+        <v>0.1651726125211033</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.253073377774018</v>
+        <v>3.223223877305178</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.70757260984084</v>
+        <v>1.63294885866874</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.182054822514989</v>
+        <v>4.137280571811729</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.2448339544207899</v>
+        <v>0.1702102032486899</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.253665854250391</v>
+        <v>3.223816353781551</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.763217066107158</v>
+        <v>1.688593314935058</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.214018936460117</v>
+        <v>4.169244685756857</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.01236008028726682</v>
+        <v>-0.08698383145936689</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.129534621990905</v>
+        <v>3.099685121522065</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.506023031399101</v>
+        <v>1.431399280227001</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.03844889725902</v>
+        <v>3.99367464655576</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.07812747033667888</v>
+        <v>-0.152751221508779</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.104245275101611</v>
+        <v>3.074395774632771</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.506023031399101</v>
+        <v>1.431399280227001</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.03946650638949</v>
+        <v>3.99469225568623</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.3104983844983536</v>
+        <v>-0.3851221356704537</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.001924941424697</v>
+        <v>2.972075440955857</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.506023031399101</v>
+        <v>1.431399280227001</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.030094538377246</v>
+        <v>3.985320287673986</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.3922702849261053</v>
+        <v>-0.4668940360982053</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.959298907208834</v>
+        <v>2.929449406739994</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.533058604805237</v>
+        <v>1.458434853633138</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.036398608376166</v>
+        <v>3.991624357672906</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.4594793927979829</v>
+        <v>-0.534103143970083</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.937180580893785</v>
+        <v>2.907331080424945</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.533058604805237</v>
+        <v>1.458434853633138</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.041163925209869</v>
+        <v>3.996389674506609</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.4480901561431815</v>
+        <v>-0.5227139073152816</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.939561071674946</v>
+        <v>2.909711571206106</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.544447841460039</v>
+        <v>1.469824090287939</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.045822263321989</v>
+        <v>4.00104801261873</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.7005680505625875</v>
+        <v>-0.7751918017346875</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.836496805412247</v>
+        <v>2.806647304943407</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.291969947040633</v>
+        <v>1.217346195868533</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.89226241817541</v>
+        <v>3.847488167472149</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.9906997171680189</v>
+        <v>-1.065323468340119</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.720310355368996</v>
+        <v>2.690460854900156</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.316051741780813</v>
+        <v>1.241427990608713</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.906577711618439</v>
+        <v>3.861803460915179</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.198703775521096</v>
+        <v>-1.273327526693196</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.642000876581691</v>
+        <v>2.612151376112851</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.316051741780813</v>
+        <v>1.241427990608713</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.911469856172364</v>
+        <v>3.866695605469104</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.260882186682066</v>
+        <v>-1.335505937854166</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.612210968455291</v>
+        <v>2.582361467986451</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.253873330619843</v>
+        <v>1.179249579447743</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.86924426581377</v>
+        <v>3.82447001511051</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.626950913826719</v>
+        <v>-1.701574664998819</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.458867776903879</v>
+        <v>2.429018276435039</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.88780460347519</v>
+        <v>0.81318085230309</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.642687328833428</v>
+        <v>3.597913078130168</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.835441695278403</v>
+        <v>-1.910065446450503</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.395809754061973</v>
+        <v>2.365960253593133</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.6793138220235055</v>
+        <v>0.6046900708514056</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.537931149701186</v>
+        <v>3.493156898997925</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.082642880043625</v>
+        <v>-2.157266631215725</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.305028030564453</v>
+        <v>2.275178530095613</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.699467175522318</v>
+        <v>0.624843424350218</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.558121912209042</v>
+        <v>3.513347661505781</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.575027908067722</v>
+        <v>-2.649651659239822</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.109180411398547</v>
+        <v>2.079330910929706</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.2070821474982212</v>
+        <v>0.1324583963261213</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.263797287438316</v>
+        <v>3.219023036735056</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.960208298997795</v>
+        <v>-3.034832050169894</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.953650793839381</v>
+        <v>1.923801293370541</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.2070821474982212</v>
+        <v>0.1324583963261213</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.262339826251179</v>
+        <v>3.217565575547919</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.210078979012376</v>
+        <v>-3.284702730184476</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.855471645288164</v>
+        <v>1.825622144819325</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.2433448673286845</v>
+        <v>0.1687211161565845</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.285866581604073</v>
+        <v>3.241092330900813</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.416590755899398</v>
+        <v>-3.491214507071497</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.768972993189614</v>
+        <v>1.739123492720774</v>
       </c>
       <c r="F1857" t="n">
-        <v>0.036833090441663</v>
+        <v>-0.03779066073043696</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.158065574128118</v>
+        <v>3.113291323424858</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.735934830979899</v>
+        <v>-3.810558582151998</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.643008289857673</v>
+        <v>1.613158789388833</v>
       </c>
       <c r="F1858" t="n">
-        <v>0.036833090441663</v>
+        <v>-0.03779066073043696</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.159838500828378</v>
+        <v>3.115064250125117</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.122144662255674</v>
+        <v>-4.196768413427773</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.474857244814767</v>
+        <v>1.445007744345927</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.05393984927578033</v>
+        <v>-0.1285636004478803</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.091707624465316</v>
+        <v>3.046933373762056</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.356838656388226</v>
+        <v>-4.431462407560326</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.369264422163837</v>
+        <v>1.339414921694997</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.04760358204652515</v>
+        <v>-0.1222273332186251</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.08379415980496</v>
+        <v>3.0390199091017</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.692501303618679</v>
+        <v>-4.767125054790778</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.233579954927621</v>
+        <v>1.203730454458781</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.11553456753543</v>
+        <v>-0.1901583187075299</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.041616160167582</v>
+        <v>2.996841909464322</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.76894563382155</v>
+        <v>-4.84356938499365</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.209489783080714</v>
+        <v>1.179640282611874</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.03508905844176807</v>
+        <v>-0.109712809613868</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.096371025858021</v>
+        <v>3.051596775154761</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.134073016460297</v>
+        <v>-5.208696767632397</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.062693345031047</v>
+        <v>1.032843844562207</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.3313998427407806</v>
+        <v>-0.4060235939128806</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.917839070284444</v>
+        <v>2.873064819581185</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.542661793640976</v>
+        <v>-5.617285544813075</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8980193781735339</v>
+        <v>0.8681698777046942</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.814612371093559</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.671447347990797</v>
+        <v>2.626673097287537</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.656422205663841</v>
+        <v>-5.73104595683594</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.8477006458358489</v>
+        <v>0.8178511453670088</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.814612371093559</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.666632780462257</v>
+        <v>2.621858529758997</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.072814079950838</v>
+        <v>-6.147437831122938</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6791379467299272</v>
+        <v>0.6492884462610871</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.814612371093559</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.664626831071135</v>
+        <v>2.619852580367874</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.433987709767826</v>
+        <v>-6.508611460939925</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5449271854718107</v>
+        <v>0.515077685002971</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.814612371093559</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.674885521739814</v>
+        <v>2.630111271036554</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.777246229410845</v>
+        <v>-6.851869980582944</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4037233427602986</v>
+        <v>0.3738738422914589</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.814612371093559</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.670985086885509</v>
+        <v>2.626210836182249</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.825449046653189</v>
+        <v>-6.900072797825288</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3828471359183618</v>
+        <v>0.3529976354495221</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.814612371093559</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.669390006940509</v>
+        <v>2.62461575623725</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.122110388463386</v>
+        <v>-7.196734139635486</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2679615751234912</v>
+        <v>0.2381120746546515</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-0.8833555068274376</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.631923101429391</v>
+        <v>2.58714885072613</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.308830096772689</v>
+        <v>-7.383453847944788</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1892473872653668</v>
+        <v>0.1593978867965271</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-0.8833555068274376</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.627896796894988</v>
+        <v>2.583122546191728</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.69183148551532</v>
+        <v>-7.76645523668742</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.03594473044673041</v>
+        <v>0.006095229977890693</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-0.8833555068274376</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.627794695573404</v>
+        <v>2.583020444870144</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.696317930716709</v>
+        <v>-7.770941681888808</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.03672166833760526</v>
+        <v>0.0068721678687651</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.8132182008567264</v>
+        <v>-0.8878419520288263</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.627674344424</v>
+        <v>2.58290009372074</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.055848253220711</v>
+        <v>-8.130472004392811</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1017401573659455</v>
+        <v>-0.1315896578347857</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.8132182008567264</v>
+        <v>-0.8878419520288263</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.63302464772205</v>
+        <v>2.588250397018791</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.106197316674933</v>
+        <v>-8.180821067847033</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1139637627904571</v>
+        <v>-0.1438132632592968</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.8635672643109484</v>
+        <v>-0.9381910154830484</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.610731229606695</v>
+        <v>2.565956978903435</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.203816594096329</v>
+        <v>-8.278440345268429</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1499697231372465</v>
+        <v>-0.1798192236060863</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.9611865417323451</v>
+        <v>-1.035810292904445</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.555201413775626</v>
+        <v>2.510427163072366</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.257888093604688</v>
+        <v>-8.332511844776787</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.168704766619018</v>
+        <v>-0.1985542670878577</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.015258041240704</v>
+        <v>-1.089881792412804</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.525652070392182</v>
+        <v>2.480877819688923</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.462146268934552</v>
+        <v>-8.536770020106651</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2448948396323209</v>
+        <v>-0.2747443401011607</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.142896985854693</v>
+        <v>-1.217520737026793</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.454581900742431</v>
+        <v>2.409807650039171</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.495799107443025</v>
+        <v>-8.570422858615125</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2538734205512743</v>
+        <v>-0.283722921020114</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.243310353771731</v>
+        <v>-1.317934104943831</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.398816434476645</v>
+        <v>2.354042183773385</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.634885222061882</v>
+        <v>-8.709508973233982</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.294136164905396</v>
+        <v>-0.3239856653742361</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.382396468390588</v>
+        <v>-1.457020219562688</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.330736467198752</v>
+        <v>2.285962216495492</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.810009639448426</v>
+        <v>-8.884633390620525</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3496307111124968</v>
+        <v>-0.3794802115813365</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.557520885777131</v>
+        <v>-1.632144636949231</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.240217037514342</v>
+        <v>2.195442786811082</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.044461733462915</v>
+        <v>-9.119085484635015</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4506307136198884</v>
+        <v>-0.4804802140887285</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.557520885777131</v>
+        <v>-1.632144636949231</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.232997872612747</v>
+        <v>2.188223621909486</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.148836464489362</v>
+        <v>-9.223460215661461</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4990527968044431</v>
+        <v>-0.5289022972732833</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.661895616803577</v>
+        <v>-1.736519367975677</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.163700843222903</v>
+        <v>2.118926592519643</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.311349930187946</v>
+        <v>-9.385973681360046</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5629423932453208</v>
+        <v>-0.5927918937141605</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.759529047222264</v>
+        <v>-1.834152798394364</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.106236574810247</v>
+        <v>2.061462324106987</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.437386723556235</v>
+        <v>-9.512010474728335</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6106633819635219</v>
+        <v>-0.6405128824323616</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.734277424412522</v>
+        <v>-1.808901175584622</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.124081277125207</v>
+        <v>2.079307026421947</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.380314951660305</v>
+        <v>-9.454938702832404</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5838443375187485</v>
+        <v>-0.6136938379875883</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.734277424412522</v>
+        <v>-1.808901175584622</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.128071612811608</v>
+        <v>2.083297362108348</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.521986793384425</v>
+        <v>-9.596610544556524</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6419883011071383</v>
+        <v>-0.6718378015759781</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.734277424412522</v>
+        <v>-1.808901175584622</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.126596385912866</v>
+        <v>2.081822135209606</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.472395948959591</v>
+        <v>-9.54701970013169</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6070985531723325</v>
+        <v>-0.6369480536411722</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.684686579987688</v>
+        <v>-1.759310331159788</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.171404302732639</v>
+        <v>2.126630052029379</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.323477614487734</v>
+        <v>-9.398101365659834</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5605823530302727</v>
+        <v>-0.5904318534991124</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.653436989252515</v>
+        <v>-1.728060740424615</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.17710292352706</v>
+        <v>2.1323286728238</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.097632461768324</v>
+        <v>-9.172256212940422</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4606652189063003</v>
+        <v>-0.4905147193751391</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.611510313665351</v>
+        <v>-1.686134064837451</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.211838001915567</v>
+        <v>2.167063751212306</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.973053805430732</v>
+        <v>-9.04767755660283</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4096946118152043</v>
+        <v>-0.4395441122840436</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.611510313665351</v>
+        <v>-1.686134064837451</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.212977146471625</v>
+        <v>2.168202895768365</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.025949093475019</v>
+        <v>-9.100572844647116</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4282189528708114</v>
+        <v>-0.4580684533396506</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.606554967576905</v>
+        <v>-1.681178718749005</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.218584128286801</v>
+        <v>2.173809877583541</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.953815918187138</v>
+        <v>-9.028439669359235</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3936319785170226</v>
+        <v>-0.4234814789858614</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.606554967576905</v>
+        <v>-1.681178718749005</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.224317832525437</v>
+        <v>2.179543581822177</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.88244952557749</v>
+        <v>-8.957073276749588</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3748226838670288</v>
+        <v>-0.404672184335868</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.535188574967257</v>
+        <v>-1.609812326139357</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.257400405697361</v>
+        <v>2.212626154994101</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.788990491592266</v>
+        <v>-8.863614242764363</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3473225515858465</v>
+        <v>-0.3771720520546857</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.535188574967257</v>
+        <v>-1.609812326139357</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.247516924384453</v>
+        <v>2.202742673681193</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.778337310038834</v>
+        <v>-8.852961061210932</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3448958394638475</v>
+        <v>-0.3747453399326868</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.535188574967257</v>
+        <v>-1.609812326139357</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.24568236388508</v>
+        <v>2.20090811318182</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.680430271362344</v>
+        <v>-8.755054022534441</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3060333389667123</v>
+        <v>-0.3358828394355515</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.467202825106701</v>
+        <v>-1.541826576278801</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.286173498827953</v>
+        <v>2.241399248124693</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.656476730386386</v>
+        <v>-8.731100481558483</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2957834164308353</v>
+        <v>-0.3256329168996746</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.443249284130743</v>
+        <v>-1.517873035302843</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.301214129559021</v>
+        <v>2.256439878855761</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.392416792063589</v>
+        <v>-8.467040543235687</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2034197572634691</v>
+        <v>-0.2332692577323079</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.179189345807947</v>
+        <v>-1.253813096980047</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.446389776390946</v>
+        <v>2.401615525687686</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.685337168558751</v>
+        <v>-7.759960919730848</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.07662505847816536</v>
+        <v>0.04677555800932653</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.179189345807947</v>
+        <v>-1.253813096980047</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.443602742730645</v>
+        <v>2.398828492027385</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.64515287019256</v>
+        <v>-7.719776621364658</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.0930424017124829</v>
+        <v>0.06319290124364407</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.139005047441756</v>
+        <v>-1.213628798613856</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.468056945638201</v>
+        <v>2.423282694934941</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.481752999253198</v>
+        <v>-7.556376750425295</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1577691713089848</v>
+        <v>0.127919670840146</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9756051765023934</v>
+        <v>-1.050228927674493</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.565463689422576</v>
+        <v>2.520689438719316</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.248271777023599</v>
+        <v>-7.322895528195697</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2590860890386768</v>
+        <v>0.2292365885698375</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.7421239542727949</v>
+        <v>-0.8167477054448948</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.713476851598187</v>
+        <v>2.668702600894927</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.098605386016084</v>
+        <v>-7.173229137188182</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3160604351287235</v>
+        <v>0.2862109346598847</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.6492204630302589</v>
+        <v>-0.7238442142023589</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.76632673603075</v>
+        <v>2.72155248532749</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.966329912385198</v>
+        <v>-7.040953663557295</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2702314105882331</v>
+        <v>0.2403819101193938</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5169449893993723</v>
+        <v>-0.5915687405714722</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.746952806216436</v>
+        <v>2.702178555513176</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.810591579825456</v>
+        <v>-6.885215330997553</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3353418042997665</v>
+        <v>0.3054923038309272</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3612066568396307</v>
+        <v>-0.4358304080117307</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.843210866439918</v>
+        <v>2.798436615736658</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.725626913096136</v>
+        <v>-6.800250664268233</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3822340122151533</v>
+        <v>0.352384511746314</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2762419901103111</v>
+        <v>-0.3508657412824111</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.907096007701168</v>
+        <v>2.862321756997908</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.83121690286924</v>
+        <v>-6.905840654041338</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2120220867066926</v>
+        <v>0.1821725862378534</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3818319798834155</v>
+        <v>-0.4564557310555155</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.715766084238087</v>
+        <v>2.670991833534827</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.762982318243813</v>
+        <v>-6.83760606941591</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2878602624339499</v>
+        <v>0.2580107619651111</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3634166570108795</v>
+        <v>-0.4380404081829795</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.775359619838695</v>
+        <v>2.730585369135435</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.873530691357055</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.615042276836213</v>
+        <v>-6.689666028008311</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2271573563088221</v>
+        <v>0.1973078558399832</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3430957411023219</v>
+        <v>-0.4177194922744219</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.667673246695662</v>
+        <v>2.622898995992402</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.864816705103577</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.562072754582225</v>
+        <v>-6.636696505754323</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2396311789569392</v>
+        <v>0.2097816784881004</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2901262188483331</v>
+        <v>-0.364749970020433</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.690740973794577</v>
+        <v>2.645966723091317</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.857856093008484</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.396284558621934</v>
+        <v>-6.470908309794032</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2989858452459626</v>
+        <v>0.2691363447771233</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2901262188483331</v>
+        <v>-0.364749970020433</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.683780361699484</v>
+        <v>2.639006110996224</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.872318447389627</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.362921352143165</v>
+        <v>-6.437545103315263</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3267934822186129</v>
+        <v>0.2969439817497741</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2901262188483331</v>
+        <v>-0.364749970020433</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.698242716080627</v>
+        <v>2.653468465377367</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.866850567848822</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.254662215020644</v>
+        <v>-6.329285966192741</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3646292575268166</v>
+        <v>0.3347797570579778</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2901262188483331</v>
+        <v>-0.364749970020433</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.692774836539822</v>
+        <v>2.648000585836562</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.864348661859399</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.131371080203513</v>
+        <v>-6.205994831375611</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4114438054642462</v>
+        <v>0.3815943049954069</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1668350840312026</v>
+        <v>-0.2414588352033025</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.764247611440677</v>
+        <v>2.719473360737417</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.872049640096724</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.078674213072222</v>
+        <v>-6.153297964244319</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4402235305540878</v>
+        <v>0.4103740300852485</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1141382168999114</v>
+        <v>-0.1887619680720113</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.803566709956777</v>
+        <v>2.758792459253517</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.867830348443774</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.834908771088777</v>
+        <v>-5.909532522260875</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5335104156945163</v>
+        <v>0.503660915225677</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1141382168999114</v>
+        <v>-0.1887619680720113</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.799347418303828</v>
+        <v>2.754573167600568</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.86995466236379</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.745133098712305</v>
+        <v>-5.819756849884403</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5715449985651211</v>
+        <v>0.5416954980962818</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.05253877198560136</v>
+        <v>-0.1271625231577013</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.83843139917243</v>
+        <v>2.79365714846917</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.862696737347493</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.49528270476323</v>
+        <v>-5.569906455935328</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6642272311284532</v>
+        <v>0.6343777306596139</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.05253877198560136</v>
+        <v>-0.1271625231577013</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.831173474156132</v>
+        <v>2.786399223452872</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.866295860868141</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.319390612295798</v>
+        <v>-5.394014363467896</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7381831916360748</v>
+        <v>0.7083336911672355</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.05253877198560136</v>
+        <v>-0.1271625231577013</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.834772597676781</v>
+        <v>2.789998346973521</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.879623366922695</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.147944149273335</v>
+        <v>-5.222567900445433</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8200892828996138</v>
+        <v>0.7902397824307745</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1189076910368618</v>
+        <v>0.04428393986476181</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.950967981544812</v>
+        <v>2.906193730841552</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.878643844538992</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.067921862164214</v>
+        <v>-5.142545613336312</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.851118675359559</v>
+        <v>0.8212691748907202</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1989299781459827</v>
+        <v>0.1243062269738828</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.998001831426582</v>
+        <v>2.953227580723322</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.883338645593309</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.004286119930279</v>
+        <v>-5.078909871102377</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8812677733074501</v>
+        <v>0.851418272838611</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2625657203799173</v>
+        <v>0.1879419692078173</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.04087807782126</v>
+        <v>2.996103827118</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.864532904377105</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.910588801713884</v>
+        <v>-4.985212552885982</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8999409593778038</v>
+        <v>0.8700914589089648</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2625657203799173</v>
+        <v>0.1879419692078173</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.022072336605055</v>
+        <v>2.977298085901796</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.866275981001982</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.921091424779173</v>
+        <v>-4.995715175951271</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8974829867765657</v>
+        <v>0.8676334863077266</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2520630973146284</v>
+        <v>0.1774393461425284</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.01751383939076</v>
+        <v>2.972739588687499</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.870205294836802</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.848848856607979</v>
+        <v>-4.923472607780076</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9303093278798638</v>
+        <v>0.9004598274110247</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2520630973146284</v>
+        <v>0.1774393461425284</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.02144315322558</v>
+        <v>2.97666890252232</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.870883878754142</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.831135169730113</v>
+        <v>-4.905758920902211</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9380733865483499</v>
+        <v>0.9082238860795107</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2552444262115452</v>
+        <v>0.1806206750394452</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.02403053448107</v>
+        <v>2.97925628377781</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.867881949974136</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.722330284250386</v>
+        <v>-4.796954035422484</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9785934119602342</v>
+        <v>0.9487439114913951</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2552444262115452</v>
+        <v>0.1806206750394452</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.021028605701063</v>
+        <v>2.976254354997804</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.86946098698475</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.502309486213376</v>
+        <v>-4.576933237385473</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.068180768185653</v>
+        <v>1.038331267716813</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3964642712795254</v>
+        <v>0.3218405201074255</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.107339549752465</v>
+        <v>3.062565299049206</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.885355169786573</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.369441797150098</v>
+        <v>-4.444065548322196</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.137222026612787</v>
+        <v>1.107372526143948</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3964642712795254</v>
+        <v>0.3218405201074255</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.123233732554289</v>
+        <v>3.078459481851029</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.886501014226875</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.249268713785599</v>
+        <v>-4.323892464957697</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.186437104398888</v>
+        <v>1.156587603930049</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5166373546440244</v>
+        <v>0.4420136034719244</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.19648342701329</v>
+        <v>3.15170917631003</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576994</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.896589116788315</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.114015352455622</v>
+        <v>-4.18863910362772</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.250626551492319</v>
+        <v>1.22077705102348</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6518907159740015</v>
+        <v>0.5772669648019015</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.287723546372716</v>
+        <v>3.242949295669456</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.882626608189741</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.173890179813315</v>
+        <v>-4.248513930985412</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.212714111950668</v>
+        <v>1.182864611481829</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5920158886163094</v>
+        <v>0.5173921374442094</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.237836141359527</v>
+        <v>3.193061890656267</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.897915777423949</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.054069948902478</v>
+        <v>-4.128693700074575</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.275931373549211</v>
+        <v>1.246081873080372</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5920158886163094</v>
+        <v>0.5173921374442094</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.253125310593735</v>
+        <v>3.208351059890475</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.805559976746391</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.056539655364284</v>
+        <v>-4.131163406536381</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.18258769028693</v>
+        <v>1.152738189818091</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5895461821545032</v>
+        <v>0.5149224309824032</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.159287686039093</v>
+        <v>3.114513435335833</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.724821838231692</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.124909841688294</v>
+        <v>-4.199533592860392</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.074501477242628</v>
+        <v>1.044651976773789</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5988218811907181</v>
+        <v>0.5241981300186181</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.084114966946124</v>
+        <v>3.039340716242863</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.715258546863584</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.138697894535341</v>
+        <v>-4.213321645707438</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.0594229647357</v>
+        <v>1.029573464266861</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5988218811907181</v>
+        <v>0.5241981300186181</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.074551675578015</v>
+        <v>3.029777424874755</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.852289383555786</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.19421797042793</v>
+        <v>-4.268841721600028</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.174245771070867</v>
+        <v>1.144396270602028</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5988218811907181</v>
+        <v>0.5241981300186181</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.211582512270217</v>
+        <v>3.166808261566957</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.856856615547574</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.01874371063546</v>
+        <v>-4.093367461807558</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.249002706979642</v>
+        <v>1.219153206510803</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5988218811907181</v>
+        <v>0.5241981300186181</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.216149744262005</v>
+        <v>3.171375493558745</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.832598644308781</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.010819336050546</v>
+        <v>-4.085443087222644</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.227914485574815</v>
+        <v>1.198064985105976</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5988218811907181</v>
+        <v>0.5241981300186181</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.191891773023212</v>
+        <v>3.147117522319952</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.761136957710231</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.004541133480697</v>
+        <v>-4.079164884652795</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.158964080004204</v>
+        <v>1.129114579535365</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6051000837605671</v>
+        <v>0.5304763325884672</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.124197007966571</v>
+        <v>3.079422757263311</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.771309344142363</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.944688514276974</v>
+        <v>-4.019312265449072</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.193077514117826</v>
+        <v>1.163228013648987</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6051000837605671</v>
+        <v>0.5304763325884672</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.134369394398703</v>
+        <v>3.089595143695444</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.766255614716223</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.858445051250596</v>
+        <v>-3.933068802422694</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.222521169902238</v>
+        <v>1.192671669433399</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6051000837605671</v>
+        <v>0.5304763325884672</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.129315664972564</v>
+        <v>3.084541414269304</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.758031390160749</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.903751870649576</v>
+        <v>-3.978375621821674</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.196174217587171</v>
+        <v>1.166324717118332</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5642899207513363</v>
+        <v>0.4896661695792364</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.096605342611551</v>
+        <v>3.051831091908291</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.75357116580319</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.75858326319385</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.96885187823265</v>
+        <v>-4.007408726523975</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.170686087587043</v>
+        <v>1.155263348270513</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5642899207513363</v>
+        <v>0.4896661695792364</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.097157215644653</v>
+        <v>3.052382964941393</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.687855955085216</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.876041396781791</v>
+        <v>-4.072559802717207</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.137082972058753</v>
+        <v>1.058475609684586</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6571004022021957</v>
+        <v>0.4245150933860053</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.082116196406534</v>
+        <v>2.94256501111682</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.689729431009817</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.920430866111218</v>
+        <v>-4.116949272046634</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.121200660251582</v>
+        <v>1.042593297877416</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.612710932872768</v>
+        <v>0.3801256240565777</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.057355990733478</v>
+        <v>2.917804805443764</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.68480513952154</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.036972471216561</v>
+        <v>-4.233490877151977</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.069659726721168</v>
+        <v>0.9910523643470022</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4961693277674253</v>
+        <v>0.2635840189512349</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.982506736181995</v>
+        <v>2.842955550892281</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.690296435352207</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.076896565799133</v>
+        <v>-4.273414971734549</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.059181384718807</v>
+        <v>0.9805740223446404</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4961693277674253</v>
+        <v>0.2635840189512349</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.987998032012662</v>
+        <v>2.848446846722948</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.701793637120746</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.104676963700486</v>
+        <v>-4.301195369635901</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.059566427326805</v>
+        <v>0.9809590649526385</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4683889298660722</v>
+        <v>0.2358036210498818</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.98282699504039</v>
+        <v>2.843275809750676</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.5401493571214</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.223057636430624</v>
+        <v>-4.41957604236604</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8505698782354025</v>
+        <v>0.7719625158612364</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.401171077715096</v>
+        <v>0.1685857688989056</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.780852003750458</v>
+        <v>2.641300818460743</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.660299017840605</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.331671714873956</v>
+        <v>-4.528190120809371</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9272739075772756</v>
+        <v>0.8486665452031095</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.401171077715096</v>
+        <v>0.1685857688989056</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.901001664469663</v>
+        <v>2.761450479179949</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.674812043942928</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.296262676625813</v>
+        <v>-4.492781082561228</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9559505489788558</v>
+        <v>0.8773431866046897</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.401171077715096</v>
+        <v>0.1685857688989056</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.915514690571986</v>
+        <v>2.775963505282272</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.672231485285297</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.257879014067662</v>
+        <v>-4.454397420003077</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.968723455344485</v>
+        <v>0.8901160929703189</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4395547402732472</v>
+        <v>0.2069694314570568</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.935964329449245</v>
+        <v>2.796413144159531</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.668960514130599</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.080762684032496</v>
+        <v>-4.277281089967911</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.036299016203853</v>
+        <v>0.9576916538296871</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4395547402732472</v>
+        <v>0.2069694314570568</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.932693358294547</v>
+        <v>2.793142173004833</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.669643905892512</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.125854928866041</v>
+        <v>-4.322373334801457</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.018945510032348</v>
+        <v>0.940338147658182</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3776586971038574</v>
+        <v>0.145073388287667</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.896239124154826</v>
+        <v>2.756687938865112</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.663430881198926</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.946479507627274</v>
+        <v>-4.142997913562689</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.08448265383427</v>
+        <v>1.005875291460103</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.534435455274576</v>
+        <v>0.3018501464583857</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.984092154363672</v>
+        <v>2.844540969073958</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.644238336530516</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.99149372114788</v>
+        <v>-4.188012127083296</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.047284423757617</v>
+        <v>0.9686770613834506</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5040865599599714</v>
+        <v>0.2715012511437811</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.946690272506499</v>
+        <v>2.807139087216785</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.649929898869462</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.258498231420315</v>
+        <v>-4.455016637355731</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9461741819875884</v>
+        <v>0.8675668196134223</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3097235219170228</v>
+        <v>0.07713821310083252</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.835764012019676</v>
+        <v>2.696212826729961</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.649133820765963</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.359696012857488</v>
+        <v>-4.556214418792903</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9048989913092207</v>
+        <v>0.8262916289350546</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2413147083717037</v>
+        <v>0.008729399555513329</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.793922645788986</v>
+        <v>2.654371460499271</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64673378232028</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.353185046243175</v>
+        <v>-4.549703452178591</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9051033395092625</v>
+        <v>0.8264959771350964</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2413147083717037</v>
+        <v>0.008729399555513329</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.791522607343302</v>
+        <v>2.651971422053588</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.643258501528525</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.334146918535878</v>
+        <v>-4.530665324471293</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9092433098004262</v>
+        <v>0.8306359474262601</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1831310970405091</v>
+        <v>-0.04945421177568121</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.753137159752831</v>
+        <v>2.613585974463116</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.762552903162715</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.386662720810699</v>
+        <v>-4.583181126746114</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.007531390524689</v>
+        <v>0.9289240281505224</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1831310970405091</v>
+        <v>-0.04945421177568121</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.872431561387021</v>
+        <v>2.732880376097307</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.763386232148849</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.400529482144616</v>
+        <v>-4.597047888080032</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.002818014977255</v>
+        <v>0.9242106526030889</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1452731803066862</v>
+        <v>-0.08731212850950415</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.850550140332861</v>
+        <v>2.710998955043146</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.769394762545775</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.355725310604686</v>
+        <v>-4.552243716540102</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.026748213990153</v>
+        <v>0.9481408516159866</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1452731803066862</v>
+        <v>-0.08731212850950415</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.856558670729787</v>
+        <v>2.717007485440072</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.667344983822974</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.207982340369684</v>
+        <v>-4.404500746305099</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9837956233613534</v>
+        <v>0.9051882609871873</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3130805375415693</v>
+        <v>0.08049522872537901</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.855193306347916</v>
+        <v>2.715642121058202</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.670138605354455</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.291803561644382</v>
+        <v>-4.488321967579798</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.953060756382955</v>
+        <v>0.8744533940087889</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3130805375415693</v>
+        <v>0.08049522872537901</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.857986927879397</v>
+        <v>2.718435742589683</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.670800953746113</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.285650855591598</v>
+        <v>-4.482169261527013</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9561841871957271</v>
+        <v>0.877576824821561</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3192332435943536</v>
+        <v>0.08664793477816329</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.862340899902726</v>
+        <v>2.722789714613012</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.669881430486224</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.3024601537421</v>
+        <v>-4.498978559677515</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9485409446756365</v>
+        <v>0.8699335823014704</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.302423945443852</v>
+        <v>0.06983863662766165</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.851335797752535</v>
+        <v>2.711784612462821</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.736216984283045</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.240162154965978</v>
+        <v>-4.436680560901393</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.039795697982906</v>
+        <v>0.9611883356087403</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.347718209718294</v>
+        <v>0.1151329009021037</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.944847910114021</v>
+        <v>2.805296724824307</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.538508985997172</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.03837195730082</v>
+        <v>-4.234890363236235</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9228037787630965</v>
+        <v>0.8441964163889304</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5457364018874484</v>
+        <v>0.3131510930712581</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.865950827129641</v>
+        <v>2.726399641839927</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.608799218319347</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.089258669987014</v>
+        <v>-4.28577707592243</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9727393260107939</v>
+        <v>0.8941319636366278</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4948496892012539</v>
+        <v>0.2622643803850636</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.905709031840099</v>
+        <v>2.766157846550385</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.623426954435391</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.002647927337208</v>
+        <v>-4.199166333272623</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.02201135918676</v>
+        <v>0.9434039968125942</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5734754204064122</v>
+        <v>0.3408901115902218</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.967512206679238</v>
+        <v>2.827961021389524</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.621962935260062</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.062857225342492</v>
+        <v>-4.259375631277908</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9964636208093183</v>
+        <v>0.917856258435152</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5132661224011277</v>
+        <v>0.2806808135849373</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.929922608700739</v>
+        <v>2.790371423411025</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.620454553299991</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.986435178910566</v>
+        <v>-4.182953584845981</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.025524057422018</v>
+        <v>0.9469166950478511</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5132661224011277</v>
+        <v>0.2806808135849373</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.928414226740668</v>
+        <v>2.788863041450953</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.620317420735427</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.942062047271997</v>
+        <v>-4.138580453207412</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.043136177512881</v>
+        <v>0.9645288151387148</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5576392540396963</v>
+        <v>0.3250539452235059</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.954900973159245</v>
+        <v>2.815349787869531</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.614711214874017</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.964542398130882</v>
+        <v>-4.161060804066297</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.028537831307918</v>
+        <v>0.9499304689337513</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5576392540396963</v>
+        <v>0.3250539452235059</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.949294767297836</v>
+        <v>2.809743582008121</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.621092971901822</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.916886667569826</v>
+        <v>-4.113405073505241</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.053981880560145</v>
+        <v>0.9753745181859783</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6052949846007519</v>
+        <v>0.3727096757845615</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.984269962662274</v>
+        <v>2.84471877737256</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.625985345276547</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.816368509071071</v>
+        <v>-4.012886915006487</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.099081517334372</v>
+        <v>1.020474154960205</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7058131430995065</v>
+        <v>0.4732278342833161</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.049473231136251</v>
+        <v>2.909922045846537</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.612740017752419</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.800463179638719</v>
+        <v>-3.996981585574134</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.092198321583185</v>
+        <v>1.013590959209018</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6267004823902675</v>
+        <v>0.3941151735740772</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.98876030718658</v>
+        <v>2.849209121896866</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.616837720363048</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.755624778030321</v>
+        <v>-3.952143183965736</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.114231384837173</v>
+        <v>1.035624022463006</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.631243915335137</v>
+        <v>0.3986586065189467</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.99558406956413</v>
+        <v>2.856032884274416</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491705</v>
+        <v>3.817932354917052</v>
       </c>
       <c r="C1982" t="n">
         <v>2.620998659994126</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.775123234272329</v>
+        <v>-3.971641640207744</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.110592941971447</v>
+        <v>1.031985579597281</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5831592740552327</v>
+        <v>0.3505739652390424</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.970894224427266</v>
+        <v>2.831343039137551</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.82668474540596</v>
       </c>
       <c r="C1983" t="n">
         <v>2.626878262521963</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.730920397186428</v>
+        <v>-3.927438803121844</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.134153679333645</v>
+        <v>1.055546316959478</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6273621111411332</v>
+        <v>0.3947768023249428</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.003295529206643</v>
+        <v>2.863744343916929</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.62528826299121</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.738480063023475</v>
+        <v>-3.934998468958891</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.129539813468073</v>
+        <v>1.050932451093907</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6821655151509525</v>
+        <v>0.4495802063347621</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.034587572081782</v>
+        <v>2.895036386792068</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.67653602817425</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.580188645484203</v>
+        <v>-3.776707051419618</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.244104145666822</v>
+        <v>1.165496783292655</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6821655151509525</v>
+        <v>0.4495802063347621</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.085835337264822</v>
+        <v>2.946284151975108</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
         <v>2.674976732768503</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.372546641849727</v>
+        <v>-3.569065047785142</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.325601651714865</v>
+        <v>1.246994289340699</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8898075187854286</v>
+        <v>0.6572222099692383</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.208861244039761</v>
+        <v>3.069310058750046</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
         <v>2.669924961006773</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.321514549127199</v>
+        <v>-3.518032955062614</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.340962717042147</v>
+        <v>1.26235535466798</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9408396115079566</v>
+        <v>0.7082543026917663</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.234428727911547</v>
+        <v>3.094877542621833</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.687112365099478</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.256290367999993</v>
+        <v>-3.452808773935408</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.384239793585734</v>
+        <v>1.305632431211567</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.006063792635162</v>
+        <v>0.7734784838189719</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.290750640680576</v>
+        <v>3.151199455390862</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.683073337398759</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.218863347928859</v>
+        <v>-3.415381753864275</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.395171573913468</v>
+        <v>1.316564211539301</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.011315330664344</v>
+        <v>0.7787300218481535</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.289862535797365</v>
+        <v>3.150311350507651</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.684330129729999</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.238975003963568</v>
+        <v>-3.435493409898983</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.388383703830825</v>
+        <v>1.309776341456658</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.022342675661763</v>
+        <v>0.7897573668455727</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.297735735127057</v>
+        <v>3.158184549837343</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84488790075121</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.210561740863684</v>
+        <v>-3.407080146799099</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.560306780091989</v>
+        <v>1.481699417717823</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9633671129153341</v>
+        <v>0.7307818040991438</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.42290816850041</v>
+        <v>3.283356983210696</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>2.965000809969027</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.135779479838671</v>
+        <v>-3.332297885774087</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.710332593719811</v>
+        <v>1.631725231345645</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.038149373940347</v>
+        <v>0.8055640651241565</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.587890434333235</v>
+        <v>3.448339249043521</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
         <v>2.956708785982886</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.109695395574863</v>
+        <v>-3.306213801510279</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.712474203439194</v>
+        <v>1.633866841065027</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.038149373940347</v>
+        <v>0.8055640651241565</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.579598410347094</v>
+        <v>3.44004722505738</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.954901981566665</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.021817482465743</v>
+        <v>-3.218335888401158</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.745818564266621</v>
+        <v>1.667211201892455</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.154075016363698</v>
+        <v>0.9214897075475076</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.647346991384884</v>
+        <v>3.50779580609517</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.972456387293457</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.012925021072459</v>
+        <v>-3.209443427007875</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.766929954550726</v>
+        <v>1.688322592176559</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.154075016363698</v>
+        <v>0.9214897075475076</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.664901397111676</v>
+        <v>3.525350211821961</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945362</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.964311434698041</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.181401138042337</v>
+        <v>-3.377919543977753</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.691394555167359</v>
+        <v>1.612787192793192</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.126127180647117</v>
+        <v>0.8935418718309268</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.639987743086311</v>
+        <v>3.500436557796597</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.945581131885902</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.735144945412897</v>
+        <v>-2.931663351348313</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.851166729406997</v>
+        <v>1.77255936703283</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.031408510977484</v>
+        <v>0.7988232021612941</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.564426238472393</v>
+        <v>3.424875053182679</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.936245154382807</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.712423841729745</v>
+        <v>-2.90894224766516</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.850919193377162</v>
+        <v>1.772311831002996</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.031408510977484</v>
+        <v>0.7988232021612941</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.555090260969298</v>
+        <v>3.415539075679584</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.095151280233976</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.841625655023787</v>
+        <v>-3.038144060959203</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.958144593910714</v>
+        <v>1.879537231536548</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.902206697683442</v>
+        <v>0.6696213888672518</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.636475298844041</v>
+        <v>3.496924113554327</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.132229102727623</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.867500053497813</v>
+        <v>-3.064018459433228</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.98487265701475</v>
+        <v>1.906265294640584</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9471183063951831</v>
+        <v>0.7145329975789929</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.700500086564733</v>
+        <v>3.560948901275018</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.128904458717168</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.860445363282639</v>
+        <v>-3.056963769218055</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.984369889090365</v>
+        <v>1.905762526716199</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9541729966103569</v>
+        <v>0.7215876877941667</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.701408256683382</v>
+        <v>3.561857071393668</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>3.138910612361909</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.833494138956151</v>
+        <v>-3.030012544891567</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.005156532465702</v>
+        <v>1.926549170091535</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9690533426380761</v>
+        <v>0.7364680338218859</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.720342617944755</v>
+        <v>3.580791432655041</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.323013744506869</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.969447147012468</v>
+        <v>-3.165965552947883</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.134878461388135</v>
+        <v>2.056271099013968</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9690533426380761</v>
+        <v>0.7364680338218859</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.904445750089715</v>
+        <v>3.764894564800001</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.315130439409862</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.99185526481734</v>
+        <v>-3.188373670752755</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.118031909169179</v>
+        <v>2.039424546795013</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9690533426380761</v>
+        <v>0.7364680338218859</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.896562444992708</v>
+        <v>3.757011259702994</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.3171844389595</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.02007950039494</v>
+        <v>-3.216597906330355</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.108796214487777</v>
+        <v>2.03018885211361</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9870300950893847</v>
+        <v>0.7544447862731944</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.909402496013131</v>
+        <v>3.769851310723416</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
         <v>3.373438156681347</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.02952042628347</v>
+        <v>-3.226038832218885</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.161273561854212</v>
+        <v>2.082666199480045</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.109457212632776</v>
+        <v>0.8768719038165859</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.039112484261013</v>
+        <v>3.899561298971299</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
         <v>3.376329251226648</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.081794033619111</v>
+        <v>-3.278312439554527</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.143255213465256</v>
+        <v>2.06464785109109</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.057183605297135</v>
+        <v>0.8245982964809446</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.010639414404928</v>
+        <v>3.871088229115215</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.374441064120423</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.158124011220017</v>
+        <v>-3.354642417155433</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.110835035318669</v>
+        <v>2.032227672944503</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.057183605297135</v>
+        <v>0.8245982964809446</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.008751227298704</v>
+        <v>3.86920004200899</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.369261293723285</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.360377731544371</v>
+        <v>-3.556896137479786</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.02475377679179</v>
+        <v>1.946146414417623</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8549298849727813</v>
+        <v>0.6223445761565911</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.882219224706954</v>
+        <v>3.74266803941724</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.367695303933437</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.521946157071626</v>
+        <v>-3.718464563007041</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.95856041679104</v>
+        <v>1.879953054416874</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.728146961174902</v>
+        <v>0.4955616523587117</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.804583480638379</v>
+        <v>3.665032295348665</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389346</v>
+        <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
         <v>3.380768710799356</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.630246818941745</v>
+        <v>-3.82676522487716</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.928313558908911</v>
+        <v>1.849706196534745</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.728146961174902</v>
+        <v>0.4955616523587117</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.817656887504298</v>
+        <v>3.678105702214583</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.372773907582296</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.723394290245112</v>
+        <v>-3.919912696180527</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.883059767170504</v>
+        <v>1.804452404796338</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6053177498923692</v>
+        <v>0.372732441076179</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.735964557517718</v>
+        <v>3.596413372228004</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.371297948709298</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.751295077354585</v>
+        <v>-3.94781348329</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.870423493453717</v>
+        <v>1.791816131079551</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5707208257494344</v>
+        <v>0.3381355169332442</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.713730444158959</v>
+        <v>3.574179258869245</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.368062392686497</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.873821180057479</v>
+        <v>-4.070339585992894</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.818177496349758</v>
+        <v>1.739570133975592</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4481947230465405</v>
+        <v>0.2156094142303503</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.636979226514421</v>
+        <v>3.497428041224707</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
         <v>3.434768352277001</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.104335676243068</v>
+        <v>-4.300854082178483</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.792677657466027</v>
+        <v>1.71407029509186</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2176802268609518</v>
+        <v>-0.01490508195523843</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.565376488393572</v>
+        <v>3.425825303103858</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.575080071278848</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.361056494237892</v>
+        <v>-4.557574900173307</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.830301049269944</v>
+        <v>1.751693686895777</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.109265652717137</v>
+        <v>-0.1233196560990533</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.64063946290913</v>
+        <v>3.501088277619416</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.644060340424487</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.515042912014033</v>
+        <v>-4.711561317949448</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.837686751305127</v>
+        <v>1.759079388930961</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.109265652717137</v>
+        <v>-0.1233196560990533</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.70961973205477</v>
+        <v>3.570068546765055</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.630111542544608</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.464521008186367</v>
+        <v>-4.661039414121782</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.843946714956315</v>
+        <v>1.765339352582148</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.109265652717137</v>
+        <v>-0.1233196560990533</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.695670934174891</v>
+        <v>3.556119748885176</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.641982031600022</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.716996162194091</v>
+        <v>-4.913514568129506</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.754827142408639</v>
+        <v>1.676219780034472</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.109265652717137</v>
+        <v>-0.1233196560990533</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.707541423230305</v>
+        <v>3.56799023794059</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
         <v>3.643192566118966</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.009891918673503</v>
+        <v>-5.206410324608918</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.638879374335818</v>
+        <v>1.560272011961651</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.109265652717137</v>
+        <v>-0.1233196560990533</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.708751957749248</v>
+        <v>3.569200772459534</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251945</v>
       </c>
       <c r="C2021" t="n">
         <v>3.647314308346287</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.196556046808311</v>
+        <v>-5.393074452743726</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.568335465309216</v>
+        <v>1.489728102935049</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.08252668189257706</v>
+        <v>-0.1500586269236132</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.696830317481834</v>
+        <v>3.55727913219212</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.642392161082477</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.342576733722273</v>
+        <v>-5.539095139657689</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.50500504327982</v>
+        <v>1.426397680905654</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.07344359009872009</v>
+        <v>-0.1591417187174701</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.686458315141709</v>
+        <v>3.546907129851995</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.804596217781521</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.434290742831858</v>
+        <v>-5.630809148767273</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.630523496335031</v>
+        <v>1.551916133960864</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.07344359009872009</v>
+        <v>-0.1591417187174701</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.848662371840753</v>
+        <v>3.709111186551039</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
         <v>3.799442855745335</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.465942401891827</v>
+        <v>-5.662460807827243</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.612709470674857</v>
+        <v>1.53410210830069</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.06827513285427989</v>
+        <v>-0.1643101759619103</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.840407935457903</v>
+        <v>3.700856750168189</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.809672273313826</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.547877220160711</v>
+        <v>-5.744395626096126</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.590164960935795</v>
+        <v>1.511557598561629</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.0583403872671997</v>
+        <v>-0.1742449215489905</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.844676505674146</v>
+        <v>3.705125320384432</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.818597911769729</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.649853342409118</v>
+        <v>-5.846371748344533</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.558300150492335</v>
+        <v>1.479692788118168</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.04363573498120787</v>
+        <v>-0.2762210437973981</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.792416470781004</v>
+        <v>3.65286528549129</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.810750799013904</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.539847058931897</v>
+        <v>-5.736365464867312</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.594455551127398</v>
+        <v>1.515848188753232</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.02043116306393267</v>
+        <v>-0.2530164718801229</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.798492101175545</v>
+        <v>3.658940915885831</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
         <v>3.815000809735878</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.396787483190971</v>
+        <v>-5.593305889126386</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.655929392145743</v>
+        <v>1.577322029771577</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.01241773647395339</v>
+        <v>-0.2450030452901436</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.807550167851506</v>
+        <v>3.667998982561792</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.779176473537764</v>
+        <v>3.822261692618414</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.095340757719133</v>
+        <v>-5.291859163654548</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.740683746136364</v>
+        <v>1.705161602842848</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2890289889978839</v>
+        <v>0.05644368018169366</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.952593866936494</v>
+        <v>3.856127900727431</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.780147651290475</v>
+        <v>3.823232870371125</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.119931001954317</v>
+        <v>-5.316449407889732</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.731818826195001</v>
+        <v>1.696296682901485</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2890289889978839</v>
+        <v>0.05644368018169366</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.953565044689205</v>
+        <v>3.857099078480141</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.78099055567023</v>
+        <v>3.82407577475088</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.068892625947797</v>
+        <v>-5.265411031883212</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.753077080977365</v>
+        <v>1.717554937683849</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2890289889978839</v>
+        <v>0.05644368018169366</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.954407949068961</v>
+        <v>3.857941982859897</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.800028654544376</v>
+        <v>3.843113873625026</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.027753331081166</v>
+        <v>-5.224271737016581</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.788570897798162</v>
+        <v>1.753048754504646</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3301682838645147</v>
+        <v>0.09758297504832447</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.998129624863084</v>
+        <v>3.901663658654021</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.61621265066831</v>
+        <v>3.65929786974896</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.931118419062526</v>
+        <v>-5.127636824997941</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.643408858729553</v>
+        <v>1.607886715436037</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4268031958831546</v>
+        <v>0.1942178870669644</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.872294568198203</v>
+        <v>3.775828601989139</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.619714694742274</v>
+        <v>3.662799913822925</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.061699153593368</v>
+        <v>-5.258217559528783</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.59467860899118</v>
+        <v>1.559156465697664</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2962224613523121</v>
+        <v>0.0636371525361219</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.797448171553662</v>
+        <v>3.700982205344598</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.604141513818357</v>
+        <v>3.647226732899007</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.897202819402406</v>
+        <v>-5.093721225337822</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.644903961743648</v>
+        <v>1.609381818450131</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.460718795543274</v>
+        <v>0.2281334867270838</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.880572791144322</v>
+        <v>3.784106824935258</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.603329224254787</v>
+        <v>3.646414443335437</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.924572752086839</v>
+        <v>-5.121091158022254</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.633143699106304</v>
+        <v>1.597621555812788</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.460718795543274</v>
+        <v>0.2281334867270838</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.879760501580751</v>
+        <v>3.783294535371688</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.613198003379859</v>
+        <v>3.656283222460509</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.934957946976728</v>
+        <v>-5.131476352912143</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.638858400275421</v>
+        <v>1.603336256981905</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4503336006533847</v>
+        <v>0.2177482918371945</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.88339816377189</v>
+        <v>3.786932197562826</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.684035009156284</v>
+        <v>3.727120228236934</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.953546105698953</v>
+        <v>-5.150064511634368</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.702260142562956</v>
+        <v>1.66673799926944</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4317454419311593</v>
+        <v>0.1991601331149691</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.94308227431498</v>
+        <v>3.846616308105916</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.680904019974583</v>
+        <v>3.723989239055233</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.953844652394989</v>
+        <v>-5.150363058330404</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.69900973470284</v>
+        <v>1.663487591409324</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4314468952351234</v>
+        <v>0.1988615864189332</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.939772157115657</v>
+        <v>3.843306190906593</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.685434914913974</v>
+        <v>3.728520133994624</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.853021518704561</v>
+        <v>-5.049539924639976</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.743869883118403</v>
+        <v>1.708347739824887</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4439111107194773</v>
+        <v>0.211325801903287</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.951781581345661</v>
+        <v>3.855315615136597</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.685564168392518</v>
+        <v>3.728649387473168</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.662240157952154</v>
+        <v>-4.858758563887569</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.820311680897909</v>
+        <v>1.784789537604393</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6346924714718847</v>
+        <v>0.4021071626556944</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.066379651275649</v>
+        <v>3.969913685066585</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.665401014130114</v>
+        <v>3.708486233210764</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.643723303910334</v>
+        <v>-4.840241709845749</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.807555268252234</v>
+        <v>1.772033124958717</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6476226008970929</v>
+        <v>0.4150372920809026</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.05397457466837</v>
+        <v>3.957508608459306</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912983</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.700367950742173</v>
+        <v>3.743453169822823</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.588392716008571</v>
+        <v>-4.784911121943987</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.864654440024997</v>
+        <v>1.829132296731481</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.702953188798855</v>
+        <v>0.4703678799826648</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.122139864021486</v>
+        <v>4.025673897812422</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.743767956539893</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.69405451864361</v>
+        <v>3.73713973772426</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.576338589095609</v>
+        <v>-4.772856995031024</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.86316265869162</v>
+        <v>1.827640515398103</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7150073157118179</v>
+        <v>0.4824220068956276</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.123058908070702</v>
+        <v>4.026592941861638</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811007</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.695935148827746</v>
+        <v>3.739020367908396</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.617493708663829</v>
+        <v>-4.814012114599245</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.848581241048467</v>
+        <v>1.813059097754951</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6738521961435969</v>
+        <v>0.4412668873274067</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.100246466513904</v>
+        <v>4.00378050030484</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382918</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.708786174705629</v>
+        <v>3.751871393786279</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.514613119135237</v>
+        <v>-4.711131525070652</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.902584502737787</v>
+        <v>1.867062359444271</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7767327856721898</v>
+        <v>0.5441474768559995</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.174825846108943</v>
+        <v>4.078359879899879</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760312</v>
+        <v>3.646857607760314</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.728988844879223</v>
+        <v>3.772074063959873</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.746213512304737</v>
+        <v>-4.942731918240153</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.830147015643581</v>
+        <v>1.794624872350065</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7767327856721898</v>
+        <v>0.5441474768559995</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.195028516282537</v>
+        <v>4.098562550073473</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781703</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.728988844879223</v>
+        <v>3.772074063959873</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.764286020596349</v>
+        <v>-4.960804426531764</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.822918012326936</v>
+        <v>1.78739586903342</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7767327856721898</v>
+        <v>0.5441474768559995</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.195028516282537</v>
+        <v>4.098562550073473</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082832</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.689240758472689</v>
+        <v>3.73232597755334</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.939392853172794</v>
+        <v>-5.135911259108209</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.713127192889825</v>
+        <v>1.677605049596309</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7767327856721898</v>
+        <v>0.5441474768559995</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.155280429876004</v>
+        <v>4.058814463666939</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.696263377469629</v>
+        <v>3.73934859655028</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.908106832632338</v>
+        <v>-5.030031400961291</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.732664220102947</v>
+        <v>1.726979611852016</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8080188062126452</v>
+        <v>0.6500273350029173</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.181074661197217</v>
+        <v>4.12936499755203</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677822</v>
+        <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.795434377042534</v>
+        <v>3.838519596123184</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.755081440519054</v>
+        <v>-4.877006008848007</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.893045376521165</v>
+        <v>1.887360768270234</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9610441983259294</v>
+        <v>0.8030527271162015</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.372060896038092</v>
+        <v>4.320351232392905</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073881</v>
+        <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.982900601950826</v>
+        <v>4.025985821031476</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.783388754392324</v>
+        <v>-4.905313322721277</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.06918867588015</v>
+        <v>2.063504067629218</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9610441983259294</v>
+        <v>0.8030527271162015</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.559527120946384</v>
+        <v>4.507817457301197</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903166</v>
+        <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.952303553304908</v>
+        <v>3.995388772385558</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.949981979505846</v>
+        <v>-5.071906547834799</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.971954337188823</v>
+        <v>1.966269728937891</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.794450973212407</v>
+        <v>0.6364595020026791</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.428974137232353</v>
+        <v>4.377264473587166</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568381</v>
+        <v>3.708202704568382</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.955979955966626</v>
+        <v>3.999065175047276</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.776917600123546</v>
+        <v>-4.898842168452499</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.04485649160346</v>
+        <v>2.039171883352529</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.794450973212407</v>
+        <v>0.6364595020026791</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.432650539894071</v>
+        <v>4.380940876248884</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682202</v>
+        <v>3.740601586682204</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.953598011090121</v>
+        <v>3.996683230170771</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.74767161966785</v>
+        <v>-4.869596187996803</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.054172938909234</v>
+        <v>2.048488330658303</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.794450973212407</v>
+        <v>0.6364595020026791</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.430268595017566</v>
+        <v>4.378558931372379</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539105</v>
+        <v>3.699424827539107</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.950891250247756</v>
+        <v>3.993976469328406</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.854597167545701</v>
+        <v>-4.976521735874654</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.008695958915729</v>
+        <v>2.003011350664798</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6875254253345556</v>
+        <v>0.5295339541248277</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.36340650544849</v>
+        <v>4.311696841803303</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983735</v>
+        <v>3.689962785983737</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.95232005239099</v>
+        <v>3.995405271471641</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.99961572605295</v>
+        <v>-5.121540294381902</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.952117337656063</v>
+        <v>1.946432729405132</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5425068668273071</v>
+        <v>0.3845153956175792</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.277824172487375</v>
+        <v>4.226114508842189</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969747</v>
+        <v>3.711872614969749</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.052251291648743</v>
+        <v>4.095336510729394</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.117957491837667</v>
+        <v>-5.23988206016662</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.00471187059993</v>
+        <v>1.999027262348998</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5531929053901972</v>
+        <v>0.3952014341804693</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.384167034882862</v>
+        <v>4.332457371237675</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073537</v>
+        <v>3.714899237073539</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.050036988774682</v>
+        <v>4.093122207855332</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.169367914158375</v>
+        <v>-5.291292482487328</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.981933398797585</v>
+        <v>1.976248790546654</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5531929053901972</v>
+        <v>0.3952014341804693</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.3819527320088</v>
+        <v>4.330243068363614</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720064</v>
+        <v>3.704778134720065</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.049940116848972</v>
+        <v>4.093025335929622</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.248787365366127</v>
+        <v>-5.370711933695079</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.950068746388774</v>
+        <v>1.944384138137843</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5531929053901972</v>
+        <v>0.3952014341804693</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.38185586008309</v>
+        <v>4.330146196437903</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581131</v>
+        <v>3.736825137581133</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.049934010407015</v>
+        <v>4.093019229487665</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.344250363283344</v>
+        <v>-5.466174931612297</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.91187744077993</v>
+        <v>1.906192832528999</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5531929053901972</v>
+        <v>0.3952014341804693</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.381849753641133</v>
+        <v>4.330140089995947</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500733</v>
+        <v>3.715393145500735</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.048030406969626</v>
+        <v>4.091115626050276</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.384270361327128</v>
+        <v>-5.506194929656081</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.893965838125028</v>
+        <v>1.888281229874096</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.5131729073464133</v>
+        <v>0.3551814361366855</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.355934151377474</v>
+        <v>4.304224487732287</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636268</v>
+        <v>3.73610959863627</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.053764224717352</v>
+        <v>4.096849443798003</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.439639523459322</v>
+        <v>-5.561564091788274</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.877551991019877</v>
+        <v>1.871867382768945</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.5131729073464133</v>
+        <v>0.3551814361366855</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.3616679691252</v>
+        <v>4.309958305480014</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396012</v>
+        <v>3.736843055396013</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.053302588060285</v>
+        <v>4.096387807140935</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.485077303290149</v>
+        <v>-5.607001871619102</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.858915242430479</v>
+        <v>1.853230634179547</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.4703279166682536</v>
+        <v>0.3123364454585258</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.335499338061238</v>
+        <v>4.283789674416052</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396421</v>
+        <v>3.790292685396422</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.073176980910604</v>
+        <v>4.116262199991255</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.401851846442485</v>
+        <v>-5.523776414771437</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.912079818019864</v>
+        <v>1.906395209768932</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.4703279166682536</v>
+        <v>0.3123364454585258</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.355373730911557</v>
+        <v>4.303664067266371</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299175</v>
+        <v>3.794507029299177</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.056877681435332</v>
+        <v>4.099962900515982</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.225561621837177</v>
+        <v>-5.34748619016613</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.966296608386715</v>
+        <v>1.960612000135783</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.4703279166682536</v>
+        <v>0.3123364454585258</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.339074431436285</v>
+        <v>4.287364767791098</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590411</v>
+        <v>3.794725278590412</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.059308630899378</v>
+        <v>4.102393849980028</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.042349958704082</v>
+        <v>-5.164274527033035</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.042012223103998</v>
+        <v>2.036327614853067</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.4703279166682536</v>
+        <v>0.3123364454585258</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.341505380900331</v>
+        <v>4.289795717255144</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.785445234918883</v>
+        <v>3.854781583667224</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.135729644065447</v>
+        <v>4.261204660323669</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.042349958704082</v>
+        <v>-5.164274527033035</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.042012223103998</v>
+        <v>2.036327614853067</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.4703279166682536</v>
+        <v>0.3123364454585258</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.128793441051815</v>
+        <v>4.254268457310037</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240826.xlsx
+++ b/tame_output/ON/bt/strategyON_20240826.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>24.2%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>87.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>114.5%</t>
+          <t>89.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.3%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.1%</t>
+          <t>124.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-604.7%</t>
+          <t>-597.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.3%</t>
+          <t>-46.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>437.8%</t>
+          <t>427.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-678.0%</t>
+          <t>-685.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-242.3%</t>
+          <t>-239.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-172.6%</t>
+          <t>-175.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-236.2%</t>
+          <t>-228.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>-309.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-192.8%</t>
+          <t>-200.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-142.1%</t>
+          <t>-137.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-45.8%</t>
         </is>
       </c>
     </row>
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.2888670980769374</v>
+        <v>0.3634908492490375</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.23776058702997</v>
+        <v>3.26761008749881</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.63294885866874</v>
+        <v>1.70757260984084</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.102339487314187</v>
+        <v>4.147113738017447</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.1651726125211033</v>
+        <v>0.2397963636932034</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.223223877305178</v>
+        <v>3.253073377774018</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.63294885866874</v>
+        <v>1.70757260984084</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.137280571811729</v>
+        <v>4.182054822514989</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.1702102032486899</v>
+        <v>0.2448339544207899</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.223816353781551</v>
+        <v>3.253665854250391</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.688593314935058</v>
+        <v>1.763217066107158</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.169244685756857</v>
+        <v>4.214018936460117</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.08698383145936689</v>
+        <v>-0.01236008028726682</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.099685121522065</v>
+        <v>3.129534621990905</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.431399280227001</v>
+        <v>1.506023031399101</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.99367464655576</v>
+        <v>4.03844889725902</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.152751221508779</v>
+        <v>-0.07812747033667888</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.074395774632771</v>
+        <v>3.104245275101611</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.431399280227001</v>
+        <v>1.506023031399101</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.99469225568623</v>
+        <v>4.03946650638949</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.3851221356704537</v>
+        <v>-0.3104983844983536</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.972075440955857</v>
+        <v>3.001924941424697</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.431399280227001</v>
+        <v>1.506023031399101</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.985320287673986</v>
+        <v>4.030094538377246</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.4668940360982053</v>
+        <v>-0.3922702849261053</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.929449406739994</v>
+        <v>2.959298907208834</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.458434853633138</v>
+        <v>1.533058604805237</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.991624357672906</v>
+        <v>4.036398608376166</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.534103143970083</v>
+        <v>-0.4594793927979829</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.907331080424945</v>
+        <v>2.937180580893785</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.458434853633138</v>
+        <v>1.533058604805237</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.996389674506609</v>
+        <v>4.041163925209869</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.5227139073152816</v>
+        <v>-0.4480901561431815</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.909711571206106</v>
+        <v>2.939561071674946</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.469824090287939</v>
+        <v>1.544447841460039</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.00104801261873</v>
+        <v>4.045822263321989</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.7751918017346875</v>
+        <v>-0.7005680505625875</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.806647304943407</v>
+        <v>2.836496805412247</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.217346195868533</v>
+        <v>1.291969947040633</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.847488167472149</v>
+        <v>3.89226241817541</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.065323468340119</v>
+        <v>-0.9906997171680189</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.690460854900156</v>
+        <v>2.720310355368996</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.241427990608713</v>
+        <v>1.316051741780813</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.861803460915179</v>
+        <v>3.906577711618439</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.273327526693196</v>
+        <v>-1.198703775521096</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.612151376112851</v>
+        <v>2.642000876581691</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.241427990608713</v>
+        <v>1.316051741780813</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.866695605469104</v>
+        <v>3.911469856172364</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.335505937854166</v>
+        <v>-1.260882186682066</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.582361467986451</v>
+        <v>2.612210968455291</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.179249579447743</v>
+        <v>1.253873330619843</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.82447001511051</v>
+        <v>3.86924426581377</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.701574664998819</v>
+        <v>-1.626950913826719</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.429018276435039</v>
+        <v>2.458867776903879</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.81318085230309</v>
+        <v>0.88780460347519</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.597913078130168</v>
+        <v>3.642687328833428</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.910065446450503</v>
+        <v>-1.835441695278403</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.365960253593133</v>
+        <v>2.395809754061973</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.6046900708514056</v>
+        <v>0.6793138220235055</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.493156898997925</v>
+        <v>3.537931149701186</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.157266631215725</v>
+        <v>-2.082642880043625</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.275178530095613</v>
+        <v>2.305028030564453</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.624843424350218</v>
+        <v>0.699467175522318</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.513347661505781</v>
+        <v>3.558121912209042</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.649651659239822</v>
+        <v>-2.575027908067722</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.079330910929706</v>
+        <v>2.109180411398547</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.1324583963261213</v>
+        <v>0.2070821474982212</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.219023036735056</v>
+        <v>3.263797287438316</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.034832050169894</v>
+        <v>-2.960208298997795</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.923801293370541</v>
+        <v>1.953650793839381</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.1324583963261213</v>
+        <v>0.2070821474982212</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.217565575547919</v>
+        <v>3.262339826251179</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.284702730184476</v>
+        <v>-3.210078979012376</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.825622144819325</v>
+        <v>1.855471645288164</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.1687211161565845</v>
+        <v>0.2433448673286845</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.241092330900813</v>
+        <v>3.285866581604073</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.491214507071497</v>
+        <v>-3.416590755899398</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.739123492720774</v>
+        <v>1.768972993189614</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.03779066073043696</v>
+        <v>0.036833090441663</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.113291323424858</v>
+        <v>3.158065574128118</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.810558582151998</v>
+        <v>-3.735934830979899</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.613158789388833</v>
+        <v>1.643008289857673</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.03779066073043696</v>
+        <v>0.036833090441663</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.115064250125117</v>
+        <v>3.159838500828378</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.196768413427773</v>
+        <v>-4.122144662255674</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.445007744345927</v>
+        <v>1.474857244814767</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.1285636004478803</v>
+        <v>-0.05393984927578033</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.046933373762056</v>
+        <v>3.091707624465316</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.431462407560326</v>
+        <v>-4.356838656388226</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.339414921694997</v>
+        <v>1.369264422163837</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.1222273332186251</v>
+        <v>-0.04760358204652515</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.0390199091017</v>
+        <v>3.08379415980496</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.767125054790778</v>
+        <v>-4.692501303618679</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.203730454458781</v>
+        <v>1.233579954927621</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.1901583187075299</v>
+        <v>-0.11553456753543</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.996841909464322</v>
+        <v>3.041616160167582</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.84356938499365</v>
+        <v>-4.76894563382155</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.179640282611874</v>
+        <v>1.209489783080714</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.109712809613868</v>
+        <v>-0.03508905844176807</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.051596775154761</v>
+        <v>3.096371025858021</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.208696767632397</v>
+        <v>-5.134073016460297</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.032843844562207</v>
+        <v>1.062693345031047</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.4060235939128806</v>
+        <v>-0.3313998427407806</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.873064819581185</v>
+        <v>2.917839070284444</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.617285544813075</v>
+        <v>-5.542661793640976</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8681698777046942</v>
+        <v>0.8980193781735339</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.814612371093559</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.626673097287537</v>
+        <v>2.671447347990797</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.73104595683594</v>
+        <v>-5.656422205663841</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.8178511453670088</v>
+        <v>0.8477006458358489</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.814612371093559</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.621858529758997</v>
+        <v>2.666632780462257</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.147437831122938</v>
+        <v>-6.072814079950838</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6492884462610871</v>
+        <v>0.6791379467299272</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.814612371093559</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.619852580367874</v>
+        <v>2.664626831071135</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.508611460939925</v>
+        <v>-6.433987709767826</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.515077685002971</v>
+        <v>0.5449271854718107</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.814612371093559</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.630111271036554</v>
+        <v>2.674885521739814</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.851869980582944</v>
+        <v>-6.777246229410845</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3738738422914589</v>
+        <v>0.4037233427602986</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.814612371093559</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.626210836182249</v>
+        <v>2.670985086885509</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.900072797825288</v>
+        <v>-6.825449046653189</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3529976354495221</v>
+        <v>0.3828471359183618</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.814612371093559</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.62461575623725</v>
+        <v>2.669390006940509</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.196734139635486</v>
+        <v>-7.122110388463386</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2381120746546515</v>
+        <v>0.2679615751234912</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.8833555068274376</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.58714885072613</v>
+        <v>2.631923101429391</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.383453847944788</v>
+        <v>-7.308830096772689</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1593978867965271</v>
+        <v>0.1892473872653668</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.8833555068274376</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.583122546191728</v>
+        <v>2.627896796894988</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.76645523668742</v>
+        <v>-7.69183148551532</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.006095229977890693</v>
+        <v>0.03594473044673041</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.8833555068274376</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.583020444870144</v>
+        <v>2.627794695573404</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.770941681888808</v>
+        <v>-7.696317930716709</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.0068721678687651</v>
+        <v>0.03672166833760526</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.8878419520288263</v>
+        <v>-0.8132182008567264</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.58290009372074</v>
+        <v>2.627674344424</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.130472004392811</v>
+        <v>-8.055848253220711</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1315896578347857</v>
+        <v>-0.1017401573659455</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.8878419520288263</v>
+        <v>-0.8132182008567264</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.588250397018791</v>
+        <v>2.63302464772205</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.180821067847033</v>
+        <v>-8.106197316674933</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1438132632592968</v>
+        <v>-0.1139637627904571</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.9381910154830484</v>
+        <v>-0.8635672643109484</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.565956978903435</v>
+        <v>2.610731229606695</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.278440345268429</v>
+        <v>-8.203816594096329</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1798192236060863</v>
+        <v>-0.1499697231372465</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.035810292904445</v>
+        <v>-0.9611865417323451</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.510427163072366</v>
+        <v>2.555201413775626</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.332511844776787</v>
+        <v>-8.257888093604688</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1985542670878577</v>
+        <v>-0.168704766619018</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.089881792412804</v>
+        <v>-1.015258041240704</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.480877819688923</v>
+        <v>2.525652070392182</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.536770020106651</v>
+        <v>-8.462146268934552</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2747443401011607</v>
+        <v>-0.2448948396323209</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.217520737026793</v>
+        <v>-1.142896985854693</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.409807650039171</v>
+        <v>2.454581900742431</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.570422858615125</v>
+        <v>-8.495799107443025</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.283722921020114</v>
+        <v>-0.2538734205512743</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.317934104943831</v>
+        <v>-1.243310353771731</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.354042183773385</v>
+        <v>2.398816434476645</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.709508973233982</v>
+        <v>-8.634885222061882</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3239856653742361</v>
+        <v>-0.294136164905396</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.457020219562688</v>
+        <v>-1.382396468390588</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.285962216495492</v>
+        <v>2.330736467198752</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608598</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.884633390620525</v>
+        <v>-8.810009639448426</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3794802115813365</v>
+        <v>-0.3496307111124968</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.632144636949231</v>
+        <v>-1.557520885777131</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.195442786811082</v>
+        <v>2.240217037514342</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.119085484635015</v>
+        <v>-9.044461733462915</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4804802140887285</v>
+        <v>-0.4506307136198884</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.632144636949231</v>
+        <v>-1.557520885777131</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.188223621909486</v>
+        <v>2.232997872612747</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.223460215661461</v>
+        <v>-9.148836464489362</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5289022972732833</v>
+        <v>-0.4990527968044431</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.736519367975677</v>
+        <v>-1.661895616803577</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.118926592519643</v>
+        <v>2.163700843222903</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.385973681360046</v>
+        <v>-9.311349930187946</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5927918937141605</v>
+        <v>-0.5629423932453208</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.834152798394364</v>
+        <v>-1.759529047222264</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.061462324106987</v>
+        <v>2.106236574810247</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.512010474728335</v>
+        <v>-9.437386723556235</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6405128824323616</v>
+        <v>-0.6106633819635219</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.808901175584622</v>
+        <v>-1.734277424412522</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.079307026421947</v>
+        <v>2.124081277125207</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.454938702832404</v>
+        <v>-9.380314951660305</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6136938379875883</v>
+        <v>-0.5838443375187485</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.808901175584622</v>
+        <v>-1.734277424412522</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.083297362108348</v>
+        <v>2.128071612811608</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.596610544556524</v>
+        <v>-9.521986793384425</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6718378015759781</v>
+        <v>-0.6419883011071383</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.808901175584622</v>
+        <v>-1.734277424412522</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.081822135209606</v>
+        <v>2.126596385912866</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.54701970013169</v>
+        <v>-9.472395948959591</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6369480536411722</v>
+        <v>-0.6070985531723325</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.759310331159788</v>
+        <v>-1.684686579987688</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.126630052029379</v>
+        <v>2.171404302732639</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.398101365659834</v>
+        <v>-9.323477614487734</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5904318534991124</v>
+        <v>-0.5605823530302727</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.728060740424615</v>
+        <v>-1.653436989252515</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.1323286728238</v>
+        <v>2.17710292352706</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.172256212940422</v>
+        <v>-9.097632461768324</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4905147193751391</v>
+        <v>-0.4606652189063003</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.686134064837451</v>
+        <v>-1.611510313665351</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.167063751212306</v>
+        <v>2.211838001915567</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.04767755660283</v>
+        <v>-8.973053805430732</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4395441122840436</v>
+        <v>-0.4096946118152043</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.686134064837451</v>
+        <v>-1.611510313665351</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.168202895768365</v>
+        <v>2.212977146471625</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.100572844647116</v>
+        <v>-9.025949093475019</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4580684533396506</v>
+        <v>-0.4282189528708114</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.681178718749005</v>
+        <v>-1.606554967576905</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.173809877583541</v>
+        <v>2.218584128286801</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.028439669359235</v>
+        <v>-8.953815918187138</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4234814789858614</v>
+        <v>-0.3936319785170226</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.681178718749005</v>
+        <v>-1.606554967576905</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.179543581822177</v>
+        <v>2.224317832525437</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.957073276749588</v>
+        <v>-8.88244952557749</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.404672184335868</v>
+        <v>-0.3748226838670288</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.609812326139357</v>
+        <v>-1.535188574967257</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.212626154994101</v>
+        <v>2.257400405697361</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.863614242764363</v>
+        <v>-8.788990491592266</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3771720520546857</v>
+        <v>-0.3473225515858465</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.609812326139357</v>
+        <v>-1.535188574967257</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.202742673681193</v>
+        <v>2.247516924384453</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.852961061210932</v>
+        <v>-8.778337310038834</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3747453399326868</v>
+        <v>-0.3448958394638475</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.609812326139357</v>
+        <v>-1.535188574967257</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.20090811318182</v>
+        <v>2.24568236388508</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.755054022534441</v>
+        <v>-8.680430271362344</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3358828394355515</v>
+        <v>-0.3060333389667123</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.541826576278801</v>
+        <v>-1.467202825106701</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.241399248124693</v>
+        <v>2.286173498827953</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.731100481558483</v>
+        <v>-8.656476730386386</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3256329168996746</v>
+        <v>-0.2957834164308353</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.517873035302843</v>
+        <v>-1.443249284130743</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.256439878855761</v>
+        <v>2.301214129559021</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.467040543235687</v>
+        <v>-8.392416792063589</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2332692577323079</v>
+        <v>-0.2034197572634691</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.253813096980047</v>
+        <v>-1.179189345807947</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.401615525687686</v>
+        <v>2.446389776390946</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.759960919730848</v>
+        <v>-7.685337168558751</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.04677555800932653</v>
+        <v>0.07662505847816536</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.253813096980047</v>
+        <v>-1.179189345807947</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.398828492027385</v>
+        <v>2.443602742730645</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.719776621364658</v>
+        <v>-7.64515287019256</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.06319290124364407</v>
+        <v>0.0930424017124829</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.213628798613856</v>
+        <v>-1.139005047441756</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.423282694934941</v>
+        <v>2.468056945638201</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.556376750425295</v>
+        <v>-7.481752999253198</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.127919670840146</v>
+        <v>0.1577691713089848</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.050228927674493</v>
+        <v>-0.9756051765023934</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.520689438719316</v>
+        <v>2.565463689422576</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.322895528195697</v>
+        <v>-7.248271777023599</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2292365885698375</v>
+        <v>0.2590860890386768</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8167477054448948</v>
+        <v>-0.7421239542727949</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.668702600894927</v>
+        <v>2.713476851598187</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.173229137188182</v>
+        <v>-7.098605386016084</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2862109346598847</v>
+        <v>0.3160604351287235</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7238442142023589</v>
+        <v>-0.6492204630302589</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.72155248532749</v>
+        <v>2.76632673603075</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.040953663557295</v>
+        <v>-6.966329912385198</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2403819101193938</v>
+        <v>0.2702314105882331</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5915687405714722</v>
+        <v>-0.5169449893993723</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.702178555513176</v>
+        <v>2.746952806216436</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.78471879410595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.885215330997553</v>
+        <v>-6.906164987058266</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3054923038309272</v>
+        <v>0.2971124414066422</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4358304080117307</v>
+        <v>-0.4567800640724407</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.798436615736658</v>
+        <v>2.785866822100232</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960984</v>
+        <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.800250664268233</v>
+        <v>-6.821200320328947</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.352384511746314</v>
+        <v>0.3440046493220286</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.3508657412824111</v>
+        <v>-0.3718153973431211</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.862321756997908</v>
+        <v>2.849751963361483</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607642</v>
+        <v>3.692931855607641</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.905840654041338</v>
+        <v>-6.926790310102051</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.1821725862378534</v>
+        <v>0.1737927238135684</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.4564557310555155</v>
+        <v>-0.4774053871162254</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.670991833534827</v>
+        <v>2.658422039898401</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987898</v>
+        <v>3.770422583987897</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.83760606941591</v>
+        <v>-6.858555725476624</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2580107619651111</v>
+        <v>0.2496308995408256</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.4380404081829795</v>
+        <v>-0.4589900642436894</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.730585369135435</v>
+        <v>2.718015575499009</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.873530691357055</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.689666028008311</v>
+        <v>-6.710615684069024</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1973078558399832</v>
+        <v>0.1889279934156978</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.4177194922744219</v>
+        <v>-0.4386691483351319</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.622898995992402</v>
+        <v>2.610329202355976</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409203</v>
+        <v>3.723566229409201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.864816705103577</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.636696505754323</v>
+        <v>-6.657646161815036</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2097816784881004</v>
+        <v>0.2014018160638149</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.364749970020433</v>
+        <v>-0.385699626081143</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.645966723091317</v>
+        <v>2.633396929454891</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.857856093008484</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.470908309794032</v>
+        <v>-6.491857965854745</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2691363447771233</v>
+        <v>0.2607564823528383</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.364749970020433</v>
+        <v>-0.385699626081143</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.639006110996224</v>
+        <v>2.626436317359798</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.872318447389627</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.437545103315263</v>
+        <v>-6.458494759375976</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2969439817497741</v>
+        <v>0.2885641193254886</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.364749970020433</v>
+        <v>-0.385699626081143</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.653468465377367</v>
+        <v>2.640898671740941</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722814</v>
+        <v>3.828551486722813</v>
       </c>
       <c r="C1914" t="n">
         <v>2.866850567848822</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.329285966192741</v>
+        <v>-6.350235622253455</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3347797570579778</v>
+        <v>0.3263998946336923</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.364749970020433</v>
+        <v>-0.385699626081143</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.648000585836562</v>
+        <v>2.635430792200136</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792043</v>
+        <v>3.828052928792042</v>
       </c>
       <c r="C1915" t="n">
         <v>2.864348661859399</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.205994831375611</v>
+        <v>-6.226944487436324</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3815943049954069</v>
+        <v>0.3732144425711215</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2414588352033025</v>
+        <v>-0.2624084912640125</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.719473360737417</v>
+        <v>2.706903567100991</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919903</v>
+        <v>3.812453678919902</v>
       </c>
       <c r="C1916" t="n">
         <v>2.872049640096724</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.153297964244319</v>
+        <v>-6.174247620305032</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4103740300852485</v>
+        <v>0.4019941676609635</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1887619680720113</v>
+        <v>-0.2097116241327213</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.758792459253517</v>
+        <v>2.746222665617091</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318088</v>
       </c>
       <c r="C1917" t="n">
         <v>2.867830348443774</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.909532522260875</v>
+        <v>-5.930482178321588</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.503660915225677</v>
+        <v>0.495281052801392</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1887619680720113</v>
+        <v>-0.2097116241327213</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.754573167600568</v>
+        <v>2.742003373964142</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057522</v>
+        <v>3.82431123305752</v>
       </c>
       <c r="C1918" t="n">
         <v>2.86995466236379</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.819756849884403</v>
+        <v>-5.840706505945116</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5416954980962818</v>
+        <v>0.5333156356719968</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1271625231577013</v>
+        <v>-0.1481121792184113</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.79365714846917</v>
+        <v>2.781087354832744</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635497427918</v>
+        <v>3.826354974279178</v>
       </c>
       <c r="C1919" t="n">
         <v>2.862696737347493</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.569906455935328</v>
+        <v>-5.590856111996041</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6343777306596139</v>
+        <v>0.6259978682353289</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1271625231577013</v>
+        <v>-0.1481121792184113</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.786399223452872</v>
+        <v>2.773829429816446</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011493</v>
+        <v>3.835957987011491</v>
       </c>
       <c r="C1920" t="n">
         <v>2.866295860868141</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.394014363467896</v>
+        <v>-5.414964019528609</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7083336911672355</v>
+        <v>0.6999538287429501</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1271625231577013</v>
+        <v>-0.1481121792184113</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.789998346973521</v>
+        <v>2.777428553337095</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392981</v>
+        <v>3.780933911392979</v>
       </c>
       <c r="C1921" t="n">
         <v>2.879623366922695</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.222567900445433</v>
+        <v>-5.243517556506146</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7902397824307745</v>
+        <v>0.7818599200064895</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.04428393986476181</v>
+        <v>0.02333428380405184</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.906193730841552</v>
+        <v>2.893623937205126</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632775</v>
+        <v>3.773765222632774</v>
       </c>
       <c r="C1922" t="n">
         <v>2.878643844538992</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.142545613336312</v>
+        <v>-5.163495269397025</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8212691748907202</v>
+        <v>0.8128893124664347</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1243062269738828</v>
+        <v>0.1033565709131728</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.953227580723322</v>
+        <v>2.940657787086896</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883069</v>
+        <v>3.764617879883067</v>
       </c>
       <c r="C1923" t="n">
         <v>2.883338645593309</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.078909871102377</v>
+        <v>-5.09985952716309</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.851418272838611</v>
+        <v>0.8430384104143256</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.1879419692078173</v>
+        <v>0.1669923131471073</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.996103827118</v>
+        <v>2.983534033481574</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074777</v>
+        <v>3.798814771074776</v>
       </c>
       <c r="C1924" t="n">
         <v>2.864532904377105</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.985212552885982</v>
+        <v>-5.006162208946695</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8700914589089648</v>
+        <v>0.8617115964846795</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.1879419692078173</v>
+        <v>0.1669923131471073</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.977298085901796</v>
+        <v>2.96472829226537</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.797694884242287</v>
       </c>
       <c r="C1925" t="n">
         <v>2.866275981001982</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.995715175951271</v>
+        <v>-5.016664832011984</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8676334863077266</v>
+        <v>0.8592536238834412</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1774393461425284</v>
+        <v>0.1564896900818185</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.972739588687499</v>
+        <v>2.960169795051073</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367679</v>
+        <v>3.821593509367677</v>
       </c>
       <c r="C1926" t="n">
         <v>2.870205294836802</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.923472607780076</v>
+        <v>-4.94442226384079</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9004598274110247</v>
+        <v>0.8920799649867392</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1774393461425284</v>
+        <v>0.1564896900818185</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.97666890252232</v>
+        <v>2.964099108885894</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879959</v>
+        <v>3.822326997879958</v>
       </c>
       <c r="C1927" t="n">
         <v>2.870883878754142</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.905758920902211</v>
+        <v>-4.926708576962924</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9082238860795107</v>
+        <v>0.8998440236552254</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1806206750394452</v>
+        <v>0.1596710189787353</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.97925628377781</v>
+        <v>2.966686490141384</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.84861662650233</v>
       </c>
       <c r="C1928" t="n">
         <v>2.867881949974136</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.796954035422484</v>
+        <v>-4.817903691483197</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9487439114913951</v>
+        <v>0.9403640490671097</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1806206750394452</v>
+        <v>0.1596710189787353</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.976254354997804</v>
+        <v>2.963684561361377</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675932</v>
       </c>
       <c r="C1929" t="n">
         <v>2.86946098698475</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.576933237385473</v>
+        <v>-4.597882893446187</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.038331267716813</v>
+        <v>1.029951405292528</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3218405201074255</v>
+        <v>0.3008908640467155</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.062565299049206</v>
+        <v>3.04999550541278</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539943</v>
       </c>
       <c r="C1930" t="n">
         <v>2.885355169786573</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.444065548322196</v>
+        <v>-4.465015204382909</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.107372526143948</v>
+        <v>1.098992663719663</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3218405201074255</v>
+        <v>0.3008908640467155</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.078459481851029</v>
+        <v>3.065889688214603</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.845047386496256</v>
       </c>
       <c r="C1931" t="n">
         <v>2.886501014226875</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.323892464957697</v>
+        <v>-4.34484212101841</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.156587603930049</v>
+        <v>1.148207741505764</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4420136034719244</v>
+        <v>0.4210639474112144</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.15170917631003</v>
+        <v>3.139139382673604</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.896589116788315</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.18863910362772</v>
+        <v>-4.209588759688433</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.22077705102348</v>
+        <v>1.212397188599195</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5772669648019015</v>
+        <v>0.5563173087411916</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.242949295669456</v>
+        <v>3.23037950203303</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358392229421</v>
+        <v>3.735839222942098</v>
       </c>
       <c r="C1933" t="n">
         <v>2.882626608189741</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.248513930985412</v>
+        <v>-4.269463587046125</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.182864611481829</v>
+        <v>1.174484749057543</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5173921374442094</v>
+        <v>0.4964424813834994</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.193061890656267</v>
+        <v>3.180492097019841</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674509</v>
       </c>
       <c r="C1934" t="n">
         <v>2.897915777423949</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.128693700074575</v>
+        <v>-4.149643356135289</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.246081873080372</v>
+        <v>1.237702010656087</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5173921374442094</v>
+        <v>0.4964424813834994</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.208351059890475</v>
+        <v>3.195781266254049</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430688</v>
       </c>
       <c r="C1935" t="n">
         <v>2.805559976746391</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.131163406536381</v>
+        <v>-4.152113062597095</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.152738189818091</v>
+        <v>1.144358327393806</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5149224309824032</v>
+        <v>0.4939727749216933</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.114513435335833</v>
+        <v>3.101943641699407</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003596</v>
+        <v>3.743220196003595</v>
       </c>
       <c r="C1936" t="n">
         <v>2.724821838231692</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.199533592860392</v>
+        <v>-4.220483248921105</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.044651976773789</v>
+        <v>1.036272114349503</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5241981300186181</v>
+        <v>0.5032484739579083</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.039340716242863</v>
+        <v>3.026770922606437</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.715258546863584</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.213321645707438</v>
+        <v>-4.234271301768151</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.029573464266861</v>
+        <v>1.021193601842576</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5241981300186181</v>
+        <v>0.5032484739579083</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.029777424874755</v>
+        <v>3.017207631238329</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417698</v>
       </c>
       <c r="C1938" t="n">
         <v>2.852289383555786</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.268841721600028</v>
+        <v>-4.289791377660741</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.144396270602028</v>
+        <v>1.136016408177742</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5241981300186181</v>
+        <v>0.5032484739579083</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.166808261566957</v>
+        <v>3.154238467930531</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205893</v>
       </c>
       <c r="C1939" t="n">
         <v>2.856856615547574</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.093367461807558</v>
+        <v>-4.114317117868271</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.219153206510803</v>
+        <v>1.210773344086518</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5241981300186181</v>
+        <v>0.5032484739579083</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.171375493558745</v>
+        <v>3.158805699922319</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225439</v>
+        <v>3.765024323225437</v>
       </c>
       <c r="C1940" t="n">
         <v>2.832598644308781</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.085443087222644</v>
+        <v>-4.106392743283357</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.198064985105976</v>
+        <v>1.189685122681691</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5241981300186181</v>
+        <v>0.5032484739579083</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.147117522319952</v>
+        <v>3.134547728683526</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.761136957710231</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.079164884652795</v>
+        <v>-4.100114540713508</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.129114579535365</v>
+        <v>1.12073471711108</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5304763325884672</v>
+        <v>0.5095266765277573</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.079422757263311</v>
+        <v>3.066852963626885</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.771309344142363</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.019312265449072</v>
+        <v>-4.040261921509785</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.163228013648987</v>
+        <v>1.154848151224702</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5304763325884672</v>
+        <v>0.5095266765277573</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.089595143695444</v>
+        <v>3.077025350059018</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.766255614716223</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.933068802422694</v>
+        <v>-3.954018458483407</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.192671669433399</v>
+        <v>1.184291807009113</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5304763325884672</v>
+        <v>0.5095266765277573</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.084541414269304</v>
+        <v>3.071971620632878</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.758031390160749</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.978375621821674</v>
+        <v>-3.999325277882387</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.166324717118332</v>
+        <v>1.157944854694047</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.4896661695792364</v>
+        <v>0.4687165135185265</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.051831091908291</v>
+        <v>3.039261298271865</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.75858326319385</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.007408726523975</v>
+        <v>-4.028358382584688</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.155263348270513</v>
+        <v>1.146883485846228</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.4896661695792364</v>
+        <v>0.4687165135185265</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.052382964941393</v>
+        <v>3.039813171304967</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.687855955085216</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.072559802717207</v>
+        <v>-3.935547901133829</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.058475609684586</v>
+        <v>1.113280370317937</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.4245150933860053</v>
+        <v>0.5615269949693859</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.94256501111682</v>
+        <v>3.024772152066848</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560423</v>
       </c>
       <c r="C1947" t="n">
         <v>2.689729431009817</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.116949272046634</v>
+        <v>-3.979937370463257</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.042593297877416</v>
+        <v>1.097398058510767</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.3801256240565777</v>
+        <v>0.5171375256399582</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.917804805443764</v>
+        <v>3.000011946393792</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472735</v>
       </c>
       <c r="C1948" t="n">
         <v>2.68480513952154</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.233490877151977</v>
+        <v>-4.0964789755686</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9910523643470022</v>
+        <v>1.045857124980353</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.2635840189512349</v>
+        <v>0.4005959205346154</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.842955550892281</v>
+        <v>2.925162691842309</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.690296435352207</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.273414971734549</v>
+        <v>-4.136403070151172</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9805740223446404</v>
+        <v>1.035378782977991</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.2635840189512349</v>
+        <v>0.4005959205346154</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.848446846722948</v>
+        <v>2.930653987672977</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.68959784049886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.701793637120746</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.301195369635901</v>
+        <v>-4.164183468052524</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9809590649526385</v>
+        <v>1.035763825585989</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.2358036210498818</v>
+        <v>0.3728155226332623</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.843275809750676</v>
+        <v>2.925482950700704</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.64306962170532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.5401493571214</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.41957604236604</v>
+        <v>-4.282564140782663</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7719625158612364</v>
+        <v>0.8267672764945873</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.1685857688989056</v>
+        <v>0.3055976704822861</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.641300818460743</v>
+        <v>2.723507959410771</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729264</v>
       </c>
       <c r="C1952" t="n">
         <v>2.660299017840605</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.528190120809371</v>
+        <v>-4.391178219225994</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8486665452031095</v>
+        <v>0.9034713058364603</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.1685857688989056</v>
+        <v>0.3055976704822861</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.761450479179949</v>
+        <v>2.843657620129977</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190764</v>
       </c>
       <c r="C1953" t="n">
         <v>2.674812043942928</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.492781082561228</v>
+        <v>-4.355769180977851</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8773431866046897</v>
+        <v>0.9321479472380405</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.1685857688989056</v>
+        <v>0.3055976704822861</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.775963505282272</v>
+        <v>2.8581706462323</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.672231485285297</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.454397420003077</v>
+        <v>-4.3173855184197</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8901160929703189</v>
+        <v>0.9449208536036697</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.2069694314570568</v>
+        <v>0.3439813330404373</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.796413144159531</v>
+        <v>2.87862028510956</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.668960514130599</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.277281089967911</v>
+        <v>-4.140269188384534</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9576916538296871</v>
+        <v>1.012496414463038</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.2069694314570568</v>
+        <v>0.3439813330404373</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.793142173004833</v>
+        <v>2.875349313954862</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.669643905892512</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.322373334801457</v>
+        <v>-4.18536143321808</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.940338147658182</v>
+        <v>0.9951429082915328</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.145073388287667</v>
+        <v>0.2820852898710475</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.756687938865112</v>
+        <v>2.838895079815141</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.663430881198926</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.142997913562689</v>
+        <v>-4.005986011979312</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.005875291460103</v>
+        <v>1.060680052093454</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.3018501464583857</v>
+        <v>0.4388620480417662</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.844540969073958</v>
+        <v>2.926748110023986</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982225</v>
       </c>
       <c r="C1958" t="n">
         <v>2.644238336530516</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.188012127083296</v>
+        <v>-4.051000225499918</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9686770613834506</v>
+        <v>1.023481822016802</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.2715012511437811</v>
+        <v>0.4085131527271616</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.807139087216785</v>
+        <v>2.889346228166813</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.649929898869462</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.455016637355731</v>
+        <v>-4.318004735772353</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8675668196134223</v>
+        <v>0.9223715802467733</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.07713821310083252</v>
+        <v>0.214150114684213</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.696212826729961</v>
+        <v>2.77841996767999</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.649133820765963</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.556214418792903</v>
+        <v>-4.419202517209525</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8262916289350546</v>
+        <v>0.8810963895684059</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.008729399555513329</v>
+        <v>0.1457413011388938</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.654371460499271</v>
+        <v>2.7365786014493</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64673378232028</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.549703452178591</v>
+        <v>-4.412691550595213</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8264959771350964</v>
+        <v>0.8813007377684476</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.008729399555513329</v>
+        <v>0.1457413011388938</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.651971422053588</v>
+        <v>2.734178563003617</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.643258501528525</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.530665324471293</v>
+        <v>-4.393653422887915</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8306359474262601</v>
+        <v>0.8854407080596114</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.04945421177568121</v>
+        <v>0.08755768980769929</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.613585974463116</v>
+        <v>2.695793115413144</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.762552903162715</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.583181126746114</v>
+        <v>-4.446169225162736</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9289240281505224</v>
+        <v>0.9837287887838735</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.04945421177568121</v>
+        <v>0.08755768980769929</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.732880376097307</v>
+        <v>2.815087517047335</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.763386232148849</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.597047888080032</v>
+        <v>-4.460035986496654</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9242106526030889</v>
+        <v>0.9790154132364399</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.08731212850950415</v>
+        <v>0.04969977307387635</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.710998955043146</v>
+        <v>2.793206095993175</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.769394762545775</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.552243716540102</v>
+        <v>-4.415231814956724</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9481408516159866</v>
+        <v>1.002945612249338</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.08731212850950415</v>
+        <v>0.04969977307387635</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.717007485440072</v>
+        <v>2.799214626390101</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.667344983822974</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.404500746305099</v>
+        <v>-4.267488844721721</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9051882609871873</v>
+        <v>0.9599930216205383</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.08049522872537901</v>
+        <v>0.2175071303087595</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.715642121058202</v>
+        <v>2.79784926200823</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.670138605354455</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.488321967579798</v>
+        <v>-4.35131006599642</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8744533940087889</v>
+        <v>0.9292581546421399</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.08049522872537901</v>
+        <v>0.2175071303087595</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.718435742589683</v>
+        <v>2.800642883539711</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.670800953746113</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.482169261527013</v>
+        <v>-4.345157359943635</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.877576824821561</v>
+        <v>0.932381585454912</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.08664793477816329</v>
+        <v>0.2236598363615438</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.722789714613012</v>
+        <v>2.80499685556304</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.669881430486224</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.498978559677515</v>
+        <v>-4.361966658094137</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8699335823014704</v>
+        <v>0.9247383429348215</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.06983863662766165</v>
+        <v>0.2068505382110422</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.711784612462821</v>
+        <v>2.793991753412849</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.736216984283045</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.436680560901393</v>
+        <v>-4.299668659318015</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9611883356087403</v>
+        <v>1.015993096242091</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.1151329009021037</v>
+        <v>0.2521448024854842</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.805296724824307</v>
+        <v>2.887503865774335</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.538508985997172</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.234890363236235</v>
+        <v>-4.097878461652857</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8441964163889304</v>
+        <v>0.8990011770222817</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.3131510930712581</v>
+        <v>0.4501629946546386</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.726399641839927</v>
+        <v>2.808606782789955</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.608799218319347</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.28577707592243</v>
+        <v>-4.148765174339052</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8941319636366278</v>
+        <v>0.9489367242699789</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.2622643803850636</v>
+        <v>0.3992762819684441</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.766157846550385</v>
+        <v>2.848364987500414</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.623426954435391</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.199166333272623</v>
+        <v>-4.062154431689245</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9434039968125942</v>
+        <v>0.9982087574459453</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.3408901115902218</v>
+        <v>0.4779020131736023</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.827961021389524</v>
+        <v>2.910168162339552</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.621962935260062</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.259375631277908</v>
+        <v>-4.12236372969453</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.917856258435152</v>
+        <v>0.972661019068503</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.2806808135849373</v>
+        <v>0.4176927151683178</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.790371423411025</v>
+        <v>2.872578564361053</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.620454553299991</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.182953584845981</v>
+        <v>-4.045941683262603</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9469166950478511</v>
+        <v>1.001721455681202</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.2806808135849373</v>
+        <v>0.4176927151683178</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.788863041450953</v>
+        <v>2.871070182400982</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.620317420735427</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.138580453207412</v>
+        <v>-4.001568551624034</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9645288151387148</v>
+        <v>1.019333575772066</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3250539452235059</v>
+        <v>0.4620658468068864</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.815349787869531</v>
+        <v>2.897556928819559</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.614711214874017</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.161060804066297</v>
+        <v>-4.024048902482919</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9499304689337513</v>
+        <v>1.004735229567103</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3250539452235059</v>
+        <v>0.4620658468068864</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.809743582008121</v>
+        <v>2.89195072295815</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.621092971901822</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.113405073505241</v>
+        <v>-3.976393171921863</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9753745181859783</v>
+        <v>1.03017927881933</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.3727096757845615</v>
+        <v>0.509721577367942</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.84471877737256</v>
+        <v>2.926925918322588</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.625985345276547</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.012886915006487</v>
+        <v>-3.875875013423109</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.020474154960205</v>
+        <v>1.075278915593556</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.4732278342833161</v>
+        <v>0.6102397358666966</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.909922045846537</v>
+        <v>2.992129186796565</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.612740017752419</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.996981585574134</v>
+        <v>-3.859969683990756</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.013590959209018</v>
+        <v>1.068395719842369</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.3941151735740772</v>
+        <v>0.5311270751574577</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.849209121896866</v>
+        <v>2.931416262846894</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.616837720363048</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.952143183965736</v>
+        <v>-3.815131282382358</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.035624022463006</v>
+        <v>1.090428783096357</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.3986586065189467</v>
+        <v>0.5356705081023272</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.856032884274416</v>
+        <v>2.938240025224444</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917052</v>
+        <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
         <v>2.620998659994126</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.971641640207744</v>
+        <v>-3.834629738624366</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.031985579597281</v>
+        <v>1.086790340230632</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.3505739652390424</v>
+        <v>0.4875858668224229</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.831343039137551</v>
+        <v>2.91355018008758</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82668474540596</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.626878262521963</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.927438803121844</v>
+        <v>-3.790426901538466</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.055546316959478</v>
+        <v>1.110351077592829</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.3947768023249428</v>
+        <v>0.5317887039083233</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.863744343916929</v>
+        <v>2.945951484866957</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.62528826299121</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.934998468958891</v>
+        <v>-3.797986567375513</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.050932451093907</v>
+        <v>1.105737211727258</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.4495802063347621</v>
+        <v>0.5865921079181426</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.895036386792068</v>
+        <v>2.977243527742096</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.67653602817425</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.776707051419618</v>
+        <v>-3.63969514983624</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.165496783292655</v>
+        <v>1.220301543926007</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.4495802063347621</v>
+        <v>0.5865921079181426</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.946284151975108</v>
+        <v>3.028491292925136</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.674976732768503</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.569065047785142</v>
+        <v>-3.432053146201764</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.246994289340699</v>
+        <v>1.30179904997405</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.6572222099692383</v>
+        <v>0.7942341115526188</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.069310058750046</v>
+        <v>3.151517199700075</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.669924961006773</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.518032955062614</v>
+        <v>-3.381021053479236</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.26235535466798</v>
+        <v>1.317160115301331</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7082543026917663</v>
+        <v>0.8452662042751468</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.094877542621833</v>
+        <v>3.177084683571862</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.687112365099478</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.452808773935408</v>
+        <v>-3.31579687235203</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.305632431211567</v>
+        <v>1.360437191844919</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.7734784838189719</v>
+        <v>0.9104903854023524</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.151199455390862</v>
+        <v>3.23340659634089</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.683073337398759</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.415381753864275</v>
+        <v>-3.278369852280897</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.316564211539301</v>
+        <v>1.371368972172653</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.7787300218481535</v>
+        <v>0.915741923431534</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.150311350507651</v>
+        <v>3.232518491457679</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.684330129729999</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.435493409898983</v>
+        <v>-3.298481508315605</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.309776341456658</v>
+        <v>1.36458110209001</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.7897573668455727</v>
+        <v>0.9267692684289532</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.158184549837343</v>
+        <v>3.240391690787371</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84488790075121</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.407080146799099</v>
+        <v>-3.270068245215721</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.481699417717823</v>
+        <v>1.536504178351174</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.7307818040991438</v>
+        <v>0.8677937056825245</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.283356983210696</v>
+        <v>3.365564124160724</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.965000809969027</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.332297885774087</v>
+        <v>-3.195285984190709</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.631725231345645</v>
+        <v>1.686529991978996</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.8055640651241565</v>
+        <v>0.9425759667075371</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.448339249043521</v>
+        <v>3.530546389993549</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.956708785982886</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.306213801510279</v>
+        <v>-3.169201899926901</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.633866841065027</v>
+        <v>1.688671601698378</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.8055640651241565</v>
+        <v>0.9425759667075371</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.44004722505738</v>
+        <v>3.522254366007408</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.954901981566665</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.218335888401158</v>
+        <v>-3.08132398681778</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.667211201892455</v>
+        <v>1.722015962525806</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9214897075475076</v>
+        <v>1.058501609130888</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.50779580609517</v>
+        <v>3.590002947045198</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.972456387293457</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.209443427007875</v>
+        <v>-3.072431525424497</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.688322592176559</v>
+        <v>1.743127352809911</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9214897075475076</v>
+        <v>1.058501609130888</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.525350211821961</v>
+        <v>3.60755735277199</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945362</v>
       </c>
       <c r="C1996" t="n">
         <v>2.964311434698041</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.377919543977753</v>
+        <v>-3.240907642394375</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.612787192793192</v>
+        <v>1.667591953426544</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.8935418718309268</v>
+        <v>1.030553773414307</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.500436557796597</v>
+        <v>3.582643698746625</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.945581131885902</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.931663351348313</v>
+        <v>-2.794651449764935</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.77255936703283</v>
+        <v>1.827364127666181</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.7988232021612941</v>
+        <v>0.9358351037446746</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.424875053182679</v>
+        <v>3.507082194132707</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.936245154382807</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.90894224766516</v>
+        <v>-2.771930346081782</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.772311831002996</v>
+        <v>1.827116591636347</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.7988232021612941</v>
+        <v>0.9358351037446746</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.415539075679584</v>
+        <v>3.497746216629612</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>3.095151280233976</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.038144060959203</v>
+        <v>-2.901132159375825</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.879537231536548</v>
+        <v>1.934341992169899</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.6696213888672518</v>
+        <v>0.8066332904506324</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.496924113554327</v>
+        <v>3.579131254504356</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>3.132229102727623</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.064018459433228</v>
+        <v>-2.92700655784985</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.906265294640584</v>
+        <v>1.961070055273935</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7145329975789929</v>
+        <v>0.8515448991623735</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.560948901275018</v>
+        <v>3.643156042225047</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.128904458717168</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.056963769218055</v>
+        <v>-2.919951867634677</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.905762526716199</v>
+        <v>1.96056728734955</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7215876877941667</v>
+        <v>0.8585995893775473</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.561857071393668</v>
+        <v>3.644064212343697</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
         <v>3.138910612361909</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.030012544891567</v>
+        <v>-2.893000643308189</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.926549170091535</v>
+        <v>1.981353930724887</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7364680338218859</v>
+        <v>0.8734799354052665</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.580791432655041</v>
+        <v>3.662998573605069</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.323013744506869</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.165965552947883</v>
+        <v>-3.028953651364505</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.056271099013968</v>
+        <v>2.11107585964732</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7364680338218859</v>
+        <v>0.8734799354052665</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.764894564800001</v>
+        <v>3.847101705750029</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.315130439409862</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.188373670752755</v>
+        <v>-3.051361769169377</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.039424546795013</v>
+        <v>2.094229307428364</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7364680338218859</v>
+        <v>0.8734799354052665</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.757011259702994</v>
+        <v>3.839218400653023</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.3171844389595</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.216597906330355</v>
+        <v>-3.079586004746977</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.03018885211361</v>
+        <v>2.084993612746961</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.7544447862731944</v>
+        <v>0.8914566878565751</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.769851310723416</v>
+        <v>3.852058451673445</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
         <v>3.373438156681347</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.226038832218885</v>
+        <v>-3.227050462234454</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.082666199480045</v>
+        <v>2.082261547473818</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8768719038165859</v>
+        <v>0.8724848518496786</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.899561298971299</v>
+        <v>3.896929067791154</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
         <v>3.376329251226648</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.278312439554527</v>
+        <v>-3.279324069570096</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.06464785109109</v>
+        <v>2.064243199084862</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8245982964809446</v>
+        <v>0.8202112445140374</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.871088229115215</v>
+        <v>3.86845599793507</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.374441064120423</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.354642417155433</v>
+        <v>-3.355654047171002</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.032227672944503</v>
+        <v>2.031823020938275</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8245982964809446</v>
+        <v>0.8202112445140374</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.86920004200899</v>
+        <v>3.866567810828845</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.369261293723285</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.556896137479786</v>
+        <v>-3.557907767495355</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.946146414417623</v>
+        <v>1.945741762411396</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.6223445761565911</v>
+        <v>0.617957524189684</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.74266803941724</v>
+        <v>3.740035808237096</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.367695303933437</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.718464563007041</v>
+        <v>-3.71947619302261</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.879953054416874</v>
+        <v>1.879548402410646</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.4955616523587117</v>
+        <v>0.4911746003918046</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.665032295348665</v>
+        <v>3.662400064168521</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.380768710799356</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.82676522487716</v>
+        <v>-3.82777685489273</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.849706196534745</v>
+        <v>1.849301544528517</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.4955616523587117</v>
+        <v>0.4911746003918046</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.678105702214583</v>
+        <v>3.675473471034439</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.372773907582296</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.919912696180527</v>
+        <v>-3.920924326196096</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.804452404796338</v>
+        <v>1.80404775279011</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.372732441076179</v>
+        <v>0.3683453891092718</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.596413372228004</v>
+        <v>3.59378114104786</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.371297948709298</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.94781348329</v>
+        <v>-3.948825113305569</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.791816131079551</v>
+        <v>1.791411479073323</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3381355169332442</v>
+        <v>0.333748464966337</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.574179258869245</v>
+        <v>3.571547027689101</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.368062392686497</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.070339585992894</v>
+        <v>-4.071351216008463</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.739570133975592</v>
+        <v>1.739165481969364</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2156094142303503</v>
+        <v>0.2112223622634432</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.497428041224707</v>
+        <v>3.494795810044563</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.434768352277001</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.300854082178483</v>
+        <v>-4.301865712194052</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.71407029509186</v>
+        <v>1.713665643085633</v>
       </c>
       <c r="F2015" t="n">
-        <v>-0.01490508195523843</v>
+        <v>-0.01929213392214557</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.425825303103858</v>
+        <v>3.423193071923714</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.575080071278848</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.557574900173307</v>
+        <v>-4.558586530188876</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.751693686895777</v>
+        <v>1.75128903488955</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.1233196560990533</v>
+        <v>-0.1277067080659604</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.501088277619416</v>
+        <v>3.498456046439272</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237091</v>
       </c>
       <c r="C2017" t="n">
         <v>3.644060340424487</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.711561317949448</v>
+        <v>-4.712572947965016</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.759079388930961</v>
+        <v>1.758674736924734</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.1233196560990533</v>
+        <v>-0.1277067080659604</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.570068546765055</v>
+        <v>3.567436315584911</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
         <v>3.630111542544608</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.661039414121782</v>
+        <v>-4.662051044137351</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.765339352582148</v>
+        <v>1.764934700575921</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.1233196560990533</v>
+        <v>-0.1277067080659604</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.556119748885176</v>
+        <v>3.553487517705032</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.641982031600022</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.913514568129506</v>
+        <v>-4.914526198145075</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.676219780034472</v>
+        <v>1.675815128028245</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.1233196560990533</v>
+        <v>-0.1277067080659604</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.56799023794059</v>
+        <v>3.565358006760446</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.643192566118966</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.206410324608918</v>
+        <v>-5.207421954624487</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.560272011961651</v>
+        <v>1.559867359955424</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.1233196560990533</v>
+        <v>-0.1277067080659604</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.569200772459534</v>
+        <v>3.56656854127939</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251945</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.647314308346287</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.393074452743726</v>
+        <v>-5.394086082759295</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.489728102935049</v>
+        <v>1.489323450928822</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1500586269236132</v>
+        <v>-0.1544456788905203</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.55727913219212</v>
+        <v>3.554646901011975</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916199</v>
       </c>
       <c r="C2022" t="n">
         <v>3.642392161082477</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.539095139657689</v>
+        <v>-5.540106769673257</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.426397680905654</v>
+        <v>1.425993028899426</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.1591417187174701</v>
+        <v>-0.1635287706843773</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.546907129851995</v>
+        <v>3.544274898671851</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
         <v>3.804596217781521</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.630809148767273</v>
+        <v>-5.631820778782842</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.551916133960864</v>
+        <v>1.551511481954637</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.1591417187174701</v>
+        <v>-0.1635287706843773</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.709111186551039</v>
+        <v>3.706478955370895</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
         <v>3.799442855745335</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.662460807827243</v>
+        <v>-5.663472437842811</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.53410210830069</v>
+        <v>1.533697456294463</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.1643101759619103</v>
+        <v>-0.1686972279288175</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.700856750168189</v>
+        <v>3.698224518988045</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.809672273313826</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.744395626096126</v>
+        <v>-5.745407256111695</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.511557598561629</v>
+        <v>1.511152946555401</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1742449215489905</v>
+        <v>-0.1786319735158977</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.705125320384432</v>
+        <v>3.702493089204288</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.818597911769729</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.846371748344533</v>
+        <v>-5.847383378360102</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.479692788118168</v>
+        <v>1.47928813611194</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2762210437973981</v>
+        <v>-0.2806080957643052</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.65286528549129</v>
+        <v>3.650233054311146</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.810750799013904</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.736365464867312</v>
+        <v>-5.737377094882881</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.515848188753232</v>
+        <v>1.515443536747004</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.2530164718801229</v>
+        <v>-0.25740352384703</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.658940915885831</v>
+        <v>3.656308684705686</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.815000809735878</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.593305889126386</v>
+        <v>-5.594317519141955</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.577322029771577</v>
+        <v>1.576917377765349</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2450030452901436</v>
+        <v>-0.2493900972570507</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.667998982561792</v>
+        <v>3.665366751381648</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.822261692618414</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.291859163654548</v>
+        <v>-5.292870793670117</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.705161602842848</v>
+        <v>1.70475695083662</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.05644368018169366</v>
+        <v>0.05205662821478652</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.856127900727431</v>
+        <v>3.853495669547287</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.823232870371125</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.316449407889732</v>
+        <v>-5.317461037905301</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.696296682901485</v>
+        <v>1.695892030895257</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.05644368018169366</v>
+        <v>0.05205662821478652</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.857099078480141</v>
+        <v>3.854466847299997</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.82407577475088</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.265411031883212</v>
+        <v>-5.266422661898781</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.717554937683849</v>
+        <v>1.717150285677621</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.05644368018169366</v>
+        <v>0.05205662821478652</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.857941982859897</v>
+        <v>3.855309751679753</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
         <v>3.843113873625026</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.224271737016581</v>
+        <v>-5.22528336703215</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.753048754504646</v>
+        <v>1.752644102498419</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.09758297504832447</v>
+        <v>0.09319592308141733</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.901663658654021</v>
+        <v>3.899031427473877</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.65929786974896</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.127636824997941</v>
+        <v>-5.12864845501351</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.607886715436037</v>
+        <v>1.607482063429809</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.1942178870669644</v>
+        <v>0.1898308351000573</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.775828601989139</v>
+        <v>3.773196370808995</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.662799913822925</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.258217559528783</v>
+        <v>-5.259229189544352</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.559156465697664</v>
+        <v>1.558751813691436</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.0636371525361219</v>
+        <v>0.05925010056921476</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.700982205344598</v>
+        <v>3.698349974164454</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.647226732899007</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.093721225337822</v>
+        <v>-5.09473285535339</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.609381818450131</v>
+        <v>1.608977166443904</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.2281334867270838</v>
+        <v>0.2237464347601766</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.784106824935258</v>
+        <v>3.781474593755113</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.646414443335437</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.121091158022254</v>
+        <v>-5.122102788037822</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.597621555812788</v>
+        <v>1.597216903806561</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.2281334867270838</v>
+        <v>0.2237464347601766</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.783294535371688</v>
+        <v>3.780662304191543</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.656283222460509</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.131476352912143</v>
+        <v>-5.132487982927712</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.603336256981905</v>
+        <v>1.602931604975677</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2177482918371945</v>
+        <v>0.2133612398702873</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.786932197562826</v>
+        <v>3.784299966382682</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.727120228236934</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.150064511634368</v>
+        <v>-5.151076141649937</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.66673799926944</v>
+        <v>1.666333347263212</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.1991601331149691</v>
+        <v>0.194773081148062</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.846616308105916</v>
+        <v>3.843984076925772</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.723989239055233</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.150363058330404</v>
+        <v>-5.151374688345973</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.663487591409324</v>
+        <v>1.663082939403096</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.1988615864189332</v>
+        <v>0.1944745344520261</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.843306190906593</v>
+        <v>3.840673959726449</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
         <v>3.728520133994624</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.049539924639976</v>
+        <v>-5.050551554655545</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.708347739824887</v>
+        <v>1.707943087818659</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.211325801903287</v>
+        <v>0.2069387499363799</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.855315615136597</v>
+        <v>3.852683383956453</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121465</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
         <v>3.728649387473168</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.858758563887569</v>
+        <v>-4.859770193903138</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.784789537604393</v>
+        <v>1.784384885598165</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.4021071626556944</v>
+        <v>0.3977201106887873</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.969913685066585</v>
+        <v>3.96728145388644</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
         <v>3.708486233210764</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.840241709845749</v>
+        <v>-4.841253339861318</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.772033124958717</v>
+        <v>1.77162847295249</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.4150372920809026</v>
+        <v>0.4106502401139955</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.957508608459306</v>
+        <v>3.954876377279161</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912983</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.743453169822823</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.784911121943987</v>
+        <v>-4.785922751959555</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.829132296731481</v>
+        <v>1.828727644725253</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.4703678799826648</v>
+        <v>0.4659808280157576</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.025673897812422</v>
+        <v>4.023041666632277</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539893</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
         <v>3.73713973772426</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.772856995031024</v>
+        <v>-4.773868625046592</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.827640515398103</v>
+        <v>1.827235863391876</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.4824220068956276</v>
+        <v>0.4780349549287204</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.026592941861638</v>
+        <v>4.023960710681493</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811007</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
         <v>3.739020367908396</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.814012114599245</v>
+        <v>-4.815023744614813</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.813059097754951</v>
+        <v>1.812654445748723</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.4412668873274067</v>
+        <v>0.4368798353604995</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.00378050030484</v>
+        <v>4.001148269124696</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382918</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.751871393786279</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.711131525070652</v>
+        <v>-4.712143155086221</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.867062359444271</v>
+        <v>1.866657707438043</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.5441474768559995</v>
+        <v>0.5397604248890924</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.078359879899879</v>
+        <v>4.075727648719734</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760314</v>
+        <v>3.646857607760312</v>
       </c>
       <c r="C2047" t="n">
         <v>3.772074063959873</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.942731918240153</v>
+        <v>-4.943743548255721</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.794624872350065</v>
+        <v>1.794220220343837</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.5441474768559995</v>
+        <v>0.5397604248890924</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.098562550073473</v>
+        <v>4.095930318893329</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
         <v>3.772074063959873</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.960804426531764</v>
+        <v>-4.961816056547333</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.78739586903342</v>
+        <v>1.786991217027192</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.5441474768559995</v>
+        <v>0.5397604248890924</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.098562550073473</v>
+        <v>4.095930318893329</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082832</v>
       </c>
       <c r="C2049" t="n">
         <v>3.73232597755334</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.135911259108209</v>
+        <v>-5.136922889123777</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.677605049596309</v>
+        <v>1.677200397590081</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.5441474768559995</v>
+        <v>0.5397604248890924</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.058814463666939</v>
+        <v>4.056182232486795</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
         <v>3.73934859655028</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.030031400961291</v>
+        <v>-5.105636868583322</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.726979611852016</v>
+        <v>1.696737424803203</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.6500273350029173</v>
+        <v>0.5710464454295477</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.12936499755203</v>
+        <v>4.081976463808008</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677824</v>
+        <v>3.730590658677821</v>
       </c>
       <c r="C2051" t="n">
         <v>3.838519596123184</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.877006008848007</v>
+        <v>-4.952611476470038</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.887360768270234</v>
+        <v>1.857118581221421</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8030527271162015</v>
+        <v>0.7240718375428319</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.320351232392905</v>
+        <v>4.272962698648883</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.74129851807388</v>
       </c>
       <c r="C2052" t="n">
         <v>4.025985821031476</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.905313322721277</v>
+        <v>-4.980918790343308</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.063504067629218</v>
+        <v>2.033261880580405</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8030527271162015</v>
+        <v>0.7240718375428319</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.507817457301197</v>
+        <v>4.460428923557176</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.699135800903165</v>
       </c>
       <c r="C2053" t="n">
         <v>3.995388772385558</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.071906547834799</v>
+        <v>-5.14751201545683</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.966269728937891</v>
+        <v>1.936027541889079</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.6364595020026791</v>
+        <v>0.5574786124293094</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.377264473587166</v>
+        <v>4.329875939843144</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568382</v>
+        <v>3.70820270456838</v>
       </c>
       <c r="C2054" t="n">
         <v>3.999065175047276</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.898842168452499</v>
+        <v>-4.97444763607453</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.039171883352529</v>
+        <v>2.008929696303717</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.6364595020026791</v>
+        <v>0.5574786124293094</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.380940876248884</v>
+        <v>4.333552342504862</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682204</v>
+        <v>3.740601586682201</v>
       </c>
       <c r="C2055" t="n">
         <v>3.996683230170771</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.869596187996803</v>
+        <v>-4.945201655618834</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.048488330658303</v>
+        <v>2.018246143609491</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.6364595020026791</v>
+        <v>0.5574786124293094</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.378558931372379</v>
+        <v>4.331170397628357</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539107</v>
+        <v>3.699424827539104</v>
       </c>
       <c r="C2056" t="n">
         <v>3.993976469328406</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.976521735874654</v>
+        <v>-5.052127203496685</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.003011350664798</v>
+        <v>1.972769163615985</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.5295339541248277</v>
+        <v>0.450553064551458</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.311696841803303</v>
+        <v>4.264308308059281</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983737</v>
+        <v>3.689962785983735</v>
       </c>
       <c r="C2057" t="n">
         <v>3.995405271471641</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.121540294381902</v>
+        <v>-5.197145762003934</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.946432729405132</v>
+        <v>1.91619054235632</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.3845153956175792</v>
+        <v>0.3055345060442095</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.226114508842189</v>
+        <v>4.178725975098167</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969749</v>
+        <v>3.711872614969746</v>
       </c>
       <c r="C2058" t="n">
         <v>4.095336510729394</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.23988206016662</v>
+        <v>-5.315487527788651</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.999027262348998</v>
+        <v>1.968785075300186</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.3952014341804693</v>
+        <v>0.3162205446070996</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.332457371237675</v>
+        <v>4.285068837493654</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073539</v>
+        <v>3.714899237073535</v>
       </c>
       <c r="C2059" t="n">
         <v>4.093122207855332</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.291292482487328</v>
+        <v>-5.366897950109359</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.976248790546654</v>
+        <v>1.946006603497841</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.3952014341804693</v>
+        <v>0.3162205446070996</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.330243068363614</v>
+        <v>4.282854534619593</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720065</v>
+        <v>3.704778134720062</v>
       </c>
       <c r="C2060" t="n">
         <v>4.093025335929622</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.370711933695079</v>
+        <v>-5.446317401317111</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.944384138137843</v>
+        <v>1.91414195108903</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.3952014341804693</v>
+        <v>0.3162205446070996</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.330146196437903</v>
+        <v>4.282757662693882</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581133</v>
+        <v>3.736825137581129</v>
       </c>
       <c r="C2061" t="n">
         <v>4.093019229487665</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.466174931612297</v>
+        <v>-5.541780399234328</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.906192832528999</v>
+        <v>1.875950645480187</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.3952014341804693</v>
+        <v>0.3162205446070996</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.330140089995947</v>
+        <v>4.282751556251926</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500735</v>
+        <v>3.715393145500731</v>
       </c>
       <c r="C2062" t="n">
         <v>4.091115626050276</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.506194929656081</v>
+        <v>-5.581800397278112</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.888281229874096</v>
+        <v>1.858039042825284</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.3551814361366855</v>
+        <v>0.2762005465633158</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.304224487732287</v>
+        <v>4.256835953988266</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.73610959863627</v>
+        <v>3.736109598636267</v>
       </c>
       <c r="C2063" t="n">
         <v>4.096849443798003</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.561564091788274</v>
+        <v>-5.637169559410306</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.871867382768945</v>
+        <v>1.841625195720133</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.3551814361366855</v>
+        <v>0.2762005465633158</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.309958305480014</v>
+        <v>4.262569771735992</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396013</v>
+        <v>3.73684305539601</v>
       </c>
       <c r="C2064" t="n">
         <v>4.096387807140935</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.607001871619102</v>
+        <v>-5.682607339241133</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.853230634179547</v>
+        <v>1.822988447130735</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.3123364454585258</v>
+        <v>0.2333555558851561</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.283789674416052</v>
+        <v>4.236401140672029</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396422</v>
+        <v>3.790292685396419</v>
       </c>
       <c r="C2065" t="n">
         <v>4.116262199991255</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.523776414771437</v>
+        <v>-5.599381882393469</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.906395209768932</v>
+        <v>1.87615302272012</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.3123364454585258</v>
+        <v>0.2333555558851561</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.303664067266371</v>
+        <v>4.256275533522349</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299177</v>
+        <v>3.794507029299173</v>
       </c>
       <c r="C2066" t="n">
         <v>4.099962900515982</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.34748619016613</v>
+        <v>-5.423091657788161</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.960612000135783</v>
+        <v>1.93036981308697</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.3123364454585258</v>
+        <v>0.2333555558851561</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.287364767791098</v>
+        <v>4.239976234047076</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590412</v>
+        <v>3.794725278590406</v>
       </c>
       <c r="C2067" t="n">
         <v>4.102393849980028</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.164274527033035</v>
+        <v>-5.239879994655066</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.036327614853067</v>
+        <v>2.006085427804254</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.3123364454585258</v>
+        <v>0.2333555558851561</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.289795717255144</v>
+        <v>4.242407183511122</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.854781583667224</v>
+        <v>3.522386512311064</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.261204660323669</v>
+        <v>4.009037798539292</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.164274527033035</v>
+        <v>-5.239879994655066</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.036327614853067</v>
+        <v>2.006085427804254</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.3123364454585258</v>
+        <v>0.2333555558851561</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.254268457310037</v>
+        <v>4.00210159552566</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240826.xlsx
+++ b/tame_output/ON/bt/strategyON_20240826.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>55.8%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>87.6%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>99.3%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>108.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.0%</t>
+          <t>124.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-29.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.7%</t>
+          <t>-46.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>427.2%</t>
+          <t>430.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-685.6%</t>
+          <t>-683.3%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-175.6%</t>
+          <t>-174.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-25.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-309.0%</t>
+          <t>-112.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-200.7%</t>
+          <t>-184.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-45.8%</t>
+          <t>-11.2%</t>
         </is>
       </c>
     </row>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.293766719760738</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706667</v>
+        <v>3.298730590706666</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296834</v>
+        <v>3.299918119296833</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201485</v>
+        <v>3.295507330201484</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153003</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.271168579537423</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.272760131382188</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074619</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911636</v>
+        <v>3.233800325911635</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213492</v>
+        <v>3.223539378213491</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416042</v>
+        <v>3.231167537416041</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382324</v>
+        <v>3.235981977382323</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495495</v>
+        <v>3.278199702495494</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.29913614634705</v>
+        <v>3.299136146347049</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130012</v>
+        <v>3.287377576130011</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178238</v>
+        <v>3.315884374178237</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207808</v>
+        <v>3.305316798207807</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310977</v>
+        <v>3.284619513310976</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.305849539006528</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309419</v>
+        <v>3.311086391309418</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.3047157169709</v>
+        <v>3.304715716970899</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330517</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191731</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108633</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097815</v>
+        <v>3.341378723097814</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309411</v>
+        <v>3.374439043094109</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199279</v>
+        <v>3.405960511199278</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969587</v>
+        <v>3.424633354969586</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923079</v>
+        <v>3.419979433923078</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297742</v>
+        <v>3.458100091297741</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131761</v>
+        <v>3.447750501317609</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737163</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.503170282341306</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539457</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937496</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.496851904729888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.148836464489362</v>
+        <v>-9.238763656773491</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4990527968044431</v>
+        <v>-0.5350236737180949</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.661895616803577</v>
+        <v>-1.751822809087708</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.163700843222903</v>
+        <v>2.109744527852425</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.311349930187946</v>
+        <v>-9.403229559448548</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5629423932453208</v>
+        <v>-0.5996942449495615</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.759529047222264</v>
+        <v>-1.870518674933411</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.106236574810247</v>
+        <v>2.039642798183559</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.437386723556235</v>
+        <v>-9.529266352816837</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6106633819635219</v>
+        <v>-0.6474152336677625</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.734277424412522</v>
+        <v>-1.845267052123669</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.124081277125207</v>
+        <v>2.057487500498519</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.57367402532254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.380314951660305</v>
+        <v>-9.472194580920906</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5838443375187485</v>
+        <v>-0.6205961892229892</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.734277424412522</v>
+        <v>-1.845267052123669</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.128071612811608</v>
+        <v>2.06147783618492</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.600038265158918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.521986793384425</v>
+        <v>-9.613866422645026</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6419883011071383</v>
+        <v>-0.678740152811379</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.734277424412522</v>
+        <v>-1.845267052123669</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.126596385912866</v>
+        <v>2.060002609286178</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940715</v>
+        <v>3.691571733940714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.472395948959591</v>
+        <v>-9.564275578220192</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6070985531723325</v>
+        <v>-0.6438504048765732</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.684686579987688</v>
+        <v>-1.795676207698835</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.171404302732639</v>
+        <v>2.10481052610595</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770575</v>
+        <v>3.676841549770574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.323477614487734</v>
+        <v>-9.415357243748335</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5605823530302727</v>
+        <v>-0.5973342047345134</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.653436989252515</v>
+        <v>-1.764426616963662</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.17710292352706</v>
+        <v>2.110509146900371</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615278</v>
+        <v>3.685161381615277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.097632461768324</v>
+        <v>-9.189512091028924</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4606652189063003</v>
+        <v>-0.4974170706105401</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.611510313665351</v>
+        <v>-1.722499941376498</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.211838001915567</v>
+        <v>2.145244225288878</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812098</v>
+        <v>3.684843823812097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.973053805430732</v>
+        <v>-9.064933434691332</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4096946118152043</v>
+        <v>-0.4464464635194445</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.611510313665351</v>
+        <v>-1.722499941376498</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.212977146471625</v>
+        <v>2.146383369844937</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646212</v>
+        <v>3.710935533646211</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.025949093475019</v>
+        <v>-9.117828722735618</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4282189528708114</v>
+        <v>-0.4649708045750511</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.606554967576905</v>
+        <v>-1.717544595288052</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.218584128286801</v>
+        <v>2.151990351660112</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.953815918187138</v>
+        <v>-9.045695547447737</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3936319785170226</v>
+        <v>-0.4303838302212624</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.606554967576905</v>
+        <v>-1.717544595288052</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.224317832525437</v>
+        <v>2.157724055898749</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955323</v>
+        <v>3.728577929955322</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.88244952557749</v>
+        <v>-8.97432915483809</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3748226838670288</v>
+        <v>-0.4115745355712686</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.535188574967257</v>
+        <v>-1.646178202678404</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.257400405697361</v>
+        <v>2.190806629070673</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232408</v>
+        <v>3.747702660232407</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.788990491592266</v>
+        <v>-8.880870120852865</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3473225515858465</v>
+        <v>-0.3840744032900862</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.535188574967257</v>
+        <v>-1.646178202678404</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.247516924384453</v>
+        <v>2.180923147757765</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436224</v>
+        <v>3.766317079436223</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.778337310038834</v>
+        <v>-8.870216939299434</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3448958394638475</v>
+        <v>-0.3816476911680877</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.535188574967257</v>
+        <v>-1.646178202678404</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.24568236388508</v>
+        <v>2.179088587258391</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311944</v>
+        <v>3.784684521311943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.680430271362344</v>
+        <v>-8.772309900622943</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3060333389667123</v>
+        <v>-0.342785190670952</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.467202825106701</v>
+        <v>-1.578192452817848</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.286173498827953</v>
+        <v>2.219579722201264</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097239</v>
+        <v>3.800829354097238</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.656476730386386</v>
+        <v>-8.748356359646985</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2957834164308353</v>
+        <v>-0.3325352681350755</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.443249284130743</v>
+        <v>-1.55423891184189</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.301214129559021</v>
+        <v>2.234620352932333</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017766</v>
+        <v>3.789311112017765</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.392416792063589</v>
+        <v>-8.484296421324188</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2034197572634691</v>
+        <v>-0.2401716089677088</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.179189345807947</v>
+        <v>-1.290178973519094</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.446389776390946</v>
+        <v>2.379795999764258</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.685337168558751</v>
+        <v>-7.77721679781935</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.07662505847816536</v>
+        <v>0.03987320677392558</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.179189345807947</v>
+        <v>-1.290178973519094</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.443602742730645</v>
+        <v>2.377008966103957</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.64515287019256</v>
+        <v>-7.73703249945316</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.0930424017124829</v>
+        <v>0.05629055000824312</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.139005047441756</v>
+        <v>-1.249994675152903</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.468056945638201</v>
+        <v>2.401463169011513</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.481752999253198</v>
+        <v>-7.573632628513797</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1577691713089848</v>
+        <v>0.121017319604745</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9756051765023934</v>
+        <v>-1.08659480421354</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.565463689422576</v>
+        <v>2.498869912795887</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.248271777023599</v>
+        <v>-7.340151406284199</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2590860890386768</v>
+        <v>0.222334237334437</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.7421239542727949</v>
+        <v>-0.8531135819839419</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.713476851598187</v>
+        <v>2.646883074971499</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.098605386016084</v>
+        <v>-7.190485015276684</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3160604351287235</v>
+        <v>0.2793085834244837</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.6492204630302589</v>
+        <v>-0.760210090741406</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.76632673603075</v>
+        <v>2.699732959404061</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.966329912385198</v>
+        <v>-7.058209541645797</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2702314105882331</v>
+        <v>0.2334795588839929</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5169449893993723</v>
+        <v>-0.6279346171105193</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.746952806216436</v>
+        <v>2.680359029589748</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471879410595</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.906164987058266</v>
+        <v>-6.902471209086055</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.2971124414066422</v>
+        <v>0.2985899525955267</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4567800640724407</v>
+        <v>-0.4721962845507778</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.785866822100232</v>
+        <v>2.77661708981323</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.821200320328947</v>
+        <v>-6.817506542356735</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3440046493220286</v>
+        <v>0.3454821605109131</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.3718153973431211</v>
+        <v>-0.3872316178214582</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.849751963361483</v>
+        <v>2.84050223107448</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.926790310102051</v>
+        <v>-6.92309653212984</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.1737927238135684</v>
+        <v>0.1752702350024529</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.4774053871162254</v>
+        <v>-0.4928216075945626</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.658422039898401</v>
+        <v>2.649172307611399</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.858555725476624</v>
+        <v>-6.854861947504412</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2496308995408256</v>
+        <v>0.2511084107297101</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.4589900642436894</v>
+        <v>-0.4744062847220266</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.718015575499009</v>
+        <v>2.708765843212007</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.873530691357055</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.710615684069024</v>
+        <v>-6.706921906096813</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1889279934156978</v>
+        <v>0.1904055046045823</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.4386691483351319</v>
+        <v>-0.454085368813469</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.610329202355976</v>
+        <v>2.601079470068974</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.864816705103577</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.657646161815036</v>
+        <v>-6.653952383842825</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2014018160638149</v>
+        <v>0.2028793272526994</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.385699626081143</v>
+        <v>-0.4011158465594801</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.633396929454891</v>
+        <v>2.624147197167889</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.857856093008484</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.491857965854745</v>
+        <v>-6.488164187882534</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2607564823528383</v>
+        <v>0.2622339935417228</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.385699626081143</v>
+        <v>-0.4011158465594801</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.626436317359798</v>
+        <v>2.617186585072796</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.872318447389627</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.458494759375976</v>
+        <v>-6.454800981403765</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2885641193254886</v>
+        <v>0.2900416305143731</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.385699626081143</v>
+        <v>-0.4011158465594801</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.640898671740941</v>
+        <v>2.631648939453939</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722813</v>
+        <v>3.828551486722814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.866850567848822</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.350235622253455</v>
+        <v>-6.346541844281243</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3263998946336923</v>
+        <v>0.3278774058225769</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.385699626081143</v>
+        <v>-0.4011158465594801</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.635430792200136</v>
+        <v>2.626181059913134</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792042</v>
+        <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
         <v>2.864348661859399</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.226944487436324</v>
+        <v>-6.223250709464113</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3732144425711215</v>
+        <v>0.374691953760006</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2624084912640125</v>
+        <v>-0.2778247117423496</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.706903567100991</v>
+        <v>2.697653834813989</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.872049640096724</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.174247620305032</v>
+        <v>-6.170553842332821</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4019941676609635</v>
+        <v>0.403471678849848</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.2097116241327213</v>
+        <v>-0.2251278446110584</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.746222665617091</v>
+        <v>2.736972933330089</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.867830348443774</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.930482178321588</v>
+        <v>-5.926788400349377</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.495281052801392</v>
+        <v>0.4967585639902765</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.2097116241327213</v>
+        <v>-0.2251278446110584</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.742003373964142</v>
+        <v>2.73275364167714</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.86995466236379</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.840706505945116</v>
+        <v>-5.837012727972905</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5333156356719968</v>
+        <v>0.5347931468608813</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1481121792184113</v>
+        <v>-0.1635283996967484</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.781087354832744</v>
+        <v>2.771837622545742</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.862696737347493</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.590856111996041</v>
+        <v>-5.58716233402383</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6259978682353289</v>
+        <v>0.6274753794242134</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1481121792184113</v>
+        <v>-0.1635283996967484</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.773829429816446</v>
+        <v>2.764579697529444</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.866295860868141</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.414964019528609</v>
+        <v>-5.411270241556398</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6999538287429501</v>
+        <v>0.7014313399318346</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1481121792184113</v>
+        <v>-0.1635283996967484</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.777428553337095</v>
+        <v>2.768178821050093</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.879623366922695</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.243517556506146</v>
+        <v>-5.239823778533935</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7818599200064895</v>
+        <v>0.783337431195374</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.02333428380405184</v>
+        <v>0.007918063325714708</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.893623937205126</v>
+        <v>2.884374204918124</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.878643844538992</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.163495269397025</v>
+        <v>-5.159801491424814</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8128893124664347</v>
+        <v>0.8143668236553192</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1033565709131728</v>
+        <v>0.08794035043483567</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.940657787086896</v>
+        <v>2.931408054799894</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.883338645593309</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.09985952716309</v>
+        <v>-5.096165749190879</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8430384104143256</v>
+        <v>0.8445159216032101</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.1669923131471073</v>
+        <v>0.1515760926687702</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.983534033481574</v>
+        <v>2.974284301194571</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.864532904377105</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.006162208946695</v>
+        <v>-5.002468430974484</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8617115964846795</v>
+        <v>0.863189107673564</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.1669923131471073</v>
+        <v>0.1515760926687702</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.96472829226537</v>
+        <v>2.955478559978367</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.866275981001982</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.016664832011984</v>
+        <v>-5.012971054039773</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8592536238834412</v>
+        <v>0.8607311350723257</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1564896900818185</v>
+        <v>0.1410734696034813</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.960169795051073</v>
+        <v>2.950920062764071</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.870205294836802</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.94442226384079</v>
+        <v>-4.940728485868578</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8920799649867392</v>
+        <v>0.8935574761756238</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1564896900818185</v>
+        <v>0.1410734696034813</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.964099108885894</v>
+        <v>2.954849376598891</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.870883878754142</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.926708576962924</v>
+        <v>-4.923014798990713</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8998440236552254</v>
+        <v>0.9013215348441099</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1596710189787353</v>
+        <v>0.1442547985003981</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.966686490141384</v>
+        <v>2.957436757854381</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.867881949974136</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.817903691483197</v>
+        <v>-4.814209913510986</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9403640490671097</v>
+        <v>0.9418415602559942</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1596710189787353</v>
+        <v>0.1442547985003981</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.963684561361377</v>
+        <v>2.954434829074375</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.86946098698475</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.597882893446187</v>
+        <v>-4.594189115473975</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.029951405292528</v>
+        <v>1.031428916481413</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3008908640467155</v>
+        <v>0.2854746435683784</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.04999550541278</v>
+        <v>3.040745773125777</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.885355169786573</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.465015204382909</v>
+        <v>-4.461321426410698</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.098992663719663</v>
+        <v>1.100470174908547</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3008908640467155</v>
+        <v>0.2854746435683784</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.065889688214603</v>
+        <v>3.056639955927601</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.886501014226875</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.34484212101841</v>
+        <v>-4.341148343046199</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.148207741505764</v>
+        <v>1.149685252694648</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4210639474112144</v>
+        <v>0.4056477269328773</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.139139382673604</v>
+        <v>3.129889650386602</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.896589116788315</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.209588759688433</v>
+        <v>-4.205894981716222</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.212397188599195</v>
+        <v>1.213874699788079</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5563173087411916</v>
+        <v>0.5409010882628544</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.23037950203303</v>
+        <v>3.221129769746028</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942098</v>
+        <v>3.735839222942099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.882626608189741</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.269463587046125</v>
+        <v>-4.265769809073914</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.174484749057543</v>
+        <v>1.175962260246428</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4964424813834994</v>
+        <v>0.4810262609051623</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.180492097019841</v>
+        <v>3.171242364732838</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674509</v>
+        <v>3.762647477674508</v>
       </c>
       <c r="C1934" t="n">
         <v>2.897915777423949</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.149643356135289</v>
+        <v>-4.145949578163077</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.237702010656087</v>
+        <v>1.239179521844971</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4964424813834994</v>
+        <v>0.4810262609051623</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.195781266254049</v>
+        <v>3.186531533967047</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430688</v>
+        <v>3.729146398430687</v>
       </c>
       <c r="C1935" t="n">
         <v>2.805559976746391</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.152113062597095</v>
+        <v>-4.148419284624883</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.144358327393806</v>
+        <v>1.14583583858269</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4939727749216933</v>
+        <v>0.4785565544433562</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.101943641699407</v>
+        <v>3.092693909412405</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003595</v>
+        <v>3.743220196003594</v>
       </c>
       <c r="C1936" t="n">
         <v>2.724821838231692</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.220483248921105</v>
+        <v>-4.216789470948894</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.036272114349503</v>
+        <v>1.037749625538388</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5032484739579083</v>
+        <v>0.4878322534795711</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.026770922606437</v>
+        <v>3.017521190319435</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508364</v>
+        <v>3.714179139508362</v>
       </c>
       <c r="C1937" t="n">
         <v>2.715258546863584</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.234271301768151</v>
+        <v>-4.23057752379594</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.021193601842576</v>
+        <v>1.02267111303146</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5032484739579083</v>
+        <v>0.4878322534795711</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.017207631238329</v>
+        <v>3.007957898951326</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417698</v>
+        <v>3.710906731417697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.852289383555786</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.289791377660741</v>
+        <v>-4.28609759968853</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.136016408177742</v>
+        <v>1.137493919366627</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5032484739579083</v>
+        <v>0.4878322534795711</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.154238467930531</v>
+        <v>3.144988735643529</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205893</v>
+        <v>3.746042526205891</v>
       </c>
       <c r="C1939" t="n">
         <v>2.856856615547574</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.114317117868271</v>
+        <v>-4.11062333989606</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.210773344086518</v>
+        <v>1.212250855275403</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5032484739579083</v>
+        <v>0.4878322534795711</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.158805699922319</v>
+        <v>3.149555967635317</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225437</v>
+        <v>3.765024323225435</v>
       </c>
       <c r="C1940" t="n">
         <v>2.832598644308781</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.106392743283357</v>
+        <v>-4.102698965311146</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.189685122681691</v>
+        <v>1.191162633870575</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5032484739579083</v>
+        <v>0.4878322534795711</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.134547728683526</v>
+        <v>3.125297996396524</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.773210297111289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.761136957710231</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.100114540713508</v>
+        <v>-4.096420762741297</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.12073471711108</v>
+        <v>1.122212228299965</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5095266765277573</v>
+        <v>0.4941104560494202</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.066852963626885</v>
+        <v>3.057603231339883</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.771309344142363</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.040261921509785</v>
+        <v>-4.036568143537574</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.154848151224702</v>
+        <v>1.156325662413586</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5095266765277573</v>
+        <v>0.4941104560494202</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.077025350059018</v>
+        <v>3.067775617772015</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.766255614716223</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.954018458483407</v>
+        <v>-3.950324680511196</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.184291807009113</v>
+        <v>1.185769318197998</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5095266765277573</v>
+        <v>0.4941104560494202</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.071971620632878</v>
+        <v>3.062721888345876</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316044</v>
+        <v>3.752027499316042</v>
       </c>
       <c r="C1944" t="n">
         <v>2.758031390160749</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.999325277882387</v>
+        <v>-3.995631499910176</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.157944854694047</v>
+        <v>1.159422365882931</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.4687165135185265</v>
+        <v>0.4533002930401894</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.039261298271865</v>
+        <v>3.030011565984863</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.75858326319385</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.028358382584688</v>
+        <v>-4.024664604612477</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.146883485846228</v>
+        <v>1.148360997035113</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.4687165135185265</v>
+        <v>0.4533002930401894</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.039813171304967</v>
+        <v>3.030563439017965</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.687855955085216</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.935547901133829</v>
+        <v>-3.931854123161618</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.113280370317937</v>
+        <v>1.114757881506822</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5615269949693859</v>
+        <v>0.5461107744910487</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.024772152066848</v>
+        <v>3.015522419779846</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560423</v>
+        <v>3.74828581656042</v>
       </c>
       <c r="C1947" t="n">
         <v>2.689729431009817</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.979937370463257</v>
+        <v>-3.976243592491045</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.097398058510767</v>
+        <v>1.098875569699651</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5171375256399582</v>
+        <v>0.5017213051616211</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.000011946393792</v>
+        <v>2.99076221410679</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472735</v>
+        <v>3.721077195472732</v>
       </c>
       <c r="C1948" t="n">
         <v>2.68480513952154</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.0964789755686</v>
+        <v>-4.092785197596388</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.045857124980353</v>
+        <v>1.047334636169237</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4005959205346154</v>
+        <v>0.3851797000562783</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.925162691842309</v>
+        <v>2.915912959555307</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.74304760379853</v>
       </c>
       <c r="C1949" t="n">
         <v>2.690296435352207</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.136403070151172</v>
+        <v>-4.13270929217896</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.035378782977991</v>
+        <v>1.036856294166876</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4005959205346154</v>
+        <v>0.3851797000562783</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.930653987672977</v>
+        <v>2.921404255385974</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498856</v>
       </c>
       <c r="C1950" t="n">
         <v>2.701793637120746</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.164183468052524</v>
+        <v>-4.160489690080313</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.035763825585989</v>
+        <v>1.037241336774874</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.3728155226332623</v>
+        <v>0.3573993021549252</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.925482950700704</v>
+        <v>2.916233218413702</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170532</v>
+        <v>3.643069621705316</v>
       </c>
       <c r="C1951" t="n">
         <v>2.5401493571214</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.282564140782663</v>
+        <v>-4.278870362810451</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8267672764945873</v>
+        <v>0.8282447876834718</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3055976704822861</v>
+        <v>0.290181450003949</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.723507959410771</v>
+        <v>2.714258227123769</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729264</v>
+        <v>3.682716310729261</v>
       </c>
       <c r="C1952" t="n">
         <v>2.660299017840605</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.391178219225994</v>
+        <v>-4.387484441253783</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9034713058364603</v>
+        <v>0.9049488170253448</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3055976704822861</v>
+        <v>0.290181450003949</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.843657620129977</v>
+        <v>2.834407887842975</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190764</v>
+        <v>3.733012441190761</v>
       </c>
       <c r="C1953" t="n">
         <v>2.674812043942928</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.355769180977851</v>
+        <v>-4.35207540300564</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9321479472380405</v>
+        <v>0.933625458426925</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3055976704822861</v>
+        <v>0.290181450003949</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.8581706462323</v>
+        <v>2.848920913945298</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913418</v>
       </c>
       <c r="C1954" t="n">
         <v>2.672231485285297</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.3173855184197</v>
+        <v>-4.313691740447489</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9449208536036697</v>
+        <v>0.9463983647925542</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3439813330404373</v>
+        <v>0.3285651125621002</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.87862028510956</v>
+        <v>2.869370552822557</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.751147197532479</v>
       </c>
       <c r="C1955" t="n">
         <v>2.668960514130599</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.140269188384534</v>
+        <v>-4.136575410412322</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.012496414463038</v>
+        <v>1.013973925651922</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3439813330404373</v>
+        <v>0.3285651125621002</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.875349313954862</v>
+        <v>2.866099581667859</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793896</v>
       </c>
       <c r="C1956" t="n">
         <v>2.669643905892512</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.18536143321808</v>
+        <v>-4.181667655245868</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9951429082915328</v>
+        <v>0.9966204194804174</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.2820852898710475</v>
+        <v>0.2666690693927104</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.838895079815141</v>
+        <v>2.829645347528138</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011227</v>
       </c>
       <c r="C1957" t="n">
         <v>2.663430881198926</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.005986011979312</v>
+        <v>-4.002292234007101</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.060680052093454</v>
+        <v>1.062157563282339</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4388620480417662</v>
+        <v>0.4234458275634291</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.926748110023986</v>
+        <v>2.917498377736984</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982225</v>
+        <v>3.716991718982221</v>
       </c>
       <c r="C1958" t="n">
         <v>2.644238336530516</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.051000225499918</v>
+        <v>-4.047306447527706</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.023481822016802</v>
+        <v>1.024959333205686</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4085131527271616</v>
+        <v>0.3930969322488245</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.889346228166813</v>
+        <v>2.880096495879811</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.73702660850953</v>
       </c>
       <c r="C1959" t="n">
         <v>2.649929898869462</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.318004735772353</v>
+        <v>-4.314310957800141</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9223715802467733</v>
+        <v>0.9238490914356579</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.214150114684213</v>
+        <v>0.1987338942058759</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.77841996767999</v>
+        <v>2.769170235392988</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.649133820765963</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.419202517209525</v>
+        <v>-4.415508739237314</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8810963895684059</v>
+        <v>0.8825739007572904</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.1457413011388938</v>
+        <v>0.1303250806605567</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.7365786014493</v>
+        <v>2.727328869162298</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815451</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64673378232028</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.412691550595213</v>
+        <v>-4.408997772623001</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8813007377684476</v>
+        <v>0.8827782489573321</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.1457413011388938</v>
+        <v>0.1303250806605567</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.734178563003617</v>
+        <v>2.724928830716614</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378097</v>
       </c>
       <c r="C1962" t="n">
         <v>2.643258501528525</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.393653422887915</v>
+        <v>-4.389959644915704</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8854407080596114</v>
+        <v>0.8869182192484959</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.08755768980769929</v>
+        <v>0.07214146932936216</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.695793115413144</v>
+        <v>2.686543383126142</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131245</v>
       </c>
       <c r="C1963" t="n">
         <v>2.762552903162715</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.446169225162736</v>
+        <v>-4.442475447190525</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9837287887838735</v>
+        <v>0.985206299972758</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.08755768980769929</v>
+        <v>0.07214146932936216</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.815087517047335</v>
+        <v>2.805837784760333</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067859</v>
       </c>
       <c r="C1964" t="n">
         <v>2.763386232148849</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.460035986496654</v>
+        <v>-4.456342208524442</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9790154132364399</v>
+        <v>0.9804929244253244</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.04969977307387635</v>
+        <v>0.03428355259553922</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.793206095993175</v>
+        <v>2.783956363706173</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789116</v>
       </c>
       <c r="C1965" t="n">
         <v>2.769394762545775</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.415231814956724</v>
+        <v>-4.411538036984513</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.002945612249338</v>
+        <v>1.004423123438222</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.04969977307387635</v>
+        <v>0.03428355259553922</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.799214626390101</v>
+        <v>2.789964894103099</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519903</v>
       </c>
       <c r="C1966" t="n">
         <v>2.667344983822974</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.267488844721721</v>
+        <v>-4.26379506674951</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9599930216205383</v>
+        <v>0.9614705328094229</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2175071303087595</v>
+        <v>0.2020909098304224</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.79784926200823</v>
+        <v>2.788599529721228</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.670138605354455</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.35131006599642</v>
+        <v>-4.347616288024208</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9292581546421399</v>
+        <v>0.9307356658310244</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2175071303087595</v>
+        <v>0.2020909098304224</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.800642883539711</v>
+        <v>2.791393151252709</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
         <v>2.670800953746113</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.345157359943635</v>
+        <v>-4.341463581971424</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.932381585454912</v>
+        <v>0.9338590966437965</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2236598363615438</v>
+        <v>0.2082436158832067</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.80499685556304</v>
+        <v>2.795747123276038</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890607</v>
       </c>
       <c r="C1969" t="n">
         <v>2.669881430486224</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.361966658094137</v>
+        <v>-4.358272880121926</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9247383429348215</v>
+        <v>0.926215854123706</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2068505382110422</v>
+        <v>0.191434317732705</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.793991753412849</v>
+        <v>2.784742021125847</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798418</v>
       </c>
       <c r="C1970" t="n">
         <v>2.736216984283045</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.299668659318015</v>
+        <v>-4.295974881345804</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.015993096242091</v>
+        <v>1.017470607430976</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2521448024854842</v>
+        <v>0.2367285820071471</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.887503865774335</v>
+        <v>2.878254133487333</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992185</v>
       </c>
       <c r="C1971" t="n">
         <v>2.538508985997172</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.097878461652857</v>
+        <v>-4.094184683680646</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8990011770222817</v>
+        <v>0.9004786882111662</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4501629946546386</v>
+        <v>0.4347467741763015</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.808606782789955</v>
+        <v>2.799357050502953</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852419</v>
       </c>
       <c r="C1972" t="n">
         <v>2.608799218319347</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.148765174339052</v>
+        <v>-4.14507139636684</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9489367242699789</v>
+        <v>0.9504142354588634</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.3992762819684441</v>
+        <v>0.3838600614901069</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.848364987500414</v>
+        <v>2.839115255213411</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319538</v>
       </c>
       <c r="C1973" t="n">
         <v>2.623426954435391</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.062154431689245</v>
+        <v>-4.058460653717034</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9982087574459453</v>
+        <v>0.9996862686348298</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.4779020131736023</v>
+        <v>0.4624857926952652</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.910168162339552</v>
+        <v>2.90091843005255</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489378</v>
       </c>
       <c r="C1974" t="n">
         <v>2.621962935260062</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.12236372969453</v>
+        <v>-4.118669951722318</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.972661019068503</v>
+        <v>0.9741385302573875</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4176927151683178</v>
+        <v>0.4022764946899807</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.872578564361053</v>
+        <v>2.863328832074051</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397787</v>
       </c>
       <c r="C1975" t="n">
         <v>2.620454553299991</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.045941683262603</v>
+        <v>-4.042247905290392</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.001721455681202</v>
+        <v>1.003198966870087</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4176927151683178</v>
+        <v>0.4022764946899807</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.871070182400982</v>
+        <v>2.861820450113979</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316242</v>
       </c>
       <c r="C1976" t="n">
         <v>2.620317420735427</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.001568551624034</v>
+        <v>-3.997874773651823</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.019333575772066</v>
+        <v>1.020811086960951</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4620658468068864</v>
+        <v>0.4466496263285493</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.897556928819559</v>
+        <v>2.888307196532557</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
         <v>2.614711214874017</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.024048902482919</v>
+        <v>-4.020355124510708</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.004735229567103</v>
+        <v>1.006212740755987</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4620658468068864</v>
+        <v>0.4466496263285493</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.89195072295815</v>
+        <v>2.882700990671147</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190319</v>
       </c>
       <c r="C1978" t="n">
         <v>2.621092971901822</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.976393171921863</v>
+        <v>-3.972699393949652</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.03017927881933</v>
+        <v>1.031656790008214</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.509721577367942</v>
+        <v>0.494305356889605</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.926925918322588</v>
+        <v>2.917676186035585</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569611</v>
       </c>
       <c r="C1979" t="n">
         <v>2.625985345276547</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.875875013423109</v>
+        <v>-3.872181235450897</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.075278915593556</v>
+        <v>1.076756426782441</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6102397358666966</v>
+        <v>0.5948235153883595</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.992129186796565</v>
+        <v>2.982879454509563</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557288</v>
       </c>
       <c r="C1980" t="n">
         <v>2.612740017752419</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.859969683990756</v>
+        <v>-3.856275906018545</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.068395719842369</v>
+        <v>1.069873231031254</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5311270751574577</v>
+        <v>0.5157108546791207</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.931416262846894</v>
+        <v>2.922166530559892</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932762</v>
       </c>
       <c r="C1981" t="n">
         <v>2.616837720363048</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.815131282382358</v>
+        <v>-3.811437504410147</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.090428783096357</v>
+        <v>1.091906294285242</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5356705081023272</v>
+        <v>0.5202542876239902</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.938240025224444</v>
+        <v>2.928990292937442</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491705</v>
+        <v>3.817932354917044</v>
       </c>
       <c r="C1982" t="n">
         <v>2.620998659994126</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.834629738624366</v>
+        <v>-3.830935960652155</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.086790340230632</v>
+        <v>1.088267851419517</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4875858668224229</v>
+        <v>0.4721696463440859</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.91355018008758</v>
+        <v>2.904300447800578</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405952</v>
       </c>
       <c r="C1983" t="n">
         <v>2.626878262521963</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.790426901538466</v>
+        <v>-3.786733123566254</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.110351077592829</v>
+        <v>1.111828588781714</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5317887039083233</v>
+        <v>0.5163724834299863</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.945951484866957</v>
+        <v>2.936701752579955</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265636</v>
       </c>
       <c r="C1984" t="n">
         <v>2.62528826299121</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.797986567375513</v>
+        <v>-3.794292789403301</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.105737211727258</v>
+        <v>1.107214722916143</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5865921079181426</v>
+        <v>0.5711758874398056</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.977243527742096</v>
+        <v>2.967993795455094</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284871</v>
       </c>
       <c r="C1985" t="n">
         <v>2.67653602817425</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.63969514983624</v>
+        <v>-3.636001371864029</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.220301543926007</v>
+        <v>1.221779055114891</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5865921079181426</v>
+        <v>0.5711758874398056</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.028491292925136</v>
+        <v>3.019241560638134</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321015</v>
       </c>
       <c r="C1986" t="n">
         <v>2.674976732768503</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.432053146201764</v>
+        <v>-3.428359368229553</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.30179904997405</v>
+        <v>1.303276561162935</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7942341115526188</v>
+        <v>0.7788178910742818</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.151517199700075</v>
+        <v>3.142267467413073</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475131</v>
       </c>
       <c r="C1987" t="n">
         <v>2.669924961006773</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.381021053479236</v>
+        <v>-3.377327275507025</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.317160115301331</v>
+        <v>1.318637626490216</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8452662042751468</v>
+        <v>0.8298499837968097</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.177084683571862</v>
+        <v>3.167834951284859</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404845</v>
       </c>
       <c r="C1988" t="n">
         <v>2.687112365099478</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.31579687235203</v>
+        <v>-3.312103094379819</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.360437191844919</v>
+        <v>1.361914703033803</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9104903854023524</v>
+        <v>0.8950741649240154</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.23340659634089</v>
+        <v>3.224156864053888</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882549</v>
       </c>
       <c r="C1989" t="n">
         <v>2.683073337398759</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.278369852280897</v>
+        <v>-3.274676074308685</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.371368972172653</v>
+        <v>1.372846483361537</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.915741923431534</v>
+        <v>0.900325702953197</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.232518491457679</v>
+        <v>3.223268759170677</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992653</v>
       </c>
       <c r="C1990" t="n">
         <v>2.684330129729999</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.298481508315605</v>
+        <v>-3.294787730343394</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.36458110209001</v>
+        <v>1.366058613278894</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9267692684289532</v>
+        <v>0.9113530479506162</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.240391690787371</v>
+        <v>3.231141958500369</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636279</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84488790075121</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.270068245215721</v>
+        <v>-3.26637446724351</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.536504178351174</v>
+        <v>1.537981689540058</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8677937056825245</v>
+        <v>0.8523774852041874</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.365564124160724</v>
+        <v>3.356314391873722</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957617</v>
       </c>
       <c r="C1992" t="n">
         <v>2.965000809969027</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.195285984190709</v>
+        <v>-3.191592206218497</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.686529991978996</v>
+        <v>1.688007503167881</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9425759667075371</v>
+        <v>0.9271597462292001</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.530546389993549</v>
+        <v>3.521296657706547</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998748</v>
       </c>
       <c r="C1993" t="n">
         <v>2.956708785982886</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.169201899926901</v>
+        <v>-3.165508121954689</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.688671601698378</v>
+        <v>1.690149112887263</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9425759667075371</v>
+        <v>0.9271597462292001</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.522254366007408</v>
+        <v>3.513004633720406</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896922</v>
       </c>
       <c r="C1994" t="n">
         <v>2.954901981566665</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.08132398681778</v>
+        <v>-3.077630208845569</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.722015962525806</v>
+        <v>1.723493473714691</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.058501609130888</v>
+        <v>1.043085388652551</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.590002947045198</v>
+        <v>3.580753214758196</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.79626414395985</v>
       </c>
       <c r="C1995" t="n">
         <v>2.972456387293457</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.072431525424497</v>
+        <v>-3.195556838256929</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.743127352809911</v>
+        <v>1.693877227676938</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.058501609130888</v>
+        <v>1.043085388652551</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.60755735277199</v>
+        <v>3.598307620484988</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945362</v>
+        <v>3.794424941945358</v>
       </c>
       <c r="C1996" t="n">
         <v>2.964311434698041</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.240907642394375</v>
+        <v>-3.364032955226807</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.667591953426544</v>
+        <v>1.618341828293571</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.030553773414307</v>
+        <v>1.01513755293597</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.582643698746625</v>
+        <v>3.573393966459623</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782701</v>
       </c>
       <c r="C1997" t="n">
         <v>2.945581131885902</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.794651449764935</v>
+        <v>-2.917776762597367</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.827364127666181</v>
+        <v>1.778114002533208</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9358351037446746</v>
+        <v>0.9204188832663376</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.507082194132707</v>
+        <v>3.497832461845705</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.78467134563263</v>
       </c>
       <c r="C1998" t="n">
         <v>2.936245154382807</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.771930346081782</v>
+        <v>-2.895055658914215</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.827116591636347</v>
+        <v>1.777866466503374</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9358351037446746</v>
+        <v>0.9204188832663376</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.497746216629612</v>
+        <v>3.48849648434261</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777666</v>
       </c>
       <c r="C1999" t="n">
         <v>3.095151280233976</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.901132159375825</v>
+        <v>-3.024257472208257</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.934341992169899</v>
+        <v>1.885091867036926</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8066332904506324</v>
+        <v>0.7912170699722954</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.579131254504356</v>
+        <v>3.569881522217353</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644406</v>
       </c>
       <c r="C2000" t="n">
         <v>3.132229102727623</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.92700655784985</v>
+        <v>-3.050131870682283</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.961070055273935</v>
+        <v>1.911819930140962</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.8515448991623735</v>
+        <v>0.8361286786840365</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.643156042225047</v>
+        <v>3.633906309938045</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799958</v>
       </c>
       <c r="C2001" t="n">
         <v>3.128904458717168</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.919951867634677</v>
+        <v>-3.04307718046711</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.96056728734955</v>
+        <v>1.911317162216577</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8585995893775473</v>
+        <v>0.8431833688992103</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.644064212343697</v>
+        <v>3.634814480056694</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331109</v>
       </c>
       <c r="C2002" t="n">
         <v>3.138910612361909</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.893000643308189</v>
+        <v>-3.016125956140622</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.981353930724887</v>
+        <v>1.932103805591913</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8734799354052665</v>
+        <v>0.8580637149269295</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.662998573605069</v>
+        <v>3.653748841318067</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784101</v>
       </c>
       <c r="C2003" t="n">
         <v>3.323013744506869</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.028953651364505</v>
+        <v>-3.152078964196938</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.11107585964732</v>
+        <v>2.061825734514347</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8734799354052665</v>
+        <v>0.8580637149269295</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.847101705750029</v>
+        <v>3.837851973463027</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.74392550571442</v>
       </c>
       <c r="C2004" t="n">
         <v>3.315130439409862</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.051361769169377</v>
+        <v>-3.17448708200181</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.094229307428364</v>
+        <v>2.044979182295391</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8734799354052665</v>
+        <v>0.8580637149269295</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.839218400653023</v>
+        <v>3.82996866836602</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155026</v>
       </c>
       <c r="C2005" t="n">
         <v>3.3171844389595</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.079586004746977</v>
+        <v>-3.20271131757941</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.084993612746961</v>
+        <v>2.035743487613988</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.8914566878565751</v>
+        <v>0.876040467378238</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.852058451673445</v>
+        <v>3.842808719386443</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.72945228516197</v>
       </c>
       <c r="C2006" t="n">
         <v>3.373438156681347</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.227050462234454</v>
+        <v>-3.21215224346794</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.082261547473818</v>
+        <v>2.088220834980423</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8724848518496786</v>
+        <v>0.9984675849216296</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.896929067791154</v>
+        <v>3.972518707634324</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321627</v>
       </c>
       <c r="C2007" t="n">
         <v>3.376329251226648</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.279324069570096</v>
+        <v>-3.264425850803581</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.064243199084862</v>
+        <v>2.070202486591468</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8202112445140374</v>
+        <v>0.9461939775859883</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.86845599793507</v>
+        <v>3.944045637778241</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347696</v>
       </c>
       <c r="C2008" t="n">
         <v>3.374441064120423</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.355654047171002</v>
+        <v>-3.340755828404487</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.031823020938275</v>
+        <v>2.03778230844488</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8202112445140374</v>
+        <v>0.9461939775859883</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.866567810828845</v>
+        <v>3.942157450672016</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887741</v>
       </c>
       <c r="C2009" t="n">
         <v>3.369261293723285</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.557907767495355</v>
+        <v>-3.543009548728841</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.945741762411396</v>
+        <v>1.951701049918002</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.617957524189684</v>
+        <v>0.7439402572616349</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.740035808237096</v>
+        <v>3.815625448080266</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.71289761234306</v>
       </c>
       <c r="C2010" t="n">
         <v>3.367695303933437</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.71947619302261</v>
+        <v>-3.704577974256096</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.879548402410646</v>
+        <v>1.885507689917252</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.4911746003918046</v>
+        <v>0.6171573334637556</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.662400064168521</v>
+        <v>3.737989704011691</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389342</v>
       </c>
       <c r="C2011" t="n">
         <v>3.380768710799356</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.82777685489273</v>
+        <v>-3.812878636126215</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.849301544528517</v>
+        <v>1.855260832035123</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.4911746003918046</v>
+        <v>0.6171573334637556</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.675473471034439</v>
+        <v>3.75106311087761</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378386</v>
       </c>
       <c r="C2012" t="n">
         <v>3.372773907582296</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.920924326196096</v>
+        <v>-3.906026107429582</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.80404775279011</v>
+        <v>1.810007040296716</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3683453891092718</v>
+        <v>0.4943281221812228</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.59378114104786</v>
+        <v>3.66937078089103</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.71581989500697</v>
       </c>
       <c r="C2013" t="n">
         <v>3.371297948709298</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.948825113305569</v>
+        <v>-3.933926894539055</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.791411479073323</v>
+        <v>1.797370766579929</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.333748464966337</v>
+        <v>0.459731198038288</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.571547027689101</v>
+        <v>3.647136667532271</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787382</v>
       </c>
       <c r="C2014" t="n">
         <v>3.368062392686497</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.071351216008463</v>
+        <v>-4.056452997241949</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.739165481969364</v>
+        <v>1.74512476947597</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2112223622634432</v>
+        <v>0.3372050953353941</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.494795810044563</v>
+        <v>3.570385449887734</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585932</v>
       </c>
       <c r="C2015" t="n">
         <v>3.434768352277001</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.301865712194052</v>
+        <v>-4.286967493427538</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.713665643085633</v>
+        <v>1.719624930592238</v>
       </c>
       <c r="F2015" t="n">
-        <v>-0.01929213392214557</v>
+        <v>0.1066905991498054</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.423193071923714</v>
+        <v>3.498782711766884</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814663</v>
+        <v>3.640750087814659</v>
       </c>
       <c r="C2016" t="n">
         <v>3.575080071278848</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.558586530188876</v>
+        <v>-4.543688311422361</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.75128903488955</v>
+        <v>1.757248322396156</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.1277067080659604</v>
+        <v>-0.001723974994009447</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.498456046439272</v>
+        <v>3.574045686282442</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237091</v>
+        <v>3.668289004237088</v>
       </c>
       <c r="C2017" t="n">
         <v>3.644060340424487</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.712572947965016</v>
+        <v>-4.697674729198502</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.758674736924734</v>
+        <v>1.764634024431339</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.1277067080659604</v>
+        <v>-0.001723974994009447</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.567436315584911</v>
+        <v>3.643025955428082</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423384</v>
+        <v>3.619923016423381</v>
       </c>
       <c r="C2018" t="n">
         <v>3.630111542544608</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.662051044137351</v>
+        <v>-4.647152825370836</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.764934700575921</v>
+        <v>1.770893988082527</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.1277067080659604</v>
+        <v>-0.001723974994009447</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.553487517705032</v>
+        <v>3.629077157548203</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609747</v>
       </c>
       <c r="C2019" t="n">
         <v>3.641982031600022</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.914526198145075</v>
+        <v>-4.89962797937856</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.675815128028245</v>
+        <v>1.681774415534851</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.1277067080659604</v>
+        <v>-0.001723974994009447</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.565358006760446</v>
+        <v>3.640947646603617</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973151</v>
       </c>
       <c r="C2020" t="n">
         <v>3.643192566118966</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.207421954624487</v>
+        <v>-5.192523735857972</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.559867359955424</v>
+        <v>1.56582664746203</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.1277067080659604</v>
+        <v>-0.001723974994009447</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.56656854127939</v>
+        <v>3.642158181122561</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.66350945725194</v>
       </c>
       <c r="C2021" t="n">
         <v>3.647314308346287</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.394086082759295</v>
+        <v>-5.37918786399278</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.489323450928822</v>
+        <v>1.495282738435428</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1544456788905203</v>
+        <v>-0.02846294581856934</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.554646901011975</v>
+        <v>3.630236540855146</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916199</v>
+        <v>3.652149152916196</v>
       </c>
       <c r="C2022" t="n">
         <v>3.642392161082477</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.540106769673257</v>
+        <v>-5.525208550906743</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.425993028899426</v>
+        <v>1.431952316406032</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.1635287706843773</v>
+        <v>-0.03754603761242631</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.544274898671851</v>
+        <v>3.619864538515021</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830323</v>
       </c>
       <c r="C2023" t="n">
         <v>3.804596217781521</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.631820778782842</v>
+        <v>-5.616922560016327</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.551511481954637</v>
+        <v>1.557470769461243</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.1635287706843773</v>
+        <v>-0.03754603761242631</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.706478955370895</v>
+        <v>3.782068595214065</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.696539468071545</v>
       </c>
       <c r="C2024" t="n">
         <v>3.799442855745335</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.663472437842811</v>
+        <v>-5.648574219076297</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.533697456294463</v>
+        <v>1.539656743801069</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.1686972279288175</v>
+        <v>-0.04271449485686651</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.698224518988045</v>
+        <v>3.773814158831216</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.75004401586814</v>
       </c>
       <c r="C2025" t="n">
         <v>3.809672273313826</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.745407256111695</v>
+        <v>-5.73050903734518</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.511152946555401</v>
+        <v>1.517112234062007</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1786319735158977</v>
+        <v>-0.0526492404439467</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.702493089204288</v>
+        <v>3.778082729047458</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332685</v>
       </c>
       <c r="C2026" t="n">
         <v>3.818597911769729</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.847383378360102</v>
+        <v>-5.832485159593587</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.47928813611194</v>
+        <v>1.485247423618546</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2806080957643052</v>
+        <v>-0.1546253626923543</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.650233054311146</v>
+        <v>3.725822694154316</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231802</v>
       </c>
       <c r="C2027" t="n">
         <v>3.810750799013904</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.737377094882881</v>
+        <v>-5.722478876116366</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.515443536747004</v>
+        <v>1.52140282425361</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.25740352384703</v>
+        <v>-0.1314207907750791</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.656308684705686</v>
+        <v>3.731898324548857</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818517</v>
       </c>
       <c r="C2028" t="n">
         <v>3.815000809735878</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.594317519141955</v>
+        <v>-5.57941930037544</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.576917377765349</v>
+        <v>1.582876665271955</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.2493900972570507</v>
+        <v>-0.1234073641850998</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.665366751381648</v>
+        <v>3.740956391224818</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051782</v>
       </c>
       <c r="C2029" t="n">
         <v>3.822261692618414</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.292870793670117</v>
+        <v>-5.277972574903602</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.70475695083662</v>
+        <v>1.710716238343226</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.05205662821478652</v>
+        <v>0.1780393612867375</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.853495669547287</v>
+        <v>3.929085309390457</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679619</v>
       </c>
       <c r="C2030" t="n">
         <v>3.823232870371125</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.317461037905301</v>
+        <v>-5.302562819138786</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.695892030895257</v>
+        <v>1.701851318401863</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.05205662821478652</v>
+        <v>0.1780393612867375</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.854466847299997</v>
+        <v>3.930056487143168</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474154</v>
       </c>
       <c r="C2031" t="n">
         <v>3.82407577475088</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.266422661898781</v>
+        <v>-5.251524443132266</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.717150285677621</v>
+        <v>1.723109573184227</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.05205662821478652</v>
+        <v>0.1780393612867375</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.855309751679753</v>
+        <v>3.930899391522924</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969537</v>
       </c>
       <c r="C2032" t="n">
         <v>3.843113873625026</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.22528336703215</v>
+        <v>-5.210385148265635</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.752644102498419</v>
+        <v>1.758603390005025</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.09319592308141733</v>
+        <v>0.2191786561533683</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.899031427473877</v>
+        <v>3.974621067317047</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700473</v>
       </c>
       <c r="C2033" t="n">
         <v>3.65929786974896</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.12864845501351</v>
+        <v>-5.113750236246995</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.607482063429809</v>
+        <v>1.613441350936415</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.1898308351000573</v>
+        <v>0.3158135681720082</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.773196370808995</v>
+        <v>3.848786010652166</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077634</v>
       </c>
       <c r="C2034" t="n">
         <v>3.662799913822925</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.259229189544352</v>
+        <v>-5.244330970777837</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.558751813691436</v>
+        <v>1.564711101198042</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.05925010056921476</v>
+        <v>0.1852328336411657</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.698349974164454</v>
+        <v>3.773939614007624</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833451</v>
       </c>
       <c r="C2035" t="n">
         <v>3.647226732899007</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.09473285535339</v>
+        <v>-5.079834636586876</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.608977166443904</v>
+        <v>1.61493645395051</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.2237464347601766</v>
+        <v>0.3497291678321276</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.781474593755113</v>
+        <v>3.857064233598284</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077623</v>
       </c>
       <c r="C2036" t="n">
         <v>3.646414443335437</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.122102788037822</v>
+        <v>-5.107204569271308</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.597216903806561</v>
+        <v>1.603176191313167</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.2237464347601766</v>
+        <v>0.3497291678321276</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.780662304191543</v>
+        <v>3.856251944034714</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147903</v>
       </c>
       <c r="C2037" t="n">
         <v>3.656283222460509</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.132487982927712</v>
+        <v>-5.117589764161197</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.602931604975677</v>
+        <v>1.608890892482283</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2133612398702873</v>
+        <v>0.3393439729422383</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.784299966382682</v>
+        <v>3.859889606225853</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735275</v>
       </c>
       <c r="C2038" t="n">
         <v>3.727120228236934</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.151076141649937</v>
+        <v>-5.136177922883422</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.666333347263212</v>
+        <v>1.672292634769818</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.194773081148062</v>
+        <v>0.3207558142200129</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.843984076925772</v>
+        <v>3.919573716768943</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496548</v>
       </c>
       <c r="C2039" t="n">
         <v>3.723989239055233</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.151374688345973</v>
+        <v>-5.136476469579458</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.663082939403096</v>
+        <v>1.669042226909702</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.1944745344520261</v>
+        <v>0.320457267523977</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.840673959726449</v>
+        <v>3.91626359956962</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.81564321210885</v>
       </c>
       <c r="C2040" t="n">
         <v>3.728520133994624</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.050551554655545</v>
+        <v>-5.03565333588903</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.707943087818659</v>
+        <v>1.713902375325265</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2069387499363799</v>
+        <v>0.3329214830083309</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.852683383956453</v>
+        <v>3.928273023799624</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121459</v>
       </c>
       <c r="C2041" t="n">
         <v>3.728649387473168</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.859770193903138</v>
+        <v>-4.844871975136623</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.784384885598165</v>
+        <v>1.790344173104771</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.3977201106887873</v>
+        <v>0.5237028437607383</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.96728145388644</v>
+        <v>4.042871093729611</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906073</v>
       </c>
       <c r="C2042" t="n">
         <v>3.708486233210764</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.841253339861318</v>
+        <v>-4.826355121094803</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.77162847295249</v>
+        <v>1.777587760459096</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.4106502401139955</v>
+        <v>0.5366329731859465</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.954876377279161</v>
+        <v>4.030466017122333</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912978</v>
       </c>
       <c r="C2043" t="n">
         <v>3.743453169822823</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.785922751959555</v>
+        <v>-4.771024533193041</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.828727644725253</v>
+        <v>1.834686932231859</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.4659808280157576</v>
+        <v>0.5919635610877086</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.023041666632277</v>
+        <v>4.098631306475448</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.743767956539887</v>
       </c>
       <c r="C2044" t="n">
         <v>3.73713973772426</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.773868625046592</v>
+        <v>-4.758970406280078</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.827235863391876</v>
+        <v>1.833195150898482</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.4780349549287204</v>
+        <v>0.6040176880006715</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.023960710681493</v>
+        <v>4.099550350524663</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811002</v>
       </c>
       <c r="C2045" t="n">
         <v>3.739020367908396</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.815023744614813</v>
+        <v>-4.800125525848299</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.812654445748723</v>
+        <v>1.818613733255329</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.4368798353604995</v>
+        <v>0.5628625684324505</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.001148269124696</v>
+        <v>4.076737908967867</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382913</v>
       </c>
       <c r="C2046" t="n">
         <v>3.751871393786279</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.712143155086221</v>
+        <v>-4.697244936319706</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.866657707438043</v>
+        <v>1.872616994944649</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.5397604248890924</v>
+        <v>0.6657431579610434</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.075727648719734</v>
+        <v>4.151317288562905</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760312</v>
+        <v>3.646857607760309</v>
       </c>
       <c r="C2047" t="n">
         <v>3.772074063959873</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.943743548255721</v>
+        <v>-4.928845329489207</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.794220220343837</v>
+        <v>1.800179507850443</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.5397604248890924</v>
+        <v>0.6657431579610434</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.095930318893329</v>
+        <v>4.171519958736499</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781703</v>
+        <v>3.666767386781699</v>
       </c>
       <c r="C2048" t="n">
         <v>3.772074063959873</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.961816056547333</v>
+        <v>-4.946917837780818</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.786991217027192</v>
+        <v>1.792950504533798</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.5397604248890924</v>
+        <v>0.6657431579610434</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.095930318893329</v>
+        <v>4.171519958736499</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082832</v>
+        <v>3.670068888082828</v>
       </c>
       <c r="C2049" t="n">
         <v>3.73232597755334</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.136922889123777</v>
+        <v>-5.122024670357263</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.677200397590081</v>
+        <v>1.683159685096687</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.5397604248890924</v>
+        <v>0.6657431579610434</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.056182232486795</v>
+        <v>4.131771872329966</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.74559333394358</v>
       </c>
       <c r="C2050" t="n">
         <v>3.73934859655028</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.105636868583322</v>
+        <v>-5.090738649816807</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.696737424803203</v>
+        <v>1.702696712309809</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.5710464454295477</v>
+        <v>0.6970291785014988</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.081976463808008</v>
+        <v>4.157566103651179</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677821</v>
+        <v>3.730590658677817</v>
       </c>
       <c r="C2051" t="n">
         <v>3.838519596123184</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.952611476470038</v>
+        <v>-4.963630709633216</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.857118581221421</v>
+        <v>1.85271088795615</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.7240718375428319</v>
+        <v>0.8241371186850894</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.272962698648883</v>
+        <v>4.333001867334238</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74129851807388</v>
+        <v>3.741298518073877</v>
       </c>
       <c r="C2052" t="n">
         <v>4.025985821031476</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.980918790343308</v>
+        <v>-4.991938023506487</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.033261880580405</v>
+        <v>2.028854187315134</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.7240718375428319</v>
+        <v>0.8241371186850894</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.460428923557176</v>
+        <v>4.52046809224253</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903165</v>
+        <v>3.699135800903162</v>
       </c>
       <c r="C2053" t="n">
         <v>3.995388772385558</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.14751201545683</v>
+        <v>-5.158531248620009</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.936027541889079</v>
+        <v>1.931619848623808</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.5574786124293094</v>
+        <v>0.657543893571567</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.329875939843144</v>
+        <v>4.389915108528498</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.70820270456838</v>
+        <v>3.708202704568376</v>
       </c>
       <c r="C2054" t="n">
         <v>3.999065175047276</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.97444763607453</v>
+        <v>-4.985466869237709</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.008929696303717</v>
+        <v>2.004522003038445</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.5574786124293094</v>
+        <v>0.657543893571567</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.333552342504862</v>
+        <v>4.393591511190216</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682201</v>
+        <v>3.740601586682198</v>
       </c>
       <c r="C2055" t="n">
         <v>3.996683230170771</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.945201655618834</v>
+        <v>-4.956220888782013</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.018246143609491</v>
+        <v>2.013838450344219</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.5574786124293094</v>
+        <v>0.657543893571567</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.331170397628357</v>
+        <v>4.391209566313711</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539104</v>
+        <v>3.699424827539101</v>
       </c>
       <c r="C2056" t="n">
         <v>3.993976469328406</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.052127203496685</v>
+        <v>-5.063146436659864</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.972769163615985</v>
+        <v>1.968361470350714</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.450553064551458</v>
+        <v>0.5506183456937156</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.264308308059281</v>
+        <v>4.324347476744636</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983735</v>
+        <v>3.689962785983731</v>
       </c>
       <c r="C2057" t="n">
         <v>3.995405271471641</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.197145762003934</v>
+        <v>-5.208164995167112</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.91619054235632</v>
+        <v>1.911782849091048</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.3055345060442095</v>
+        <v>0.4055997871864671</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.178725975098167</v>
+        <v>4.238765143783521</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969746</v>
+        <v>3.711872614969742</v>
       </c>
       <c r="C2058" t="n">
         <v>4.095336510729394</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.315487527788651</v>
+        <v>-5.32650676095183</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.968785075300186</v>
+        <v>1.964377382034914</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.3162205446070996</v>
+        <v>0.4162858257493571</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.285068837493654</v>
+        <v>4.345108006179008</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073535</v>
+        <v>3.714899237073531</v>
       </c>
       <c r="C2059" t="n">
         <v>4.093122207855332</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.366897950109359</v>
+        <v>-5.377917183272538</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.946006603497841</v>
+        <v>1.94159891023257</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.3162205446070996</v>
+        <v>0.4162858257493571</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.282854534619593</v>
+        <v>4.342893703304947</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720062</v>
+        <v>3.704778134720058</v>
       </c>
       <c r="C2060" t="n">
         <v>4.093025335929622</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.446317401317111</v>
+        <v>-5.457336634480289</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.91414195108903</v>
+        <v>1.909734257823759</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.3162205446070996</v>
+        <v>0.4162858257493571</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.282757662693882</v>
+        <v>4.342796831379236</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581129</v>
+        <v>3.736825137581126</v>
       </c>
       <c r="C2061" t="n">
         <v>4.093019229487665</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.541780399234328</v>
+        <v>-5.552799632397507</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.875950645480187</v>
+        <v>1.871542952214915</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.3162205446070996</v>
+        <v>0.4162858257493571</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.282751556251926</v>
+        <v>4.34279072493728</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500731</v>
+        <v>3.715393145500728</v>
       </c>
       <c r="C2062" t="n">
         <v>4.091115626050276</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.581800397278112</v>
+        <v>-5.592819630441291</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.858039042825284</v>
+        <v>1.853631349560013</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.2762005465633158</v>
+        <v>0.3762658277055733</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.256835953988266</v>
+        <v>4.31687512267362</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636267</v>
+        <v>3.736109598636263</v>
       </c>
       <c r="C2063" t="n">
         <v>4.096849443798003</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.637169559410306</v>
+        <v>-5.648188792573484</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.841625195720133</v>
+        <v>1.837217502454862</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.2762005465633158</v>
+        <v>0.3762658277055733</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.262569771735992</v>
+        <v>4.322608940421347</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.73684305539601</v>
+        <v>3.736843055396006</v>
       </c>
       <c r="C2064" t="n">
         <v>4.096387807140935</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.682607339241133</v>
+        <v>-5.693626572404312</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.822988447130735</v>
+        <v>1.818580753865464</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.2333555558851561</v>
+        <v>0.3334208370274137</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.236401140672029</v>
+        <v>4.296440309357384</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396419</v>
+        <v>3.790292685396415</v>
       </c>
       <c r="C2065" t="n">
         <v>4.116262199991255</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.599381882393469</v>
+        <v>-5.610401115556647</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.87615302272012</v>
+        <v>1.871745329454849</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.2333555558851561</v>
+        <v>0.3334208370274137</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.256275533522349</v>
+        <v>4.316314702207703</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299173</v>
+        <v>3.79450702929917</v>
       </c>
       <c r="C2066" t="n">
         <v>4.099962900515982</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.423091657788161</v>
+        <v>-5.43411089095134</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.93036981308697</v>
+        <v>1.925962119821699</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.2333555558851561</v>
+        <v>0.3334208370274137</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.239976234047076</v>
+        <v>4.300015402732431</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590406</v>
+        <v>3.794725278590403</v>
       </c>
       <c r="C2067" t="n">
         <v>4.102393849980028</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.239879994655066</v>
+        <v>-5.250899227818245</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.006085427804254</v>
+        <v>2.001677734538983</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.2333555558851561</v>
+        <v>0.3334208370274137</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.242407183511122</v>
+        <v>4.302446352196476</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.522386512311064</v>
+        <v>3.838354070604751</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.009037798539292</v>
+        <v>4.109453169012617</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.239879994655066</v>
+        <v>-5.21697667578629</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.006085427804254</v>
+        <v>2.022306074384354</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.2333555558851561</v>
+        <v>0.3977089841663782</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.00210159552566</v>
+        <v>4.348078559512444</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240826.xlsx
+++ b/tame_output/ON/bt/strategyON_20240826.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>32.1%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>87.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>90.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-78.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.3%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>124.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-597.3%</t>
+          <t>-616.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.9%</t>
+          <t>-48.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.1%</t>
+          <t>422.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-683.3%</t>
+          <t>-665.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-239.3%</t>
+          <t>-246.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-35.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-174.0%</t>
+          <t>-176.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-112.4%</t>
+          <t>-293.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-184.2%</t>
+          <t>-170.6%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>84.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-12.1%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.4594793927979829</v>
+        <v>-0.6472051500124485</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.937180580893785</v>
+        <v>2.862090278007999</v>
       </c>
       <c r="F1845" t="n">
         <v>1.533058604805237</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201484</v>
+        <v>3.295507330201485</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.4480901561431815</v>
+        <v>-0.6358159133576471</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.939561071674946</v>
+        <v>2.86447076878916</v>
       </c>
       <c r="F1846" t="n">
         <v>1.544447841460039</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.7005680505625875</v>
+        <v>-0.888293807777053</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.836496805412247</v>
+        <v>2.761406502526461</v>
       </c>
       <c r="F1847" t="n">
         <v>1.291969947040633</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537423</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.9906997171680189</v>
+        <v>-1.178425474382484</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.720310355368996</v>
+        <v>2.64522005248321</v>
       </c>
       <c r="F1848" t="n">
         <v>1.316051741780813</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382188</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.198703775521096</v>
+        <v>-1.386429532735562</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.642000876581691</v>
+        <v>2.566910573695904</v>
       </c>
       <c r="F1849" t="n">
         <v>1.316051741780813</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074619</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.260882186682066</v>
+        <v>-1.448607943896532</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.612210968455291</v>
+        <v>2.537120665569505</v>
       </c>
       <c r="F1850" t="n">
         <v>1.253873330619843</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911635</v>
+        <v>3.233800325911636</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.626950913826719</v>
+        <v>-1.814676671041185</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.458867776903879</v>
+        <v>2.383777474018093</v>
       </c>
       <c r="F1851" t="n">
         <v>0.88780460347519</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213491</v>
+        <v>3.223539378213492</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.835441695278403</v>
+        <v>-2.023167452492869</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.395809754061973</v>
+        <v>2.320719451176187</v>
       </c>
       <c r="F1852" t="n">
         <v>0.6793138220235055</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416041</v>
+        <v>3.231167537416042</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.082642880043625</v>
+        <v>-2.270368637258091</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.305028030564453</v>
+        <v>2.229937727678667</v>
       </c>
       <c r="F1853" t="n">
         <v>0.699467175522318</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382323</v>
+        <v>3.235981977382324</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.575027908067722</v>
+        <v>-2.762753665282188</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.109180411398547</v>
+        <v>2.034090108512761</v>
       </c>
       <c r="F1854" t="n">
         <v>0.2070821474982212</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495494</v>
+        <v>3.278199702495495</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.960208298997795</v>
+        <v>-3.14793405621226</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.953650793839381</v>
+        <v>1.878560490953594</v>
       </c>
       <c r="F1855" t="n">
         <v>0.2070821474982212</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347049</v>
+        <v>3.29913614634705</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.210078979012376</v>
+        <v>-3.397804736226842</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.855471645288164</v>
+        <v>1.780381342402378</v>
       </c>
       <c r="F1856" t="n">
         <v>0.2433448673286845</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130011</v>
+        <v>3.287377576130012</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.416590755899398</v>
+        <v>-3.604316513113863</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.768972993189614</v>
+        <v>1.693882690303827</v>
       </c>
       <c r="F1857" t="n">
         <v>0.036833090441663</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178237</v>
+        <v>3.315884374178238</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.735934830979899</v>
+        <v>-3.923660588194364</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.643008289857673</v>
+        <v>1.567917986971886</v>
       </c>
       <c r="F1858" t="n">
         <v>0.036833090441663</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207807</v>
+        <v>3.305316798207808</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.122144662255674</v>
+        <v>-4.309870419470139</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.474857244814767</v>
+        <v>1.399766941928981</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.05393984927578033</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310976</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.356838656388226</v>
+        <v>-4.544564413602691</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.369264422163837</v>
+        <v>1.29417411927805</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.04760358204652515</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006528</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.692501303618679</v>
+        <v>-4.880227060833144</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.233579954927621</v>
+        <v>1.158489652041835</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.11553456753543</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309418</v>
+        <v>3.311086391309419</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.76894563382155</v>
+        <v>-4.956671391036015</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.209489783080714</v>
+        <v>1.134399480194928</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.03508905844176807</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970899</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.134073016460297</v>
+        <v>-5.321798773674762</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.062693345031047</v>
+        <v>0.9876030421452602</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.3313998427407806</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330517</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.542661793640976</v>
+        <v>-5.730387550855441</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8980193781735339</v>
+        <v>0.8229290752877478</v>
       </c>
       <c r="F1864" t="n">
         <v>-0.739988619921459</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191731</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.656422205663841</v>
+        <v>-5.844147962878306</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.8477006458358489</v>
+        <v>0.7726103429500624</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.739988619921459</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108633</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.072814079950838</v>
+        <v>-6.260539837165303</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6791379467299272</v>
+        <v>0.6040476438441407</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.739988619921459</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097814</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.433987709767826</v>
+        <v>-6.621713466982291</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5449271854718107</v>
+        <v>0.4698368825860246</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.739988619921459</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094109</v>
+        <v>3.37443904309411</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.777246229410845</v>
+        <v>-6.96497198662531</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4037233427602986</v>
+        <v>0.3286330398745121</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.739988619921459</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199278</v>
+        <v>3.405960511199279</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.825449046653189</v>
+        <v>-7.013174803867654</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3828471359183618</v>
+        <v>0.3077568330325757</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.739988619921459</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969586</v>
+        <v>3.424633354969587</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.122110388463386</v>
+        <v>-7.309836145677851</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2679615751234912</v>
+        <v>0.1928712722377051</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.8087317556553376</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923078</v>
+        <v>3.419979433923079</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.308830096772689</v>
+        <v>-7.496555853987154</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1892473872653668</v>
+        <v>0.1141570843795807</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.8087317556553376</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297741</v>
+        <v>3.458100091297742</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.69183148551532</v>
+        <v>-7.879557242729785</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.03594473044673041</v>
+        <v>-0.0391455724390557</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.8087317556553376</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317609</v>
+        <v>3.44775050131761</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.696317930716709</v>
+        <v>-7.884043687931173</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.03672166833760526</v>
+        <v>-0.03836863454818129</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.8132182008567264</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737163</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.055848253220711</v>
+        <v>-8.243574010435175</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1017401573659455</v>
+        <v>-0.1768304602517321</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.8132182008567264</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341306</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.106197316674933</v>
+        <v>-8.293923073889397</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1139637627904571</v>
+        <v>-0.1890540656762432</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.8635672643109484</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539457</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.203816594096329</v>
+        <v>-8.391542351310793</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1499697231372465</v>
+        <v>-0.2250600260230331</v>
       </c>
       <c r="F1876" t="n">
         <v>-0.9611865417323451</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937496</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.257888093604688</v>
+        <v>-8.445613850819152</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.168704766619018</v>
+        <v>-0.2437950695048041</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.015258041240704</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141699</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.462146268934552</v>
+        <v>-8.649872026149016</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2448948396323209</v>
+        <v>-0.3199851425181075</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.142896985854693</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729888</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.495799107443025</v>
+        <v>-8.683524864657489</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2538734205512743</v>
+        <v>-0.3289637234370608</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.243310353771731</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.634885222061882</v>
+        <v>-8.822610979276346</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.294136164905396</v>
+        <v>-0.3692264677911825</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.382396468390588</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608598</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.810009639448426</v>
+        <v>-8.99773539666289</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3496307111124968</v>
+        <v>-0.4247210139982829</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.557520885777131</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.044461733462915</v>
+        <v>-9.232187490677379</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4506307136198884</v>
+        <v>-0.5257210165056749</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.557520885777131</v>
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.238763656773491</v>
+        <v>-9.336562221703826</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5350236737180949</v>
+        <v>-0.5741430996902297</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.751822809087708</v>
+        <v>-1.661895616803577</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.109744527852425</v>
+        <v>2.163700843222903</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390583</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.403229559448548</v>
+        <v>-9.49907568740241</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5996942449495615</v>
+        <v>-0.6380326961311069</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.870518674933411</v>
+        <v>-1.759529047222264</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.039642798183559</v>
+        <v>2.106236574810247</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297395</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.529266352816837</v>
+        <v>-9.625112480770699</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6474152336677625</v>
+        <v>-0.685753684849308</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.845267052123669</v>
+        <v>-1.734277424412522</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.057487500498519</v>
+        <v>2.124081277125207</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367402532254</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.472194580920906</v>
+        <v>-9.568040708874769</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6205961892229892</v>
+        <v>-0.6589346404045351</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.845267052123669</v>
+        <v>-1.734277424412522</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.06147783618492</v>
+        <v>2.128071612811608</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158918</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.613866422645026</v>
+        <v>-9.709712550598889</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.678740152811379</v>
+        <v>-0.7170786039929249</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.845267052123669</v>
+        <v>-1.734277424412522</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.060002609286178</v>
+        <v>2.126596385912866</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940714</v>
+        <v>3.691571733940715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.564275578220192</v>
+        <v>-9.660121706174055</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6438504048765732</v>
+        <v>-0.6821888560581186</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.795676207698835</v>
+        <v>-1.684686579987688</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.10481052610595</v>
+        <v>2.171404302732639</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770574</v>
+        <v>3.676841549770575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.415357243748335</v>
+        <v>-9.511203371702198</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5973342047345134</v>
+        <v>-0.6356726559160593</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.764426616963662</v>
+        <v>-1.653436989252515</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.110509146900371</v>
+        <v>2.17710292352706</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615277</v>
+        <v>3.685161381615278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.189512091028924</v>
+        <v>-9.285358218982788</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4974170706105401</v>
+        <v>-0.5357555217920864</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.722499941376498</v>
+        <v>-1.611510313665351</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.145244225288878</v>
+        <v>2.211838001915567</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812097</v>
+        <v>3.684843823812098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.064933434691332</v>
+        <v>-9.160779562645196</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4464464635194445</v>
+        <v>-0.4847849147009908</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.722499941376498</v>
+        <v>-1.611510313665351</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.146383369844937</v>
+        <v>2.212977146471625</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646211</v>
+        <v>3.710935533646212</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.117828722735618</v>
+        <v>-9.213674850689483</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4649708045750511</v>
+        <v>-0.5033092557565979</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.717544595288052</v>
+        <v>-1.606554967576905</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.151990351660112</v>
+        <v>2.218584128286801</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.045695547447737</v>
+        <v>-9.141541675401601</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4303838302212624</v>
+        <v>-0.4687222814028087</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.717544595288052</v>
+        <v>-1.606554967576905</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.157724055898749</v>
+        <v>2.224317832525437</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955322</v>
+        <v>3.728577929955323</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.97432915483809</v>
+        <v>-9.070175282791954</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4115745355712686</v>
+        <v>-0.4499129867528149</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.646178202678404</v>
+        <v>-1.535188574967257</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.190806629070673</v>
+        <v>2.257400405697361</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232407</v>
+        <v>3.747702660232408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.880870120852865</v>
+        <v>-8.97671624880673</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3840744032900862</v>
+        <v>-0.422412854471633</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.646178202678404</v>
+        <v>-1.535188574967257</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.180923147757765</v>
+        <v>2.247516924384453</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436223</v>
+        <v>3.766317079436224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.870216939299434</v>
+        <v>-8.966063067253298</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3816476911680877</v>
+        <v>-0.4199861423496341</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.646178202678404</v>
+        <v>-1.535188574967257</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.179088587258391</v>
+        <v>2.24568236388508</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311943</v>
+        <v>3.784684521311944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.772309900622943</v>
+        <v>-8.868156028576808</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.342785190670952</v>
+        <v>-0.3811236418524984</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.578192452817848</v>
+        <v>-1.467202825106701</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.219579722201264</v>
+        <v>2.286173498827953</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097238</v>
+        <v>3.800829354097239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.748356359646985</v>
+        <v>-8.84420248760085</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3325352681350755</v>
+        <v>-0.3708737193166218</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.55423891184189</v>
+        <v>-1.443249284130743</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.234620352932333</v>
+        <v>2.301214129559021</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017765</v>
+        <v>3.789311112017766</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.484296421324188</v>
+        <v>-8.580142549278053</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2401716089677088</v>
+        <v>-0.2785100601492552</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.290178973519094</v>
+        <v>-1.179189345807947</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.379795999764258</v>
+        <v>2.446389776390946</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.77721679781935</v>
+        <v>-7.873062925773215</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.03987320677392558</v>
+        <v>0.001534755592379256</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.290178973519094</v>
+        <v>-1.179189345807947</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.377008966103957</v>
+        <v>2.443602742730645</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.73703249945316</v>
+        <v>-7.832878627407024</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.05629055000824312</v>
+        <v>0.01795209882669679</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.249994675152903</v>
+        <v>-1.139005047441756</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.401463169011513</v>
+        <v>2.468056945638201</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.573632628513797</v>
+        <v>-7.669478756467662</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.121017319604745</v>
+        <v>0.08267886842319871</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.08659480421354</v>
+        <v>-0.9756051765023934</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.498869912795887</v>
+        <v>2.565463689422576</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.340151406284199</v>
+        <v>-7.435997534238063</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.222334237334437</v>
+        <v>0.1839957861528907</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8531135819839419</v>
+        <v>-0.7421239542727949</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.646883074971499</v>
+        <v>2.713476851598187</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.190485015276684</v>
+        <v>-7.286331143230548</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2793085834244837</v>
+        <v>0.2409701322429374</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.760210090741406</v>
+        <v>-0.6492204630302589</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.699732959404061</v>
+        <v>2.76632673603075</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.058209541645797</v>
+        <v>-7.154055669599662</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2334795588839929</v>
+        <v>0.1951411077024465</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6279346171105193</v>
+        <v>-0.5169449893993723</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.680359029589748</v>
+        <v>2.746952806216436</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.902471209086055</v>
+        <v>-6.99831733703992</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.2985899525955267</v>
+        <v>0.2602515014139799</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4721962845507778</v>
+        <v>-0.3612066568396307</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.77661708981323</v>
+        <v>2.843210866439918</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.817506542356735</v>
+        <v>-6.9133526703106</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3454821605109131</v>
+        <v>0.3071437093293667</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.3872316178214582</v>
+        <v>-0.2762419901103111</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.84050223107448</v>
+        <v>2.907096007701168</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.92309653212984</v>
+        <v>-7.018942660083704</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.1752702350024529</v>
+        <v>0.1369317838209065</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.4928216075945626</v>
+        <v>-0.3818319798834155</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.649172307611399</v>
+        <v>2.715766084238087</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.854861947504412</v>
+        <v>-6.950708075458277</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2511084107297101</v>
+        <v>0.2127699595481638</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.4744062847220266</v>
+        <v>-0.3634166570108795</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.708765843212007</v>
+        <v>2.775359619838695</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.873530691357055</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.706921906096813</v>
+        <v>-6.802768034050677</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1904055046045823</v>
+        <v>0.1520670534230359</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.454085368813469</v>
+        <v>-0.3430957411023219</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.601079470068974</v>
+        <v>2.667673246695662</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.864816705103577</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.653952383842825</v>
+        <v>-6.749798511796689</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2028793272526994</v>
+        <v>0.1645408760711531</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.4011158465594801</v>
+        <v>-0.2901262188483331</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.624147197167889</v>
+        <v>2.690740973794577</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.857856093008484</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.488164187882534</v>
+        <v>-6.584010315836398</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2622339935417228</v>
+        <v>0.2238955423601761</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.4011158465594801</v>
+        <v>-0.2901262188483331</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.617186585072796</v>
+        <v>2.683780361699484</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.872318447389627</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.454800981403765</v>
+        <v>-6.550647109357629</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2900416305143731</v>
+        <v>0.2517031793328268</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.4011158465594801</v>
+        <v>-0.2901262188483331</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.631648939453939</v>
+        <v>2.698242716080627</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.866850567848822</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.346541844281243</v>
+        <v>-6.442387972235108</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3278774058225769</v>
+        <v>0.2895389546410305</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.4011158465594801</v>
+        <v>-0.2901262188483331</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.626181059913134</v>
+        <v>2.692774836539822</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.864348661859399</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.223250709464113</v>
+        <v>-6.319096837417977</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.374691953760006</v>
+        <v>0.3363535025784596</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2778247117423496</v>
+        <v>-0.1668350840312026</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.697653834813989</v>
+        <v>2.764247611440677</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.872049640096724</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.170553842332821</v>
+        <v>-6.266399970286685</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.403471678849848</v>
+        <v>0.3651332276683013</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.2251278446110584</v>
+        <v>-0.1141382168999114</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.736972933330089</v>
+        <v>2.803566709956777</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.867830348443774</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.926788400349377</v>
+        <v>-6.022634528303241</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4967585639902765</v>
+        <v>0.4584201128087297</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.2251278446110584</v>
+        <v>-0.1141382168999114</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.73275364167714</v>
+        <v>2.799347418303828</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.86995466236379</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.837012727972905</v>
+        <v>-5.932858855926769</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5347931468608813</v>
+        <v>0.496454695679335</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1635283996967484</v>
+        <v>-0.05253877198560136</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.771837622545742</v>
+        <v>2.83843139917243</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.862696737347493</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.58716233402383</v>
+        <v>-5.683008461977694</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6274753794242134</v>
+        <v>0.5891369282426666</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1635283996967484</v>
+        <v>-0.05253877198560136</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.764579697529444</v>
+        <v>2.831173474156132</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.866295860868141</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.411270241556398</v>
+        <v>-5.507116369510262</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7014313399318346</v>
+        <v>0.6630928887502883</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1635283996967484</v>
+        <v>-0.05253877198560136</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.768178821050093</v>
+        <v>2.834772597676781</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.879623366922695</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.239823778533935</v>
+        <v>-5.335669906487799</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.783337431195374</v>
+        <v>0.7449989800138272</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.007918063325714708</v>
+        <v>0.1189076910368618</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.884374204918124</v>
+        <v>2.950967981544812</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.878643844538992</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.159801491424814</v>
+        <v>-5.255647619378678</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8143668236553192</v>
+        <v>0.7760283724737729</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.08794035043483567</v>
+        <v>0.1989299781459827</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.931408054799894</v>
+        <v>2.998001831426582</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.883338645593309</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.096165749190879</v>
+        <v>-5.192011877144743</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8445159216032101</v>
+        <v>0.8061774704216638</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.1515760926687702</v>
+        <v>0.2625657203799173</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.974284301194571</v>
+        <v>3.04087807782126</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.864532904377105</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.002468430974484</v>
+        <v>-5.098314558928348</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.863189107673564</v>
+        <v>0.8248506564920177</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.1515760926687702</v>
+        <v>0.2625657203799173</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.955478559978367</v>
+        <v>3.022072336605055</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.866275981001982</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.012971054039773</v>
+        <v>-5.108817181993637</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8607311350723257</v>
+        <v>0.8223926838907794</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1410734696034813</v>
+        <v>0.2520630973146284</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.950920062764071</v>
+        <v>3.01751383939076</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.870205294836802</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.940728485868578</v>
+        <v>-5.036574613822443</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8935574761756238</v>
+        <v>0.8552190249940774</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1410734696034813</v>
+        <v>0.2520630973146284</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.954849376598891</v>
+        <v>3.02144315322558</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.870883878754142</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.923014798990713</v>
+        <v>-5.018860926944577</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9013215348441099</v>
+        <v>0.8629830836625634</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1442547985003981</v>
+        <v>0.2552444262115452</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.957436757854381</v>
+        <v>3.02403053448107</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.867881949974136</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.814209913510986</v>
+        <v>-4.91005604146485</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9418415602559942</v>
+        <v>0.9035031090744479</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1442547985003981</v>
+        <v>0.2552444262115452</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.954434829074375</v>
+        <v>3.021028605701063</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.86946098698475</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.594189115473975</v>
+        <v>-4.69003524342784</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.031428916481413</v>
+        <v>0.9930904652998662</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2854746435683784</v>
+        <v>0.3964642712795254</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.040745773125777</v>
+        <v>3.107339549752465</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.885355169786573</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.461321426410698</v>
+        <v>-4.557167554364562</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.100470174908547</v>
+        <v>1.062131723727</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2854746435683784</v>
+        <v>0.3964642712795254</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.056639955927601</v>
+        <v>3.123233732554289</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.886501014226875</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.341148343046199</v>
+        <v>-4.436994471000063</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.149685252694648</v>
+        <v>1.111346801513102</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4056477269328773</v>
+        <v>0.5166373546440244</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.129889650386602</v>
+        <v>3.19648342701329</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.896589116788315</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.205894981716222</v>
+        <v>-4.301741109670086</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.213874699788079</v>
+        <v>1.175536248606533</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5409010882628544</v>
+        <v>0.6518907159740015</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.221129769746028</v>
+        <v>3.287723546372716</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.882626608189741</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.265769809073914</v>
+        <v>-4.361615937027779</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.175962260246428</v>
+        <v>1.137623809064882</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4810262609051623</v>
+        <v>0.5920158886163094</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.171242364732838</v>
+        <v>3.237836141359527</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.897915777423949</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.145949578163077</v>
+        <v>-4.241795706116942</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.239179521844971</v>
+        <v>1.200841070663425</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4810262609051623</v>
+        <v>0.5920158886163094</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.186531533967047</v>
+        <v>3.253125310593735</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430687</v>
+        <v>3.729146398430688</v>
       </c>
       <c r="C1935" t="n">
         <v>2.805559976746391</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.148419284624883</v>
+        <v>-4.244265412578748</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.14583583858269</v>
+        <v>1.107497387401144</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4785565544433562</v>
+        <v>0.5895461821545032</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.092693909412405</v>
+        <v>3.159287686039093</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003594</v>
+        <v>3.743220196003595</v>
       </c>
       <c r="C1936" t="n">
         <v>2.724821838231692</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.216789470948894</v>
+        <v>-4.312635598902758</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.037749625538388</v>
+        <v>0.9994111743568412</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4878322534795711</v>
+        <v>0.5988218811907181</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.017521190319435</v>
+        <v>3.084114966946124</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508362</v>
+        <v>3.714179139508364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.715258546863584</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.23057752379594</v>
+        <v>-4.326423651749804</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.02267111303146</v>
+        <v>0.984332661849914</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4878322534795711</v>
+        <v>0.5988218811907181</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.007957898951326</v>
+        <v>3.074551675578015</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417697</v>
+        <v>3.710906731417698</v>
       </c>
       <c r="C1938" t="n">
         <v>2.852289383555786</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.28609759968853</v>
+        <v>-4.381943727642394</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.137493919366627</v>
+        <v>1.099155468185081</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4878322534795711</v>
+        <v>0.5988218811907181</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.144988735643529</v>
+        <v>3.211582512270217</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205891</v>
+        <v>3.746042526205893</v>
       </c>
       <c r="C1939" t="n">
         <v>2.856856615547574</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.11062333989606</v>
+        <v>-4.206469467849924</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.212250855275403</v>
+        <v>1.173912404093856</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4878322534795711</v>
+        <v>0.5988218811907181</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.149555967635317</v>
+        <v>3.216149744262005</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225435</v>
+        <v>3.765024323225437</v>
       </c>
       <c r="C1940" t="n">
         <v>2.832598644308781</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.102698965311146</v>
+        <v>-4.19854509326501</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.191162633870575</v>
+        <v>1.152824182689029</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4878322534795711</v>
+        <v>0.5988218811907181</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.125297996396524</v>
+        <v>3.191891773023212</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111289</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.761136957710231</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.096420762741297</v>
+        <v>-4.192266890695161</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.122212228299965</v>
+        <v>1.083873777118418</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4941104560494202</v>
+        <v>0.6051000837605671</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.057603231339883</v>
+        <v>3.124197007966571</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264159</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.771309344142363</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.036568143537574</v>
+        <v>-4.132414271491438</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.156325662413586</v>
+        <v>1.11798721123204</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4941104560494202</v>
+        <v>0.6051000837605671</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.067775617772015</v>
+        <v>3.134369394398703</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742295</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.766255614716223</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.950324680511196</v>
+        <v>-4.04617080846506</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.185769318197998</v>
+        <v>1.147430867016451</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4941104560494202</v>
+        <v>0.6051000837605671</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.062721888345876</v>
+        <v>3.129315664972564</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316042</v>
+        <v>3.752027499316044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.758031390160749</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.995631499910176</v>
+        <v>-4.09147762786404</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.159422365882931</v>
+        <v>1.121083914701385</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.4533002930401894</v>
+        <v>0.5642899207513363</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.030011565984863</v>
+        <v>3.096605342611551</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803187</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.75858326319385</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.024664604612477</v>
+        <v>-4.120510732566341</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.148360997035113</v>
+        <v>1.110022545853566</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.4533002930401894</v>
+        <v>0.5642899207513363</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.030563439017965</v>
+        <v>3.097157215644653</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.687855955085216</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.931854123161618</v>
+        <v>-4.027700251115482</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.114757881506822</v>
+        <v>1.076419430325275</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5461107744910487</v>
+        <v>0.6571004022021957</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.015522419779846</v>
+        <v>3.082116196406534</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.74828581656042</v>
+        <v>3.748285816560423</v>
       </c>
       <c r="C1947" t="n">
         <v>2.689729431009817</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.976243592491045</v>
+        <v>-4.072089720444909</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.098875569699651</v>
+        <v>1.060537118518105</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5017213051616211</v>
+        <v>0.612710932872768</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.99076221410679</v>
+        <v>3.057355990733478</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472732</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.68480513952154</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.092785197596388</v>
+        <v>-4.16278749479395</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.047334636169237</v>
+        <v>1.019333717290212</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.3851797000562783</v>
+        <v>0.5220131585237272</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.915912959555307</v>
+        <v>2.998013034635777</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.74304760379853</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.690296435352207</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.13270929217896</v>
+        <v>-4.202711589376522</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.036856294166876</v>
+        <v>1.008855375287851</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.3851797000562783</v>
+        <v>0.5220131585237272</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.921404255385974</v>
+        <v>3.003504330466444</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498856</v>
+        <v>3.68959784049886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.701793637120746</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.160489690080313</v>
+        <v>-4.230491987277874</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.037241336774874</v>
+        <v>1.009240417895849</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.3573993021549252</v>
+        <v>0.4942327606223742</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.916233218413702</v>
+        <v>2.998333293494171</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705316</v>
+        <v>3.64306962170532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.5401493571214</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.278870362810451</v>
+        <v>-4.348872660008013</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8282447876834718</v>
+        <v>0.8002438688044464</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.290181450003949</v>
+        <v>0.427014908471398</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.714258227123769</v>
+        <v>2.796358302204239</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729261</v>
+        <v>3.682716310729264</v>
       </c>
       <c r="C1952" t="n">
         <v>2.660299017840605</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.387484441253783</v>
+        <v>-4.457486738451344</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9049488170253448</v>
+        <v>0.8769478981463197</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.290181450003949</v>
+        <v>0.427014908471398</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.834407887842975</v>
+        <v>2.916507962923444</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190761</v>
+        <v>3.733012441190764</v>
       </c>
       <c r="C1953" t="n">
         <v>2.674812043942928</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.35207540300564</v>
+        <v>-4.422077700203201</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.933625458426925</v>
+        <v>0.9056245395478997</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.290181450003949</v>
+        <v>0.427014908471398</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.848920913945298</v>
+        <v>2.931020989025767</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913418</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.672231485285297</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.313691740447489</v>
+        <v>-4.38369403764505</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9463983647925542</v>
+        <v>0.9183974459135289</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3285651125621002</v>
+        <v>0.4653985710295492</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.869370552822557</v>
+        <v>2.951470627903027</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532479</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.668960514130599</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.136575410412322</v>
+        <v>-4.206577707609884</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.013973925651922</v>
+        <v>0.9859730067728973</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3285651125621002</v>
+        <v>0.4653985710295492</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.866099581667859</v>
+        <v>2.948199656748328</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793896</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.669643905892512</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.181667655245868</v>
+        <v>-4.25166995244343</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9966204194804174</v>
+        <v>0.968619500601392</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.2666690693927104</v>
+        <v>0.4035025278601594</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.829645347528138</v>
+        <v>2.911745422608608</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011227</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.663430881198926</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.002292234007101</v>
+        <v>-4.072294531204662</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.062157563282339</v>
+        <v>1.034156644403313</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4234458275634291</v>
+        <v>0.5602792860308781</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.917498377736984</v>
+        <v>2.999598452817454</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982221</v>
+        <v>3.716991718982225</v>
       </c>
       <c r="C1958" t="n">
         <v>2.644238336530516</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.047306447527706</v>
+        <v>-4.117308744725268</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.024959333205686</v>
+        <v>0.996958414326661</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.3930969322488245</v>
+        <v>0.5299303907162735</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.880096495879811</v>
+        <v>2.96219657096028</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702660850953</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.649929898869462</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.314310957800141</v>
+        <v>-4.384313254997703</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9238490914356579</v>
+        <v>0.8958481725566327</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.1987338942058759</v>
+        <v>0.3355673526733249</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.769170235392988</v>
+        <v>2.851270310473457</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760806</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.649133820765963</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.415508739237314</v>
+        <v>-4.485511036434875</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8825739007572904</v>
+        <v>0.854572981878265</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.1303250806605567</v>
+        <v>0.2671585391280057</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.727328869162298</v>
+        <v>2.809428944242767</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815451</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64673378232028</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.408997772623001</v>
+        <v>-4.479000069820563</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8827782489573321</v>
+        <v>0.8547773300783068</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.1303250806605567</v>
+        <v>0.2671585391280057</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.724928830716614</v>
+        <v>2.807028905797083</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378097</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.643258501528525</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.389959644915704</v>
+        <v>-4.459961942113265</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8869182192484959</v>
+        <v>0.8589173003694706</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.07214146932936216</v>
+        <v>0.2089749277968111</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.686543383126142</v>
+        <v>2.768643458206612</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131245</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.762552903162715</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.442475447190525</v>
+        <v>-4.512477744388086</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.985206299972758</v>
+        <v>0.9572053810937329</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.07214146932936216</v>
+        <v>0.2089749277968111</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.805837784760333</v>
+        <v>2.887937859840802</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067859</v>
+        <v>3.722447362067861</v>
       </c>
       <c r="C1964" t="n">
         <v>2.763386232148849</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.456342208524442</v>
+        <v>-4.526344505722004</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9804929244253244</v>
+        <v>0.9524920055462993</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.03428355259553922</v>
+        <v>0.1711170110629882</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.783956363706173</v>
+        <v>2.866056438786642</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789116</v>
+        <v>3.787425580789118</v>
       </c>
       <c r="C1965" t="n">
         <v>2.769394762545775</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.411538036984513</v>
+        <v>-4.481540334182074</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.004423123438222</v>
+        <v>0.976422204559197</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.03428355259553922</v>
+        <v>0.1711170110629882</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.789964894103099</v>
+        <v>2.872064969183568</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519903</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.667344983822974</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.26379506674951</v>
+        <v>-4.333797363947071</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9614705328094229</v>
+        <v>0.9334696139303977</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2020909098304224</v>
+        <v>0.3389243682978714</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.788599529721228</v>
+        <v>2.870699604801697</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.670138605354455</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.347616288024208</v>
+        <v>-4.41761858522177</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9307356658310244</v>
+        <v>0.9027347469519993</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2020909098304224</v>
+        <v>0.3389243682978714</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.791393151252709</v>
+        <v>2.873493226333178</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394724</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.670800953746113</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.341463581971424</v>
+        <v>-4.411465879168985</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9338590966437965</v>
+        <v>0.9058581777647714</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2082436158832067</v>
+        <v>0.3450770743506557</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.795747123276038</v>
+        <v>2.877847198356507</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890607</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.669881430486224</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.358272880121926</v>
+        <v>-4.428275177319487</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.926215854123706</v>
+        <v>0.8982149352446809</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.191434317732705</v>
+        <v>0.328267776200154</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.784742021125847</v>
+        <v>2.866842096206316</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798418</v>
+        <v>3.867362636798421</v>
       </c>
       <c r="C1970" t="n">
         <v>2.736216984283045</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.295974881345804</v>
+        <v>-4.365977178543365</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.017470607430976</v>
+        <v>0.9894696885519507</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2367285820071471</v>
+        <v>0.3735620404745961</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.878254133487333</v>
+        <v>2.960354208567803</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992185</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
         <v>2.538508985997172</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.094184683680646</v>
+        <v>-4.164186980878207</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9004786882111662</v>
+        <v>0.8724777693321408</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4347467741763015</v>
+        <v>0.5715802326437505</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.799357050502953</v>
+        <v>2.881457125583422</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852419</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.608799218319347</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.14507139636684</v>
+        <v>-4.215073693564402</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9504142354588634</v>
+        <v>0.9224133165798383</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.3838600614901069</v>
+        <v>0.520693519957556</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.839115255213411</v>
+        <v>2.921215330293881</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319538</v>
+        <v>3.81906330031954</v>
       </c>
       <c r="C1973" t="n">
         <v>2.623426954435391</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.058460653717034</v>
+        <v>-4.128462950914595</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9996862686348298</v>
+        <v>0.9716853497558047</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.4624857926952652</v>
+        <v>0.5993192511627142</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.90091843005255</v>
+        <v>2.983018505133019</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489378</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.621962935260062</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.118669951722318</v>
+        <v>-4.18867224891988</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9741385302573875</v>
+        <v>0.9461376113783624</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4022764946899807</v>
+        <v>0.5391099531574297</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.863328832074051</v>
+        <v>2.94542890715452</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397787</v>
+        <v>3.836411672397789</v>
       </c>
       <c r="C1975" t="n">
         <v>2.620454553299991</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.042247905290392</v>
+        <v>-4.112250202487953</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.003198966870087</v>
+        <v>0.9751980479910616</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4022764946899807</v>
+        <v>0.5391099531574297</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.861820450113979</v>
+        <v>2.943920525194449</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316242</v>
+        <v>3.833513460316244</v>
       </c>
       <c r="C1976" t="n">
         <v>2.620317420735427</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.997874773651823</v>
+        <v>-4.067877070849384</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.020811086960951</v>
+        <v>0.9928101680819252</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4466496263285493</v>
+        <v>0.5834830847959983</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.888307196532557</v>
+        <v>2.970407271613026</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105961</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.614711214874017</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.020355124510708</v>
+        <v>-4.090357421708269</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.006212740755987</v>
+        <v>0.9782118218769618</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4466496263285493</v>
+        <v>0.5834830847959983</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.882700990671147</v>
+        <v>2.964801065751617</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190319</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.621092971901822</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.972699393949652</v>
+        <v>-4.042701691147213</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.031656790008214</v>
+        <v>1.003655871129189</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.494305356889605</v>
+        <v>0.631138815357054</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.917676186035585</v>
+        <v>2.999776261116055</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569611</v>
+        <v>3.822678210569613</v>
       </c>
       <c r="C1979" t="n">
         <v>2.625985345276547</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.872181235450897</v>
+        <v>-3.942183532648459</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.076756426782441</v>
+        <v>1.048755507903415</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5948235153883595</v>
+        <v>0.7316569738558085</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.982879454509563</v>
+        <v>3.064979529590032</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557288</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.612740017752419</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.856275906018545</v>
+        <v>-3.926278203216106</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.069873231031254</v>
+        <v>1.041872312152229</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5157108546791207</v>
+        <v>0.6525443131465696</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.922166530559892</v>
+        <v>3.004266605640361</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932762</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
         <v>2.616837720363048</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.811437504410147</v>
+        <v>-3.881439801607708</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.091906294285242</v>
+        <v>1.063905375406216</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5202542876239902</v>
+        <v>0.6570877460914391</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.928990292937442</v>
+        <v>3.011090368017912</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917044</v>
+        <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
         <v>2.620998659994126</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.830935960652155</v>
+        <v>-3.900938257849716</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.088267851419517</v>
+        <v>1.060266932540491</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4721696463440859</v>
+        <v>0.6090031048115347</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.904300447800578</v>
+        <v>2.986400522881047</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405952</v>
+        <v>3.826684745405954</v>
       </c>
       <c r="C1983" t="n">
         <v>2.626878262521963</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.786733123566254</v>
+        <v>-3.856735420763816</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.111828588781714</v>
+        <v>1.083827669902689</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5163724834299863</v>
+        <v>0.6532059418974352</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.936701752579955</v>
+        <v>3.018801827660424</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265636</v>
+        <v>3.838199629265638</v>
       </c>
       <c r="C1984" t="n">
         <v>2.62528826299121</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.794292789403301</v>
+        <v>-3.864295086600863</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.107214722916143</v>
+        <v>1.079213804037117</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5711758874398056</v>
+        <v>0.7080093459072545</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.967993795455094</v>
+        <v>3.050093870535564</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284871</v>
+        <v>3.863895080284873</v>
       </c>
       <c r="C1985" t="n">
         <v>2.67653602817425</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.636001371864029</v>
+        <v>-3.706003669061591</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.221779055114891</v>
+        <v>1.193778136235866</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5711758874398056</v>
+        <v>0.7080093459072545</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.019241560638134</v>
+        <v>3.101341635718603</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321015</v>
+        <v>3.865338681321017</v>
       </c>
       <c r="C1986" t="n">
         <v>2.674976732768503</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.428359368229553</v>
+        <v>-3.498361665427114</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.303276561162935</v>
+        <v>1.27527564228391</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7788178910742818</v>
+        <v>0.9156513495417307</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.142267467413073</v>
+        <v>3.224367542493542</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475131</v>
+        <v>3.864489842475133</v>
       </c>
       <c r="C1987" t="n">
         <v>2.669924961006773</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.377327275507025</v>
+        <v>-3.447329572704586</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.318637626490216</v>
+        <v>1.290636707611191</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8298499837968097</v>
+        <v>0.9666834422642586</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.167834951284859</v>
+        <v>3.249935026365328</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404845</v>
+        <v>3.842547360404847</v>
       </c>
       <c r="C1988" t="n">
         <v>2.687112365099478</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.312103094379819</v>
+        <v>-3.38210539157738</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.361914703033803</v>
+        <v>1.333913784154778</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8950741649240154</v>
+        <v>1.031907623391464</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.224156864053888</v>
+        <v>3.306256939134357</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882549</v>
+        <v>3.840061186882551</v>
       </c>
       <c r="C1989" t="n">
         <v>2.683073337398759</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.274676074308685</v>
+        <v>-3.344678371506247</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.372846483361537</v>
+        <v>1.344845564482512</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.900325702953197</v>
+        <v>1.037159161420646</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.223268759170677</v>
+        <v>3.305368834251146</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992653</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
         <v>2.684330129729999</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.294787730343394</v>
+        <v>-3.364790027540955</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.366058613278894</v>
+        <v>1.338057694399869</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9113530479506162</v>
+        <v>1.048186506418065</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.231141958500369</v>
+        <v>3.313242033580838</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636279</v>
+        <v>3.828661445636281</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84488790075121</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.26637446724351</v>
+        <v>-3.336376764441071</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.537981689540058</v>
+        <v>1.509980770661033</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8523774852041874</v>
+        <v>0.9892109436716361</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.356314391873722</v>
+        <v>3.438414466954192</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957617</v>
+        <v>3.813222820957619</v>
       </c>
       <c r="C1992" t="n">
         <v>2.965000809969027</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.191592206218497</v>
+        <v>-3.261594503416059</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.688007503167881</v>
+        <v>1.660006584288855</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9271597462292001</v>
+        <v>1.063993204696649</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.521296657706547</v>
+        <v>3.603396732787016</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998748</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.956708785982886</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.165508121954689</v>
+        <v>-3.235510419152251</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.690149112887263</v>
+        <v>1.662148194008237</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9271597462292001</v>
+        <v>1.063993204696649</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.513004633720406</v>
+        <v>3.595104708800875</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896922</v>
+        <v>3.803397818896924</v>
       </c>
       <c r="C1994" t="n">
         <v>2.954901981566665</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.077630208845569</v>
+        <v>-3.14763250604313</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.723493473714691</v>
+        <v>1.695492554835665</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.043085388652551</v>
+        <v>1.17991884712</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.580753214758196</v>
+        <v>3.662853289838665</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.79626414395985</v>
+        <v>3.796264143959852</v>
       </c>
       <c r="C1995" t="n">
         <v>2.972456387293457</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.195556838256929</v>
+        <v>-3.138740044649847</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.693877227676938</v>
+        <v>1.71660394511977</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.043085388652551</v>
+        <v>1.17991884712</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.598307620484988</v>
+        <v>3.680407695565457</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945358</v>
+        <v>3.794424941945359</v>
       </c>
       <c r="C1996" t="n">
         <v>2.964311434698041</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.364032955226807</v>
+        <v>-3.307216161619725</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.618341828293571</v>
+        <v>1.641068545736403</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.01513755293597</v>
+        <v>1.151971011403419</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.573393966459623</v>
+        <v>3.655494041540092</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782701</v>
+        <v>3.795574066782703</v>
       </c>
       <c r="C1997" t="n">
         <v>2.945581131885902</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.917776762597367</v>
+        <v>-2.860959968990285</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.778114002533208</v>
+        <v>1.800840719976041</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9204188832663376</v>
+        <v>1.057252341733786</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.497832461845705</v>
+        <v>3.579932536926175</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.78467134563263</v>
+        <v>3.784671345632631</v>
       </c>
       <c r="C1998" t="n">
         <v>2.936245154382807</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.895055658914215</v>
+        <v>-2.838238865307132</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.777866466503374</v>
+        <v>1.800593183946206</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9204188832663376</v>
+        <v>1.057252341733786</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.48849648434261</v>
+        <v>3.570596559423079</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777666</v>
+        <v>3.783205696777668</v>
       </c>
       <c r="C1999" t="n">
         <v>3.095151280233976</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.024257472208257</v>
+        <v>-2.967440678601175</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.885091867036926</v>
+        <v>1.907818584479758</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7912170699722954</v>
+        <v>0.928050528439744</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.569881522217353</v>
+        <v>3.651981597297823</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644406</v>
+        <v>3.779933725644407</v>
       </c>
       <c r="C2000" t="n">
         <v>3.132229102727623</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.050131870682283</v>
+        <v>-2.9933150770752</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.911819930140962</v>
+        <v>1.934546647583795</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.8361286786840365</v>
+        <v>0.9729621371514852</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.633906309938045</v>
+        <v>3.716006385018514</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799958</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>3.128904458717168</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.04307718046711</v>
+        <v>-2.986260386860027</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.911317162216577</v>
+        <v>1.934043879659409</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8431833688992103</v>
+        <v>0.980016827366659</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.634814480056694</v>
+        <v>3.716914555137163</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331109</v>
+        <v>3.76667349633111</v>
       </c>
       <c r="C2002" t="n">
         <v>3.138910612361909</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.016125956140622</v>
+        <v>-2.959309162533539</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.932103805591913</v>
+        <v>1.954830523034746</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8580637149269295</v>
+        <v>0.9948971733943781</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.653748841318067</v>
+        <v>3.735848916398536</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784101</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
         <v>3.323013744506869</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.152078964196938</v>
+        <v>-3.095262170589855</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.061825734514347</v>
+        <v>2.084552451957179</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8580637149269295</v>
+        <v>0.9948971733943781</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.837851973463027</v>
+        <v>3.919952048543496</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74392550571442</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.315130439409862</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.17448708200181</v>
+        <v>-3.117670288394727</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.044979182295391</v>
+        <v>2.067705899738224</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8580637149269295</v>
+        <v>0.9948971733943781</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.82996866836602</v>
+        <v>3.912068743446489</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155026</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
         <v>3.3171844389595</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.20271131757941</v>
+        <v>-3.145894523972327</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.035743487613988</v>
+        <v>2.058470205056821</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.876040467378238</v>
+        <v>1.012873925845687</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.842808719386443</v>
+        <v>3.924908794466912</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516197</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.373438156681347</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.21215224346794</v>
+        <v>-3.155335449860857</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.088220834980423</v>
+        <v>2.110947552423256</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.9984675849216296</v>
+        <v>1.135301043389078</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.972518707634324</v>
+        <v>4.054618782714794</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321627</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.376329251226648</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.264425850803581</v>
+        <v>-3.207609057196499</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.070202486591468</v>
+        <v>2.0929292040343</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9461939775859883</v>
+        <v>1.083027436053437</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.944045637778241</v>
+        <v>4.02614571285871</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347696</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
         <v>3.374441064120423</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.340755828404487</v>
+        <v>-3.283939034797405</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.03778230844488</v>
+        <v>2.060509025887713</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9461939775859883</v>
+        <v>1.083027436053437</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.942157450672016</v>
+        <v>4.024257525752486</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887741</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.369261293723285</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.543009548728841</v>
+        <v>-3.486192755121758</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.951701049918002</v>
+        <v>1.974427767360834</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7439402572616349</v>
+        <v>0.8807737157290834</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.815625448080266</v>
+        <v>3.897725523160736</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.71289761234306</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.367695303933437</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.704577974256096</v>
+        <v>-3.647761180649013</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.885507689917252</v>
+        <v>1.908234407360084</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6171573334637556</v>
+        <v>0.753990791931204</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.737989704011691</v>
+        <v>3.82008977909216</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389342</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.380768710799356</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.812878636126215</v>
+        <v>-3.756061842519133</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.855260832035123</v>
+        <v>1.877987549477955</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6171573334637556</v>
+        <v>0.753990791931204</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.75106311087761</v>
+        <v>3.833163185958079</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378386</v>
+        <v>3.749882691378388</v>
       </c>
       <c r="C2012" t="n">
         <v>3.372773907582296</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.906026107429582</v>
+        <v>-3.849209313822499</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.810007040296716</v>
+        <v>1.832733757739548</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4943281221812228</v>
+        <v>0.6311615806486712</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.66937078089103</v>
+        <v>3.751470855971499</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.71581989500697</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.371297948709298</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.933926894539055</v>
+        <v>-3.877110100931972</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.797370766579929</v>
+        <v>1.820097484022761</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.459731198038288</v>
+        <v>0.5965646565057364</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.647136667532271</v>
+        <v>3.72923674261274</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787382</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.368062392686497</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.056452997241949</v>
+        <v>-3.999636203634866</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.74512476947597</v>
+        <v>1.767851486918802</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3372050953353941</v>
+        <v>0.4740385538028425</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.570385449887734</v>
+        <v>3.652485524968203</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585932</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
         <v>3.434768352277001</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.286967493427538</v>
+        <v>-4.230150699820455</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.719624930592238</v>
+        <v>1.74235164803507</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.1066905991498054</v>
+        <v>0.2435240576172538</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.498782711766884</v>
+        <v>3.580882786847353</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814659</v>
+        <v>3.640750087814661</v>
       </c>
       <c r="C2016" t="n">
         <v>3.575080071278848</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.543688311422361</v>
+        <v>-4.486871517815279</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.757248322396156</v>
+        <v>1.779975039838988</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.001723974994009447</v>
+        <v>0.135109483473439</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.574045686282442</v>
+        <v>3.656145761362911</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237088</v>
+        <v>3.668289004237089</v>
       </c>
       <c r="C2017" t="n">
         <v>3.644060340424487</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.697674729198502</v>
+        <v>-4.64085793559142</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.764634024431339</v>
+        <v>1.787360741874171</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.001723974994009447</v>
+        <v>0.135109483473439</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.643025955428082</v>
+        <v>3.725126030508551</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423381</v>
+        <v>3.619923016423383</v>
       </c>
       <c r="C2018" t="n">
         <v>3.630111542544608</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.647152825370836</v>
+        <v>-4.590336031763754</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.770893988082527</v>
+        <v>1.793620705525359</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.001723974994009447</v>
+        <v>0.135109483473439</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.629077157548203</v>
+        <v>3.711177232628672</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609747</v>
+        <v>3.656332733609749</v>
       </c>
       <c r="C2019" t="n">
         <v>3.641982031600022</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.89962797937856</v>
+        <v>-4.842811185771478</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.681774415534851</v>
+        <v>1.704501132977683</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.001723974994009447</v>
+        <v>0.135109483473439</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.640947646603617</v>
+        <v>3.723047721684086</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973151</v>
+        <v>3.674028535973153</v>
       </c>
       <c r="C2020" t="n">
         <v>3.643192566118966</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.192523735857972</v>
+        <v>-5.135706942250891</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.56582664746203</v>
+        <v>1.588553364904862</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.001723974994009447</v>
+        <v>0.135109483473439</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.642158181122561</v>
+        <v>3.72425825620303</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.66350945725194</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.647314308346287</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.37918786399278</v>
+        <v>-5.322371070385699</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.495282738435428</v>
+        <v>1.51800945587826</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.02846294581856934</v>
+        <v>0.1083705126488791</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.630236540855146</v>
+        <v>3.712336615935615</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916196</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
         <v>3.642392161082477</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.525208550906743</v>
+        <v>-5.468391757299661</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.431952316406032</v>
+        <v>1.454679033848865</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.03754603761242631</v>
+        <v>0.09928742085502212</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.619864538515021</v>
+        <v>3.70196461359549</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830323</v>
+        <v>3.667962306830324</v>
       </c>
       <c r="C2023" t="n">
         <v>3.804596217781521</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.616922560016327</v>
+        <v>-5.560105766409245</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.557470769461243</v>
+        <v>1.580197486904075</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.03754603761242631</v>
+        <v>0.09928742085502212</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.782068595214065</v>
+        <v>3.864168670294534</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071545</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
         <v>3.799442855745335</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.648574219076297</v>
+        <v>-5.591757425469215</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.539656743801069</v>
+        <v>1.562383461243901</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.04271449485686651</v>
+        <v>0.09411896361058192</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.773814158831216</v>
+        <v>3.855914233911685</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.75004401586814</v>
+        <v>3.750044015868141</v>
       </c>
       <c r="C2025" t="n">
         <v>3.809672273313826</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.73050903734518</v>
+        <v>-5.673692243738098</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.517112234062007</v>
+        <v>1.539838951504839</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.0526492404439467</v>
+        <v>0.08418421802350173</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.778082729047458</v>
+        <v>3.860182804127927</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332685</v>
+        <v>3.783632867332686</v>
       </c>
       <c r="C2026" t="n">
         <v>3.818597911769729</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.832485159593587</v>
+        <v>-5.775668365986506</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.485247423618546</v>
+        <v>1.507974141061379</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1546253626923543</v>
+        <v>-0.01779190422490584</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.725822694154316</v>
+        <v>3.807922769234785</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231802</v>
+        <v>3.798296784231804</v>
       </c>
       <c r="C2027" t="n">
         <v>3.810750799013904</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.722478876116366</v>
+        <v>-5.665662082509284</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.52140282425361</v>
+        <v>1.544129541696442</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1314207907750791</v>
+        <v>0.005412667692369366</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.731898324548857</v>
+        <v>3.813998399629326</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818517</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.815000809735878</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.57941930037544</v>
+        <v>-5.522602506768358</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.582876665271955</v>
+        <v>1.605603382714787</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1234073641850998</v>
+        <v>0.01342609428234864</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.740956391224818</v>
+        <v>3.823056466305288</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051782</v>
+        <v>3.777237412051784</v>
       </c>
       <c r="C2029" t="n">
         <v>3.822261692618414</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.277972574903602</v>
+        <v>-5.22115578129652</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.710716238343226</v>
+        <v>1.733442955786058</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1780393612867375</v>
+        <v>0.3148728197541859</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.929085309390457</v>
+        <v>4.011185384470926</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679619</v>
+        <v>3.81263594067962</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.823232870371125</v>
+        <v>3.742154866542755</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.302562819138786</v>
+        <v>-5.245746025531704</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.701851318401863</v>
+        <v>1.643500032016326</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1780393612867375</v>
+        <v>0.3148728197541859</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.930056487143168</v>
+        <v>3.931078558395267</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474154</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.82407577475088</v>
+        <v>3.742997770922511</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.251524443132266</v>
+        <v>-5.194707649525184</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.723109573184227</v>
+        <v>1.664758286798689</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1780393612867375</v>
+        <v>0.3148728197541859</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.930899391522924</v>
+        <v>3.931921462775023</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969537</v>
+        <v>3.831734516969538</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.843113873625026</v>
+        <v>3.762035869796656</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.210385148265635</v>
+        <v>-5.153568354658553</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.758603390005025</v>
+        <v>1.700252103619487</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2191786561533683</v>
+        <v>0.3560121146208167</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.974621067317047</v>
+        <v>3.975643138569146</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700473</v>
+        <v>3.825752932700474</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.65929786974896</v>
+        <v>3.578219865920591</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.113750236246995</v>
+        <v>-5.056933442639913</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.613441350936415</v>
+        <v>1.555090064550877</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3158135681720082</v>
+        <v>0.4526470266394567</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.848786010652166</v>
+        <v>3.849808081904265</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077634</v>
+        <v>3.804688961077635</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.662799913822925</v>
+        <v>3.581721909994554</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.244330970777837</v>
+        <v>-5.187514177170756</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.564711101198042</v>
+        <v>1.506359814812504</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.1852328336411657</v>
+        <v>0.3220662921086141</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.773939614007624</v>
+        <v>3.774961685259723</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833451</v>
+        <v>3.775028860833452</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.647226732899007</v>
+        <v>3.566148729070637</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.079834636586876</v>
+        <v>-5.023017842979794</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.61493645395051</v>
+        <v>1.556585167564971</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3497291678321276</v>
+        <v>0.486562626299576</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.857064233598284</v>
+        <v>3.858086304850383</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077623</v>
+        <v>3.821030660077624</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.646414443335437</v>
+        <v>3.565336439507067</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.107204569271308</v>
+        <v>-5.050387775664226</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.603176191313167</v>
+        <v>1.544824904927628</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3497291678321276</v>
+        <v>0.486562626299576</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.856251944034714</v>
+        <v>3.857274015286813</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147903</v>
+        <v>3.832307024147904</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.656283222460509</v>
+        <v>3.575205218632139</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.117589764161197</v>
+        <v>-5.060772970554115</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.608890892482283</v>
+        <v>1.550539606096745</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3393439729422383</v>
+        <v>0.4761774314096867</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.859889606225853</v>
+        <v>3.860911677477951</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735275</v>
+        <v>3.834415493735276</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.727120228236934</v>
+        <v>3.646042224408564</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.136177922883422</v>
+        <v>-5.07936112927634</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.672292634769818</v>
+        <v>1.61394134838428</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3207558142200129</v>
+        <v>0.4575892726874614</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.919573716768943</v>
+        <v>3.920595788021041</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496548</v>
+        <v>3.855120535496549</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.723989239055233</v>
+        <v>3.642911235226863</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.136476469579458</v>
+        <v>-5.079659675972376</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.669042226909702</v>
+        <v>1.610690940524164</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.320457267523977</v>
+        <v>0.4572907259914255</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.91626359956962</v>
+        <v>3.917285670821718</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.81564321210885</v>
+        <v>3.815643212108851</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.728520133994624</v>
+        <v>3.647442130166254</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.03565333588903</v>
+        <v>-4.978836542281948</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.713902375325265</v>
+        <v>1.655551088939727</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3329214830083309</v>
+        <v>0.4697549414757793</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.928273023799624</v>
+        <v>3.929295095051722</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121459</v>
+        <v>3.80735616812146</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.728649387473168</v>
+        <v>3.647571383644797</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.844871975136623</v>
+        <v>-4.788055181529542</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.790344173104771</v>
+        <v>1.731992886719233</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5237028437607383</v>
+        <v>0.6605363022281867</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.042871093729611</v>
+        <v>4.04389316498171</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906073</v>
+        <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.708486233210764</v>
+        <v>3.627408229382394</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.826355121094803</v>
+        <v>-4.769538327487721</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.777587760459096</v>
+        <v>1.719236474073558</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5366329731859465</v>
+        <v>0.6734664316533949</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.030466017122333</v>
+        <v>4.031488088374431</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912978</v>
+        <v>3.785761685912979</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.743453169822823</v>
+        <v>3.662375165994452</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.771024533193041</v>
+        <v>-4.714207739585959</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.834686932231859</v>
+        <v>1.776335645846321</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.5919635610877086</v>
+        <v>0.7287970195551571</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.098631306475448</v>
+        <v>4.099653377727547</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539887</v>
+        <v>3.743767956539888</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.73713973772426</v>
+        <v>3.65606173389589</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.758970406280078</v>
+        <v>-4.702153612672996</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.833195150898482</v>
+        <v>1.774843864512944</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6040176880006715</v>
+        <v>0.7408511464681199</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.099550350524663</v>
+        <v>4.100572421776763</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811002</v>
+        <v>3.725010844811003</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.739020367908396</v>
+        <v>3.657942364080026</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.800125525848299</v>
+        <v>-4.743308732241217</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.818613733255329</v>
+        <v>1.760262446869791</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5628625684324505</v>
+        <v>0.699696026899899</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.076737908967867</v>
+        <v>4.077759980219966</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382913</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.751871393786279</v>
+        <v>3.670793389957908</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.697244936319706</v>
+        <v>-4.640428142712624</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.872616994944649</v>
+        <v>1.814265708559111</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6657431579610434</v>
+        <v>0.8025766164284919</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.151317288562905</v>
+        <v>4.152339359815004</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.646857607760309</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.772074063959873</v>
+        <v>3.690996060131503</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.928845329489207</v>
+        <v>-4.872028535882125</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.800179507850443</v>
+        <v>1.741828221464905</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6657431579610434</v>
+        <v>0.8025766164284919</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.171519958736499</v>
+        <v>4.172542029988598</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781699</v>
+        <v>3.6667673867817</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.772074063959873</v>
+        <v>3.690996060131503</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.946917837780818</v>
+        <v>-4.890101044173736</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.792950504533798</v>
+        <v>1.73459921814826</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6657431579610434</v>
+        <v>0.8025766164284919</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.171519958736499</v>
+        <v>4.172542029988598</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082828</v>
+        <v>3.670068888082829</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.73232597755334</v>
+        <v>3.651247973724969</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.122024670357263</v>
+        <v>-5.065207876750181</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.683159685096687</v>
+        <v>1.624808398711149</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6657431579610434</v>
+        <v>0.8025766164284919</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.131771872329966</v>
+        <v>4.132793943582064</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.74559333394358</v>
+        <v>3.745593333943581</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.73934859655028</v>
+        <v>3.658270592721909</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.090738649816807</v>
+        <v>-5.033921856209726</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.702696712309809</v>
+        <v>1.644345425924271</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.6970291785014988</v>
+        <v>0.8338626369689472</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.157566103651179</v>
+        <v>4.158588174903278</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677817</v>
+        <v>3.730590658677818</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.838519596123184</v>
+        <v>3.757441592294814</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.963630709633216</v>
+        <v>-4.880896464096441</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.85271088795615</v>
+        <v>1.804726582342489</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8241371186850894</v>
+        <v>0.9868880290822314</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.333001867334238</v>
+        <v>4.349574409744153</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073877</v>
+        <v>3.741298518073878</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.025985821031476</v>
+        <v>3.944907817203106</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.991938023506487</v>
+        <v>-4.909203777969712</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.028854187315134</v>
+        <v>1.980869881701473</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8241371186850894</v>
+        <v>0.9868880290822314</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.52046809224253</v>
+        <v>4.537040634652445</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903162</v>
+        <v>3.699135800903163</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.995388772385558</v>
+        <v>3.914310768557189</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.158531248620009</v>
+        <v>-5.075797003083234</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.931619848623808</v>
+        <v>1.883635543010147</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.657543893571567</v>
+        <v>0.820294803968709</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.389915108528498</v>
+        <v>4.406487650938415</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568376</v>
+        <v>3.708202704568377</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.999065175047276</v>
+        <v>3.917987171218907</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.985466869237709</v>
+        <v>-4.902732623700934</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.004522003038445</v>
+        <v>1.956537697424785</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.657543893571567</v>
+        <v>0.820294803968709</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.393591511190216</v>
+        <v>4.410164053600132</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682198</v>
+        <v>3.740601586682199</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.996683230170771</v>
+        <v>3.915605226342402</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.956220888782013</v>
+        <v>-4.873486643245237</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.013838450344219</v>
+        <v>1.965854144730559</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.657543893571567</v>
+        <v>0.820294803968709</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.391209566313711</v>
+        <v>4.407782108723628</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539101</v>
+        <v>3.699424827539102</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.993976469328406</v>
+        <v>3.912898465500037</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.063146436659864</v>
+        <v>-4.980412191123088</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.968361470350714</v>
+        <v>1.920377164737054</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.5506183456937156</v>
+        <v>0.7133692560908577</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.324347476744636</v>
+        <v>4.340920019154551</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983731</v>
+        <v>3.689962785983732</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.995405271471641</v>
+        <v>3.914327267643271</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.208164995167112</v>
+        <v>-5.125430749630337</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.911782849091048</v>
+        <v>1.863798543477388</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.4055997871864671</v>
+        <v>0.5683506975836091</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.238765143783521</v>
+        <v>4.255337686193437</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969742</v>
+        <v>3.711872614969743</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.095336510729394</v>
+        <v>4.014258506901024</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.32650676095183</v>
+        <v>-5.243772515415055</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.964377382034914</v>
+        <v>1.916393076421254</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.4162858257493571</v>
+        <v>0.5790367361464992</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.345108006179008</v>
+        <v>4.361680548588924</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073531</v>
+        <v>3.714899237073533</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.093122207855332</v>
+        <v>4.012044204026963</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.377917183272538</v>
+        <v>-5.295182937735762</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.94159891023257</v>
+        <v>1.89361460461891</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.4162858257493571</v>
+        <v>0.5790367361464992</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.342893703304947</v>
+        <v>4.359466245714863</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720058</v>
+        <v>3.70477813472006</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.093025335929622</v>
+        <v>4.011947332101252</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.457336634480289</v>
+        <v>-5.374602388943514</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.909734257823759</v>
+        <v>1.861749952210099</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.4162858257493571</v>
+        <v>0.5790367361464992</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.342796831379236</v>
+        <v>4.359369373789153</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581126</v>
+        <v>3.736825137581127</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.093019229487665</v>
+        <v>4.011941225659296</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.552799632397507</v>
+        <v>-5.470065386860732</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.871542952214915</v>
+        <v>1.823558646601255</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.4162858257493571</v>
+        <v>0.5790367361464992</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.34279072493728</v>
+        <v>4.359363267347196</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500728</v>
+        <v>3.715393145500729</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.091115626050276</v>
+        <v>4.010037622221907</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.592819630441291</v>
+        <v>-5.510085384904515</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.853631349560013</v>
+        <v>1.805647043946352</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.3762658277055733</v>
+        <v>0.5390167381027153</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.31687512267362</v>
+        <v>4.333447665083536</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636263</v>
+        <v>3.736109598636265</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.096849443798003</v>
+        <v>4.015771439969633</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.648188792573484</v>
+        <v>-5.565454547036709</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.837217502454862</v>
+        <v>1.789233196841201</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.3762658277055733</v>
+        <v>0.5390167381027153</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.322608940421347</v>
+        <v>4.339181482831263</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396006</v>
+        <v>3.736843055396008</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.096387807140935</v>
+        <v>4.015309803312565</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.693626572404312</v>
+        <v>-5.610892326867536</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.818580753865464</v>
+        <v>1.770596448251803</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.3334208370274137</v>
+        <v>0.4961717474245557</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.296440309357384</v>
+        <v>4.313012851767299</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396415</v>
+        <v>3.790292685396417</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.116262199991255</v>
+        <v>4.035184196162884</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.610401115556647</v>
+        <v>-5.527666870019872</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.871745329454849</v>
+        <v>1.823761023841187</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.3334208370274137</v>
+        <v>0.4961717474245557</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.316314702207703</v>
+        <v>4.332887244617618</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.79450702929917</v>
+        <v>3.794507029299171</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.099962900515982</v>
+        <v>4.018884896687612</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.43411089095134</v>
+        <v>-5.351376645414565</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.925962119821699</v>
+        <v>1.877977814208038</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.3334208370274137</v>
+        <v>0.4961717474245557</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.300015402732431</v>
+        <v>4.316587945142346</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590403</v>
+        <v>3.794725278590401</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.102393849980028</v>
+        <v>4.021315846151658</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.250899227818245</v>
+        <v>-5.168164982281469</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.001677734538983</v>
+        <v>1.953693428925322</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.3334208370274137</v>
+        <v>0.4961717474245557</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.302446352196476</v>
+        <v>4.319018894606391</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.838354070604751</v>
+        <v>3.601538816763996</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.109453169012617</v>
+        <v>4.019159591273531</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.21697667578629</v>
+        <v>-5.040366029880105</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.022306074384354</v>
+        <v>2.002656755007741</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.3977089841663782</v>
+        <v>0.5340777658290073</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.348078559512444</v>
+        <v>4.339606250770935</v>
       </c>
     </row>
   </sheetData>
